--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$S$123</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$S$125</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -622,7 +622,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>For the testing team · last updated 22 Oct 2026 · last automated run 22 Oct 2026 10:22 AST (95/95 browser checks passed)</t>
+          <t>For the testing team · last updated 22 Oct 2026 · last automated run 22 Oct 2026 15:16 AST (95/95 browser checks passed)</t>
         </is>
       </c>
     </row>
@@ -861,27 +861,27 @@
         </is>
       </c>
       <c r="B5" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A5)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A5,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A5,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A5,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A5,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A5,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H5" s="16">
@@ -889,7 +889,7 @@
         <v/>
       </c>
       <c r="I5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A5,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A5,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -900,27 +900,27 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A6)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A6,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A6,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A6,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A6,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A6,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H6" s="16">
@@ -928,7 +928,7 @@
         <v/>
       </c>
       <c r="I6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A6,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A6,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -939,27 +939,27 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A7)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A7,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A7,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A7,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A7,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A7,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H7" s="16">
@@ -967,7 +967,7 @@
         <v/>
       </c>
       <c r="I7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A7,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A7,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -978,27 +978,27 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A8)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A8,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A8,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A8,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A8,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A8,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H8" s="16">
@@ -1006,7 +1006,7 @@
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A8,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A8,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1017,27 +1017,27 @@
         </is>
       </c>
       <c r="B9" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A9)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A9,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A9,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A9,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A9,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A9,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H9" s="16">
@@ -1045,7 +1045,7 @@
         <v/>
       </c>
       <c r="I9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A9,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A9,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1056,27 +1056,27 @@
         </is>
       </c>
       <c r="B10" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A10)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A10,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A10,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A10,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A10,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A10,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H10" s="16">
@@ -1084,7 +1084,7 @@
         <v/>
       </c>
       <c r="I10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A10,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A10,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1095,27 +1095,27 @@
         </is>
       </c>
       <c r="B11" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A11)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A11,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A11,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A11,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A11,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A11,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H11" s="16">
@@ -1123,7 +1123,7 @@
         <v/>
       </c>
       <c r="I11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A11,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A11,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1134,27 +1134,27 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A12)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A12,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A12,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A12,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A12,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A12,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H12" s="16">
@@ -1162,7 +1162,7 @@
         <v/>
       </c>
       <c r="I12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A12,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A12,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A13)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A13,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A13,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A13,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A13,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A13,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H13" s="16">
@@ -1201,7 +1201,7 @@
         <v/>
       </c>
       <c r="I13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A13,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A13,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1212,27 +1212,27 @@
         </is>
       </c>
       <c r="B14" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A14)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A14,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A14,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A14,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A14,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A14,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H14" s="16">
@@ -1240,7 +1240,7 @@
         <v/>
       </c>
       <c r="I14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A14,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A14,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1251,27 +1251,27 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A15)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A15,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A15,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A15,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A15,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A15,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H15" s="16">
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="I15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A15,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A15,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1290,27 +1290,27 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$323,$A16)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A16,'Test Cases'!$M$2:$M$323,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,C$4)</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A16,'Test Cases'!$M$2:$M$323,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,D$4)</f>
         <v/>
       </c>
       <c r="E16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A16,'Test Cases'!$M$2:$M$323,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,E$4)</f>
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A16,'Test Cases'!$M$2:$M$323,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,F$4)</f>
         <v/>
       </c>
       <c r="G16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A16,'Test Cases'!$M$2:$M$323,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,G$4)</f>
         <v/>
       </c>
       <c r="H16" s="16">
@@ -1318,7 +1318,7 @@
         <v/>
       </c>
       <c r="I16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$323,$A16,'Test Cases'!$I$2:$I$323,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$323,$A16,'Test Cases'!$I$2:$I$323,"Critical",'Test Cases'!$M$2:$M$323,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>COUNTIF('Test Cases'!$L$2:$L$323,"Pass")</f>
+        <f>COUNTIF('Test Cases'!$L$2:$L$325,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>COUNTIF('Test Cases'!$L$2:$L$323,"Fail")</f>
+        <f>COUNTIF('Test Cases'!$L$2:$L$325,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B22" s="15">
-        <f>COUNTA('Test Cases'!$L$2:$L$123)-B20-B21</f>
+        <f>COUNTA('Test Cases'!$L$2:$L$125)-B20-B21</f>
         <v/>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S123"/>
+  <dimension ref="A1:S125"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -9286,7 +9286,7 @@
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-10</t>
+          <t>TC-REC-13</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
@@ -9296,40 +9296,40 @@
       </c>
       <c r="C97" s="19" t="inlineStr">
         <is>
-          <t>Academic hire needs the college e-mail</t>
+          <t>Phone number with country code</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t>An Accepted applicant from an Instructor link.</t>
+          <t>A valid application link.</t>
         </is>
       </c>
       <c r="F97" s="19" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Leave Company Email empty (or a gmail address).
-3. Confirm.
-4. Then enter a @alriyada.edu.sa address and confirm again.</t>
+          <t>1. Open the link.
+2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
+3. Send.
+4. Correct it and send again.</t>
         </is>
       </c>
       <c r="G97" s="19" t="inlineStr">
         <is>
-          <t>Personal e-mail, then college e-mail</t>
+          <t>123, then a full mobile number</t>
         </is>
       </c>
       <c r="H97" s="19" t="inlineStr">
         <is>
-          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
+          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
         </is>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
@@ -9339,12 +9339,12 @@
       </c>
       <c r="K97" s="15" t="inlineStr">
         <is>
-          <t>REC-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L97" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M97" s="20" t="inlineStr">
@@ -9358,59 +9358,59 @@
       <c r="Q97" s="20" t="inlineStr"/>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="S97" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-01</t>
+          <t>TC-REC-14</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C98" s="19" t="inlineStr">
         <is>
-          <t>Faculty schedules</t>
+          <t>Receipt after sending the application</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="E98" s="19" t="inlineStr">
         <is>
-          <t>Published class timetables.</t>
+          <t>TC-REC-13 done (application sent).</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
         <is>
-          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
+          <t>On the confirmation screen click the receipt download button.</t>
         </is>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
-          <t>6–12 Sep 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H98" s="19" t="inlineStr">
         <is>
-          <t>Sessions per faculty member with day, time, course, room and mode.</t>
+          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J98" s="15" t="inlineStr">
@@ -9420,12 +9420,12 @@
       </c>
       <c r="K98" s="15" t="inlineStr">
         <is>
-          <t>PRS-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L98" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M98" s="20" t="inlineStr">
@@ -9439,29 +9439,29 @@
       <c r="Q98" s="20" t="inlineStr"/>
       <c r="R98" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="S98" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-02</t>
+          <t>TC-REC-10</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C99" s="19" t="inlineStr">
         <is>
-          <t>Filter one faculty member</t>
+          <t>Academic hire needs the college e-mail</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
@@ -9471,37 +9471,40 @@
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>An Accepted applicant from an Instructor link.</t>
         </is>
       </c>
       <c r="F99" s="19" t="inlineStr">
         <is>
-          <t>Pick a faculty member in the filter.</t>
+          <t>1. Create Employee.
+2. Leave Company Email empty (or a gmail address).
+3. Confirm.
+4. Then enter a @alriyada.edu.sa address and confirm again.</t>
         </is>
       </c>
       <c r="G99" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Personal e-mail, then college e-mail</t>
         </is>
       </c>
       <c r="H99" s="19" t="inlineStr">
         <is>
-          <t>Only that person's sessions.</t>
+          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
         </is>
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J99" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K99" s="15" t="inlineStr">
         <is>
-          <t>PRS-02</t>
+          <t>REC-08</t>
         </is>
       </c>
       <c r="L99" s="15" t="inlineStr">
@@ -9532,7 +9535,7 @@
     <row r="100">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-03</t>
+          <t>TC-PRS-01</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
@@ -9542,7 +9545,7 @@
       </c>
       <c r="C100" s="19" t="inlineStr">
         <is>
-          <t>Proctor schedules</t>
+          <t>Faculty schedules</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
@@ -9552,27 +9555,27 @@
       </c>
       <c r="E100" s="19" t="inlineStr">
         <is>
-          <t>Exam committees with proctors.</t>
+          <t>Published class timetables.</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
         <is>
-          <t>Open Proctor Schedules for the exam week.</t>
+          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
         </is>
       </c>
       <c r="G100" s="19" t="inlineStr">
         <is>
-          <t>Exam week</t>
+          <t>6–12 Sep 2026</t>
         </is>
       </c>
       <c r="H100" s="19" t="inlineStr">
         <is>
-          <t>Proctor assignments, or a clear 'no assignments' message.</t>
+          <t>Sessions per faculty member with day, time, course, room and mode.</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J100" s="15" t="inlineStr">
@@ -9582,7 +9585,7 @@
       </c>
       <c r="K100" s="15" t="inlineStr">
         <is>
-          <t>PRS-03</t>
+          <t>PRS-01</t>
         </is>
       </c>
       <c r="L100" s="15" t="inlineStr">
@@ -9613,7 +9616,7 @@
     <row r="101">
       <c r="A101" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-04</t>
+          <t>TC-PRS-02</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr">
@@ -9623,7 +9626,7 @@
       </c>
       <c r="C101" s="19" t="inlineStr">
         <is>
-          <t>Students on campus per hour</t>
+          <t>Filter one faculty member</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
@@ -9633,27 +9636,27 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t>Attendance recorded.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F101" s="19" t="inlineStr">
         <is>
-          <t>Open Students on Campus for a teaching day.</t>
+          <t>Pick a faculty member in the filter.</t>
         </is>
       </c>
       <c r="G101" s="19" t="inlineStr">
         <is>
-          <t>8 Sep 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
+          <t>Only that person's sessions.</t>
         </is>
       </c>
       <c r="I101" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J101" s="15" t="inlineStr">
@@ -9663,7 +9666,7 @@
       </c>
       <c r="K101" s="15" t="inlineStr">
         <is>
-          <t>PRS-04</t>
+          <t>PRS-02</t>
         </is>
       </c>
       <c r="L101" s="15" t="inlineStr">
@@ -9694,7 +9697,7 @@
     <row r="102">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-05</t>
+          <t>TC-PRS-03</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -9704,7 +9707,7 @@
       </c>
       <c r="C102" s="19" t="inlineStr">
         <is>
-          <t>Faculty after 4 PM</t>
+          <t>Proctor schedules</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
@@ -9714,27 +9717,27 @@
       </c>
       <c r="E102" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Exam committees with proctors.</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
-          <t>Open Faculty After 4 PM for a week.</t>
+          <t>Open Proctor Schedules for the exam week.</t>
         </is>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Exam week</t>
         </is>
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
+          <t>Proctor assignments, or a clear 'no assignments' message.</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J102" s="15" t="inlineStr">
@@ -9744,7 +9747,7 @@
       </c>
       <c r="K102" s="15" t="inlineStr">
         <is>
-          <t>PRS-05</t>
+          <t>PRS-03</t>
         </is>
       </c>
       <c r="L102" s="15" t="inlineStr">
@@ -9775,7 +9778,7 @@
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-06</t>
+          <t>TC-PRS-04</t>
         </is>
       </c>
       <c r="B103" s="15" t="inlineStr">
@@ -9785,7 +9788,7 @@
       </c>
       <c r="C103" s="19" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Students on campus per hour</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
@@ -9795,27 +9798,27 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t>A tab with data.</t>
+          <t>Attendance recorded.</t>
         </is>
       </c>
       <c r="F103" s="19" t="inlineStr">
         <is>
-          <t>Click Export (Excel CSV).</t>
+          <t>Open Students on Campus for a teaching day.</t>
         </is>
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8 Sep 2026</t>
         </is>
       </c>
       <c r="H103" s="19" t="inlineStr">
         <is>
-          <t>A CSV file downloads and opens in Excel with the same rows.</t>
+          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
         </is>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J103" s="15" t="inlineStr">
@@ -9825,7 +9828,7 @@
       </c>
       <c r="K103" s="15" t="inlineStr">
         <is>
-          <t>PRS-06</t>
+          <t>PRS-04</t>
         </is>
       </c>
       <c r="L103" s="15" t="inlineStr">
@@ -9856,7 +9859,7 @@
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-07</t>
+          <t>TC-PRS-05</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -9866,7 +9869,7 @@
       </c>
       <c r="C104" s="19" t="inlineStr">
         <is>
-          <t>Holiday and exam days</t>
+          <t>Faculty after 4 PM</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
@@ -9876,12 +9879,12 @@
       </c>
       <c r="E104" s="19" t="inlineStr">
         <is>
-          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
         <is>
-          <t>Open Faculty Schedules over a holiday or exam week.</t>
+          <t>Open Faculty After 4 PM for a week.</t>
         </is>
       </c>
       <c r="G104" s="19" t="inlineStr">
@@ -9891,12 +9894,12 @@
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
-          <t>No regular sessions on those days; the skipped dates are listed.</t>
+          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J104" s="15" t="inlineStr">
@@ -9906,12 +9909,12 @@
       </c>
       <c r="K104" s="15" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>PRS-05</t>
         </is>
       </c>
       <c r="L104" s="15" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M104" s="20" t="inlineStr">
@@ -9937,7 +9940,7 @@
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-08</t>
+          <t>TC-PRS-06</t>
         </is>
       </c>
       <c r="B105" s="15" t="inlineStr">
@@ -9947,7 +9950,7 @@
       </c>
       <c r="C105" s="19" t="inlineStr">
         <is>
-          <t>Cut-off time setting</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -9957,27 +9960,27 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
+          <t>A tab with data.</t>
+        </is>
+      </c>
+      <c r="F105" s="19" t="inlineStr">
+        <is>
+          <t>Click Export (Excel CSV).</t>
+        </is>
+      </c>
+      <c r="G105" s="19" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F105" s="19" t="inlineStr">
-        <is>
-          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
-        </is>
-      </c>
-      <c r="G105" s="19" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="H105" s="19" t="inlineStr">
         <is>
-          <t>List uses the new time.</t>
+          <t>A CSV file downloads and opens in Excel with the same rows.</t>
         </is>
       </c>
       <c r="I105" s="15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J105" s="15" t="inlineStr">
@@ -9987,12 +9990,12 @@
       </c>
       <c r="K105" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PRS-06</t>
         </is>
       </c>
       <c r="L105" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M105" s="20" t="inlineStr">
@@ -10018,17 +10021,17 @@
     <row r="106">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-01</t>
+          <t>TC-PRS-07</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C106" s="19" t="inlineStr">
         <is>
-          <t>Jameah Data Check page</t>
+          <t>Holiday and exam days</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
@@ -10038,27 +10041,27 @@
       </c>
       <c r="E106" s="19" t="inlineStr">
         <is>
+          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
+        </is>
+      </c>
+      <c r="F106" s="19" t="inlineStr">
+        <is>
+          <t>Open Faculty Schedules over a holiday or exam week.</t>
+        </is>
+      </c>
+      <c r="G106" s="19" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F106" s="19" t="inlineStr">
-        <is>
-          <t>HR Dashboard -&gt; Jameah Data Check.</t>
-        </is>
-      </c>
-      <c r="G106" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H106" s="19" t="inlineStr">
         <is>
-          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
+          <t>No regular sessions on those days; the skipped dates are listed.</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J106" s="15" t="inlineStr">
@@ -10068,12 +10071,12 @@
       </c>
       <c r="K106" s="15" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M106" s="20" t="inlineStr">
@@ -10099,22 +10102,22 @@
     <row r="107">
       <c r="A107" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-02</t>
+          <t>TC-PRS-08</t>
         </is>
       </c>
       <c r="B107" s="15" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C107" s="19" t="inlineStr">
         <is>
-          <t>Jameah Settings pickers</t>
+          <t>Cut-off time setting</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E107" s="19" t="inlineStr">
@@ -10124,37 +10127,37 @@
       </c>
       <c r="F107" s="19" t="inlineStr">
         <is>
-          <t>Open Jameah Settings; open the College picker.</t>
+          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
         </is>
       </c>
       <c r="G107" s="19" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H107" s="19" t="inlineStr">
+        <is>
+          <t>List uses the new time.</t>
+        </is>
+      </c>
+      <c r="I107" s="15" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J107" s="15" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K107" s="15" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H107" s="19" t="inlineStr">
-        <is>
-          <t>Only College Coding Guide codes are offered.</t>
-        </is>
-      </c>
-      <c r="I107" s="15" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J107" s="15" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K107" s="15" t="inlineStr">
-        <is>
-          <t>JM-02</t>
-        </is>
-      </c>
       <c r="L107" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M107" s="20" t="inlineStr">
@@ -10180,7 +10183,7 @@
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-03</t>
+          <t>TC-JM-01</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
@@ -10190,37 +10193,37 @@
       </c>
       <c r="C108" s="19" t="inlineStr">
         <is>
-          <t>Fill a setting and see it in the views</t>
+          <t>Jameah Data Check page</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E108" s="19" t="inlineStr">
         <is>
-          <t>Decision on the college code (DEC-02).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F108" s="19" t="inlineStr">
         <is>
-          <t>Set College; Save; reopen Jameah Data Check.</t>
+          <t>HR Dashboard -&gt; Jameah Data Check.</t>
         </is>
       </c>
       <c r="G108" s="19" t="inlineStr">
         <is>
-          <t>College code</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H108" s="19" t="inlineStr">
         <is>
-          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
+          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J108" s="15" t="inlineStr">
@@ -10230,12 +10233,12 @@
       </c>
       <c r="K108" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M108" s="20" t="inlineStr">
@@ -10261,7 +10264,7 @@
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-04</t>
+          <t>TC-JM-02</t>
         </is>
       </c>
       <c r="B109" s="15" t="inlineStr">
@@ -10271,7 +10274,7 @@
       </c>
       <c r="C109" s="19" t="inlineStr">
         <is>
-          <t>Map a value in the Code Map</t>
+          <t>Jameah Settings pickers</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
@@ -10281,22 +10284,22 @@
       </c>
       <c r="E109" s="19" t="inlineStr">
         <is>
-          <t>A 'Needs Review' row.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F109" s="19" t="inlineStr">
         <is>
-          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
+          <t>Open Jameah Settings; open the College picker.</t>
         </is>
       </c>
       <c r="G109" s="19" t="inlineStr">
         <is>
-          <t>e.g. Internship -&gt; 0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H109" s="19" t="inlineStr">
         <is>
-          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
+          <t>Only College Coding Guide codes are offered.</t>
         </is>
       </c>
       <c r="I109" s="15" t="inlineStr">
@@ -10311,7 +10314,7 @@
       </c>
       <c r="K109" s="15" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="L109" s="15" t="inlineStr">
@@ -10342,7 +10345,7 @@
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-05</t>
+          <t>TC-JM-03</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -10352,7 +10355,7 @@
       </c>
       <c r="C110" s="19" t="inlineStr">
         <is>
-          <t>Code Map refuses a code from another list</t>
+          <t>Fill a setting and see it in the views</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
@@ -10362,42 +10365,42 @@
       </c>
       <c r="E110" s="19" t="inlineStr">
         <is>
+          <t>Decision on the college code (DEC-02).</t>
+        </is>
+      </c>
+      <c r="F110" s="19" t="inlineStr">
+        <is>
+          <t>Set College; Save; reopen Jameah Data Check.</t>
+        </is>
+      </c>
+      <c r="G110" s="19" t="inlineStr">
+        <is>
+          <t>College code</t>
+        </is>
+      </c>
+      <c r="H110" s="19" t="inlineStr">
+        <is>
+          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
+        </is>
+      </c>
+      <c r="I110" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J110" s="15" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K110" s="15" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F110" s="19" t="inlineStr">
-        <is>
-          <t>Try to save a Religion row with a Gender code.</t>
-        </is>
-      </c>
-      <c r="G110" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="H110" s="19" t="inlineStr">
-        <is>
-          <t>Refused with a clear message.</t>
-        </is>
-      </c>
-      <c r="I110" s="15" t="inlineStr">
-        <is>
-          <t>Medium</t>
-        </is>
-      </c>
-      <c r="J110" s="15" t="inlineStr">
-        <is>
-          <t>Negative</t>
-        </is>
-      </c>
-      <c r="K110" s="15" t="inlineStr">
-        <is>
-          <t>unit test</t>
-        </is>
-      </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M110" s="20" t="inlineStr">
@@ -10423,7 +10426,7 @@
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-06</t>
+          <t>TC-JM-04</t>
         </is>
       </c>
       <c r="B111" s="15" t="inlineStr">
@@ -10433,37 +10436,37 @@
       </c>
       <c r="C111" s="19" t="inlineStr">
         <is>
-          <t>Refresh academic figures</t>
+          <t>Map a value in the Code Map</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A 'Needs Review' row.</t>
         </is>
       </c>
       <c r="F111" s="19" t="inlineStr">
         <is>
-          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
+          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
         </is>
       </c>
       <c r="G111" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>e.g. Internship -&gt; 0</t>
         </is>
       </c>
       <c r="H111" s="19" t="inlineStr">
         <is>
-          <t>'Last refreshed' time updates.</t>
+          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
         </is>
       </c>
       <c r="I111" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J111" s="15" t="inlineStr">
@@ -10473,12 +10476,12 @@
       </c>
       <c r="K111" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="L111" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M111" s="20" t="inlineStr">
@@ -10504,7 +10507,7 @@
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-07</t>
+          <t>TC-JM-05</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
@@ -10514,22 +10517,22 @@
       </c>
       <c r="C112" s="19" t="inlineStr">
         <is>
-          <t>Employee data reaches the Employee views</t>
+          <t>Code Map refuses a code from another list</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E112" s="19" t="inlineStr">
         <is>
-          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>Open their Ministry (Jameah) Data preview.</t>
+          <t>Try to save a Religion row with a Gender code.</t>
         </is>
       </c>
       <c r="G112" s="19" t="inlineStr">
@@ -10539,27 +10542,27 @@
       </c>
       <c r="H112" s="19" t="inlineStr">
         <is>
-          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
+          <t>Refused with a clear message.</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J112" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K112" s="15" t="inlineStr">
         <is>
-          <t>REC-06</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M112" s="20" t="inlineStr">
@@ -10585,7 +10588,7 @@
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-10</t>
+          <t>TC-JM-06</t>
         </is>
       </c>
       <c r="B113" s="15" t="inlineStr">
@@ -10595,52 +10598,52 @@
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>Ministry GPA and hours equal the student's transcript</t>
+          <t>Refresh academic figures</t>
         </is>
       </c>
       <c r="D113" s="15" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
         <is>
-          <t>Academic figures refreshed (TC-JM-06).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F113" s="19" t="inlineStr">
         <is>
-          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
+          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
         </is>
       </c>
       <c r="G113" s="19" t="inlineStr">
         <is>
-          <t>10 students</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H113" s="19" t="inlineStr">
         <is>
-          <t>All four figures are identical for every student.</t>
+          <t>'Last refreshed' time updates.</t>
         </is>
       </c>
       <c r="I113" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J113" s="15" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K113" s="15" t="inlineStr">
         <is>
-          <t>verify.run</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L113" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M113" s="20" t="inlineStr">
@@ -10666,7 +10669,7 @@
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-08</t>
+          <t>TC-JM-07</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
@@ -10676,22 +10679,22 @@
       </c>
       <c r="C114" s="19" t="inlineStr">
         <is>
-          <t>Full value-by-value check (developer)</t>
+          <t>Employee data reaches the Employee views</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E114" s="19" t="inlineStr">
         <is>
-          <t>Server access.</t>
+          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
         <is>
-          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
+          <t>Open their Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="G114" s="19" t="inlineStr">
@@ -10701,7 +10704,7 @@
       </c>
       <c r="H114" s="19" t="inlineStr">
         <is>
-          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
+          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
@@ -10711,12 +10714,12 @@
       </c>
       <c r="J114" s="15" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K114" s="15" t="inlineStr">
         <is>
-          <t>verify.run</t>
+          <t>REC-06</t>
         </is>
       </c>
       <c r="L114" s="15" t="inlineStr">
@@ -10747,7 +10750,7 @@
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-09</t>
+          <t>TC-JM-10</t>
         </is>
       </c>
       <c r="B115" s="15" t="inlineStr">
@@ -10757,52 +10760,52 @@
       </c>
       <c r="C115" s="19" t="inlineStr">
         <is>
-          <t>Ministry read-only account</t>
+          <t>Ministry GPA and hours equal the student's transcript</t>
         </is>
       </c>
       <c r="D115" s="15" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t>Account created with the grant statements.</t>
+          <t>Academic figures refreshed (TC-JM-06).</t>
         </is>
       </c>
       <c r="F115" s="19" t="inlineStr">
         <is>
-          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
+          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
         </is>
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 students</t>
         </is>
       </c>
       <c r="H115" s="19" t="inlineStr">
         <is>
-          <t>Views readable; ERP tables refused.</t>
+          <t>All four figures are identical for every student.</t>
         </is>
       </c>
       <c r="I115" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J115" s="15" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="K115" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verify.run</t>
         </is>
       </c>
       <c r="L115" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M115" s="20" t="inlineStr">
@@ -10828,7 +10831,7 @@
     <row r="116">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-11</t>
+          <t>TC-JM-08</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
@@ -10838,47 +10841,47 @@
       </c>
       <c r="C116" s="19" t="inlineStr">
         <is>
-          <t>Faculty views on the Data Check page</t>
+          <t>Full value-by-value check (developer)</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="E116" s="19" t="inlineStr">
         <is>
+          <t>Server access.</t>
+        </is>
+      </c>
+      <c r="F116" s="19" t="inlineStr">
+        <is>
+          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
+        </is>
+      </c>
+      <c r="G116" s="19" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F116" s="19" t="inlineStr">
-        <is>
-          <t>Open Jameah Data Check and look at the Views table.</t>
-        </is>
-      </c>
-      <c r="G116" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H116" s="19" t="inlineStr">
         <is>
-          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
+          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J116" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="K116" s="15" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>verify.run</t>
         </is>
       </c>
       <c r="L116" s="15" t="inlineStr">
@@ -10909,7 +10912,7 @@
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-12</t>
+          <t>TC-JM-09</t>
         </is>
       </c>
       <c r="B117" s="15" t="inlineStr">
@@ -10919,23 +10922,22 @@
       </c>
       <c r="C117" s="19" t="inlineStr">
         <is>
-          <t>A teacher is sent once, as Faculty</t>
+          <t>Ministry read-only account</t>
         </is>
       </c>
       <c r="D117" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
+          <t>Account created with the grant statements.</t>
         </is>
       </c>
       <c r="F117" s="19" t="inlineStr">
         <is>
-          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
-2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
+          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
         </is>
       </c>
       <c r="G117" s="19" t="inlineStr">
@@ -10945,27 +10947,27 @@
       </c>
       <c r="H117" s="19" t="inlineStr">
         <is>
-          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
+          <t>Views readable; ERP tables refused.</t>
         </is>
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J117" s="15" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K117" s="15" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L117" s="15" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M117" s="20" t="inlineStr">
@@ -10991,7 +10993,7 @@
     <row r="118">
       <c r="A118" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-13</t>
+          <t>TC-JM-11</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
@@ -11001,23 +11003,22 @@
       </c>
       <c r="C118" s="19" t="inlineStr">
         <is>
-          <t>Faculty status and contract codes</t>
+          <t>Faculty views on the Data Check page</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E118" s="19" t="inlineStr">
         <is>
-          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
-          <t>1. Open each row, pick the Ministry code, Status = Verified.
-2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+          <t>Open Jameah Data Check and look at the Views table.</t>
         </is>
       </c>
       <c r="G118" s="19" t="inlineStr">
@@ -11027,27 +11028,27 @@
       </c>
       <c r="H118" s="19" t="inlineStr">
         <is>
-          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
+          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J118" s="15" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K118" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M118" s="20" t="inlineStr">
@@ -11073,42 +11074,43 @@
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-01</t>
+          <t>TC-JM-12</t>
         </is>
       </c>
       <c r="B119" s="15" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="C119" s="19" t="inlineStr">
         <is>
-          <t>Error Log after each test day</t>
+          <t>A teacher is sent once, as Faculty</t>
         </is>
       </c>
       <c r="D119" s="15" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
+          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
+        </is>
+      </c>
+      <c r="F119" s="19" t="inlineStr">
+        <is>
+          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
+2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
+        </is>
+      </c>
+      <c r="G119" s="19" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F119" s="19" t="inlineStr">
-        <is>
-          <t>Open /app/error-log; sort by newest.</t>
-        </is>
-      </c>
-      <c r="G119" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H119" s="19" t="inlineStr">
         <is>
-          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
+          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
         </is>
       </c>
       <c r="I119" s="15" t="inlineStr">
@@ -11118,17 +11120,17 @@
       </c>
       <c r="J119" s="15" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="K119" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="L119" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M119" s="20" t="inlineStr">
@@ -11154,52 +11156,53 @@
     <row r="120">
       <c r="A120" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-02</t>
+          <t>TC-JM-13</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="C120" s="19" t="inlineStr">
         <is>
-          <t>System e-mail works</t>
+          <t>Faculty status and contract codes</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E120" s="19" t="inlineStr">
         <is>
+          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+        </is>
+      </c>
+      <c r="F120" s="19" t="inlineStr">
+        <is>
+          <t>1. Open each row, pick the Ministry code, Status = Verified.
+2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+        </is>
+      </c>
+      <c r="G120" s="19" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F120" s="19" t="inlineStr">
-        <is>
-          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
-        </is>
-      </c>
-      <c r="G120" s="19" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H120" s="19" t="inlineStr">
         <is>
-          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
+          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J120" s="15" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="K120" s="15" t="inlineStr">
@@ -11235,7 +11238,7 @@
     <row r="121">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-03</t>
+          <t>TC-ERR-01</t>
         </is>
       </c>
       <c r="B121" s="15" t="inlineStr">
@@ -11245,7 +11248,7 @@
       </c>
       <c r="C121" s="19" t="inlineStr">
         <is>
-          <t>Background jobs</t>
+          <t>Error Log after each test day</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
@@ -11260,7 +11263,7 @@
       </c>
       <c r="F121" s="19" t="inlineStr">
         <is>
-          <t>Open Scheduled Job Log; filter Status = Failed.</t>
+          <t>Open /app/error-log; sort by newest.</t>
         </is>
       </c>
       <c r="G121" s="19" t="inlineStr">
@@ -11270,12 +11273,12 @@
       </c>
       <c r="H121" s="19" t="inlineStr">
         <is>
-          <t>No failed jobs (or each one reported).</t>
+          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
         </is>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J121" s="15" t="inlineStr">
@@ -11316,7 +11319,7 @@
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-04</t>
+          <t>TC-ERR-02</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
@@ -11326,22 +11329,22 @@
       </c>
       <c r="C122" s="19" t="inlineStr">
         <is>
-          <t>Browser console during testing</t>
+          <t>System e-mail works</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="E122" s="19" t="inlineStr">
         <is>
-          <t>Chrome DevTools open (F12 -&gt; Console).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F122" s="19" t="inlineStr">
         <is>
-          <t>Use the system as normal while the console is open.</t>
+          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
         </is>
       </c>
       <c r="G122" s="19" t="inlineStr">
@@ -11351,12 +11354,12 @@
       </c>
       <c r="H122" s="19" t="inlineStr">
         <is>
-          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
+          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J122" s="15" t="inlineStr">
@@ -11366,12 +11369,12 @@
       </c>
       <c r="K122" s="15" t="inlineStr">
         <is>
-          <t>Error sweep SWP-01..04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L122" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M122" s="20" t="inlineStr">
@@ -11397,7 +11400,7 @@
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-05</t>
+          <t>TC-ERR-03</t>
         </is>
       </c>
       <c r="B123" s="15" t="inlineStr">
@@ -11407,7 +11410,7 @@
       </c>
       <c r="C123" s="19" t="inlineStr">
         <is>
-          <t>Migrate output after deploying</t>
+          <t>Background jobs</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
@@ -11417,12 +11420,12 @@
       </c>
       <c r="E123" s="19" t="inlineStr">
         <is>
-          <t>New branch pulled on the server.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F123" s="19" t="inlineStr">
         <is>
-          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
+          <t>Open Scheduled Job Log; filter Status = Failed.</t>
         </is>
       </c>
       <c r="G123" s="19" t="inlineStr">
@@ -11432,12 +11435,12 @@
       </c>
       <c r="H123" s="19" t="inlineStr">
         <is>
-          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
+          <t>No failed jobs (or each one reported).</t>
         </is>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J123" s="15" t="inlineStr">
@@ -11475,9 +11478,171 @@
         </is>
       </c>
     </row>
+    <row r="124">
+      <c r="A124" s="17" t="inlineStr">
+        <is>
+          <t>TC-ERR-04</t>
+        </is>
+      </c>
+      <c r="B124" s="15" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="C124" s="19" t="inlineStr">
+        <is>
+          <t>Browser console during testing</t>
+        </is>
+      </c>
+      <c r="D124" s="15" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="E124" s="19" t="inlineStr">
+        <is>
+          <t>Chrome DevTools open (F12 -&gt; Console).</t>
+        </is>
+      </c>
+      <c r="F124" s="19" t="inlineStr">
+        <is>
+          <t>Use the system as normal while the console is open.</t>
+        </is>
+      </c>
+      <c r="G124" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H124" s="19" t="inlineStr">
+        <is>
+          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
+        </is>
+      </c>
+      <c r="I124" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J124" s="15" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="K124" s="15" t="inlineStr">
+        <is>
+          <t>Error sweep SWP-01..04</t>
+        </is>
+      </c>
+      <c r="L124" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M124" s="20" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="N124" s="20" t="inlineStr"/>
+      <c r="O124" s="20" t="inlineStr"/>
+      <c r="P124" s="21" t="inlineStr"/>
+      <c r="Q124" s="20" t="inlineStr"/>
+      <c r="R124" s="15" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="S124" s="15" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="17" t="inlineStr">
+        <is>
+          <t>TC-ERR-05</t>
+        </is>
+      </c>
+      <c r="B125" s="15" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="C125" s="19" t="inlineStr">
+        <is>
+          <t>Migrate output after deploying</t>
+        </is>
+      </c>
+      <c r="D125" s="15" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="E125" s="19" t="inlineStr">
+        <is>
+          <t>New branch pulled on the server.</t>
+        </is>
+      </c>
+      <c r="F125" s="19" t="inlineStr">
+        <is>
+          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
+        </is>
+      </c>
+      <c r="G125" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H125" s="19" t="inlineStr">
+        <is>
+          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
+        </is>
+      </c>
+      <c r="I125" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J125" s="15" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="K125" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L125" s="15" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="M125" s="20" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="N125" s="20" t="inlineStr"/>
+      <c r="O125" s="20" t="inlineStr"/>
+      <c r="P125" s="21" t="inlineStr"/>
+      <c r="Q125" s="20" t="inlineStr"/>
+      <c r="R125" s="15" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="S125" s="15" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S123"/>
-  <conditionalFormatting sqref="M2:M323">
+  <autoFilter ref="A1:S125"/>
+  <conditionalFormatting sqref="M2:M325">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$M2="Not run"</formula>
     </cfRule>
@@ -11494,7 +11659,7 @@
       <formula>$M2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L323">
+  <conditionalFormatting sqref="L2:L325">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>$L2="Not run"</formula>
     </cfRule>
@@ -11512,7 +11677,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="M2:M323" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M325" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13393,7 +13558,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E9"/>
+  <dimension ref="A1:E10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13443,12 +13608,12 @@
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
@@ -13465,17 +13630,17 @@
       </c>
       <c r="B3" s="15" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -13487,22 +13652,22 @@
     <row r="4">
       <c r="A4" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -13519,17 +13684,17 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -13546,17 +13711,17 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -13568,7 +13733,7 @@
     <row r="7">
       <c r="A7" s="15" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B7" s="15" t="inlineStr">
@@ -13578,12 +13743,12 @@
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -13595,7 +13760,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -13605,12 +13770,12 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -13622,25 +13787,52 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D9" s="19" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E9" s="15" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="15" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B9" s="15" t="inlineStr">
+      <c r="B10" s="15" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr">
+      <c r="C10" s="19" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D9" s="19" t="inlineStr">
+      <c r="D10" s="19" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E9" s="15" t="inlineStr">
+      <c r="E10" s="15" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$S$125</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$S$130</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -622,7 +622,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>For the testing team · last updated 22 Oct 2026 · last automated run 22 Oct 2026 15:16 AST (95/95 browser checks passed)</t>
+          <t>For the testing team · last updated 23 Oct 2026 · last automated run 23 Oct 2026 06:20 AST (95/95 browser checks passed)</t>
         </is>
       </c>
     </row>
@@ -861,27 +861,27 @@
         </is>
       </c>
       <c r="B5" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A5)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H5" s="16">
@@ -889,7 +889,7 @@
         <v/>
       </c>
       <c r="I5" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A5,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -900,27 +900,27 @@
         </is>
       </c>
       <c r="B6" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A6)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H6" s="16">
@@ -928,7 +928,7 @@
         <v/>
       </c>
       <c r="I6" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A6,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -939,27 +939,27 @@
         </is>
       </c>
       <c r="B7" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A7)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H7" s="16">
@@ -967,7 +967,7 @@
         <v/>
       </c>
       <c r="I7" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A7,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -978,27 +978,27 @@
         </is>
       </c>
       <c r="B8" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A8)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H8" s="16">
@@ -1006,7 +1006,7 @@
         <v/>
       </c>
       <c r="I8" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A8,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1017,27 +1017,27 @@
         </is>
       </c>
       <c r="B9" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A9)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H9" s="16">
@@ -1045,7 +1045,7 @@
         <v/>
       </c>
       <c r="I9" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A9,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1056,27 +1056,27 @@
         </is>
       </c>
       <c r="B10" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A10)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H10" s="16">
@@ -1084,7 +1084,7 @@
         <v/>
       </c>
       <c r="I10" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A10,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1095,27 +1095,27 @@
         </is>
       </c>
       <c r="B11" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A11)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H11" s="16">
@@ -1123,7 +1123,7 @@
         <v/>
       </c>
       <c r="I11" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A11,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1134,27 +1134,27 @@
         </is>
       </c>
       <c r="B12" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A12)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H12" s="16">
@@ -1162,7 +1162,7 @@
         <v/>
       </c>
       <c r="I12" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A12,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1173,27 +1173,27 @@
         </is>
       </c>
       <c r="B13" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A13)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H13" s="16">
@@ -1201,7 +1201,7 @@
         <v/>
       </c>
       <c r="I13" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A13,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1212,27 +1212,27 @@
         </is>
       </c>
       <c r="B14" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A14)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H14" s="16">
@@ -1240,7 +1240,7 @@
         <v/>
       </c>
       <c r="I14" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A14,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1251,27 +1251,27 @@
         </is>
       </c>
       <c r="B15" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A15)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H15" s="16">
@@ -1279,7 +1279,7 @@
         <v/>
       </c>
       <c r="I15" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A15,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1290,27 +1290,27 @@
         </is>
       </c>
       <c r="B16" s="15">
-        <f>COUNTIF('Test Cases'!$B$2:$B$325,$A16)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,C$4)</f>
         <v/>
       </c>
       <c r="D16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,D$4)</f>
         <v/>
       </c>
       <c r="E16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,E$4)</f>
         <v/>
       </c>
       <c r="F16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,F$4)</f>
         <v/>
       </c>
       <c r="G16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$M$2:$M$325,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,G$4)</f>
         <v/>
       </c>
       <c r="H16" s="16">
@@ -1318,7 +1318,7 @@
         <v/>
       </c>
       <c r="I16" s="15">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$I$2:$I$325,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$325,$A16,'Test Cases'!$I$2:$I$325,"Critical",'Test Cases'!$M$2:$M$325,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
         </is>
       </c>
       <c r="B20" s="15">
-        <f>COUNTIF('Test Cases'!$L$2:$L$325,"Pass")</f>
+        <f>COUNTIF('Test Cases'!$L$2:$L$330,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1386,7 +1386,7 @@
         </is>
       </c>
       <c r="B21" s="15">
-        <f>COUNTIF('Test Cases'!$L$2:$L$325,"Fail")</f>
+        <f>COUNTIF('Test Cases'!$L$2:$L$330,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -1397,7 +1397,7 @@
         </is>
       </c>
       <c r="B22" s="15">
-        <f>COUNTA('Test Cases'!$L$2:$L$125)-B20-B21</f>
+        <f>COUNTA('Test Cases'!$L$2:$L$130)-B20-B21</f>
         <v/>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S125"/>
+  <dimension ref="A1:S130"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7244,42 +7244,42 @@
     <row r="72">
       <c r="A72" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-01</t>
+          <t>TC-SEC-10</t>
         </is>
       </c>
       <c r="B72" s="15" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="C72" s="19" t="inlineStr">
         <is>
-          <t>Edit and save an employee who has a login</t>
+          <t>Server methods refuse the wrong role</t>
         </is>
       </c>
       <c r="D72" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="E72" s="19" t="inlineStr">
         <is>
-          <t>Employee with a user login.</t>
+          <t>QA logins loaded (qa_fixtures.py), bench running.</t>
         </is>
       </c>
       <c r="F72" s="19" t="inlineStr">
         <is>
-          <t>Change the mobile number; Save.</t>
+          <t>python3 tests/checks/api_methods.py</t>
         </is>
       </c>
       <c r="G72" s="19" t="inlineStr">
         <is>
-          <t>New mobile</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H72" s="19" t="inlineStr">
         <is>
-          <t>Saved with no error (this used to fail with 'Could not find Gender').</t>
+          <t>Every method: refused (403) for a visitor except the job form and receipt; HR-only methods refused for employees; no server error (500); no method left out of the check.</t>
         </is>
       </c>
       <c r="I72" s="15" t="inlineStr">
@@ -7289,17 +7289,17 @@
       </c>
       <c r="J72" s="15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K72" s="15" t="inlineStr">
         <is>
-          <t>EMP-01</t>
+          <t>tests/checks/api_methods.py</t>
         </is>
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M72" s="20" t="inlineStr">
@@ -7313,19 +7313,19 @@
       <c r="Q72" s="20" t="inlineStr"/>
       <c r="R72" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="S72" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-02</t>
+          <t>TC-EMP-01</t>
         </is>
       </c>
       <c r="B73" s="15" t="inlineStr">
@@ -7335,7 +7335,7 @@
       </c>
       <c r="C73" s="19" t="inlineStr">
         <is>
-          <t>Lookup fields only offer their own list</t>
+          <t>Edit and save an employee who has a login</t>
         </is>
       </c>
       <c r="D73" s="15" t="inlineStr">
@@ -7345,37 +7345,37 @@
       </c>
       <c r="E73" s="19" t="inlineStr">
         <is>
-          <t>Employee form open.</t>
+          <t>Employee with a user login.</t>
         </is>
       </c>
       <c r="F73" s="19" t="inlineStr">
         <is>
-          <t>Open Gender, Nationality, Identity Type and Religion drop-downs.</t>
+          <t>Change the mobile number; Save.</t>
         </is>
       </c>
       <c r="G73" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>New mobile</t>
         </is>
       </c>
       <c r="H73" s="19" t="inlineStr">
         <is>
-          <t>Each shows only its Ministry list (e.g. Gender: Male, Female).</t>
+          <t>Saved with no error (this used to fail with 'Could not find Gender').</t>
         </is>
       </c>
       <c r="I73" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J73" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K73" s="15" t="inlineStr">
         <is>
-          <t>EMP-02/03</t>
+          <t>EMP-01</t>
         </is>
       </c>
       <c r="L73" s="15" t="inlineStr">
@@ -7406,7 +7406,7 @@
     <row r="74">
       <c r="A74" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-03</t>
+          <t>TC-EMP-02</t>
         </is>
       </c>
       <c r="B74" s="15" t="inlineStr">
@@ -7416,7 +7416,7 @@
       </c>
       <c r="C74" s="19" t="inlineStr">
         <is>
-          <t>Invalid national ID</t>
+          <t>Lookup fields only offer their own list</t>
         </is>
       </c>
       <c r="D74" s="15" t="inlineStr">
@@ -7426,22 +7426,22 @@
       </c>
       <c r="E74" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Employee form open.</t>
         </is>
       </c>
       <c r="F74" s="19" t="inlineStr">
         <is>
-          <t>Set Identity Number to 12345 and Save.</t>
+          <t>Open Gender, Nationality, Identity Type and Religion drop-downs.</t>
         </is>
       </c>
       <c r="G74" s="19" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H74" s="19" t="inlineStr">
         <is>
-          <t>Refused: a National ID has exactly 10 digits.</t>
+          <t>Each shows only its Ministry list (e.g. Gender: Male, Female).</t>
         </is>
       </c>
       <c r="I74" s="15" t="inlineStr">
@@ -7451,12 +7451,12 @@
       </c>
       <c r="J74" s="15" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K74" s="15" t="inlineStr">
         <is>
-          <t>EMP-05</t>
+          <t>EMP-02/03</t>
         </is>
       </c>
       <c r="L74" s="15" t="inlineStr">
@@ -7487,7 +7487,7 @@
     <row r="75">
       <c r="A75" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-04</t>
+          <t>TC-EMP-03</t>
         </is>
       </c>
       <c r="B75" s="15" t="inlineStr">
@@ -7497,7 +7497,7 @@
       </c>
       <c r="C75" s="19" t="inlineStr">
         <is>
-          <t>Duplicate identity number</t>
+          <t>Invalid national ID</t>
         </is>
       </c>
       <c r="D75" s="15" t="inlineStr">
@@ -7507,22 +7507,22 @@
       </c>
       <c r="E75" s="19" t="inlineStr">
         <is>
-          <t>Another employee's ID number.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F75" s="19" t="inlineStr">
         <is>
-          <t>Enter it on a different employee; Save.</t>
+          <t>Set Identity Number to 12345 and Save.</t>
         </is>
       </c>
       <c r="G75" s="19" t="inlineStr">
         <is>
-          <t>Existing ID</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="H75" s="19" t="inlineStr">
         <is>
-          <t>Refused: already registered to &lt;employee&gt;.</t>
+          <t>Refused: a National ID has exactly 10 digits.</t>
         </is>
       </c>
       <c r="I75" s="15" t="inlineStr">
@@ -7537,7 +7537,7 @@
       </c>
       <c r="K75" s="15" t="inlineStr">
         <is>
-          <t>EMP-06</t>
+          <t>EMP-05</t>
         </is>
       </c>
       <c r="L75" s="15" t="inlineStr">
@@ -7568,7 +7568,7 @@
     <row r="76">
       <c r="A76" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-05</t>
+          <t>TC-EMP-04</t>
         </is>
       </c>
       <c r="B76" s="15" t="inlineStr">
@@ -7578,7 +7578,7 @@
       </c>
       <c r="C76" s="19" t="inlineStr">
         <is>
-          <t>National ID for a non-Saudi</t>
+          <t>Duplicate identity number</t>
         </is>
       </c>
       <c r="D76" s="15" t="inlineStr">
@@ -7588,27 +7588,27 @@
       </c>
       <c r="E76" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Another employee's ID number.</t>
         </is>
       </c>
       <c r="F76" s="19" t="inlineStr">
         <is>
-          <t>Nationality not Saudi, Identity Type National ID; Save.</t>
+          <t>Enter it on a different employee; Save.</t>
         </is>
       </c>
       <c r="G76" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Existing ID</t>
         </is>
       </c>
       <c r="H76" s="19" t="inlineStr">
         <is>
-          <t>Refused: National ID is only for Saudis.</t>
+          <t>Refused: already registered to &lt;employee&gt;.</t>
         </is>
       </c>
       <c r="I76" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J76" s="15" t="inlineStr">
@@ -7618,12 +7618,12 @@
       </c>
       <c r="K76" s="15" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>EMP-06</t>
         </is>
       </c>
       <c r="L76" s="15" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M76" s="20" t="inlineStr">
@@ -7649,7 +7649,7 @@
     <row r="77">
       <c r="A77" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-09</t>
+          <t>TC-EMP-05</t>
         </is>
       </c>
       <c r="B77" s="15" t="inlineStr">
@@ -7659,7 +7659,7 @@
       </c>
       <c r="C77" s="19" t="inlineStr">
         <is>
-          <t>Non-Saudi employee with an Iqama</t>
+          <t>National ID for a non-Saudi</t>
         </is>
       </c>
       <c r="D77" s="15" t="inlineStr">
@@ -7669,44 +7669,42 @@
       </c>
       <c r="E77" s="19" t="inlineStr">
         <is>
-          <t>An employee whose Nationality is not Saudi and Identity Type is Iqama.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F77" s="19" t="inlineStr">
         <is>
-          <t>1. Open the employee.
-2. Look at Identity Number and ID Number in Country of Origin.
-3. Change any field and Save.</t>
+          <t>Nationality not Saudi, Identity Type National ID; Save.</t>
         </is>
       </c>
       <c r="G77" s="19" t="inlineStr">
         <is>
-          <t>Iqama 2XXXXXXXXX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H77" s="19" t="inlineStr">
         <is>
-          <t>The record opens without 'Not Saved'. Identity Number still shows the Iqama and is mandatory; the home-country ID is optional. Save works.</t>
+          <t>Refused: National ID is only for Saudis.</t>
         </is>
       </c>
       <c r="I77" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J77" s="15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K77" s="15" t="inlineStr">
         <is>
-          <t>EMP-08</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="L77" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M77" s="20" t="inlineStr">
@@ -7732,7 +7730,7 @@
     <row r="78">
       <c r="A78" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-06</t>
+          <t>TC-EMP-09</t>
         </is>
       </c>
       <c r="B78" s="15" t="inlineStr">
@@ -7742,7 +7740,7 @@
       </c>
       <c r="C78" s="19" t="inlineStr">
         <is>
-          <t>Qualification 'Appreciation' list</t>
+          <t>Non-Saudi employee with an Iqama</t>
         </is>
       </c>
       <c r="D78" s="15" t="inlineStr">
@@ -7752,27 +7750,29 @@
       </c>
       <c r="E78" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>An employee whose Nationality is not Saudi and Identity Type is Iqama.</t>
         </is>
       </c>
       <c r="F78" s="19" t="inlineStr">
         <is>
-          <t>Add a qualification row; open Appreciation.</t>
+          <t>1. Open the employee.
+2. Look at Identity Number and ID Number in Country of Origin.
+3. Change any field and Save.</t>
         </is>
       </c>
       <c r="G78" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Iqama 2XXXXXXXXX</t>
         </is>
       </c>
       <c r="H78" s="19" t="inlineStr">
         <is>
-          <t>Grades are offered (Excellent, Very good, Good...), not GPA systems.</t>
+          <t>The record opens without 'Not Saved'. Identity Number still shows the Iqama and is mandatory; the home-country ID is optional. Save works.</t>
         </is>
       </c>
       <c r="I78" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J78" s="15" t="inlineStr">
@@ -7782,7 +7782,7 @@
       </c>
       <c r="K78" s="15" t="inlineStr">
         <is>
-          <t>REC-05</t>
+          <t>EMP-08</t>
         </is>
       </c>
       <c r="L78" s="15" t="inlineStr">
@@ -7813,7 +7813,7 @@
     <row r="79">
       <c r="A79" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-07</t>
+          <t>TC-EMP-06</t>
         </is>
       </c>
       <c r="B79" s="15" t="inlineStr">
@@ -7823,7 +7823,7 @@
       </c>
       <c r="C79" s="19" t="inlineStr">
         <is>
-          <t>Ministry (Jameah) Data preview</t>
+          <t>Qualification 'Appreciation' list</t>
         </is>
       </c>
       <c r="D79" s="15" t="inlineStr">
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E79" s="19" t="inlineStr">
         <is>
-          <t>An employee of Al Riyada College.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F79" s="19" t="inlineStr">
         <is>
-          <t>Employee form -&gt; View -&gt; Ministry (Jameah) Data.</t>
+          <t>Add a qualification row; open Appreciation.</t>
         </is>
       </c>
       <c r="G79" s="19" t="inlineStr">
@@ -7848,22 +7848,22 @@
       </c>
       <c r="H79" s="19" t="inlineStr">
         <is>
-          <t>Pop-up with the 5 Ministry sections; lookup columns show codes (e.g. Nationality 101).</t>
+          <t>Grades are offered (Excellent, Very good, Good...), not GPA systems.</t>
         </is>
       </c>
       <c r="I79" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J79" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K79" s="15" t="inlineStr">
         <is>
-          <t>EMP-07</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="L79" s="15" t="inlineStr">
@@ -7894,7 +7894,7 @@
     <row r="80">
       <c r="A80" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-08</t>
+          <t>TC-EMP-07</t>
         </is>
       </c>
       <c r="B80" s="15" t="inlineStr">
@@ -7904,7 +7904,7 @@
       </c>
       <c r="C80" s="19" t="inlineStr">
         <is>
-          <t>Teaching staff are not sent as Employees</t>
+          <t>Ministry (Jameah) Data preview</t>
         </is>
       </c>
       <c r="D80" s="15" t="inlineStr">
@@ -7914,12 +7914,12 @@
       </c>
       <c r="E80" s="19" t="inlineStr">
         <is>
-          <t>An employee linked to an Instructor.</t>
+          <t>An employee of Al Riyada College.</t>
         </is>
       </c>
       <c r="F80" s="19" t="inlineStr">
         <is>
-          <t>Open the Ministry (Jameah) Data preview.</t>
+          <t>Employee form -&gt; View -&gt; Ministry (Jameah) Data.</t>
         </is>
       </c>
       <c r="G80" s="19" t="inlineStr">
@@ -7929,7 +7929,7 @@
       </c>
       <c r="H80" s="19" t="inlineStr">
         <is>
-          <t>Says the person is sent as Faculty, not as an Employee.</t>
+          <t>Pop-up with the 5 Ministry sections; lookup columns show codes (e.g. Nationality 101).</t>
         </is>
       </c>
       <c r="I80" s="15" t="inlineStr">
@@ -7944,7 +7944,7 @@
       </c>
       <c r="K80" s="15" t="inlineStr">
         <is>
-          <t>REC-07</t>
+          <t>EMP-07</t>
         </is>
       </c>
       <c r="L80" s="15" t="inlineStr">
@@ -7975,7 +7975,7 @@
     <row r="81">
       <c r="A81" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-10</t>
+          <t>TC-EMP-08</t>
         </is>
       </c>
       <c r="B81" s="15" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="C81" s="19" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Teaching staff are not sent as Employees</t>
         </is>
       </c>
       <c r="D81" s="15" t="inlineStr">
@@ -7995,14 +7995,12 @@
       </c>
       <c r="E81" s="19" t="inlineStr">
         <is>
-          <t>Some employees with empty Ministry fields.</t>
+          <t>An employee linked to an Instructor.</t>
         </is>
       </c>
       <c r="F81" s="19" t="inlineStr">
         <is>
-          <t>1. HR Portal menu &gt; Ministry (Jameah) &gt; Employees Missing Ministry Data.
-2. Tick 'Show complete employees too'.
-3. Filter by a department.</t>
+          <t>Open the Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="G81" s="19" t="inlineStr">
@@ -8012,12 +8010,12 @@
       </c>
       <c r="H81" s="19" t="inlineStr">
         <is>
-          <t>Each employee with gaps is listed with the number of missing values and their names as on the Employee form (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). The tick also lists complete employees; the filter works.</t>
+          <t>Says the person is sent as Faculty, not as an Employee.</t>
         </is>
       </c>
       <c r="I81" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J81" s="15" t="inlineStr">
@@ -8027,7 +8025,7 @@
       </c>
       <c r="K81" s="15" t="inlineStr">
         <is>
-          <t>RPT-01</t>
+          <t>REC-07</t>
         </is>
       </c>
       <c r="L81" s="15" t="inlineStr">
@@ -8058,7 +8056,7 @@
     <row r="82">
       <c r="A82" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-11</t>
+          <t>TC-EMP-10</t>
         </is>
       </c>
       <c r="B82" s="15" t="inlineStr">
@@ -8068,7 +8066,7 @@
       </c>
       <c r="C82" s="19" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff: download, check, import</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="D82" s="15" t="inlineStr">
@@ -8078,25 +8076,24 @@
       </c>
       <c r="E82" s="19" t="inlineStr">
         <is>
-          <t>HR Manager account.</t>
+          <t>Some employees with empty Ministry fields.</t>
         </is>
       </c>
       <c r="F82" s="19" t="inlineStr">
         <is>
-          <t>1. In the report: Download Data Sheet.
-2. Fill one red cell for an employee; type 31-31-2020 as another employee's date of birth.
-3. Check / Import Data Sheet &gt; attach the file &gt; Check.
-4. Fix the date and click Import.</t>
+          <t>1. HR Portal menu &gt; Ministry (Jameah) &gt; Employees Missing Ministry Data.
+2. Tick 'Show complete employees too'.
+3. Filter by a department.</t>
         </is>
       </c>
       <c r="G82" s="19" t="inlineStr">
         <is>
-          <t>Edited .xlsx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H82" s="19" t="inlineStr">
         <is>
-          <t>The sheet lists the non-teaching employees, red = Ministry-required and empty. Check reports the wrong date and saves nothing. Import updates only the changed cells; the result sheet gives each row's status.</t>
+          <t>Each employee with gaps is listed with the number of missing values and their names as on the Employee form (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). The tick also lists complete employees; the filter works.</t>
         </is>
       </c>
       <c r="I82" s="15" t="inlineStr">
@@ -8111,12 +8108,12 @@
       </c>
       <c r="K82" s="15" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>RPT-01</t>
         </is>
       </c>
       <c r="L82" s="15" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M82" s="20" t="inlineStr">
@@ -8142,7 +8139,7 @@
     <row r="83">
       <c r="A83" s="17" t="inlineStr">
         <is>
-          <t>TC-EMP-12</t>
+          <t>TC-EMP-11</t>
         </is>
       </c>
       <c r="B83" s="15" t="inlineStr">
@@ -8152,52 +8149,55 @@
       </c>
       <c r="C83" s="19" t="inlineStr">
         <is>
-          <t>Only an HR Manager can import the data sheet</t>
+          <t>Data sheet for non-academic staff: download, check, import</t>
         </is>
       </c>
       <c r="D83" s="15" t="inlineStr">
         <is>
-          <t>HR User</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E83" s="19" t="inlineStr">
         <is>
-          <t>HR User account.</t>
+          <t>HR Manager account.</t>
         </is>
       </c>
       <c r="F83" s="19" t="inlineStr">
         <is>
-          <t>Open the Employees Missing Ministry Data report.</t>
+          <t>1. In the report: Download Data Sheet.
+2. Fill one red cell for an employee; type 31-31-2020 as another employee's date of birth.
+3. Check / Import Data Sheet &gt; attach the file &gt; Check.
+4. Fix the date and click Import.</t>
         </is>
       </c>
       <c r="G83" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Edited .xlsx</t>
         </is>
       </c>
       <c r="H83" s="19" t="inlineStr">
         <is>
-          <t>The report opens; there are no Download Data Sheet / Check / Import buttons.</t>
+          <t>The sheet lists the non-teaching employees, red = Ministry-required and empty. Check reports the wrong date and saves nothing. Import updates only the changed cells; the result sheet gives each row's status.</t>
         </is>
       </c>
       <c r="I83" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J83" s="15" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K83" s="15" t="inlineStr">
         <is>
-          <t>RPT-02</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="L83" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M83" s="20" t="inlineStr">
@@ -8223,32 +8223,32 @@
     <row r="84">
       <c r="A84" s="17" t="inlineStr">
         <is>
-          <t>TC-LIC-01</t>
+          <t>TC-EMP-12</t>
         </is>
       </c>
       <c r="B84" s="15" t="inlineStr">
         <is>
-          <t>Medical licences</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="C84" s="19" t="inlineStr">
         <is>
-          <t>HR creates a licence</t>
+          <t>Only an HR Manager can import the data sheet</t>
         </is>
       </c>
       <c r="D84" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>HR User</t>
         </is>
       </c>
       <c r="E84" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>HR User account.</t>
         </is>
       </c>
       <c r="F84" s="19" t="inlineStr">
         <is>
-          <t>New Employee Medical License: employee, type, number, expiry; Save.</t>
+          <t>Open the Employees Missing Ministry Data report.</t>
         </is>
       </c>
       <c r="G84" s="19" t="inlineStr">
@@ -8258,7 +8258,7 @@
       </c>
       <c r="H84" s="19" t="inlineStr">
         <is>
-          <t>Saved.</t>
+          <t>The report opens; there are no Download Data Sheet / Check / Import buttons.</t>
         </is>
       </c>
       <c r="I84" s="15" t="inlineStr">
@@ -8268,12 +8268,12 @@
       </c>
       <c r="J84" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K84" s="15" t="inlineStr">
         <is>
-          <t>LIC-01</t>
+          <t>RPT-02</t>
         </is>
       </c>
       <c r="L84" s="15" t="inlineStr">
@@ -8304,7 +8304,7 @@
     <row r="85">
       <c r="A85" s="17" t="inlineStr">
         <is>
-          <t>TC-LIC-02</t>
+          <t>TC-LIC-01</t>
         </is>
       </c>
       <c r="B85" s="15" t="inlineStr">
@@ -8314,22 +8314,22 @@
       </c>
       <c r="C85" s="19" t="inlineStr">
         <is>
-          <t>Employees see only their own licence</t>
+          <t>HR creates a licence</t>
         </is>
       </c>
       <c r="D85" s="15" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E85" s="19" t="inlineStr">
         <is>
-          <t>Licences for two employees.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F85" s="19" t="inlineStr">
         <is>
-          <t>Each employee opens the licence list.</t>
+          <t>New Employee Medical License: employee, type, number, expiry; Save.</t>
         </is>
       </c>
       <c r="G85" s="19" t="inlineStr">
@@ -8339,22 +8339,22 @@
       </c>
       <c r="H85" s="19" t="inlineStr">
         <is>
-          <t>Only their own licence.</t>
+          <t>Saved.</t>
         </is>
       </c>
       <c r="I85" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J85" s="15" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K85" s="15" t="inlineStr">
         <is>
-          <t>LIC-02</t>
+          <t>LIC-01</t>
         </is>
       </c>
       <c r="L85" s="15" t="inlineStr">
@@ -8385,35 +8385,32 @@
     <row r="86">
       <c r="A86" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-01</t>
+          <t>TC-LIC-02</t>
         </is>
       </c>
       <c r="B86" s="15" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Medical licences</t>
         </is>
       </c>
       <c r="C86" s="19" t="inlineStr">
         <is>
-          <t>Create and generate an application link</t>
+          <t>Employees see only their own licence</t>
         </is>
       </c>
       <c r="D86" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E86" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Licences for two employees.</t>
         </is>
       </c>
       <c r="F86" s="19" t="inlineStr">
         <is>
-          <t>1. New Job Application Link.
-2. Category Academic Staff, Role Instructor, valid from/until.
-3. Save.
-4. Generate Link.</t>
+          <t>Each employee opens the licence list.</t>
         </is>
       </c>
       <c r="G86" s="19" t="inlineStr">
@@ -8423,7 +8420,7 @@
       </c>
       <c r="H86" s="19" t="inlineStr">
         <is>
-          <t>A link is shown and can be copied.</t>
+          <t>Only their own licence.</t>
         </is>
       </c>
       <c r="I86" s="15" t="inlineStr">
@@ -8433,12 +8430,12 @@
       </c>
       <c r="J86" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K86" s="15" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>LIC-02</t>
         </is>
       </c>
       <c r="L86" s="15" t="inlineStr">
@@ -8469,7 +8466,7 @@
     <row r="87">
       <c r="A87" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-02</t>
+          <t>TC-REC-01</t>
         </is>
       </c>
       <c r="B87" s="15" t="inlineStr">
@@ -8479,12 +8476,12 @@
       </c>
       <c r="C87" s="19" t="inlineStr">
         <is>
-          <t>Invalid or expired link</t>
+          <t>Create and generate an application link</t>
         </is>
       </c>
       <c r="D87" s="15" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E87" s="19" t="inlineStr">
@@ -8494,7 +8491,10 @@
       </c>
       <c r="F87" s="19" t="inlineStr">
         <is>
-          <t>Open /job-application/abc123 and an expired link.</t>
+          <t>1. New Job Application Link.
+2. Category Academic Staff, Role Instructor, valid from/until.
+3. Save.
+4. Generate Link.</t>
         </is>
       </c>
       <c r="G87" s="19" t="inlineStr">
@@ -8504,22 +8504,22 @@
       </c>
       <c r="H87" s="19" t="inlineStr">
         <is>
-          <t>'Link is invalid / not active' message; no form.</t>
+          <t>A link is shown and can be copied.</t>
         </is>
       </c>
       <c r="I87" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J87" s="15" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K87" s="15" t="inlineStr">
         <is>
-          <t>REC-01</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="L87" s="15" t="inlineStr">
@@ -8550,7 +8550,7 @@
     <row r="88">
       <c r="A88" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-03</t>
+          <t>TC-REC-02</t>
         </is>
       </c>
       <c r="B88" s="15" t="inlineStr">
@@ -8560,7 +8560,7 @@
       </c>
       <c r="C88" s="19" t="inlineStr">
         <is>
-          <t>Required fields on the public form</t>
+          <t>Invalid or expired link</t>
         </is>
       </c>
       <c r="D88" s="15" t="inlineStr">
@@ -8570,12 +8570,12 @@
       </c>
       <c r="E88" s="19" t="inlineStr">
         <is>
-          <t>Valid link.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F88" s="19" t="inlineStr">
         <is>
-          <t>Click Submit with the form empty.</t>
+          <t>Open /job-application/abc123 and an expired link.</t>
         </is>
       </c>
       <c r="G88" s="19" t="inlineStr">
@@ -8585,7 +8585,7 @@
       </c>
       <c r="H88" s="19" t="inlineStr">
         <is>
-          <t>Browser highlights the required fields; nothing is sent.</t>
+          <t>'Link is invalid / not active' message; no form.</t>
         </is>
       </c>
       <c r="I88" s="15" t="inlineStr">
@@ -8600,12 +8600,12 @@
       </c>
       <c r="K88" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-01</t>
         </is>
       </c>
       <c r="L88" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M88" s="20" t="inlineStr">
@@ -8631,7 +8631,7 @@
     <row r="89">
       <c r="A89" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-04</t>
+          <t>TC-REC-03</t>
         </is>
       </c>
       <c r="B89" s="15" t="inlineStr">
@@ -8641,7 +8641,7 @@
       </c>
       <c r="C89" s="19" t="inlineStr">
         <is>
-          <t>Applicant submits the full form</t>
+          <t>Required fields on the public form</t>
         </is>
       </c>
       <c r="D89" s="15" t="inlineStr">
@@ -8656,37 +8656,37 @@
       </c>
       <c r="F89" s="19" t="inlineStr">
         <is>
-          <t>Fill every section (names in Arabic and English, ID, qualifications, experience) and Submit.</t>
+          <t>Click Submit with the form empty.</t>
         </is>
       </c>
       <c r="G89" s="19" t="inlineStr">
         <is>
-          <t>Saudi national ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H89" s="19" t="inlineStr">
         <is>
-          <t>'Thank you' with a reference number APP-....</t>
+          <t>Browser highlights the required fields; nothing is sent.</t>
         </is>
       </c>
       <c r="I89" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J89" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K89" s="15" t="inlineStr">
         <is>
-          <t>REC-03..05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L89" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M89" s="20" t="inlineStr">
@@ -8712,7 +8712,7 @@
     <row r="90">
       <c r="A90" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-05</t>
+          <t>TC-REC-04</t>
         </is>
       </c>
       <c r="B90" s="15" t="inlineStr">
@@ -8722,35 +8722,32 @@
       </c>
       <c r="C90" s="19" t="inlineStr">
         <is>
-          <t>Accept and create an Instructor</t>
+          <t>Applicant submits the full form</t>
         </is>
       </c>
       <c r="D90" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="E90" s="19" t="inlineStr">
         <is>
-          <t>TC-REC-04 for an Instructor link.</t>
+          <t>Valid link.</t>
         </is>
       </c>
       <c r="F90" s="19" t="inlineStr">
         <is>
-          <t>1. Open the applicant.
-2. Accept.
-3. Create Employee: Company Email = official college address, department.
-4. Confirm.</t>
+          <t>Fill every section (names in Arabic and English, ID, qualifications, experience) and Submit.</t>
         </is>
       </c>
       <c r="G90" s="19" t="inlineStr">
         <is>
-          <t>name.surname@alriyada.edu.sa</t>
+          <t>Saudi national ID</t>
         </is>
       </c>
       <c r="H90" s="19" t="inlineStr">
         <is>
-          <t>Message lists Employee and Instructor created; the new login has Employee + Instructor roles.</t>
+          <t>'Thank you' with a reference number APP-....</t>
         </is>
       </c>
       <c r="I90" s="15" t="inlineStr">
@@ -8765,7 +8762,7 @@
       </c>
       <c r="K90" s="15" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>REC-03..05</t>
         </is>
       </c>
       <c r="L90" s="15" t="inlineStr">
@@ -8796,7 +8793,7 @@
     <row r="91">
       <c r="A91" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-06</t>
+          <t>TC-REC-05</t>
         </is>
       </c>
       <c r="B91" s="15" t="inlineStr">
@@ -8806,7 +8803,7 @@
       </c>
       <c r="C91" s="19" t="inlineStr">
         <is>
-          <t>Hire an Academic Advisor</t>
+          <t>Accept and create an Instructor</t>
         </is>
       </c>
       <c r="D91" s="15" t="inlineStr">
@@ -8816,37 +8813,40 @@
       </c>
       <c r="E91" s="19" t="inlineStr">
         <is>
-          <t>Applicant for an Academic Advisor link with a phone like 05XXXXXXXX.</t>
+          <t>TC-REC-04 for an Instructor link.</t>
         </is>
       </c>
       <c r="F91" s="19" t="inlineStr">
         <is>
-          <t>Accept -&gt; Create Employee with a @alriyada.edu.sa Company Email.</t>
+          <t>1. Open the applicant.
+2. Accept.
+3. Create Employee: Company Email = official college address, department.
+4. Confirm.</t>
         </is>
       </c>
       <c r="G91" s="19" t="inlineStr">
         <is>
-          <t>Local phone number</t>
+          <t>name.surname@alriyada.edu.sa</t>
         </is>
       </c>
       <c r="H91" s="19" t="inlineStr">
         <is>
-          <t>Employee, Academic Advisor and Instructor records created; no 'record not created' warning.</t>
+          <t>Message lists Employee and Instructor created; the new login has Employee + Instructor roles.</t>
         </is>
       </c>
       <c r="I91" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J91" s="15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K91" s="15" t="inlineStr">
         <is>
-          <t>REC-04</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="L91" s="15" t="inlineStr">
@@ -8877,7 +8877,7 @@
     <row r="92">
       <c r="A92" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-07</t>
+          <t>TC-REC-06</t>
         </is>
       </c>
       <c r="B92" s="15" t="inlineStr">
@@ -8887,7 +8887,7 @@
       </c>
       <c r="C92" s="19" t="inlineStr">
         <is>
-          <t>Hire non-academic staff</t>
+          <t>Hire an Academic Advisor</t>
         </is>
       </c>
       <c r="D92" s="15" t="inlineStr">
@@ -8897,22 +8897,22 @@
       </c>
       <c r="E92" s="19" t="inlineStr">
         <is>
-          <t>Applicant for a Non-Academic link.</t>
+          <t>Applicant for an Academic Advisor link with a phone like 05XXXXXXXX.</t>
         </is>
       </c>
       <c r="F92" s="19" t="inlineStr">
         <is>
-          <t>Accept -&gt; Create Employee.</t>
+          <t>Accept -&gt; Create Employee with a @alriyada.edu.sa Company Email.</t>
         </is>
       </c>
       <c r="G92" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Local phone number</t>
         </is>
       </c>
       <c r="H92" s="19" t="inlineStr">
         <is>
-          <t>Employee created; work phone and extension kept on the Employee.</t>
+          <t>Employee, Academic Advisor and Instructor records created; no 'record not created' warning.</t>
         </is>
       </c>
       <c r="I92" s="15" t="inlineStr">
@@ -8922,12 +8922,12 @@
       </c>
       <c r="J92" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K92" s="15" t="inlineStr">
         <is>
-          <t>REC-05/06</t>
+          <t>REC-04</t>
         </is>
       </c>
       <c r="L92" s="15" t="inlineStr">
@@ -8958,7 +8958,7 @@
     <row r="93">
       <c r="A93" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-08</t>
+          <t>TC-REC-07</t>
         </is>
       </c>
       <c r="B93" s="15" t="inlineStr">
@@ -8968,7 +8968,7 @@
       </c>
       <c r="C93" s="19" t="inlineStr">
         <is>
-          <t>Reject an applicant</t>
+          <t>Hire non-academic staff</t>
         </is>
       </c>
       <c r="D93" s="15" t="inlineStr">
@@ -8978,12 +8978,12 @@
       </c>
       <c r="E93" s="19" t="inlineStr">
         <is>
-          <t>A Pending applicant.</t>
+          <t>Applicant for a Non-Academic link.</t>
         </is>
       </c>
       <c r="F93" s="19" t="inlineStr">
         <is>
-          <t>Click Reject.</t>
+          <t>Accept -&gt; Create Employee.</t>
         </is>
       </c>
       <c r="G93" s="19" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="H93" s="19" t="inlineStr">
         <is>
-          <t>Status Rejected; Create Employee not offered.</t>
+          <t>Employee created; work phone and extension kept on the Employee.</t>
         </is>
       </c>
       <c r="I93" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J93" s="15" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="K93" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-05/06</t>
         </is>
       </c>
       <c r="L93" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M93" s="20" t="inlineStr">
@@ -9039,7 +9039,7 @@
     <row r="94">
       <c r="A94" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-09</t>
+          <t>TC-REC-08</t>
         </is>
       </c>
       <c r="B94" s="15" t="inlineStr">
@@ -9049,32 +9049,32 @@
       </c>
       <c r="C94" s="19" t="inlineStr">
         <is>
-          <t>Duplicate applicant identity</t>
+          <t>Reject an applicant</t>
         </is>
       </c>
       <c r="D94" s="15" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E94" s="19" t="inlineStr">
         <is>
-          <t>An employee already has the ID number.</t>
+          <t>A Pending applicant.</t>
         </is>
       </c>
       <c r="F94" s="19" t="inlineStr">
         <is>
-          <t>Submit a new application with that ID; HR tries to create the Employee.</t>
+          <t>Click Reject.</t>
         </is>
       </c>
       <c r="G94" s="19" t="inlineStr">
         <is>
-          <t>Existing ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H94" s="19" t="inlineStr">
         <is>
-          <t>Creating the Employee is refused as a duplicate.</t>
+          <t>Status Rejected; Create Employee not offered.</t>
         </is>
       </c>
       <c r="I94" s="15" t="inlineStr">
@@ -9084,7 +9084,7 @@
       </c>
       <c r="J94" s="15" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K94" s="15" t="inlineStr">
@@ -9120,7 +9120,7 @@
     <row r="95">
       <c r="A95" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-11</t>
+          <t>TC-REC-09</t>
         </is>
       </c>
       <c r="B95" s="15" t="inlineStr">
@@ -9130,53 +9130,52 @@
       </c>
       <c r="C95" s="19" t="inlineStr">
         <is>
-          <t>A new hire's record opens clean</t>
+          <t>Duplicate applicant identity</t>
         </is>
       </c>
       <c r="D95" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="E95" s="19" t="inlineStr">
         <is>
-          <t>An applicant who answered 'Has Special Needs = No' but also picked a type (and, if Saudi, typed a home-country ID).</t>
+          <t>An employee already has the ID number.</t>
         </is>
       </c>
       <c r="F95" s="19" t="inlineStr">
         <is>
-          <t>1. Hire them (Create Employee).
-2. Open the new Employee record.</t>
+          <t>Submit a new application with that ID; HR tries to create the Employee.</t>
         </is>
       </c>
       <c r="G95" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Existing ID</t>
         </is>
       </c>
       <c r="H95" s="19" t="inlineStr">
         <is>
-          <t>The record shows its status (not 'Not Saved'); special-needs type and home-country ID are empty.</t>
+          <t>Creating the Employee is refused as a duplicate.</t>
         </is>
       </c>
       <c r="I95" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J95" s="15" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K95" s="15" t="inlineStr">
         <is>
-          <t>REC-09</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L95" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M95" s="20" t="inlineStr">
@@ -9202,7 +9201,7 @@
     <row r="96">
       <c r="A96" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-12</t>
+          <t>TC-REC-11</t>
         </is>
       </c>
       <c r="B96" s="15" t="inlineStr">
@@ -9212,7 +9211,7 @@
       </c>
       <c r="C96" s="19" t="inlineStr">
         <is>
-          <t>Create Employee asks for what the Employee form requires</t>
+          <t>A new hire's record opens clean</t>
         </is>
       </c>
       <c r="D96" s="15" t="inlineStr">
@@ -9222,15 +9221,13 @@
       </c>
       <c r="E96" s="19" t="inlineStr">
         <is>
-          <t>An Accepted applicant.</t>
+          <t>An applicant who answered 'Has Special Needs = No' but also picked a type (and, if Saudi, typed a home-country ID).</t>
         </is>
       </c>
       <c r="F96" s="19" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Look at the Employee Record section of the dialog.
-3. Fill it and confirm.
-4. Open the new Employee, change any field, Save.</t>
+          <t>1. Hire them (Create Employee).
+2. Open the new Employee record.</t>
         </is>
       </c>
       <c r="G96" s="19" t="inlineStr">
@@ -9240,7 +9237,7 @@
       </c>
       <c r="H96" s="19" t="inlineStr">
         <is>
-          <t>The dialog asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application), and Gender / Date of Birth only when the application left them empty. The Employee saves with no 'Missing Fields'.</t>
+          <t>The record shows its status (not 'Not Saved'); special-needs type and home-country ID are empty.</t>
         </is>
       </c>
       <c r="I96" s="15" t="inlineStr">
@@ -9255,7 +9252,7 @@
       </c>
       <c r="K96" s="15" t="inlineStr">
         <is>
-          <t>REC-10</t>
+          <t>REC-09</t>
         </is>
       </c>
       <c r="L96" s="15" t="inlineStr">
@@ -9286,7 +9283,7 @@
     <row r="97">
       <c r="A97" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-13</t>
+          <t>TC-REC-12</t>
         </is>
       </c>
       <c r="B97" s="15" t="inlineStr">
@@ -9296,55 +9293,55 @@
       </c>
       <c r="C97" s="19" t="inlineStr">
         <is>
-          <t>Phone number with country code</t>
+          <t>Create Employee asks for what the Employee form requires</t>
         </is>
       </c>
       <c r="D97" s="15" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E97" s="19" t="inlineStr">
         <is>
-          <t>A valid application link.</t>
+          <t>An Accepted applicant.</t>
         </is>
       </c>
       <c r="F97" s="19" t="inlineStr">
         <is>
-          <t>1. Open the link.
-2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
-3. Send.
-4. Correct it and send again.</t>
+          <t>1. Create Employee.
+2. Look at the Employee Record section of the dialog.
+3. Fill it and confirm.
+4. Open the new Employee, change any field, Save.</t>
         </is>
       </c>
       <c r="G97" s="19" t="inlineStr">
         <is>
-          <t>123, then a full mobile number</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H97" s="19" t="inlineStr">
         <is>
-          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
+          <t>The dialog asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application), and Gender / Date of Birth only when the application left them empty. The Employee saves with no 'Missing Fields'.</t>
         </is>
       </c>
       <c r="I97" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J97" s="15" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K97" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-10</t>
         </is>
       </c>
       <c r="L97" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M97" s="20" t="inlineStr">
@@ -9358,19 +9355,19 @@
       <c r="Q97" s="20" t="inlineStr"/>
       <c r="R97" s="15" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="S97" s="15" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-14</t>
+          <t>TC-REC-13</t>
         </is>
       </c>
       <c r="B98" s="15" t="inlineStr">
@@ -9380,7 +9377,7 @@
       </c>
       <c r="C98" s="19" t="inlineStr">
         <is>
-          <t>Receipt after sending the application</t>
+          <t>Phone number with country code</t>
         </is>
       </c>
       <c r="D98" s="15" t="inlineStr">
@@ -9390,22 +9387,25 @@
       </c>
       <c r="E98" s="19" t="inlineStr">
         <is>
-          <t>TC-REC-13 done (application sent).</t>
+          <t>A valid application link.</t>
         </is>
       </c>
       <c r="F98" s="19" t="inlineStr">
         <is>
-          <t>On the confirmation screen click the receipt download button.</t>
+          <t>1. Open the link.
+2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
+3. Send.
+4. Correct it and send again.</t>
         </is>
       </c>
       <c r="G98" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123, then a full mobile number</t>
         </is>
       </c>
       <c r="H98" s="19" t="inlineStr">
         <is>
-          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
+          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
         </is>
       </c>
       <c r="I98" s="15" t="inlineStr">
@@ -9415,7 +9415,7 @@
       </c>
       <c r="J98" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K98" s="15" t="inlineStr">
@@ -9451,7 +9451,7 @@
     <row r="99">
       <c r="A99" s="17" t="inlineStr">
         <is>
-          <t>TC-REC-10</t>
+          <t>TC-REC-14</t>
         </is>
       </c>
       <c r="B99" s="15" t="inlineStr">
@@ -9461,55 +9461,52 @@
       </c>
       <c r="C99" s="19" t="inlineStr">
         <is>
-          <t>Academic hire needs the college e-mail</t>
+          <t>Receipt after sending the application</t>
         </is>
       </c>
       <c r="D99" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="E99" s="19" t="inlineStr">
         <is>
-          <t>An Accepted applicant from an Instructor link.</t>
+          <t>TC-REC-13 done (application sent).</t>
         </is>
       </c>
       <c r="F99" s="19" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Leave Company Email empty (or a gmail address).
-3. Confirm.
-4. Then enter a @alriyada.edu.sa address and confirm again.</t>
+          <t>On the confirmation screen click the receipt download button.</t>
         </is>
       </c>
       <c r="G99" s="19" t="inlineStr">
         <is>
-          <t>Personal e-mail, then college e-mail</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H99" s="19" t="inlineStr">
         <is>
-          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
+          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
         </is>
       </c>
       <c r="I99" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J99" s="15" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K99" s="15" t="inlineStr">
         <is>
-          <t>REC-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L99" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M99" s="20" t="inlineStr">
@@ -9523,29 +9520,29 @@
       <c r="Q99" s="20" t="inlineStr"/>
       <c r="R99" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="S99" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-01</t>
+          <t>TC-REC-10</t>
         </is>
       </c>
       <c r="B100" s="15" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C100" s="19" t="inlineStr">
         <is>
-          <t>Faculty schedules</t>
+          <t>Academic hire needs the college e-mail</t>
         </is>
       </c>
       <c r="D100" s="15" t="inlineStr">
@@ -9555,22 +9552,25 @@
       </c>
       <c r="E100" s="19" t="inlineStr">
         <is>
-          <t>Published class timetables.</t>
+          <t>An Accepted applicant from an Instructor link.</t>
         </is>
       </c>
       <c r="F100" s="19" t="inlineStr">
         <is>
-          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
+          <t>1. Create Employee.
+2. Leave Company Email empty (or a gmail address).
+3. Confirm.
+4. Then enter a @alriyada.edu.sa address and confirm again.</t>
         </is>
       </c>
       <c r="G100" s="19" t="inlineStr">
         <is>
-          <t>6–12 Sep 2026</t>
+          <t>Personal e-mail, then college e-mail</t>
         </is>
       </c>
       <c r="H100" s="19" t="inlineStr">
         <is>
-          <t>Sessions per faculty member with day, time, course, room and mode.</t>
+          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
         </is>
       </c>
       <c r="I100" s="15" t="inlineStr">
@@ -9580,12 +9580,12 @@
       </c>
       <c r="J100" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K100" s="15" t="inlineStr">
         <is>
-          <t>PRS-01</t>
+          <t>REC-08</t>
         </is>
       </c>
       <c r="L100" s="15" t="inlineStr">
@@ -9616,7 +9616,7 @@
     <row r="101">
       <c r="A101" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-02</t>
+          <t>TC-PRS-01</t>
         </is>
       </c>
       <c r="B101" s="15" t="inlineStr">
@@ -9626,7 +9626,7 @@
       </c>
       <c r="C101" s="19" t="inlineStr">
         <is>
-          <t>Filter one faculty member</t>
+          <t>Faculty schedules</t>
         </is>
       </c>
       <c r="D101" s="15" t="inlineStr">
@@ -9636,27 +9636,27 @@
       </c>
       <c r="E101" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Published class timetables.</t>
         </is>
       </c>
       <c r="F101" s="19" t="inlineStr">
         <is>
-          <t>Pick a faculty member in the filter.</t>
+          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
         </is>
       </c>
       <c r="G101" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6–12 Sep 2026</t>
         </is>
       </c>
       <c r="H101" s="19" t="inlineStr">
         <is>
-          <t>Only that person's sessions.</t>
+          <t>Sessions per faculty member with day, time, course, room and mode.</t>
         </is>
       </c>
       <c r="I101" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J101" s="15" t="inlineStr">
@@ -9666,7 +9666,7 @@
       </c>
       <c r="K101" s="15" t="inlineStr">
         <is>
-          <t>PRS-02</t>
+          <t>PRS-01</t>
         </is>
       </c>
       <c r="L101" s="15" t="inlineStr">
@@ -9697,7 +9697,7 @@
     <row r="102">
       <c r="A102" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-03</t>
+          <t>TC-PRS-02</t>
         </is>
       </c>
       <c r="B102" s="15" t="inlineStr">
@@ -9707,7 +9707,7 @@
       </c>
       <c r="C102" s="19" t="inlineStr">
         <is>
-          <t>Proctor schedules</t>
+          <t>Filter one faculty member</t>
         </is>
       </c>
       <c r="D102" s="15" t="inlineStr">
@@ -9717,22 +9717,22 @@
       </c>
       <c r="E102" s="19" t="inlineStr">
         <is>
-          <t>Exam committees with proctors.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F102" s="19" t="inlineStr">
         <is>
-          <t>Open Proctor Schedules for the exam week.</t>
+          <t>Pick a faculty member in the filter.</t>
         </is>
       </c>
       <c r="G102" s="19" t="inlineStr">
         <is>
-          <t>Exam week</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H102" s="19" t="inlineStr">
         <is>
-          <t>Proctor assignments, or a clear 'no assignments' message.</t>
+          <t>Only that person's sessions.</t>
         </is>
       </c>
       <c r="I102" s="15" t="inlineStr">
@@ -9747,7 +9747,7 @@
       </c>
       <c r="K102" s="15" t="inlineStr">
         <is>
-          <t>PRS-03</t>
+          <t>PRS-02</t>
         </is>
       </c>
       <c r="L102" s="15" t="inlineStr">
@@ -9778,7 +9778,7 @@
     <row r="103">
       <c r="A103" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-04</t>
+          <t>TC-PRS-03</t>
         </is>
       </c>
       <c r="B103" s="15" t="inlineStr">
@@ -9788,7 +9788,7 @@
       </c>
       <c r="C103" s="19" t="inlineStr">
         <is>
-          <t>Students on campus per hour</t>
+          <t>Proctor schedules</t>
         </is>
       </c>
       <c r="D103" s="15" t="inlineStr">
@@ -9798,27 +9798,27 @@
       </c>
       <c r="E103" s="19" t="inlineStr">
         <is>
-          <t>Attendance recorded.</t>
+          <t>Exam committees with proctors.</t>
         </is>
       </c>
       <c r="F103" s="19" t="inlineStr">
         <is>
-          <t>Open Students on Campus for a teaching day.</t>
+          <t>Open Proctor Schedules for the exam week.</t>
         </is>
       </c>
       <c r="G103" s="19" t="inlineStr">
         <is>
-          <t>8 Sep 2026</t>
+          <t>Exam week</t>
         </is>
       </c>
       <c r="H103" s="19" t="inlineStr">
         <is>
-          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
+          <t>Proctor assignments, or a clear 'no assignments' message.</t>
         </is>
       </c>
       <c r="I103" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J103" s="15" t="inlineStr">
@@ -9828,7 +9828,7 @@
       </c>
       <c r="K103" s="15" t="inlineStr">
         <is>
-          <t>PRS-04</t>
+          <t>PRS-03</t>
         </is>
       </c>
       <c r="L103" s="15" t="inlineStr">
@@ -9859,7 +9859,7 @@
     <row r="104">
       <c r="A104" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-05</t>
+          <t>TC-PRS-04</t>
         </is>
       </c>
       <c r="B104" s="15" t="inlineStr">
@@ -9869,7 +9869,7 @@
       </c>
       <c r="C104" s="19" t="inlineStr">
         <is>
-          <t>Faculty after 4 PM</t>
+          <t>Students on campus per hour</t>
         </is>
       </c>
       <c r="D104" s="15" t="inlineStr">
@@ -9879,22 +9879,22 @@
       </c>
       <c r="E104" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Attendance recorded.</t>
         </is>
       </c>
       <c r="F104" s="19" t="inlineStr">
         <is>
-          <t>Open Faculty After 4 PM for a week.</t>
+          <t>Open Students on Campus for a teaching day.</t>
         </is>
       </c>
       <c r="G104" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8 Sep 2026</t>
         </is>
       </c>
       <c r="H104" s="19" t="inlineStr">
         <is>
-          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
+          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
         </is>
       </c>
       <c r="I104" s="15" t="inlineStr">
@@ -9909,7 +9909,7 @@
       </c>
       <c r="K104" s="15" t="inlineStr">
         <is>
-          <t>PRS-05</t>
+          <t>PRS-04</t>
         </is>
       </c>
       <c r="L104" s="15" t="inlineStr">
@@ -9940,7 +9940,7 @@
     <row r="105">
       <c r="A105" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-06</t>
+          <t>TC-PRS-05</t>
         </is>
       </c>
       <c r="B105" s="15" t="inlineStr">
@@ -9950,7 +9950,7 @@
       </c>
       <c r="C105" s="19" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Faculty after 4 PM</t>
         </is>
       </c>
       <c r="D105" s="15" t="inlineStr">
@@ -9960,12 +9960,12 @@
       </c>
       <c r="E105" s="19" t="inlineStr">
         <is>
-          <t>A tab with data.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F105" s="19" t="inlineStr">
         <is>
-          <t>Click Export (Excel CSV).</t>
+          <t>Open Faculty After 4 PM for a week.</t>
         </is>
       </c>
       <c r="G105" s="19" t="inlineStr">
@@ -9975,12 +9975,12 @@
       </c>
       <c r="H105" s="19" t="inlineStr">
         <is>
-          <t>A CSV file downloads and opens in Excel with the same rows.</t>
+          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
         </is>
       </c>
       <c r="I105" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J105" s="15" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="K105" s="15" t="inlineStr">
         <is>
-          <t>PRS-06</t>
+          <t>PRS-05</t>
         </is>
       </c>
       <c r="L105" s="15" t="inlineStr">
@@ -10021,7 +10021,7 @@
     <row r="106">
       <c r="A106" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-07</t>
+          <t>TC-PRS-06</t>
         </is>
       </c>
       <c r="B106" s="15" t="inlineStr">
@@ -10031,7 +10031,7 @@
       </c>
       <c r="C106" s="19" t="inlineStr">
         <is>
-          <t>Holiday and exam days</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="D106" s="15" t="inlineStr">
@@ -10041,12 +10041,12 @@
       </c>
       <c r="E106" s="19" t="inlineStr">
         <is>
-          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
+          <t>A tab with data.</t>
         </is>
       </c>
       <c r="F106" s="19" t="inlineStr">
         <is>
-          <t>Open Faculty Schedules over a holiday or exam week.</t>
+          <t>Click Export (Excel CSV).</t>
         </is>
       </c>
       <c r="G106" s="19" t="inlineStr">
@@ -10056,7 +10056,7 @@
       </c>
       <c r="H106" s="19" t="inlineStr">
         <is>
-          <t>No regular sessions on those days; the skipped dates are listed.</t>
+          <t>A CSV file downloads and opens in Excel with the same rows.</t>
         </is>
       </c>
       <c r="I106" s="15" t="inlineStr">
@@ -10071,12 +10071,12 @@
       </c>
       <c r="K106" s="15" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>PRS-06</t>
         </is>
       </c>
       <c r="L106" s="15" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M106" s="20" t="inlineStr">
@@ -10102,7 +10102,7 @@
     <row r="107">
       <c r="A107" s="17" t="inlineStr">
         <is>
-          <t>TC-PRS-08</t>
+          <t>TC-PRS-07</t>
         </is>
       </c>
       <c r="B107" s="15" t="inlineStr">
@@ -10112,7 +10112,7 @@
       </c>
       <c r="C107" s="19" t="inlineStr">
         <is>
-          <t>Cut-off time setting</t>
+          <t>Holiday and exam days</t>
         </is>
       </c>
       <c r="D107" s="15" t="inlineStr">
@@ -10122,27 +10122,27 @@
       </c>
       <c r="E107" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
         </is>
       </c>
       <c r="F107" s="19" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
+          <t>Open Faculty Schedules over a holiday or exam week.</t>
         </is>
       </c>
       <c r="G107" s="19" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H107" s="19" t="inlineStr">
         <is>
-          <t>List uses the new time.</t>
+          <t>No regular sessions on those days; the skipped dates are listed.</t>
         </is>
       </c>
       <c r="I107" s="15" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J107" s="15" t="inlineStr">
@@ -10152,12 +10152,12 @@
       </c>
       <c r="K107" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="L107" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M107" s="20" t="inlineStr">
@@ -10183,17 +10183,17 @@
     <row r="108">
       <c r="A108" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-01</t>
+          <t>TC-PRS-08</t>
         </is>
       </c>
       <c r="B108" s="15" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C108" s="19" t="inlineStr">
         <is>
-          <t>Jameah Data Check page</t>
+          <t>Cut-off time setting</t>
         </is>
       </c>
       <c r="D108" s="15" t="inlineStr">
@@ -10208,22 +10208,22 @@
       </c>
       <c r="F108" s="19" t="inlineStr">
         <is>
-          <t>HR Dashboard -&gt; Jameah Data Check.</t>
+          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
         </is>
       </c>
       <c r="G108" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="H108" s="19" t="inlineStr">
         <is>
-          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
+          <t>List uses the new time.</t>
         </is>
       </c>
       <c r="I108" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J108" s="15" t="inlineStr">
@@ -10233,12 +10233,12 @@
       </c>
       <c r="K108" s="15" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L108" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M108" s="20" t="inlineStr">
@@ -10264,7 +10264,7 @@
     <row r="109">
       <c r="A109" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-02</t>
+          <t>TC-JM-01</t>
         </is>
       </c>
       <c r="B109" s="15" t="inlineStr">
@@ -10274,12 +10274,12 @@
       </c>
       <c r="C109" s="19" t="inlineStr">
         <is>
-          <t>Jameah Settings pickers</t>
+          <t>Jameah Data Check page</t>
         </is>
       </c>
       <c r="D109" s="15" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E109" s="19" t="inlineStr">
@@ -10289,7 +10289,7 @@
       </c>
       <c r="F109" s="19" t="inlineStr">
         <is>
-          <t>Open Jameah Settings; open the College picker.</t>
+          <t>HR Dashboard -&gt; Jameah Data Check.</t>
         </is>
       </c>
       <c r="G109" s="19" t="inlineStr">
@@ -10299,12 +10299,12 @@
       </c>
       <c r="H109" s="19" t="inlineStr">
         <is>
-          <t>Only College Coding Guide codes are offered.</t>
+          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
         </is>
       </c>
       <c r="I109" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J109" s="15" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="K109" s="15" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="L109" s="15" t="inlineStr">
@@ -10345,7 +10345,7 @@
     <row r="110">
       <c r="A110" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-03</t>
+          <t>TC-JM-02</t>
         </is>
       </c>
       <c r="B110" s="15" t="inlineStr">
@@ -10355,7 +10355,7 @@
       </c>
       <c r="C110" s="19" t="inlineStr">
         <is>
-          <t>Fill a setting and see it in the views</t>
+          <t>Jameah Settings pickers</t>
         </is>
       </c>
       <c r="D110" s="15" t="inlineStr">
@@ -10365,22 +10365,22 @@
       </c>
       <c r="E110" s="19" t="inlineStr">
         <is>
-          <t>Decision on the college code (DEC-02).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F110" s="19" t="inlineStr">
         <is>
-          <t>Set College; Save; reopen Jameah Data Check.</t>
+          <t>Open Jameah Settings; open the College picker.</t>
         </is>
       </c>
       <c r="G110" s="19" t="inlineStr">
         <is>
-          <t>College code</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H110" s="19" t="inlineStr">
         <is>
-          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
+          <t>Only College Coding Guide codes are offered.</t>
         </is>
       </c>
       <c r="I110" s="15" t="inlineStr">
@@ -10395,12 +10395,12 @@
       </c>
       <c r="K110" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="L110" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M110" s="20" t="inlineStr">
@@ -10426,7 +10426,7 @@
     <row r="111">
       <c r="A111" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-04</t>
+          <t>TC-JM-03</t>
         </is>
       </c>
       <c r="B111" s="15" t="inlineStr">
@@ -10436,7 +10436,7 @@
       </c>
       <c r="C111" s="19" t="inlineStr">
         <is>
-          <t>Map a value in the Code Map</t>
+          <t>Fill a setting and see it in the views</t>
         </is>
       </c>
       <c r="D111" s="15" t="inlineStr">
@@ -10446,22 +10446,22 @@
       </c>
       <c r="E111" s="19" t="inlineStr">
         <is>
-          <t>A 'Needs Review' row.</t>
+          <t>Decision on the college code (DEC-02).</t>
         </is>
       </c>
       <c r="F111" s="19" t="inlineStr">
         <is>
-          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
+          <t>Set College; Save; reopen Jameah Data Check.</t>
         </is>
       </c>
       <c r="G111" s="19" t="inlineStr">
         <is>
-          <t>e.g. Internship -&gt; 0</t>
+          <t>College code</t>
         </is>
       </c>
       <c r="H111" s="19" t="inlineStr">
         <is>
-          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
+          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
         </is>
       </c>
       <c r="I111" s="15" t="inlineStr">
@@ -10476,12 +10476,12 @@
       </c>
       <c r="K111" s="15" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L111" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M111" s="20" t="inlineStr">
@@ -10507,7 +10507,7 @@
     <row r="112">
       <c r="A112" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-05</t>
+          <t>TC-JM-04</t>
         </is>
       </c>
       <c r="B112" s="15" t="inlineStr">
@@ -10517,7 +10517,7 @@
       </c>
       <c r="C112" s="19" t="inlineStr">
         <is>
-          <t>Code Map refuses a code from another list</t>
+          <t>Map a value in the Code Map</t>
         </is>
       </c>
       <c r="D112" s="15" t="inlineStr">
@@ -10527,42 +10527,42 @@
       </c>
       <c r="E112" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A 'Needs Review' row.</t>
         </is>
       </c>
       <c r="F112" s="19" t="inlineStr">
         <is>
-          <t>Try to save a Religion row with a Gender code.</t>
+          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
         </is>
       </c>
       <c r="G112" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>e.g. Internship -&gt; 0</t>
         </is>
       </c>
       <c r="H112" s="19" t="inlineStr">
         <is>
-          <t>Refused with a clear message.</t>
+          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
         </is>
       </c>
       <c r="I112" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J112" s="15" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K112" s="15" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="L112" s="15" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M112" s="20" t="inlineStr">
@@ -10588,7 +10588,7 @@
     <row r="113">
       <c r="A113" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-06</t>
+          <t>TC-JM-05</t>
         </is>
       </c>
       <c r="B113" s="15" t="inlineStr">
@@ -10598,12 +10598,12 @@
       </c>
       <c r="C113" s="19" t="inlineStr">
         <is>
-          <t>Refresh academic figures</t>
+          <t>Code Map refuses a code from another list</t>
         </is>
       </c>
       <c r="D113" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E113" s="19" t="inlineStr">
@@ -10613,7 +10613,7 @@
       </c>
       <c r="F113" s="19" t="inlineStr">
         <is>
-          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
+          <t>Try to save a Religion row with a Gender code.</t>
         </is>
       </c>
       <c r="G113" s="19" t="inlineStr">
@@ -10623,7 +10623,7 @@
       </c>
       <c r="H113" s="19" t="inlineStr">
         <is>
-          <t>'Last refreshed' time updates.</t>
+          <t>Refused with a clear message.</t>
         </is>
       </c>
       <c r="I113" s="15" t="inlineStr">
@@ -10633,17 +10633,17 @@
       </c>
       <c r="J113" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K113" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="L113" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M113" s="20" t="inlineStr">
@@ -10669,7 +10669,7 @@
     <row r="114">
       <c r="A114" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-07</t>
+          <t>TC-JM-06</t>
         </is>
       </c>
       <c r="B114" s="15" t="inlineStr">
@@ -10679,7 +10679,7 @@
       </c>
       <c r="C114" s="19" t="inlineStr">
         <is>
-          <t>Employee data reaches the Employee views</t>
+          <t>Refresh academic figures</t>
         </is>
       </c>
       <c r="D114" s="15" t="inlineStr">
@@ -10689,12 +10689,12 @@
       </c>
       <c r="E114" s="19" t="inlineStr">
         <is>
-          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F114" s="19" t="inlineStr">
         <is>
-          <t>Open their Ministry (Jameah) Data preview.</t>
+          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
         </is>
       </c>
       <c r="G114" s="19" t="inlineStr">
@@ -10704,12 +10704,12 @@
       </c>
       <c r="H114" s="19" t="inlineStr">
         <is>
-          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
+          <t>'Last refreshed' time updates.</t>
         </is>
       </c>
       <c r="I114" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J114" s="15" t="inlineStr">
@@ -10719,12 +10719,12 @@
       </c>
       <c r="K114" s="15" t="inlineStr">
         <is>
-          <t>REC-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L114" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M114" s="20" t="inlineStr">
@@ -10750,7 +10750,7 @@
     <row r="115">
       <c r="A115" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-10</t>
+          <t>TC-JM-07</t>
         </is>
       </c>
       <c r="B115" s="15" t="inlineStr">
@@ -10760,32 +10760,32 @@
       </c>
       <c r="C115" s="19" t="inlineStr">
         <is>
-          <t>Ministry GPA and hours equal the student's transcript</t>
+          <t>Employee data reaches the Employee views</t>
         </is>
       </c>
       <c r="D115" s="15" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E115" s="19" t="inlineStr">
         <is>
-          <t>Academic figures refreshed (TC-JM-06).</t>
+          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
         </is>
       </c>
       <c r="F115" s="19" t="inlineStr">
         <is>
-          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
+          <t>Open their Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="G115" s="19" t="inlineStr">
         <is>
-          <t>10 students</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H115" s="19" t="inlineStr">
         <is>
-          <t>All four figures are identical for every student.</t>
+          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
         </is>
       </c>
       <c r="I115" s="15" t="inlineStr">
@@ -10795,12 +10795,12 @@
       </c>
       <c r="J115" s="15" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K115" s="15" t="inlineStr">
         <is>
-          <t>verify.run</t>
+          <t>REC-06</t>
         </is>
       </c>
       <c r="L115" s="15" t="inlineStr">
@@ -10831,7 +10831,7 @@
     <row r="116">
       <c r="A116" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-08</t>
+          <t>TC-JM-10</t>
         </is>
       </c>
       <c r="B116" s="15" t="inlineStr">
@@ -10841,32 +10841,32 @@
       </c>
       <c r="C116" s="19" t="inlineStr">
         <is>
-          <t>Full value-by-value check (developer)</t>
+          <t>Ministry GPA and hours equal the student's transcript</t>
         </is>
       </c>
       <c r="D116" s="15" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E116" s="19" t="inlineStr">
         <is>
-          <t>Server access.</t>
+          <t>Academic figures refreshed (TC-JM-06).</t>
         </is>
       </c>
       <c r="F116" s="19" t="inlineStr">
         <is>
-          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
+          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
         </is>
       </c>
       <c r="G116" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 students</t>
         </is>
       </c>
       <c r="H116" s="19" t="inlineStr">
         <is>
-          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
+          <t>All four figures are identical for every student.</t>
         </is>
       </c>
       <c r="I116" s="15" t="inlineStr">
@@ -10912,7 +10912,7 @@
     <row r="117">
       <c r="A117" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-09</t>
+          <t>TC-JM-08</t>
         </is>
       </c>
       <c r="B117" s="15" t="inlineStr">
@@ -10922,22 +10922,22 @@
       </c>
       <c r="C117" s="19" t="inlineStr">
         <is>
-          <t>Ministry read-only account</t>
+          <t>Full value-by-value check (developer)</t>
         </is>
       </c>
       <c r="D117" s="15" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="E117" s="19" t="inlineStr">
         <is>
-          <t>Account created with the grant statements.</t>
+          <t>Server access.</t>
         </is>
       </c>
       <c r="F117" s="19" t="inlineStr">
         <is>
-          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
+          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="G117" s="19" t="inlineStr">
@@ -10947,27 +10947,27 @@
       </c>
       <c r="H117" s="19" t="inlineStr">
         <is>
-          <t>Views readable; ERP tables refused.</t>
+          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
         </is>
       </c>
       <c r="I117" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J117" s="15" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="K117" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verify.run</t>
         </is>
       </c>
       <c r="L117" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M117" s="20" t="inlineStr">
@@ -10993,7 +10993,7 @@
     <row r="118">
       <c r="A118" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-11</t>
+          <t>TC-JM-09</t>
         </is>
       </c>
       <c r="B118" s="15" t="inlineStr">
@@ -11003,22 +11003,22 @@
       </c>
       <c r="C118" s="19" t="inlineStr">
         <is>
-          <t>Faculty views on the Data Check page</t>
+          <t>Ministry read-only account</t>
         </is>
       </c>
       <c r="D118" s="15" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="E118" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Account created with the grant statements.</t>
         </is>
       </c>
       <c r="F118" s="19" t="inlineStr">
         <is>
-          <t>Open Jameah Data Check and look at the Views table.</t>
+          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
         </is>
       </c>
       <c r="G118" s="19" t="inlineStr">
@@ -11028,7 +11028,7 @@
       </c>
       <c r="H118" s="19" t="inlineStr">
         <is>
-          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
+          <t>Views readable; ERP tables refused.</t>
         </is>
       </c>
       <c r="I118" s="15" t="inlineStr">
@@ -11038,17 +11038,17 @@
       </c>
       <c r="J118" s="15" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K118" s="15" t="inlineStr">
         <is>
-          <t>JM-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L118" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M118" s="20" t="inlineStr">
@@ -11074,7 +11074,7 @@
     <row r="119">
       <c r="A119" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-12</t>
+          <t>TC-JM-11</t>
         </is>
       </c>
       <c r="B119" s="15" t="inlineStr">
@@ -11084,7 +11084,7 @@
       </c>
       <c r="C119" s="19" t="inlineStr">
         <is>
-          <t>A teacher is sent once, as Faculty</t>
+          <t>Faculty views on the Data Check page</t>
         </is>
       </c>
       <c r="D119" s="15" t="inlineStr">
@@ -11094,13 +11094,12 @@
       </c>
       <c r="E119" s="19" t="inlineStr">
         <is>
-          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F119" s="19" t="inlineStr">
         <is>
-          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
-2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
+          <t>Open Jameah Data Check and look at the Views table.</t>
         </is>
       </c>
       <c r="G119" s="19" t="inlineStr">
@@ -11110,27 +11109,27 @@
       </c>
       <c r="H119" s="19" t="inlineStr">
         <is>
-          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
+          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
         </is>
       </c>
       <c r="I119" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J119" s="15" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K119" s="15" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="L119" s="15" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M119" s="20" t="inlineStr">
@@ -11156,7 +11155,7 @@
     <row r="120">
       <c r="A120" s="17" t="inlineStr">
         <is>
-          <t>TC-JM-13</t>
+          <t>TC-JM-12</t>
         </is>
       </c>
       <c r="B120" s="15" t="inlineStr">
@@ -11166,23 +11165,23 @@
       </c>
       <c r="C120" s="19" t="inlineStr">
         <is>
-          <t>Faculty status and contract codes</t>
+          <t>A teacher is sent once, as Faculty</t>
         </is>
       </c>
       <c r="D120" s="15" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E120" s="19" t="inlineStr">
         <is>
-          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
         </is>
       </c>
       <c r="F120" s="19" t="inlineStr">
         <is>
-          <t>1. Open each row, pick the Ministry code, Status = Verified.
-2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
+2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
         </is>
       </c>
       <c r="G120" s="19" t="inlineStr">
@@ -11192,12 +11191,12 @@
       </c>
       <c r="H120" s="19" t="inlineStr">
         <is>
-          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
+          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
         </is>
       </c>
       <c r="I120" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J120" s="15" t="inlineStr">
@@ -11207,12 +11206,12 @@
       </c>
       <c r="K120" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="L120" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M120" s="20" t="inlineStr">
@@ -11238,32 +11237,33 @@
     <row r="121">
       <c r="A121" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-01</t>
+          <t>TC-JM-13</t>
         </is>
       </c>
       <c r="B121" s="15" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="C121" s="19" t="inlineStr">
         <is>
-          <t>Error Log after each test day</t>
+          <t>Faculty status and contract codes</t>
         </is>
       </c>
       <c r="D121" s="15" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E121" s="19" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
         </is>
       </c>
       <c r="F121" s="19" t="inlineStr">
         <is>
-          <t>Open /app/error-log; sort by newest.</t>
+          <t>1. Open each row, pick the Ministry code, Status = Verified.
+2. Refresh Academic Figures / reopen Jameah Data Check.</t>
         </is>
       </c>
       <c r="G121" s="19" t="inlineStr">
@@ -11273,17 +11273,17 @@
       </c>
       <c r="H121" s="19" t="inlineStr">
         <is>
-          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
+          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
         </is>
       </c>
       <c r="I121" s="15" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J121" s="15" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="K121" s="15" t="inlineStr">
@@ -11319,7 +11319,7 @@
     <row r="122">
       <c r="A122" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-02</t>
+          <t>TC-ERR-01</t>
         </is>
       </c>
       <c r="B122" s="15" t="inlineStr">
@@ -11329,7 +11329,7 @@
       </c>
       <c r="C122" s="19" t="inlineStr">
         <is>
-          <t>System e-mail works</t>
+          <t>Error Log after each test day</t>
         </is>
       </c>
       <c r="D122" s="15" t="inlineStr">
@@ -11344,7 +11344,7 @@
       </c>
       <c r="F122" s="19" t="inlineStr">
         <is>
-          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
+          <t>Open /app/error-log; sort by newest.</t>
         </is>
       </c>
       <c r="G122" s="19" t="inlineStr">
@@ -11354,7 +11354,7 @@
       </c>
       <c r="H122" s="19" t="inlineStr">
         <is>
-          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
+          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
         </is>
       </c>
       <c r="I122" s="15" t="inlineStr">
@@ -11400,7 +11400,7 @@
     <row r="123">
       <c r="A123" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-03</t>
+          <t>TC-ERR-02</t>
         </is>
       </c>
       <c r="B123" s="15" t="inlineStr">
@@ -11410,7 +11410,7 @@
       </c>
       <c r="C123" s="19" t="inlineStr">
         <is>
-          <t>Background jobs</t>
+          <t>System e-mail works</t>
         </is>
       </c>
       <c r="D123" s="15" t="inlineStr">
@@ -11425,7 +11425,7 @@
       </c>
       <c r="F123" s="19" t="inlineStr">
         <is>
-          <t>Open Scheduled Job Log; filter Status = Failed.</t>
+          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
         </is>
       </c>
       <c r="G123" s="19" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="H123" s="19" t="inlineStr">
         <is>
-          <t>No failed jobs (or each one reported).</t>
+          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
         </is>
       </c>
       <c r="I123" s="15" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J123" s="15" t="inlineStr">
@@ -11481,7 +11481,7 @@
     <row r="124">
       <c r="A124" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-04</t>
+          <t>TC-ERR-03</t>
         </is>
       </c>
       <c r="B124" s="15" t="inlineStr">
@@ -11491,22 +11491,22 @@
       </c>
       <c r="C124" s="19" t="inlineStr">
         <is>
-          <t>Browser console during testing</t>
+          <t>Background jobs</t>
         </is>
       </c>
       <c r="D124" s="15" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="E124" s="19" t="inlineStr">
         <is>
-          <t>Chrome DevTools open (F12 -&gt; Console).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F124" s="19" t="inlineStr">
         <is>
-          <t>Use the system as normal while the console is open.</t>
+          <t>Open Scheduled Job Log; filter Status = Failed.</t>
         </is>
       </c>
       <c r="G124" s="19" t="inlineStr">
@@ -11516,12 +11516,12 @@
       </c>
       <c r="H124" s="19" t="inlineStr">
         <is>
-          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
+          <t>No failed jobs (or each one reported).</t>
         </is>
       </c>
       <c r="I124" s="15" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J124" s="15" t="inlineStr">
@@ -11531,12 +11531,12 @@
       </c>
       <c r="K124" s="15" t="inlineStr">
         <is>
-          <t>Error sweep SWP-01..04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L124" s="15" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M124" s="20" t="inlineStr">
@@ -11562,7 +11562,7 @@
     <row r="125">
       <c r="A125" s="17" t="inlineStr">
         <is>
-          <t>TC-ERR-05</t>
+          <t>TC-ERR-04</t>
         </is>
       </c>
       <c r="B125" s="15" t="inlineStr">
@@ -11572,22 +11572,22 @@
       </c>
       <c r="C125" s="19" t="inlineStr">
         <is>
-          <t>Migrate output after deploying</t>
+          <t>Browser console during testing</t>
         </is>
       </c>
       <c r="D125" s="15" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E125" s="19" t="inlineStr">
         <is>
-          <t>New branch pulled on the server.</t>
+          <t>Chrome DevTools open (F12 -&gt; Console).</t>
         </is>
       </c>
       <c r="F125" s="19" t="inlineStr">
         <is>
-          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
+          <t>Use the system as normal while the console is open.</t>
         </is>
       </c>
       <c r="G125" s="19" t="inlineStr">
@@ -11597,7 +11597,7 @@
       </c>
       <c r="H125" s="19" t="inlineStr">
         <is>
-          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
+          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
         </is>
       </c>
       <c r="I125" s="15" t="inlineStr">
@@ -11612,12 +11612,12 @@
       </c>
       <c r="K125" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Error sweep SWP-01..04</t>
         </is>
       </c>
       <c r="L125" s="15" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M125" s="20" t="inlineStr">
@@ -11640,9 +11640,414 @@
         </is>
       </c>
     </row>
+    <row r="126">
+      <c r="A126" s="17" t="inlineStr">
+        <is>
+          <t>TC-ERR-05</t>
+        </is>
+      </c>
+      <c r="B126" s="15" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="C126" s="19" t="inlineStr">
+        <is>
+          <t>Migrate output after deploying</t>
+        </is>
+      </c>
+      <c r="D126" s="15" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="E126" s="19" t="inlineStr">
+        <is>
+          <t>New branch pulled on the server.</t>
+        </is>
+      </c>
+      <c r="F126" s="19" t="inlineStr">
+        <is>
+          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
+        </is>
+      </c>
+      <c r="G126" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H126" s="19" t="inlineStr">
+        <is>
+          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
+        </is>
+      </c>
+      <c r="I126" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J126" s="15" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="K126" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="L126" s="15" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="M126" s="20" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="N126" s="20" t="inlineStr"/>
+      <c r="O126" s="20" t="inlineStr"/>
+      <c r="P126" s="21" t="inlineStr"/>
+      <c r="Q126" s="20" t="inlineStr"/>
+      <c r="R126" s="15" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="S126" s="15" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="17" t="inlineStr">
+        <is>
+          <t>TC-ERR-06</t>
+        </is>
+      </c>
+      <c r="B127" s="15" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="C127" s="19" t="inlineStr">
+        <is>
+          <t>Every Medical HRMS page and form opens</t>
+        </is>
+      </c>
+      <c r="D127" s="15" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="E127" s="19" t="inlineStr">
+        <is>
+          <t>Logged in as HR Manager (then repeat as HR User).</t>
+        </is>
+      </c>
+      <c r="F127" s="19" t="inlineStr">
+        <is>
+          <t>Open each Medical HRMS doctype list, its New form and its newest saved record; the four pages, the report and both workspaces.</t>
+        </is>
+      </c>
+      <c r="G127" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H127" s="19" t="inlineStr">
+        <is>
+          <t>Each opens; no red error, no 'Not permitted' for HR, no blank page.</t>
+        </is>
+      </c>
+      <c r="I127" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J127" s="15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K127" s="15" t="inlineStr">
+        <is>
+          <t>SWP-01/02</t>
+        </is>
+      </c>
+      <c r="L127" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M127" s="20" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="N127" s="20" t="inlineStr"/>
+      <c r="O127" s="20" t="inlineStr"/>
+      <c r="P127" s="21" t="inlineStr"/>
+      <c r="Q127" s="20" t="inlineStr"/>
+      <c r="R127" s="15" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="S127" s="15" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="17" t="inlineStr">
+        <is>
+          <t>TC-ERR-07</t>
+        </is>
+      </c>
+      <c r="B128" s="15" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="C128" s="19" t="inlineStr">
+        <is>
+          <t>Employees' own request lists open</t>
+        </is>
+      </c>
+      <c r="D128" s="15" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="E128" s="19" t="inlineStr">
+        <is>
+          <t>Logged in as an employee.</t>
+        </is>
+      </c>
+      <c r="F128" s="19" t="inlineStr">
+        <is>
+          <t>Open the list of each self-service request type (Permission Request ... Employee Medical License) and the Employee Self Service workspace.</t>
+        </is>
+      </c>
+      <c r="G128" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H128" s="19" t="inlineStr">
+        <is>
+          <t>Each opens with only the employee's own records; no error.</t>
+        </is>
+      </c>
+      <c r="I128" s="15" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J128" s="15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K128" s="15" t="inlineStr">
+        <is>
+          <t>SWP-03</t>
+        </is>
+      </c>
+      <c r="L128" s="15" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M128" s="20" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="N128" s="20" t="inlineStr"/>
+      <c r="O128" s="20" t="inlineStr"/>
+      <c r="P128" s="21" t="inlineStr"/>
+      <c r="Q128" s="20" t="inlineStr"/>
+      <c r="R128" s="15" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="S128" s="15" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="17" t="inlineStr">
+        <is>
+          <t>TC-ERR-08</t>
+        </is>
+      </c>
+      <c r="B129" s="15" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="C129" s="19" t="inlineStr">
+        <is>
+          <t>Every file of the app is valid</t>
+        </is>
+      </c>
+      <c r="D129" s="15" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="E129" s="19" t="inlineStr">
+        <is>
+          <t>A checkout of develop.</t>
+        </is>
+      </c>
+      <c r="F129" s="19" t="inlineStr">
+        <is>
+          <t>python3 tests/checks/files.py</t>
+        </is>
+      </c>
+      <c r="G129" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H129" s="19" t="inlineStr">
+        <is>
+          <t>PROBLEMS: 0 (Python compiles, JS parses, JSON loads, translations keep their placeholders, no stray files).</t>
+        </is>
+      </c>
+      <c r="I129" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J129" s="15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K129" s="15" t="inlineStr">
+        <is>
+          <t>tests/checks/files.py</t>
+        </is>
+      </c>
+      <c r="L129" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M129" s="20" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="N129" s="20" t="inlineStr"/>
+      <c r="O129" s="20" t="inlineStr"/>
+      <c r="P129" s="21" t="inlineStr"/>
+      <c r="Q129" s="20" t="inlineStr"/>
+      <c r="R129" s="15" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="S129" s="15" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="17" t="inlineStr">
+        <is>
+          <t>TC-ERR-09</t>
+        </is>
+      </c>
+      <c r="B130" s="15" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="C130" s="19" t="inlineStr">
+        <is>
+          <t>Every hook, doctype and record is valid on the site</t>
+        </is>
+      </c>
+      <c r="D130" s="15" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="E130" s="19" t="inlineStr">
+        <is>
+          <t>Site migrated.</t>
+        </is>
+      </c>
+      <c r="F130" s="19" t="inlineStr">
+        <is>
+          <t>../../env/bin/python tests/e2e/fx.py tests/checks/site.py</t>
+        </is>
+      </c>
+      <c r="G130" s="19" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H130" s="19" t="inlineStr">
+        <is>
+          <t>PROBLEMS: 0; every hook, patch and asset resolves; saved records pass validation.</t>
+        </is>
+      </c>
+      <c r="I130" s="15" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J130" s="15" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K130" s="15" t="inlineStr">
+        <is>
+          <t>tests/checks/site.py</t>
+        </is>
+      </c>
+      <c r="L130" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M130" s="20" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="N130" s="20" t="inlineStr"/>
+      <c r="O130" s="20" t="inlineStr"/>
+      <c r="P130" s="21" t="inlineStr"/>
+      <c r="Q130" s="20" t="inlineStr"/>
+      <c r="R130" s="15" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="S130" s="15" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S125"/>
-  <conditionalFormatting sqref="M2:M325">
+  <autoFilter ref="A1:S130"/>
+  <conditionalFormatting sqref="M2:M330">
     <cfRule type="expression" priority="1" dxfId="0">
       <formula>$M2="Not run"</formula>
     </cfRule>
@@ -11659,7 +12064,7 @@
       <formula>$M2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L325">
+  <conditionalFormatting sqref="L2:L330">
     <cfRule type="expression" priority="2" dxfId="0">
       <formula>$L2="Not run"</formula>
     </cfRule>
@@ -11677,7 +12082,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="M2:M325" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M330" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13558,7 +13963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E10"/>
+  <dimension ref="A1:E11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -13598,7 +14003,7 @@
     <row r="2">
       <c r="A2" s="15" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B2" s="15" t="inlineStr">
@@ -13608,12 +14013,12 @@
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
@@ -13635,12 +14040,12 @@
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -13657,17 +14062,17 @@
       </c>
       <c r="B4" s="15" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -13679,22 +14084,22 @@
     <row r="5">
       <c r="A5" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -13711,17 +14116,17 @@
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -13738,17 +14143,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -13760,7 +14165,7 @@
     <row r="8">
       <c r="A8" s="15" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="15" t="inlineStr">
@@ -13770,12 +14175,12 @@
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -13787,7 +14192,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -13797,12 +14202,12 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -13814,25 +14219,52 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D10" s="19" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E10" s="15" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="15" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B10" s="15" t="inlineStr">
+      <c r="B11" s="15" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr">
+      <c r="C11" s="19" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D10" s="19" t="inlineStr">
+      <c r="D11" s="19" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E10" s="15" t="inlineStr">
+      <c r="E11" s="15" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -690,7 +690,7 @@
       </c>
       <c r="C13" s="6" t="inlineStr">
         <is>
-          <t>Result of the same check in the developer's automated browser run. A case can pass there and still fail for you — please test it anyway.</t>
+          <t>Result of the same check in the developer's automated run (browser suite, or a tests/checks script for file / site / server-method checks). A case can pass there and still fail for you — please test it anyway.</t>
         </is>
       </c>
     </row>
@@ -7299,7 +7299,7 @@
       </c>
       <c r="L72" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M72" s="20" t="inlineStr">
@@ -11941,7 +11941,7 @@
       </c>
       <c r="L129" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M129" s="20" t="inlineStr">
@@ -12022,7 +12022,7 @@
       </c>
       <c r="L130" s="15" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M130" s="20" t="inlineStr">
@@ -13963,7 +13963,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E11"/>
+  <dimension ref="A1:E12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14008,17 +14008,17 @@
       </c>
       <c r="B2" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C2" s="19" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D2" s="19" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E2" s="15" t="inlineStr">
@@ -14030,7 +14030,7 @@
     <row r="3">
       <c r="A3" s="15" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B3" s="15" t="inlineStr">
@@ -14040,12 +14040,12 @@
       </c>
       <c r="C3" s="19" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D3" s="19" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E3" s="15" t="inlineStr">
@@ -14067,12 +14067,12 @@
       </c>
       <c r="C4" s="19" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D4" s="19" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E4" s="15" t="inlineStr">
@@ -14089,17 +14089,17 @@
       </c>
       <c r="B5" s="15" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D5" s="19" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E5" s="15" t="inlineStr">
@@ -14111,22 +14111,22 @@
     <row r="6">
       <c r="A6" s="15" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C6" s="19" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D6" s="19" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="15" t="inlineStr">
@@ -14143,17 +14143,17 @@
       </c>
       <c r="B7" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D7" s="19" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E7" s="15" t="inlineStr">
@@ -14170,17 +14170,17 @@
       </c>
       <c r="B8" s="15" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C8" s="19" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D8" s="19" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E8" s="15" t="inlineStr">
@@ -14192,7 +14192,7 @@
     <row r="9">
       <c r="A9" s="15" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="15" t="inlineStr">
@@ -14202,12 +14202,12 @@
       </c>
       <c r="C9" s="19" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D9" s="19" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E9" s="15" t="inlineStr">
@@ -14219,7 +14219,7 @@
     <row r="10">
       <c r="A10" s="15" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="15" t="inlineStr">
@@ -14229,12 +14229,12 @@
       </c>
       <c r="C10" s="19" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D10" s="19" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E10" s="15" t="inlineStr">
@@ -14246,25 +14246,52 @@
     <row r="11">
       <c r="A11" s="15" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D11" s="19" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E11" s="15" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="15" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B11" s="15" t="inlineStr">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C12" s="19" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D11" s="19" t="inlineStr">
+      <c r="D12" s="19" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E11" s="15" t="inlineStr">
+      <c r="E12" s="15" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -14125,12 +14125,12 @@
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>HR-04 - HR-06, HR-11, HR-28 - HR-30, HR-48, HR-66, HR-70, JM-12, JM-13, JM-16, JM-17, B-26</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>Owners corrected: Medical HRMS and Jameah are built by the HRMS team only, so no task is owned by the Education team (HR-11, HR-28, HR-48, JM-16, JM-17 now Abdul Hakeem; JM-12 Academic Affairs + Abdul Hakeem; JM-13 Registrar). Employee application: Dinesh + Abdul Hakeem built it (HR-06); Fathir handles its UI (HR-70) and Dinesh's open items (HR-04, HR-05). Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -14346,7 +14346,7 @@
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from Education's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$S$130</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$S$131</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>For the testing team · last updated 23 Oct 2026 · last automated run 23 Oct 2026 06:20 AST (95/95 browser checks passed)</t>
+          <t>For the testing team · last updated 23 Oct 2026 · last automated run 23 Oct 2026 11:15 AST (95/95 browser checks passed)</t>
         </is>
       </c>
     </row>
@@ -928,27 +928,27 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A5)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A5,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A5,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A5,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A5,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A5,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H5" s="15">
@@ -956,7 +956,7 @@
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A5,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A5,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A5,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -967,27 +967,27 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A6)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A6,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A6,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A6,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A6,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A6,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H6" s="15">
@@ -995,7 +995,7 @@
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A6,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A6,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A6,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1006,27 +1006,27 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A7)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A7,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A7,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A7,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A7,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A7,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H7" s="15">
@@ -1034,7 +1034,7 @@
         <v/>
       </c>
       <c r="I7" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A7,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A7,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A7,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1045,27 +1045,27 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A8)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A8,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A8,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A8,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A8,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A8,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H8" s="15">
@@ -1073,7 +1073,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A8,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A8,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A8,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1084,27 +1084,27 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A9)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A9,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A9,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A9,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A9,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A9,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H9" s="15">
@@ -1112,7 +1112,7 @@
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A9,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A9,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A9,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1123,27 +1123,27 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A10)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A10,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A10,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A10,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A10,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A10,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H10" s="15">
@@ -1151,7 +1151,7 @@
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A10,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A10,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A10,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1162,27 +1162,27 @@
         </is>
       </c>
       <c r="B11" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A11)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A11,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D11" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A11,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E11" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A11,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A11,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A11,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H11" s="15">
@@ -1190,7 +1190,7 @@
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A11,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A11,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A11,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1201,27 +1201,27 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A12)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A12,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A12,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A12,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A12,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G12" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A12,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H12" s="15">
@@ -1229,7 +1229,7 @@
         <v/>
       </c>
       <c r="I12" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A12,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A12,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A12,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1240,27 +1240,27 @@
         </is>
       </c>
       <c r="B13" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A13)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A13,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A13,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E13" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A13,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F13" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A13,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G13" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A13,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H13" s="15">
@@ -1268,7 +1268,7 @@
         <v/>
       </c>
       <c r="I13" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A13,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A13,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A13,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1279,27 +1279,27 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A14)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A14,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A14,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A14,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F14" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A14,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G14" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A14,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H14" s="15">
@@ -1307,7 +1307,7 @@
         <v/>
       </c>
       <c r="I14" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A14,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A14,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A14,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1318,27 +1318,27 @@
         </is>
       </c>
       <c r="B15" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A15)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A15,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D15" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A15,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E15" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A15,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F15" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A15,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G15" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A15,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H15" s="15">
@@ -1346,7 +1346,7 @@
         <v/>
       </c>
       <c r="I15" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A15,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A15,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A15,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1357,27 +1357,27 @@
         </is>
       </c>
       <c r="B16" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$330,$A16)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$331,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A16,'Test Cases'!$M$2:$M$331,C$4)</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A16,'Test Cases'!$M$2:$M$331,D$4)</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A16,'Test Cases'!$M$2:$M$331,E$4)</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A16,'Test Cases'!$M$2:$M$331,F$4)</f>
         <v/>
       </c>
       <c r="G16" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$M$2:$M$330,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A16,'Test Cases'!$M$2:$M$331,G$4)</f>
         <v/>
       </c>
       <c r="H16" s="15">
@@ -1385,7 +1385,7 @@
         <v/>
       </c>
       <c r="I16" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$I$2:$I$330,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$330,$A16,'Test Cases'!$I$2:$I$330,"Critical",'Test Cases'!$M$2:$M$330,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$331,$A16,'Test Cases'!$I$2:$I$331,"Critical")-COUNTIFS('Test Cases'!$B$2:$B$331,$A16,'Test Cases'!$I$2:$I$331,"Critical",'Test Cases'!$M$2:$M$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1442,7 +1442,7 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>COUNTIF('Test Cases'!$L$2:$L$330,"Pass")</f>
+        <f>COUNTIF('Test Cases'!$L$2:$L$331,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1453,7 +1453,7 @@
         </is>
       </c>
       <c r="B21" s="14">
-        <f>COUNTIF('Test Cases'!$L$2:$L$330,"Fail")</f>
+        <f>COUNTIF('Test Cases'!$L$2:$L$331,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -1464,7 +1464,7 @@
         </is>
       </c>
       <c r="B22" s="14">
-        <f>COUNTA('Test Cases'!$L$2:$L$130)-B20-B21</f>
+        <f>COUNTA('Test Cases'!$L$2:$L$131)-B20-B21</f>
         <v/>
       </c>
     </row>
@@ -1479,7 +1479,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S130"/>
+  <dimension ref="A1:S131"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -3441,7 +3441,7 @@
       </c>
       <c r="H24" s="18" t="inlineStr">
         <is>
-          <t>'Request sent for review'. In My Requests the times show 10:15 and 11:45; status Pending.</t>
+          <t>'Request sent for review'. In My Requests the times show 10:15 and 11:45; status Pending. HR sees Duration (Hours) 1.5.</t>
         </is>
       </c>
       <c r="I24" s="14" t="inlineStr">
@@ -3480,7 +3480,7 @@
       </c>
       <c r="S24" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
@@ -3603,7 +3603,7 @@
       </c>
       <c r="H26" s="18" t="inlineStr">
         <is>
-          <t>Status Pending.</t>
+          <t>Status Pending; HR sees Duration (Days) 1 (working days are counted, holidays are not).</t>
         </is>
       </c>
       <c r="I26" s="14" t="inlineStr">
@@ -3642,14 +3642,14 @@
       </c>
       <c r="S26" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-05</t>
+          <t>TC-ESS-16</t>
         </is>
       </c>
       <c r="B27" s="14" t="inlineStr">
@@ -3659,7 +3659,7 @@
       </c>
       <c r="C27" s="18" t="inlineStr">
         <is>
-          <t>Salary Certificate Request</t>
+          <t>Permission with the To Time before the From Time</t>
         </is>
       </c>
       <c r="D27" s="14" t="inlineStr">
@@ -3674,37 +3674,37 @@
       </c>
       <c r="F27" s="18" t="inlineStr">
         <is>
-          <t>New Request -&gt; purpose, addressee -&gt; Send.</t>
+          <t>Permission Request -&gt; From 11:00 AM, To 10:00 AM -&gt; Send Request.</t>
         </is>
       </c>
       <c r="G27" s="18" t="inlineStr">
         <is>
-          <t>Bank Loan</t>
+          <t>11:00 AM – 10:00 AM</t>
         </is>
       </c>
       <c r="H27" s="18" t="inlineStr">
         <is>
-          <t>Status Pending.</t>
+          <t>Refused: 'To Time must be after From Time.'; nothing is saved.</t>
         </is>
       </c>
       <c r="I27" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J27" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K27" s="14" t="inlineStr">
         <is>
-          <t>ESS-07</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="L27" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M27" s="19" t="inlineStr">
@@ -3718,19 +3718,19 @@
       <c r="Q27" s="19" t="inlineStr"/>
       <c r="R27" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="S27" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-06</t>
+          <t>TC-ESS-05</t>
         </is>
       </c>
       <c r="B28" s="14" t="inlineStr">
@@ -3740,7 +3740,7 @@
       </c>
       <c r="C28" s="18" t="inlineStr">
         <is>
-          <t>Overtime pre-approval</t>
+          <t>Salary Certificate Request</t>
         </is>
       </c>
       <c r="D28" s="14" t="inlineStr">
@@ -3755,12 +3755,12 @@
       </c>
       <c r="F28" s="18" t="inlineStr">
         <is>
-          <t>New Request -&gt; date, hours, type, justification -&gt; Send.</t>
+          <t>New Request -&gt; purpose, addressee -&gt; Send.</t>
         </is>
       </c>
       <c r="G28" s="18" t="inlineStr">
         <is>
-          <t>2 hours</t>
+          <t>Bank Loan</t>
         </is>
       </c>
       <c r="H28" s="18" t="inlineStr">
@@ -3770,7 +3770,7 @@
       </c>
       <c r="I28" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J28" s="14" t="inlineStr">
@@ -3780,7 +3780,7 @@
       </c>
       <c r="K28" s="14" t="inlineStr">
         <is>
-          <t>ESS-08</t>
+          <t>ESS-07</t>
         </is>
       </c>
       <c r="L28" s="14" t="inlineStr">
@@ -3811,7 +3811,7 @@
     <row r="29">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-07</t>
+          <t>TC-ESS-06</t>
         </is>
       </c>
       <c r="B29" s="14" t="inlineStr">
@@ -3821,7 +3821,7 @@
       </c>
       <c r="C29" s="18" t="inlineStr">
         <is>
-          <t>Training Request</t>
+          <t>Overtime pre-approval</t>
         </is>
       </c>
       <c r="D29" s="14" t="inlineStr">
@@ -3836,12 +3836,12 @@
       </c>
       <c r="F29" s="18" t="inlineStr">
         <is>
-          <t>New Request -&gt; course, provider, cost, benefit -&gt; Send.</t>
+          <t>New Request -&gt; date, hours, type, justification -&gt; Send.</t>
         </is>
       </c>
       <c r="G29" s="18" t="inlineStr">
         <is>
-          <t>Cost 1500</t>
+          <t>2 hours</t>
         </is>
       </c>
       <c r="H29" s="18" t="inlineStr">
@@ -3861,7 +3861,7 @@
       </c>
       <c r="K29" s="14" t="inlineStr">
         <is>
-          <t>ESS-09</t>
+          <t>ESS-08</t>
         </is>
       </c>
       <c r="L29" s="14" t="inlineStr">
@@ -3892,7 +3892,7 @@
     <row r="30">
       <c r="A30" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-08</t>
+          <t>TC-ESS-07</t>
         </is>
       </c>
       <c r="B30" s="14" t="inlineStr">
@@ -3902,7 +3902,7 @@
       </c>
       <c r="C30" s="18" t="inlineStr">
         <is>
-          <t>Children Medical Allowance with invoice</t>
+          <t>Training Request</t>
         </is>
       </c>
       <c r="D30" s="14" t="inlineStr">
@@ -3912,30 +3912,27 @@
       </c>
       <c r="E30" s="18" t="inlineStr">
         <is>
-          <t>A small PDF invoice.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F30" s="18" t="inlineStr">
         <is>
-          <t>1. New Request.
-2. Fill child, school, year, amount, payment.
-3. Attach the invoice (Upload).
-4. Send.</t>
+          <t>New Request -&gt; course, provider, cost, benefit -&gt; Send.</t>
         </is>
       </c>
       <c r="G30" s="18" t="inlineStr">
         <is>
-          <t>PDF invoice</t>
+          <t>Cost 1500</t>
         </is>
       </c>
       <c r="H30" s="18" t="inlineStr">
         <is>
-          <t>Upload succeeds; request Pending; the file is private (see TC-SEC-08).</t>
+          <t>Status Pending.</t>
         </is>
       </c>
       <c r="I30" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J30" s="14" t="inlineStr">
@@ -3945,7 +3942,7 @@
       </c>
       <c r="K30" s="14" t="inlineStr">
         <is>
-          <t>ESS-12</t>
+          <t>ESS-09</t>
         </is>
       </c>
       <c r="L30" s="14" t="inlineStr">
@@ -3976,7 +3973,7 @@
     <row r="31">
       <c r="A31" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-09</t>
+          <t>TC-ESS-08</t>
         </is>
       </c>
       <c r="B31" s="14" t="inlineStr">
@@ -3986,7 +3983,7 @@
       </c>
       <c r="C31" s="18" t="inlineStr">
         <is>
-          <t>Company Car Request</t>
+          <t>Children Medical Allowance with invoice</t>
         </is>
       </c>
       <c r="D31" s="14" t="inlineStr">
@@ -3996,27 +3993,30 @@
       </c>
       <c r="E31" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A small PDF invoice.</t>
         </is>
       </c>
       <c r="F31" s="18" t="inlineStr">
         <is>
-          <t>New Request -&gt; justification, visits per week -&gt; Send.</t>
+          <t>1. New Request.
+2. Fill child, school, year, amount, payment.
+3. Attach the invoice (Upload).
+4. Send.</t>
         </is>
       </c>
       <c r="G31" s="18" t="inlineStr">
         <is>
-          <t>3 visits</t>
+          <t>PDF invoice</t>
         </is>
       </c>
       <c r="H31" s="18" t="inlineStr">
         <is>
-          <t>Status Pending.</t>
+          <t>Upload succeeds; request Pending; the file is private (see TC-SEC-08).</t>
         </is>
       </c>
       <c r="I31" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J31" s="14" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="K31" s="14" t="inlineStr">
         <is>
-          <t>ESS-10</t>
+          <t>ESS-12</t>
         </is>
       </c>
       <c r="L31" s="14" t="inlineStr">
@@ -4057,7 +4057,7 @@
     <row r="32">
       <c r="A32" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-10</t>
+          <t>TC-ESS-09</t>
         </is>
       </c>
       <c r="B32" s="14" t="inlineStr">
@@ -4067,7 +4067,7 @@
       </c>
       <c r="C32" s="18" t="inlineStr">
         <is>
-          <t>Update My Data</t>
+          <t>Company Car Request</t>
         </is>
       </c>
       <c r="D32" s="14" t="inlineStr">
@@ -4082,12 +4082,12 @@
       </c>
       <c r="F32" s="18" t="inlineStr">
         <is>
-          <t>New Request -&gt; type Address, new value -&gt; Send.</t>
+          <t>New Request -&gt; justification, visits per week -&gt; Send.</t>
         </is>
       </c>
       <c r="G32" s="18" t="inlineStr">
         <is>
-          <t>New address</t>
+          <t>3 visits</t>
         </is>
       </c>
       <c r="H32" s="18" t="inlineStr">
@@ -4097,7 +4097,7 @@
       </c>
       <c r="I32" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J32" s="14" t="inlineStr">
@@ -4107,7 +4107,7 @@
       </c>
       <c r="K32" s="14" t="inlineStr">
         <is>
-          <t>ESS-11</t>
+          <t>ESS-10</t>
         </is>
       </c>
       <c r="L32" s="14" t="inlineStr">
@@ -4138,7 +4138,7 @@
     <row r="33">
       <c r="A33" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-11</t>
+          <t>TC-ESS-10</t>
         </is>
       </c>
       <c r="B33" s="14" t="inlineStr">
@@ -4148,7 +4148,7 @@
       </c>
       <c r="C33" s="18" t="inlineStr">
         <is>
-          <t>Save Draft</t>
+          <t>Update My Data</t>
         </is>
       </c>
       <c r="D33" s="14" t="inlineStr">
@@ -4163,17 +4163,17 @@
       </c>
       <c r="F33" s="18" t="inlineStr">
         <is>
-          <t>Salary Certificate -&gt; fill -&gt; Save Draft.</t>
+          <t>New Request -&gt; type Address, new value -&gt; Send.</t>
         </is>
       </c>
       <c r="G33" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>New address</t>
         </is>
       </c>
       <c r="H33" s="18" t="inlineStr">
         <is>
-          <t>Status Draft; not counted as Pending on the dashboard.</t>
+          <t>Status Pending.</t>
         </is>
       </c>
       <c r="I33" s="14" t="inlineStr">
@@ -4188,7 +4188,7 @@
       </c>
       <c r="K33" s="14" t="inlineStr">
         <is>
-          <t>ESS-13</t>
+          <t>ESS-11</t>
         </is>
       </c>
       <c r="L33" s="14" t="inlineStr">
@@ -4219,7 +4219,7 @@
     <row r="34">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-12</t>
+          <t>TC-ESS-11</t>
         </is>
       </c>
       <c r="B34" s="14" t="inlineStr">
@@ -4229,7 +4229,7 @@
       </c>
       <c r="C34" s="18" t="inlineStr">
         <is>
-          <t>My Requests and details</t>
+          <t>Save Draft</t>
         </is>
       </c>
       <c r="D34" s="14" t="inlineStr">
@@ -4239,13 +4239,12 @@
       </c>
       <c r="E34" s="18" t="inlineStr">
         <is>
-          <t>Some requests sent.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F34" s="18" t="inlineStr">
         <is>
-          <t>1. Click 'N request(s)' on a card.
-2. Click a request.</t>
+          <t>Salary Certificate -&gt; fill -&gt; Save Draft.</t>
         </is>
       </c>
       <c r="G34" s="18" t="inlineStr">
@@ -4255,7 +4254,7 @@
       </c>
       <c r="H34" s="18" t="inlineStr">
         <is>
-          <t>List shows each request and status; details show the values entered.</t>
+          <t>Status Draft; not counted as Pending on the dashboard.</t>
         </is>
       </c>
       <c r="I34" s="14" t="inlineStr">
@@ -4270,7 +4269,7 @@
       </c>
       <c r="K34" s="14" t="inlineStr">
         <is>
-          <t>ESS-16</t>
+          <t>ESS-13</t>
         </is>
       </c>
       <c r="L34" s="14" t="inlineStr">
@@ -4301,7 +4300,7 @@
     <row r="35">
       <c r="A35" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-13</t>
+          <t>TC-ESS-12</t>
         </is>
       </c>
       <c r="B35" s="14" t="inlineStr">
@@ -4311,7 +4310,7 @@
       </c>
       <c r="C35" s="18" t="inlineStr">
         <is>
-          <t>Counters and Recent Requests</t>
+          <t>My Requests and details</t>
         </is>
       </c>
       <c r="D35" s="14" t="inlineStr">
@@ -4321,12 +4320,13 @@
       </c>
       <c r="E35" s="18" t="inlineStr">
         <is>
-          <t>Requests sent.</t>
+          <t>Some requests sent.</t>
         </is>
       </c>
       <c r="F35" s="18" t="inlineStr">
         <is>
-          <t>Reload the Employee Dashboard.</t>
+          <t>1. Click 'N request(s)' on a card.
+2. Click a request.</t>
         </is>
       </c>
       <c r="G35" s="18" t="inlineStr">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="H35" s="18" t="inlineStr">
         <is>
-          <t>My Requests / Pending / Approved counters and the Recent Requests list match what was sent.</t>
+          <t>List shows each request and status; details show the values entered.</t>
         </is>
       </c>
       <c r="I35" s="14" t="inlineStr">
@@ -4351,7 +4351,7 @@
       </c>
       <c r="K35" s="14" t="inlineStr">
         <is>
-          <t>ESS-15</t>
+          <t>ESS-16</t>
         </is>
       </c>
       <c r="L35" s="14" t="inlineStr">
@@ -4382,7 +4382,7 @@
     <row r="36">
       <c r="A36" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-14</t>
+          <t>TC-ESS-13</t>
         </is>
       </c>
       <c r="B36" s="14" t="inlineStr">
@@ -4392,7 +4392,7 @@
       </c>
       <c r="C36" s="18" t="inlineStr">
         <is>
-          <t>My Profile</t>
+          <t>Counters and Recent Requests</t>
         </is>
       </c>
       <c r="D36" s="14" t="inlineStr">
@@ -4402,27 +4402,27 @@
       </c>
       <c r="E36" s="18" t="inlineStr">
         <is>
+          <t>Requests sent.</t>
+        </is>
+      </c>
+      <c r="F36" s="18" t="inlineStr">
+        <is>
+          <t>Reload the Employee Dashboard.</t>
+        </is>
+      </c>
+      <c r="G36" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F36" s="18" t="inlineStr">
-        <is>
-          <t>Click 'My Employee Profile'.</t>
-        </is>
-      </c>
-      <c r="G36" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H36" s="18" t="inlineStr">
         <is>
-          <t>Pop-up with own name, designation, department, company.</t>
+          <t>My Requests / Pending / Approved counters and the Recent Requests list match what was sent.</t>
         </is>
       </c>
       <c r="I36" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J36" s="14" t="inlineStr">
@@ -4432,7 +4432,7 @@
       </c>
       <c r="K36" s="14" t="inlineStr">
         <is>
-          <t>ESS-17</t>
+          <t>ESS-15</t>
         </is>
       </c>
       <c r="L36" s="14" t="inlineStr">
@@ -4463,7 +4463,7 @@
     <row r="37">
       <c r="A37" s="16" t="inlineStr">
         <is>
-          <t>TC-ESS-15</t>
+          <t>TC-ESS-14</t>
         </is>
       </c>
       <c r="B37" s="14" t="inlineStr">
@@ -4473,7 +4473,7 @@
       </c>
       <c r="C37" s="18" t="inlineStr">
         <is>
-          <t>Dashboard on a phone</t>
+          <t>My Profile</t>
         </is>
       </c>
       <c r="D37" s="14" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="E37" s="18" t="inlineStr">
         <is>
-          <t>Phone or narrow browser window.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F37" s="18" t="inlineStr">
         <is>
-          <t>Open the Employee Dashboard and send one request.</t>
+          <t>Click 'My Employee Profile'.</t>
         </is>
       </c>
       <c r="G37" s="18" t="inlineStr">
@@ -4498,27 +4498,27 @@
       </c>
       <c r="H37" s="18" t="inlineStr">
         <is>
-          <t>Layout fits the screen; dialogs usable; no sideways scrolling.</t>
+          <t>Pop-up with own name, designation, department, company.</t>
         </is>
       </c>
       <c r="I37" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J37" s="14" t="inlineStr">
         <is>
-          <t>Usability</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K37" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>ESS-17</t>
         </is>
       </c>
       <c r="L37" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M37" s="19" t="inlineStr">
@@ -4544,17 +4544,17 @@
     <row r="38">
       <c r="A38" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-01</t>
+          <t>TC-ESS-15</t>
         </is>
       </c>
       <c r="B38" s="14" t="inlineStr">
         <is>
-          <t>Leave</t>
+          <t>Employee self-service</t>
         </is>
       </c>
       <c r="C38" s="18" t="inlineStr">
         <is>
-          <t>Apply for annual leave</t>
+          <t>Dashboard on a phone</t>
         </is>
       </c>
       <c r="D38" s="14" t="inlineStr">
@@ -4564,44 +4564,42 @@
       </c>
       <c r="E38" s="18" t="inlineStr">
         <is>
-          <t>Employee has an Annual Leave allocation and a leave approver.</t>
+          <t>Phone or narrow browser window.</t>
         </is>
       </c>
       <c r="F38" s="18" t="inlineStr">
         <is>
-          <t>1. Leave Application -&gt; New Request.
-2. Leave Type 'Annual Leave (N days left)', 2 days, reason.
-3. Send.</t>
+          <t>Open the Employee Dashboard and send one request.</t>
         </is>
       </c>
       <c r="G38" s="18" t="inlineStr">
         <is>
-          <t>2 days</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H38" s="18" t="inlineStr">
         <is>
-          <t>Leave Application with status Open; approver set automatically.</t>
+          <t>Layout fits the screen; dialogs usable; no sideways scrolling.</t>
         </is>
       </c>
       <c r="I38" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J38" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Usability</t>
         </is>
       </c>
       <c r="K38" s="14" t="inlineStr">
         <is>
-          <t>ESS-14</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L38" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M38" s="19" t="inlineStr">
@@ -4620,14 +4618,14 @@
       </c>
       <c r="S38" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-02</t>
+          <t>TC-LV-01</t>
         </is>
       </c>
       <c r="B39" s="14" t="inlineStr">
@@ -4637,34 +4635,34 @@
       </c>
       <c r="C39" s="18" t="inlineStr">
         <is>
-          <t>Approver approves and submits</t>
+          <t>Apply for annual leave</t>
         </is>
       </c>
       <c r="D39" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E39" s="18" t="inlineStr">
         <is>
-          <t>TC-LV-01 done; logged in as the leave approver.</t>
+          <t>Employee has an Annual Leave allocation and a leave approver.</t>
         </is>
       </c>
       <c r="F39" s="18" t="inlineStr">
         <is>
-          <t>1. Open the Leave Application.
-2. Status = Approved, Save.
-3. Submit, confirm.</t>
+          <t>1. Leave Application -&gt; New Request.
+2. Leave Type 'Annual Leave (N days left)', 2 days, reason.
+3. Send.</t>
         </is>
       </c>
       <c r="G39" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>2 days</t>
         </is>
       </c>
       <c r="H39" s="18" t="inlineStr">
         <is>
-          <t>Submitted; status Approved.</t>
+          <t>Leave Application with status Open; approver set automatically.</t>
         </is>
       </c>
       <c r="I39" s="14" t="inlineStr">
@@ -4679,7 +4677,7 @@
       </c>
       <c r="K39" s="14" t="inlineStr">
         <is>
-          <t>APR-04</t>
+          <t>ESS-14</t>
         </is>
       </c>
       <c r="L39" s="14" t="inlineStr">
@@ -4703,14 +4701,14 @@
       </c>
       <c r="S39" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-03</t>
+          <t>TC-LV-02</t>
         </is>
       </c>
       <c r="B40" s="14" t="inlineStr">
@@ -4720,22 +4718,24 @@
       </c>
       <c r="C40" s="18" t="inlineStr">
         <is>
-          <t>Balance goes down</t>
+          <t>Approver approves and submits</t>
         </is>
       </c>
       <c r="D40" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E40" s="18" t="inlineStr">
         <is>
-          <t>TC-LV-02 done.</t>
+          <t>TC-LV-01 done; logged in as the leave approver.</t>
         </is>
       </c>
       <c r="F40" s="18" t="inlineStr">
         <is>
-          <t>Open the Employee Dashboard.</t>
+          <t>1. Open the Leave Application.
+2. Status = Approved, Save.
+3. Submit, confirm.</t>
         </is>
       </c>
       <c r="G40" s="18" t="inlineStr">
@@ -4745,7 +4745,7 @@
       </c>
       <c r="H40" s="18" t="inlineStr">
         <is>
-          <t>Annual Leave balance reduced by the approved days (e.g. 21 -&gt; 19).</t>
+          <t>Submitted; status Approved.</t>
         </is>
       </c>
       <c r="I40" s="14" t="inlineStr">
@@ -4760,7 +4760,7 @@
       </c>
       <c r="K40" s="14" t="inlineStr">
         <is>
-          <t>APR-05</t>
+          <t>APR-04</t>
         </is>
       </c>
       <c r="L40" s="14" t="inlineStr">
@@ -4791,7 +4791,7 @@
     <row r="41">
       <c r="A41" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-04</t>
+          <t>TC-LV-03</t>
         </is>
       </c>
       <c r="B41" s="14" t="inlineStr">
@@ -4801,22 +4801,22 @@
       </c>
       <c r="C41" s="18" t="inlineStr">
         <is>
-          <t>Approver rejects a leave</t>
+          <t>Balance goes down</t>
         </is>
       </c>
       <c r="D41" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E41" s="18" t="inlineStr">
         <is>
-          <t>A new Open leave.</t>
+          <t>TC-LV-02 done.</t>
         </is>
       </c>
       <c r="F41" s="18" t="inlineStr">
         <is>
-          <t>Status = Rejected, Save, Submit.</t>
+          <t>Open the Employee Dashboard.</t>
         </is>
       </c>
       <c r="G41" s="18" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="H41" s="18" t="inlineStr">
         <is>
-          <t>Status Rejected; balance unchanged.</t>
+          <t>Annual Leave balance reduced by the approved days (e.g. 21 -&gt; 19).</t>
         </is>
       </c>
       <c r="I41" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J41" s="14" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="K41" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APR-05</t>
         </is>
       </c>
       <c r="L41" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M41" s="19" t="inlineStr">
@@ -4872,7 +4872,7 @@
     <row r="42">
       <c r="A42" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-05</t>
+          <t>TC-LV-04</t>
         </is>
       </c>
       <c r="B42" s="14" t="inlineStr">
@@ -4882,22 +4882,22 @@
       </c>
       <c r="C42" s="18" t="inlineStr">
         <is>
-          <t>Employee cannot approve their own leave</t>
+          <t>Approver rejects a leave</t>
         </is>
       </c>
       <c r="D42" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E42" s="18" t="inlineStr">
         <is>
-          <t>Own Open leave.</t>
+          <t>A new Open leave.</t>
         </is>
       </c>
       <c r="F42" s="18" t="inlineStr">
         <is>
-          <t>Try to change the status or submit from the form (or ask a developer to try through the API).</t>
+          <t>Status = Rejected, Save, Submit.</t>
         </is>
       </c>
       <c r="G42" s="18" t="inlineStr">
@@ -4907,27 +4907,27 @@
       </c>
       <c r="H42" s="18" t="inlineStr">
         <is>
-          <t>Not allowed; leave stays Open.</t>
+          <t>Status Rejected; balance unchanged.</t>
         </is>
       </c>
       <c r="I42" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J42" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K42" s="14" t="inlineStr">
         <is>
-          <t>SEC-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L42" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M42" s="19" t="inlineStr">
@@ -4953,7 +4953,7 @@
     <row r="43">
       <c r="A43" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-06</t>
+          <t>TC-LV-05</t>
         </is>
       </c>
       <c r="B43" s="14" t="inlineStr">
@@ -4963,7 +4963,7 @@
       </c>
       <c r="C43" s="18" t="inlineStr">
         <is>
-          <t>Half-day monthly limit</t>
+          <t>Employee cannot approve their own leave</t>
         </is>
       </c>
       <c r="D43" s="14" t="inlineStr">
@@ -4973,42 +4973,42 @@
       </c>
       <c r="E43" s="18" t="inlineStr">
         <is>
-          <t>HR enabled the half-day limit in HR Settings.</t>
+          <t>Own Open leave.</t>
         </is>
       </c>
       <c r="F43" s="18" t="inlineStr">
         <is>
-          <t>Request more half days in one month than the limit.</t>
+          <t>Try to change the status or submit from the form (or ask a developer to try through the API).</t>
         </is>
       </c>
       <c r="G43" s="18" t="inlineStr">
         <is>
-          <t>Limit + 1</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H43" s="18" t="inlineStr">
         <is>
-          <t>The extra request is refused with a message about the monthly limit.</t>
+          <t>Not allowed; leave stays Open.</t>
         </is>
       </c>
       <c r="I43" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J43" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K43" s="14" t="inlineStr">
         <is>
-          <t>unit tests</t>
+          <t>SEC-08</t>
         </is>
       </c>
       <c r="L43" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M43" s="19" t="inlineStr">
@@ -5034,7 +5034,7 @@
     <row r="44">
       <c r="A44" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-07</t>
+          <t>TC-LV-06</t>
         </is>
       </c>
       <c r="B44" s="14" t="inlineStr">
@@ -5044,33 +5044,32 @@
       </c>
       <c r="C44" s="18" t="inlineStr">
         <is>
-          <t>Sick leave stages are used in order</t>
+          <t>Half-day monthly limit</t>
         </is>
       </c>
       <c r="D44" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E44" s="18" t="inlineStr">
         <is>
-          <t>Sick leave year started for an employee (TC-HRD-05).</t>
+          <t>HR enabled the half-day limit in HR Settings.</t>
         </is>
       </c>
       <c r="F44" s="18" t="inlineStr">
         <is>
-          <t>1. Request Sick Leave 2 while Sick Leave 1 still has days.
-2. Request sick leave across the Sick Leave 1 / 2 boundary.</t>
+          <t>Request more half days in one month than the limit.</t>
         </is>
       </c>
       <c r="G44" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Limit + 1</t>
         </is>
       </c>
       <c r="H44" s="18" t="inlineStr">
         <is>
-          <t>Both refused: 'Sick leave is used in order: Sick Leave 1 (full pay), then 2 (75% pay), then 3 (unpaid)' / split the request at the stage boundary.</t>
+          <t>The extra request is refused with a message about the monthly limit.</t>
         </is>
       </c>
       <c r="I44" s="14" t="inlineStr">
@@ -5109,14 +5108,14 @@
       </c>
       <c r="S44" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-08</t>
+          <t>TC-LV-07</t>
         </is>
       </c>
       <c r="B45" s="14" t="inlineStr">
@@ -5126,22 +5125,23 @@
       </c>
       <c r="C45" s="18" t="inlineStr">
         <is>
-          <t>Leave Return after annual leave</t>
+          <t>Sick leave stages are used in order</t>
         </is>
       </c>
       <c r="D45" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E45" s="18" t="inlineStr">
         <is>
-          <t>An approved annual leave.</t>
+          <t>Sick leave year started for an employee (TC-HRD-05).</t>
         </is>
       </c>
       <c r="F45" s="18" t="inlineStr">
         <is>
-          <t>Leave Return -&gt; pick the approved leave -&gt; return date -&gt; Send.</t>
+          <t>1. Request Sick Leave 2 while Sick Leave 1 still has days.
+2. Request sick leave across the Sick Leave 1 / 2 boundary.</t>
         </is>
       </c>
       <c r="G45" s="18" t="inlineStr">
@@ -5151,27 +5151,27 @@
       </c>
       <c r="H45" s="18" t="inlineStr">
         <is>
-          <t>Status Pending HR Review; only own approved leave is offered; 'You were due back on ...' shows the day after the leave; no fitness certificate asked.</t>
+          <t>Both refused: 'Sick leave is used in order: Sick Leave 1 (full pay), then 2 (75% pay), then 3 (unpaid)' / split the request at the stage boundary.</t>
         </is>
       </c>
       <c r="I45" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J45" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K45" s="14" t="inlineStr">
         <is>
-          <t>APR-06, LV-04</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="L45" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M45" s="19" t="inlineStr">
@@ -5197,7 +5197,7 @@
     <row r="46">
       <c r="A46" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-09</t>
+          <t>TC-LV-08</t>
         </is>
       </c>
       <c r="B46" s="14" t="inlineStr">
@@ -5207,7 +5207,7 @@
       </c>
       <c r="C46" s="18" t="inlineStr">
         <is>
-          <t>Leave Application lists only the leave you hold</t>
+          <t>Leave Return after annual leave</t>
         </is>
       </c>
       <c r="D46" s="14" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="E46" s="18" t="inlineStr">
         <is>
-          <t>Employee has Annual Leave this year.</t>
+          <t>An approved annual leave.</t>
         </is>
       </c>
       <c r="F46" s="18" t="inlineStr">
         <is>
-          <t>Leave Application -&gt; New Request -&gt; open the Leave Type list.</t>
+          <t>Leave Return -&gt; pick the approved leave -&gt; return date -&gt; Send.</t>
         </is>
       </c>
       <c r="G46" s="18" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="H46" s="18" t="inlineStr">
         <is>
-          <t>Only leave the employee holds, each with the days left (e.g. 'Annual Leave (21 days left)'), and Leave Without Pay last. No Casual, Privilege, Compensatory Off or Sick Leave types.</t>
+          <t>Status Pending HR Review; only own approved leave is offered; 'You were due back on ...' shows the day after the leave; no fitness certificate asked.</t>
         </is>
       </c>
       <c r="I46" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J46" s="14" t="inlineStr">
@@ -5247,7 +5247,7 @@
       </c>
       <c r="K46" s="14" t="inlineStr">
         <is>
-          <t>LV-01</t>
+          <t>APR-06, LV-04</t>
         </is>
       </c>
       <c r="L46" s="14" t="inlineStr">
@@ -5266,7 +5266,7 @@
       <c r="Q46" s="19" t="inlineStr"/>
       <c r="R46" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="S46" s="14" t="inlineStr">
@@ -5278,7 +5278,7 @@
     <row r="47">
       <c r="A47" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-10</t>
+          <t>TC-LV-09</t>
         </is>
       </c>
       <c r="B47" s="14" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="C47" s="18" t="inlineStr">
         <is>
-          <t>Send a Leave Plan</t>
+          <t>Leave Application lists only the leave you hold</t>
         </is>
       </c>
       <c r="D47" s="14" t="inlineStr">
@@ -5298,29 +5298,27 @@
       </c>
       <c r="E47" s="18" t="inlineStr">
         <is>
+          <t>Employee has Annual Leave this year.</t>
+        </is>
+      </c>
+      <c r="F47" s="18" t="inlineStr">
+        <is>
+          <t>Leave Application -&gt; New Request -&gt; open the Leave Type list.</t>
+        </is>
+      </c>
+      <c r="G47" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F47" s="18" t="inlineStr">
-        <is>
-          <t>1. Leave Plan -&gt; New Request.
-2. Annual Leave, 4 days in December, notes.
-3. Send.</t>
-        </is>
-      </c>
-      <c r="G47" s="18" t="inlineStr">
-        <is>
-          <t>4 days</t>
-        </is>
-      </c>
       <c r="H47" s="18" t="inlineStr">
         <is>
-          <t>Status Pending Manager; Leave Days = working days in the period; For Year set; the balance does not change.</t>
+          <t>Only leave the employee holds, each with the days left (e.g. 'Annual Leave (21 days left)'), and Leave Without Pay last. No Casual, Privilege, Compensatory Off or Sick Leave types.</t>
         </is>
       </c>
       <c r="I47" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J47" s="14" t="inlineStr">
@@ -5330,7 +5328,7 @@
       </c>
       <c r="K47" s="14" t="inlineStr">
         <is>
-          <t>LV-02</t>
+          <t>LV-01</t>
         </is>
       </c>
       <c r="L47" s="14" t="inlineStr">
@@ -5361,7 +5359,7 @@
     <row r="48">
       <c r="A48" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-11</t>
+          <t>TC-LV-10</t>
         </is>
       </c>
       <c r="B48" s="14" t="inlineStr">
@@ -5371,7 +5369,7 @@
       </c>
       <c r="C48" s="18" t="inlineStr">
         <is>
-          <t>Overlapping or backwards plan is refused</t>
+          <t>Send a Leave Plan</t>
         </is>
       </c>
       <c r="D48" s="14" t="inlineStr">
@@ -5381,43 +5379,44 @@
       </c>
       <c r="E48" s="18" t="inlineStr">
         <is>
-          <t>TC-LV-10 done.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F48" s="18" t="inlineStr">
         <is>
-          <t>1. Send a plan that overlaps the first one.
-2. Send a plan whose To Date is before its From Date.</t>
+          <t>1. Leave Plan -&gt; New Request.
+2. Annual Leave, 4 days in December, notes.
+3. Send.</t>
         </is>
       </c>
       <c r="G48" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>4 days</t>
         </is>
       </c>
       <c r="H48" s="18" t="inlineStr">
         <is>
-          <t>Both refused with a clear message; nothing saved.</t>
+          <t>Status Pending Manager; Leave Days = working days in the period; For Year set; the balance does not change.</t>
         </is>
       </c>
       <c r="I48" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J48" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K48" s="14" t="inlineStr">
         <is>
-          <t>unit tests</t>
+          <t>LV-02</t>
         </is>
       </c>
       <c r="L48" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M48" s="19" t="inlineStr">
@@ -5443,7 +5442,7 @@
     <row r="49">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-12</t>
+          <t>TC-LV-11</t>
         </is>
       </c>
       <c r="B49" s="14" t="inlineStr">
@@ -5453,12 +5452,12 @@
       </c>
       <c r="C49" s="18" t="inlineStr">
         <is>
-          <t>Manager and department head approve the plan</t>
+          <t>Overlapping or backwards plan is refused</t>
         </is>
       </c>
       <c r="D49" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E49" s="18" t="inlineStr">
@@ -5468,7 +5467,8 @@
       </c>
       <c r="F49" s="18" t="inlineStr">
         <is>
-          <t>Open the Leave Plan Request; set Status Pending Dept Head, Save; then Approved, Save.</t>
+          <t>1. Send a plan that overlaps the first one.
+2. Send a plan whose To Date is before its From Date.</t>
         </is>
       </c>
       <c r="G49" s="18" t="inlineStr">
@@ -5478,27 +5478,27 @@
       </c>
       <c r="H49" s="18" t="inlineStr">
         <is>
-          <t>Approved; the form says the employee applies from the Employee Portal (Apply now).</t>
+          <t>Both refused with a clear message; nothing saved.</t>
         </is>
       </c>
       <c r="I49" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J49" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K49" s="14" t="inlineStr">
         <is>
-          <t>LV-03</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="L49" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M49" s="19" t="inlineStr">
@@ -5524,7 +5524,7 @@
     <row r="50">
       <c r="A50" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-13</t>
+          <t>TC-LV-12</t>
         </is>
       </c>
       <c r="B50" s="14" t="inlineStr">
@@ -5534,22 +5534,22 @@
       </c>
       <c r="C50" s="18" t="inlineStr">
         <is>
-          <t>Apply now from an approved plan</t>
+          <t>Manager and department head approve the plan</t>
         </is>
       </c>
       <c r="D50" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E50" s="18" t="inlineStr">
         <is>
-          <t>TC-LV-12 done.</t>
+          <t>TC-LV-10 done.</t>
         </is>
       </c>
       <c r="F50" s="18" t="inlineStr">
         <is>
-          <t>Employee Dashboard &gt; My Leave &gt; 'Plan approved ...' &gt; Apply now -&gt; Send.</t>
+          <t>Open the Leave Plan Request; set Status Pending Dept Head, Save; then Approved, Save.</t>
         </is>
       </c>
       <c r="G50" s="18" t="inlineStr">
@@ -5559,7 +5559,7 @@
       </c>
       <c r="H50" s="18" t="inlineStr">
         <is>
-          <t>The Leave Application opens with the plan's type and dates; after sending it is Open and the plan shows it under 'Applied As'.</t>
+          <t>Approved; the form says the employee applies from the Employee Portal (Apply now).</t>
         </is>
       </c>
       <c r="I50" s="14" t="inlineStr">
@@ -5605,7 +5605,7 @@
     <row r="51">
       <c r="A51" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-14</t>
+          <t>TC-LV-13</t>
         </is>
       </c>
       <c r="B51" s="14" t="inlineStr">
@@ -5615,7 +5615,7 @@
       </c>
       <c r="C51" s="18" t="inlineStr">
         <is>
-          <t>The dashboard asks for the return after a leave</t>
+          <t>Apply now from an approved plan</t>
         </is>
       </c>
       <c r="D51" s="14" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="E51" s="18" t="inlineStr">
         <is>
-          <t>An approved leave that ended yesterday or earlier.</t>
+          <t>TC-LV-12 done.</t>
         </is>
       </c>
       <c r="F51" s="18" t="inlineStr">
         <is>
-          <t>Employee Dashboard &gt; My Leave &gt; Send Leave Return -&gt; Send.</t>
+          <t>Employee Dashboard &gt; My Leave &gt; 'Plan approved ...' &gt; Apply now -&gt; Send.</t>
         </is>
       </c>
       <c r="G51" s="18" t="inlineStr">
@@ -5640,7 +5640,7 @@
       </c>
       <c r="H51" s="18" t="inlineStr">
         <is>
-          <t>'Your leave ended on ... Tell HR you are back.'; the dialog is pre-filled with that leave and the day after it; no certificate for annual leave; sent as Pending HR Review.</t>
+          <t>The Leave Application opens with the plan's type and dates; after sending it is Open and the plan shows it under 'Applied As'.</t>
         </is>
       </c>
       <c r="I51" s="14" t="inlineStr">
@@ -5655,7 +5655,7 @@
       </c>
       <c r="K51" s="14" t="inlineStr">
         <is>
-          <t>LV-04</t>
+          <t>LV-03</t>
         </is>
       </c>
       <c r="L51" s="14" t="inlineStr">
@@ -5686,7 +5686,7 @@
     <row r="52">
       <c r="A52" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-15</t>
+          <t>TC-LV-14</t>
         </is>
       </c>
       <c r="B52" s="14" t="inlineStr">
@@ -5696,33 +5696,32 @@
       </c>
       <c r="C52" s="18" t="inlineStr">
         <is>
-          <t>Return after sick leave: certificate and clearance</t>
+          <t>The dashboard asks for the return after a leave</t>
         </is>
       </c>
       <c r="D52" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E52" s="18" t="inlineStr">
         <is>
-          <t>An approved Sick Leave 1 application that has ended.</t>
+          <t>An approved leave that ended yesterday or earlier.</t>
         </is>
       </c>
       <c r="F52" s="18" t="inlineStr">
         <is>
-          <t>1. As the employee send the Leave Return without a fitness certificate, then with one.
-2. As HR set Status Completed without a clearance; then Occupational Health Clearance = Cleared for Full Duty and Completed.</t>
+          <t>Employee Dashboard &gt; My Leave &gt; Send Leave Return -&gt; Send.</t>
         </is>
       </c>
       <c r="G52" s="18" t="inlineStr">
         <is>
-          <t>Small PDF</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H52" s="18" t="inlineStr">
         <is>
-          <t>Without the certificate: refused. Completed without clearance: refused. With the clearance: Completed.</t>
+          <t>'Your leave ended on ... Tell HR you are back.'; the dialog is pre-filled with that leave and the day after it; no certificate for annual leave; sent as Pending HR Review.</t>
         </is>
       </c>
       <c r="I52" s="14" t="inlineStr">
@@ -5737,12 +5736,12 @@
       </c>
       <c r="K52" s="14" t="inlineStr">
         <is>
-          <t>unit tests</t>
+          <t>LV-04</t>
         </is>
       </c>
       <c r="L52" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M52" s="19" t="inlineStr">
@@ -5768,7 +5767,7 @@
     <row r="53">
       <c r="A53" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-16</t>
+          <t>TC-LV-15</t>
         </is>
       </c>
       <c r="B53" s="14" t="inlineStr">
@@ -5778,7 +5777,7 @@
       </c>
       <c r="C53" s="18" t="inlineStr">
         <is>
-          <t>One return per leave; annual leave skips occupational health</t>
+          <t>Return after sick leave: certificate and clearance</t>
         </is>
       </c>
       <c r="D53" s="14" t="inlineStr">
@@ -5788,43 +5787,43 @@
       </c>
       <c r="E53" s="18" t="inlineStr">
         <is>
-          <t>TC-LV-14 done.</t>
+          <t>An approved Sick Leave 1 application that has ended.</t>
         </is>
       </c>
       <c r="F53" s="18" t="inlineStr">
         <is>
-          <t>1. Send a second return for the same leave.
-2. As HR set the annual-leave return to Pending Occupational Health.</t>
+          <t>1. As the employee send the Leave Return without a fitness certificate, then with one.
+2. As HR set Status Completed without a clearance; then Occupational Health Clearance = Cleared for Full Duty and Completed.</t>
         </is>
       </c>
       <c r="G53" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Small PDF</t>
         </is>
       </c>
       <c r="H53" s="18" t="inlineStr">
         <is>
-          <t>Both refused with a message; HR can set it to Completed.</t>
+          <t>Without the certificate: refused. Completed without clearance: refused. With the clearance: Completed.</t>
         </is>
       </c>
       <c r="I53" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J53" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K53" s="14" t="inlineStr">
         <is>
-          <t>LV-05; unit tests</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="L53" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M53" s="19" t="inlineStr">
@@ -5850,7 +5849,7 @@
     <row r="54">
       <c r="A54" s="16" t="inlineStr">
         <is>
-          <t>TC-LV-17</t>
+          <t>TC-LV-16</t>
         </is>
       </c>
       <c r="B54" s="14" t="inlineStr">
@@ -5860,7 +5859,7 @@
       </c>
       <c r="C54" s="18" t="inlineStr">
         <is>
-          <t>Sick leave types in pay order</t>
+          <t>One return per leave; annual leave skips occupational health</t>
         </is>
       </c>
       <c r="D54" s="14" t="inlineStr">
@@ -5870,12 +5869,13 @@
       </c>
       <c r="E54" s="18" t="inlineStr">
         <is>
-          <t>After migrate.</t>
+          <t>TC-LV-14 done.</t>
         </is>
       </c>
       <c r="F54" s="18" t="inlineStr">
         <is>
-          <t>Open /app/leave-type.</t>
+          <t>1. Send a second return for the same leave.
+2. As HR set the annual-leave return to Pending Occupational Health.</t>
         </is>
       </c>
       <c r="G54" s="18" t="inlineStr">
@@ -5885,22 +5885,22 @@
       </c>
       <c r="H54" s="18" t="inlineStr">
         <is>
-          <t>Sick Leave 1 - Full Pay, Sick Leave 2 - 75% Pay, Sick Leave 3 - Unpaid; employees' sick balances kept.</t>
+          <t>Both refused with a message; HR can set it to Completed.</t>
         </is>
       </c>
       <c r="I54" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J54" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K54" s="14" t="inlineStr">
         <is>
-          <t>LV-07</t>
+          <t>LV-05; unit tests</t>
         </is>
       </c>
       <c r="L54" s="14" t="inlineStr">
@@ -5931,17 +5931,17 @@
     <row r="55">
       <c r="A55" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-01</t>
+          <t>TC-LV-17</t>
         </is>
       </c>
       <c r="B55" s="14" t="inlineStr">
         <is>
-          <t>HR approvals</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="C55" s="18" t="inlineStr">
         <is>
-          <t>Approve a Permission Request</t>
+          <t>Sick leave types in pay order</t>
         </is>
       </c>
       <c r="D55" s="14" t="inlineStr">
@@ -5951,12 +5951,12 @@
       </c>
       <c r="E55" s="18" t="inlineStr">
         <is>
-          <t>A Pending request.</t>
+          <t>After migrate.</t>
         </is>
       </c>
       <c r="F55" s="18" t="inlineStr">
         <is>
-          <t>Open it, Status = Approved, Save.</t>
+          <t>Open /app/leave-type.</t>
         </is>
       </c>
       <c r="G55" s="18" t="inlineStr">
@@ -5966,22 +5966,22 @@
       </c>
       <c r="H55" s="18" t="inlineStr">
         <is>
-          <t>Saved; the employee sees Approved.</t>
+          <t>Sick Leave 1 - Full Pay, Sick Leave 2 - 75% Pay, Sick Leave 3 - Unpaid; employees' sick balances kept.</t>
         </is>
       </c>
       <c r="I55" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J55" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K55" s="14" t="inlineStr">
         <is>
-          <t>APR-01</t>
+          <t>LV-07</t>
         </is>
       </c>
       <c r="L55" s="14" t="inlineStr">
@@ -6000,19 +6000,19 @@
       <c r="Q55" s="19" t="inlineStr"/>
       <c r="R55" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="S55" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-02</t>
+          <t>TC-APR-01</t>
         </is>
       </c>
       <c r="B56" s="14" t="inlineStr">
@@ -6022,7 +6022,7 @@
       </c>
       <c r="C56" s="18" t="inlineStr">
         <is>
-          <t>Reject a Training Request</t>
+          <t>Approve a Permission Request</t>
         </is>
       </c>
       <c r="D56" s="14" t="inlineStr">
@@ -6037,7 +6037,7 @@
       </c>
       <c r="F56" s="18" t="inlineStr">
         <is>
-          <t>Status = Rejected, Save.</t>
+          <t>Open it, Status = Approved, Save.</t>
         </is>
       </c>
       <c r="G56" s="18" t="inlineStr">
@@ -6047,7 +6047,7 @@
       </c>
       <c r="H56" s="18" t="inlineStr">
         <is>
-          <t>Saved as Rejected.</t>
+          <t>Saved; the employee sees Approved.</t>
         </is>
       </c>
       <c r="I56" s="14" t="inlineStr">
@@ -6062,7 +6062,7 @@
       </c>
       <c r="K56" s="14" t="inlineStr">
         <is>
-          <t>APR-02</t>
+          <t>APR-01</t>
         </is>
       </c>
       <c r="L56" s="14" t="inlineStr">
@@ -6093,7 +6093,7 @@
     <row r="57">
       <c r="A57" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-03</t>
+          <t>TC-APR-02</t>
         </is>
       </c>
       <c r="B57" s="14" t="inlineStr">
@@ -6103,7 +6103,7 @@
       </c>
       <c r="C57" s="18" t="inlineStr">
         <is>
-          <t>Issue a Salary Certificate</t>
+          <t>Reject a Training Request</t>
         </is>
       </c>
       <c r="D57" s="14" t="inlineStr">
@@ -6118,7 +6118,7 @@
       </c>
       <c r="F57" s="18" t="inlineStr">
         <is>
-          <t>Status = Issued, Save.</t>
+          <t>Status = Rejected, Save.</t>
         </is>
       </c>
       <c r="G57" s="18" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H57" s="18" t="inlineStr">
         <is>
-          <t>Saved as Issued.</t>
+          <t>Saved as Rejected.</t>
         </is>
       </c>
       <c r="I57" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J57" s="14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="K57" s="14" t="inlineStr">
         <is>
-          <t>APR-03</t>
+          <t>APR-02</t>
         </is>
       </c>
       <c r="L57" s="14" t="inlineStr">
@@ -6174,7 +6174,7 @@
     <row r="58">
       <c r="A58" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-04</t>
+          <t>TC-APR-03</t>
         </is>
       </c>
       <c r="B58" s="14" t="inlineStr">
@@ -6184,22 +6184,22 @@
       </c>
       <c r="C58" s="18" t="inlineStr">
         <is>
-          <t>HR User sees all employees' requests</t>
+          <t>Issue a Salary Certificate</t>
         </is>
       </c>
       <c r="D58" s="14" t="inlineStr">
         <is>
-          <t>HR User</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E58" s="18" t="inlineStr">
         <is>
-          <t>Requests from two employees.</t>
+          <t>A Pending request.</t>
         </is>
       </c>
       <c r="F58" s="18" t="inlineStr">
         <is>
-          <t>Open each request list.</t>
+          <t>Status = Issued, Save.</t>
         </is>
       </c>
       <c r="G58" s="18" t="inlineStr">
@@ -6209,12 +6209,12 @@
       </c>
       <c r="H58" s="18" t="inlineStr">
         <is>
-          <t>Requests of all employees are listed, including Leave Return Request.</t>
+          <t>Saved as Issued.</t>
         </is>
       </c>
       <c r="I58" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J58" s="14" t="inlineStr">
@@ -6224,7 +6224,7 @@
       </c>
       <c r="K58" s="14" t="inlineStr">
         <is>
-          <t>APR-07</t>
+          <t>APR-03</t>
         </is>
       </c>
       <c r="L58" s="14" t="inlineStr">
@@ -6255,7 +6255,7 @@
     <row r="59">
       <c r="A59" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-05</t>
+          <t>TC-APR-04</t>
         </is>
       </c>
       <c r="B59" s="14" t="inlineStr">
@@ -6265,22 +6265,22 @@
       </c>
       <c r="C59" s="18" t="inlineStr">
         <is>
-          <t>Finance step on money requests</t>
+          <t>HR User sees all employees' requests</t>
         </is>
       </c>
       <c r="D59" s="14" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>HR User</t>
         </is>
       </c>
       <c r="E59" s="18" t="inlineStr">
         <is>
-          <t>A Training / Car / Allowance request at the finance step.</t>
+          <t>Requests from two employees.</t>
         </is>
       </c>
       <c r="F59" s="18" t="inlineStr">
         <is>
-          <t>Open and approve.</t>
+          <t>Open each request list.</t>
         </is>
       </c>
       <c r="G59" s="18" t="inlineStr">
@@ -6290,7 +6290,7 @@
       </c>
       <c r="H59" s="18" t="inlineStr">
         <is>
-          <t>Finance Manager can approve; HR cannot skip the finance step.</t>
+          <t>Requests of all employees are listed, including Leave Return Request.</t>
         </is>
       </c>
       <c r="I59" s="14" t="inlineStr">
@@ -6305,12 +6305,12 @@
       </c>
       <c r="K59" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APR-07</t>
         </is>
       </c>
       <c r="L59" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M59" s="19" t="inlineStr">
@@ -6336,7 +6336,7 @@
     <row r="60">
       <c r="A60" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-06</t>
+          <t>TC-APR-05</t>
         </is>
       </c>
       <c r="B60" s="14" t="inlineStr">
@@ -6346,52 +6346,52 @@
       </c>
       <c r="C60" s="18" t="inlineStr">
         <is>
-          <t>Travel Request</t>
+          <t>Finance step on money requests</t>
         </is>
       </c>
       <c r="D60" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="E60" s="18" t="inlineStr">
         <is>
+          <t>A Training / Car / Allowance request at the finance step.</t>
+        </is>
+      </c>
+      <c r="F60" s="18" t="inlineStr">
+        <is>
+          <t>Open and approve.</t>
+        </is>
+      </c>
+      <c r="G60" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F60" s="18" t="inlineStr">
-        <is>
-          <t>Create a Travel Request with costings; save; submit.</t>
-        </is>
-      </c>
-      <c r="G60" s="18" t="inlineStr">
-        <is>
-          <t>Costs</t>
-        </is>
-      </c>
       <c r="H60" s="18" t="inlineStr">
         <is>
-          <t>Saves and submits without error.</t>
+          <t>Finance Manager can approve; HR cannot skip the finance step.</t>
         </is>
       </c>
       <c r="I60" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J60" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K60" s="14" t="inlineStr">
         <is>
-          <t>HRD-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L60" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M60" s="19" t="inlineStr">
@@ -6417,7 +6417,7 @@
     <row r="61">
       <c r="A61" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-07</t>
+          <t>TC-APR-06</t>
         </is>
       </c>
       <c r="B61" s="14" t="inlineStr">
@@ -6427,7 +6427,7 @@
       </c>
       <c r="C61" s="18" t="inlineStr">
         <is>
-          <t>HR opens a new Expense Claim</t>
+          <t>Travel Request</t>
         </is>
       </c>
       <c r="D61" s="14" t="inlineStr">
@@ -6437,27 +6437,27 @@
       </c>
       <c r="E61" s="18" t="inlineStr">
         <is>
-          <t>HR account (also try the HR User account).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F61" s="18" t="inlineStr">
         <is>
-          <t>Open Expense Claim -&gt; + Add.</t>
+          <t>Create a Travel Request with costings; save; submit.</t>
         </is>
       </c>
       <c r="G61" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Costs</t>
         </is>
       </c>
       <c r="H61" s="18" t="inlineStr">
         <is>
-          <t>Form opens with the cost center filled; NO 'You do not have Read or Select Permissions for Cost Center' pop-up.</t>
+          <t>Saves and submits without error.</t>
         </is>
       </c>
       <c r="I61" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J61" s="14" t="inlineStr">
@@ -6467,7 +6467,7 @@
       </c>
       <c r="K61" s="14" t="inlineStr">
         <is>
-          <t>SWP-01/02</t>
+          <t>HRD-03</t>
         </is>
       </c>
       <c r="L61" s="14" t="inlineStr">
@@ -6498,7 +6498,7 @@
     <row r="62">
       <c r="A62" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-08</t>
+          <t>TC-APR-07</t>
         </is>
       </c>
       <c r="B62" s="14" t="inlineStr">
@@ -6508,23 +6508,22 @@
       </c>
       <c r="C62" s="18" t="inlineStr">
         <is>
-          <t>HR User opens the Holiday List</t>
+          <t>HR opens a new Expense Claim</t>
         </is>
       </c>
       <c r="D62" s="14" t="inlineStr">
         <is>
-          <t>HR User</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E62" s="18" t="inlineStr">
         <is>
-          <t>HR User account.</t>
+          <t>HR account (also try the HR User account).</t>
         </is>
       </c>
       <c r="F62" s="18" t="inlineStr">
         <is>
-          <t>1. Open /app/holiday-list.
-2. Open a holiday list.</t>
+          <t>Open Expense Claim -&gt; + Add.</t>
         </is>
       </c>
       <c r="G62" s="18" t="inlineStr">
@@ -6534,12 +6533,12 @@
       </c>
       <c r="H62" s="18" t="inlineStr">
         <is>
-          <t>List and record open read-only; no 'Not permitted'.</t>
+          <t>Form opens with the cost center filled; NO 'You do not have Read or Select Permissions for Cost Center' pop-up.</t>
         </is>
       </c>
       <c r="I62" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J62" s="14" t="inlineStr">
@@ -6549,7 +6548,7 @@
       </c>
       <c r="K62" s="14" t="inlineStr">
         <is>
-          <t>SWP-02</t>
+          <t>SWP-01/02</t>
         </is>
       </c>
       <c r="L62" s="14" t="inlineStr">
@@ -6580,32 +6579,33 @@
     <row r="63">
       <c r="A63" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-01</t>
+          <t>TC-APR-08</t>
         </is>
       </c>
       <c r="B63" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>HR approvals</t>
         </is>
       </c>
       <c r="C63" s="18" t="inlineStr">
         <is>
-          <t>Employees see only their own requests</t>
+          <t>HR User opens the Holiday List</t>
         </is>
       </c>
       <c r="D63" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR User</t>
         </is>
       </c>
       <c r="E63" s="18" t="inlineStr">
         <is>
-          <t>Two employees each sent a request.</t>
+          <t>HR User account.</t>
         </is>
       </c>
       <c r="F63" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 opens each request list.</t>
+          <t>1. Open /app/holiday-list.
+2. Open a holiday list.</t>
         </is>
       </c>
       <c r="G63" s="18" t="inlineStr">
@@ -6615,22 +6615,22 @@
       </c>
       <c r="H63" s="18" t="inlineStr">
         <is>
-          <t>Only their own requests appear.</t>
+          <t>List and record open read-only; no 'Not permitted'.</t>
         </is>
       </c>
       <c r="I63" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J63" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K63" s="14" t="inlineStr">
         <is>
-          <t>SEC-01</t>
+          <t>SWP-02</t>
         </is>
       </c>
       <c r="L63" s="14" t="inlineStr">
@@ -6661,7 +6661,7 @@
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-02</t>
+          <t>TC-SEC-01</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="C64" s="18" t="inlineStr">
         <is>
-          <t>Another employee's request URL</t>
+          <t>Employees see only their own requests</t>
         </is>
       </c>
       <c r="D64" s="14" t="inlineStr">
@@ -6681,22 +6681,22 @@
       </c>
       <c r="E64" s="18" t="inlineStr">
         <is>
-          <t>URL of employee 2's request.</t>
+          <t>Two employees each sent a request.</t>
         </is>
       </c>
       <c r="F64" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 opens that URL.</t>
+          <t>Employee 1 opens each request list.</t>
         </is>
       </c>
       <c r="G64" s="18" t="inlineStr">
         <is>
-          <t>Employee 2 request link</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H64" s="18" t="inlineStr">
         <is>
-          <t>Not permitted; none of its details are shown.</t>
+          <t>Only their own requests appear.</t>
         </is>
       </c>
       <c r="I64" s="14" t="inlineStr">
@@ -6711,7 +6711,7 @@
       </c>
       <c r="K64" s="14" t="inlineStr">
         <is>
-          <t>SEC-02</t>
+          <t>SEC-01</t>
         </is>
       </c>
       <c r="L64" s="14" t="inlineStr">
@@ -6742,7 +6742,7 @@
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-03</t>
+          <t>TC-SEC-02</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
@@ -6752,7 +6752,7 @@
       </c>
       <c r="C65" s="18" t="inlineStr">
         <is>
-          <t>Own Employee record only, read-only</t>
+          <t>Another employee's request URL</t>
         </is>
       </c>
       <c r="D65" s="14" t="inlineStr">
@@ -6762,28 +6762,27 @@
       </c>
       <c r="E65" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>URL of employee 2's request.</t>
         </is>
       </c>
       <c r="F65" s="18" t="inlineStr">
         <is>
-          <t>1. Open /app/employee.
-2. Try to edit own record.</t>
+          <t>Employee 1 opens that URL.</t>
         </is>
       </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Employee 2 request link</t>
         </is>
       </c>
       <c r="H65" s="18" t="inlineStr">
         <is>
-          <t>Only own record listed; cannot edit.</t>
+          <t>Not permitted; none of its details are shown.</t>
         </is>
       </c>
       <c r="I65" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J65" s="14" t="inlineStr">
@@ -6793,7 +6792,7 @@
       </c>
       <c r="K65" s="14" t="inlineStr">
         <is>
-          <t>SEC-03/04</t>
+          <t>SEC-02</t>
         </is>
       </c>
       <c r="L65" s="14" t="inlineStr">
@@ -6824,7 +6823,7 @@
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-04</t>
+          <t>TC-SEC-03</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
@@ -6834,7 +6833,7 @@
       </c>
       <c r="C66" s="18" t="inlineStr">
         <is>
-          <t>HR-only processes</t>
+          <t>Own Employee record only, read-only</t>
         </is>
       </c>
       <c r="D66" s="14" t="inlineStr">
@@ -6849,8 +6848,8 @@
       </c>
       <c r="F66" s="18" t="inlineStr">
         <is>
-          <t>1. Try to create a Contract Renewal request.
-2. Send a Leave Plan, then try to set its status to Approved (or ask a developer to try through the API).</t>
+          <t>1. Open /app/employee.
+2. Try to edit own record.</t>
         </is>
       </c>
       <c r="G66" s="18" t="inlineStr">
@@ -6860,7 +6859,7 @@
       </c>
       <c r="H66" s="18" t="inlineStr">
         <is>
-          <t>Contract Renewal refused ('managed by HR'); the Leave Plan is sent but the employee cannot approve it.</t>
+          <t>Only own record listed; cannot edit.</t>
         </is>
       </c>
       <c r="I66" s="14" t="inlineStr">
@@ -6875,7 +6874,7 @@
       </c>
       <c r="K66" s="14" t="inlineStr">
         <is>
-          <t>SEC-07</t>
+          <t>SEC-03/04</t>
         </is>
       </c>
       <c r="L66" s="14" t="inlineStr">
@@ -6899,14 +6898,14 @@
       </c>
       <c r="S66" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-05</t>
+          <t>TC-SEC-04</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -6916,7 +6915,7 @@
       </c>
       <c r="C67" s="18" t="inlineStr">
         <is>
-          <t>Employee cannot open HR pages</t>
+          <t>HR-only processes</t>
         </is>
       </c>
       <c r="D67" s="14" t="inlineStr">
@@ -6931,7 +6930,8 @@
       </c>
       <c r="F67" s="18" t="inlineStr">
         <is>
-          <t>Open /app/hr-dashboard, /app/hr-academic-presence/faculty and /app/jameah-data-check.</t>
+          <t>1. Try to create a Contract Renewal request.
+2. Send a Leave Plan, then try to set its status to Approved (or ask a developer to try through the API).</t>
         </is>
       </c>
       <c r="G67" s="18" t="inlineStr">
@@ -6941,12 +6941,12 @@
       </c>
       <c r="H67" s="18" t="inlineStr">
         <is>
-          <t>'Not authorized' or 'Not permitted'; no HR data.</t>
+          <t>Contract Renewal refused ('managed by HR'); the Leave Plan is sent but the employee cannot approve it.</t>
         </is>
       </c>
       <c r="I67" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J67" s="14" t="inlineStr">
@@ -6956,7 +6956,7 @@
       </c>
       <c r="K67" s="14" t="inlineStr">
         <is>
-          <t>SEC-09</t>
+          <t>SEC-07</t>
         </is>
       </c>
       <c r="L67" s="14" t="inlineStr">
@@ -6980,14 +6980,14 @@
       </c>
       <c r="S67" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-06</t>
+          <t>TC-SEC-05</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -6997,12 +6997,12 @@
       </c>
       <c r="C68" s="18" t="inlineStr">
         <is>
-          <t>Login without an Employee record</t>
+          <t>Employee cannot open HR pages</t>
         </is>
       </c>
       <c r="D68" s="14" t="inlineStr">
         <is>
-          <t>User with no Employee record</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E68" s="18" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="F68" s="18" t="inlineStr">
         <is>
-          <t>Log in and open the Employee Dashboard.</t>
+          <t>Open /app/hr-dashboard, /app/hr-academic-presence/faculty and /app/jameah-data-check.</t>
         </is>
       </c>
       <c r="G68" s="18" t="inlineStr">
@@ -7022,12 +7022,12 @@
       </c>
       <c r="H68" s="18" t="inlineStr">
         <is>
-          <t>Not permitted / not linked message; cannot send requests.</t>
+          <t>'Not authorized' or 'Not permitted'; no HR data.</t>
         </is>
       </c>
       <c r="I68" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J68" s="14" t="inlineStr">
@@ -7037,7 +7037,7 @@
       </c>
       <c r="K68" s="14" t="inlineStr">
         <is>
-          <t>SEC-11</t>
+          <t>SEC-09</t>
         </is>
       </c>
       <c r="L68" s="14" t="inlineStr">
@@ -7068,7 +7068,7 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-07</t>
+          <t>TC-SEC-06</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
@@ -7078,12 +7078,12 @@
       </c>
       <c r="C69" s="18" t="inlineStr">
         <is>
-          <t>Staff without HR/Employee roles</t>
+          <t>Login without an Employee record</t>
         </is>
       </c>
       <c r="D69" s="14" t="inlineStr">
         <is>
-          <t>Other staff</t>
+          <t>User with no Employee record</t>
         </is>
       </c>
       <c r="E69" s="18" t="inlineStr">
@@ -7093,7 +7093,7 @@
       </c>
       <c r="F69" s="18" t="inlineStr">
         <is>
-          <t>Open the HR and Employee dashboards.</t>
+          <t>Log in and open the Employee Dashboard.</t>
         </is>
       </c>
       <c r="G69" s="18" t="inlineStr">
@@ -7103,7 +7103,7 @@
       </c>
       <c r="H69" s="18" t="inlineStr">
         <is>
-          <t>Both refused.</t>
+          <t>Not permitted / not linked message; cannot send requests.</t>
         </is>
       </c>
       <c r="I69" s="14" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>SEC-12</t>
+          <t>SEC-11</t>
         </is>
       </c>
       <c r="L69" s="14" t="inlineStr">
@@ -7149,7 +7149,7 @@
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-08</t>
+          <t>TC-SEC-07</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -7159,37 +7159,37 @@
       </c>
       <c r="C70" s="18" t="inlineStr">
         <is>
-          <t>Private attachments</t>
+          <t>Staff without HR/Employee roles</t>
         </is>
       </c>
       <c r="D70" s="14" t="inlineStr">
         <is>
-          <t>Second employee</t>
+          <t>Other staff</t>
         </is>
       </c>
       <c r="E70" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 uploaded an invoice (TC-ESS-08).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F70" s="18" t="inlineStr">
         <is>
-          <t>Employee 2 opens the file link.</t>
+          <t>Open the HR and Employee dashboards.</t>
         </is>
       </c>
       <c r="G70" s="18" t="inlineStr">
         <is>
-          <t>File URL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H70" s="18" t="inlineStr">
         <is>
-          <t>Refused (403/404). HR can open it.</t>
+          <t>Both refused.</t>
         </is>
       </c>
       <c r="I70" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J70" s="14" t="inlineStr">
@@ -7199,7 +7199,7 @@
       </c>
       <c r="K70" s="14" t="inlineStr">
         <is>
-          <t>APR-08</t>
+          <t>SEC-12</t>
         </is>
       </c>
       <c r="L70" s="14" t="inlineStr">
@@ -7230,7 +7230,7 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-09</t>
+          <t>TC-SEC-08</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -7240,32 +7240,32 @@
       </c>
       <c r="C71" s="18" t="inlineStr">
         <is>
-          <t>Job application cannot grant admin rights</t>
+          <t>Private attachments</t>
         </is>
       </c>
       <c r="D71" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Second employee</t>
         </is>
       </c>
       <c r="E71" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Employee 1 uploaded an invoice (TC-ESS-08).</t>
         </is>
       </c>
       <c r="F71" s="18" t="inlineStr">
         <is>
-          <t>Create a Job Application Link and look at the Role list.</t>
+          <t>Employee 2 opens the file link.</t>
         </is>
       </c>
       <c r="G71" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>File URL</t>
         </is>
       </c>
       <c r="H71" s="18" t="inlineStr">
         <is>
-          <t>Only hireable roles are offered (Employee, Instructor, Academic Advisor...), never System Manager or HR roles.</t>
+          <t>Refused (403/404). HR can open it.</t>
         </is>
       </c>
       <c r="I71" s="14" t="inlineStr">
@@ -7280,7 +7280,7 @@
       </c>
       <c r="K71" s="14" t="inlineStr">
         <is>
-          <t>REC-02</t>
+          <t>APR-08</t>
         </is>
       </c>
       <c r="L71" s="14" t="inlineStr">
@@ -7311,7 +7311,7 @@
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-10</t>
+          <t>TC-SEC-09</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
@@ -7321,22 +7321,22 @@
       </c>
       <c r="C72" s="18" t="inlineStr">
         <is>
-          <t>Server methods refuse the wrong role</t>
+          <t>Job application cannot grant admin rights</t>
         </is>
       </c>
       <c r="D72" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E72" s="18" t="inlineStr">
         <is>
-          <t>QA logins loaded (qa_fixtures.py), bench running.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
         <is>
-          <t>python3 tests/checks/api_methods.py</t>
+          <t>Create a Job Application Link and look at the Role list.</t>
         </is>
       </c>
       <c r="G72" s="18" t="inlineStr">
@@ -7346,7 +7346,7 @@
       </c>
       <c r="H72" s="18" t="inlineStr">
         <is>
-          <t>Every method: refused (403) for a visitor except the job form and receipt; HR-only methods refused for employees; no server error (500); no method left out of the check.</t>
+          <t>Only hireable roles are offered (Employee, Instructor, Academic Advisor...), never System Manager or HR roles.</t>
         </is>
       </c>
       <c r="I72" s="14" t="inlineStr">
@@ -7361,7 +7361,7 @@
       </c>
       <c r="K72" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/api_methods.py</t>
+          <t>REC-02</t>
         </is>
       </c>
       <c r="L72" s="14" t="inlineStr">
@@ -7380,54 +7380,54 @@
       <c r="Q72" s="19" t="inlineStr"/>
       <c r="R72" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="S72" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-01</t>
+          <t>TC-SEC-10</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="C73" s="18" t="inlineStr">
         <is>
-          <t>Edit and save an employee who has a login</t>
+          <t>Server methods refuse the wrong role</t>
         </is>
       </c>
       <c r="D73" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="E73" s="18" t="inlineStr">
         <is>
-          <t>Employee with a user login.</t>
+          <t>QA logins loaded (qa_fixtures.py), bench running.</t>
         </is>
       </c>
       <c r="F73" s="18" t="inlineStr">
         <is>
-          <t>Change the mobile number; Save.</t>
+          <t>python3 tests/checks/api_methods.py</t>
         </is>
       </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
-          <t>New mobile</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H73" s="18" t="inlineStr">
         <is>
-          <t>Saved with no error (this used to fail with 'Could not find Gender').</t>
+          <t>Every method: refused (403) for a visitor except the job form and receipt; HR-only methods refused for employees; no server error (500); no method left out of the check.</t>
         </is>
       </c>
       <c r="I73" s="14" t="inlineStr">
@@ -7437,12 +7437,12 @@
       </c>
       <c r="J73" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>EMP-01</t>
+          <t>tests/checks/api_methods.py</t>
         </is>
       </c>
       <c r="L73" s="14" t="inlineStr">
@@ -7461,19 +7461,19 @@
       <c r="Q73" s="19" t="inlineStr"/>
       <c r="R73" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="S73" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-02</t>
+          <t>TC-EMP-01</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -7483,7 +7483,7 @@
       </c>
       <c r="C74" s="18" t="inlineStr">
         <is>
-          <t>Lookup fields only offer their own list</t>
+          <t>Edit and save an employee who has a login</t>
         </is>
       </c>
       <c r="D74" s="14" t="inlineStr">
@@ -7493,37 +7493,37 @@
       </c>
       <c r="E74" s="18" t="inlineStr">
         <is>
-          <t>Employee form open.</t>
+          <t>Employee with a user login.</t>
         </is>
       </c>
       <c r="F74" s="18" t="inlineStr">
         <is>
-          <t>Open Gender, Nationality, Identity Type and Religion drop-downs.</t>
+          <t>Change the mobile number; Save.</t>
         </is>
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>New mobile</t>
         </is>
       </c>
       <c r="H74" s="18" t="inlineStr">
         <is>
-          <t>Each shows only its Ministry list (e.g. Gender: Male, Female).</t>
+          <t>Saved with no error (this used to fail with 'Could not find Gender').</t>
         </is>
       </c>
       <c r="I74" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K74" s="14" t="inlineStr">
         <is>
-          <t>EMP-02/03</t>
+          <t>EMP-01</t>
         </is>
       </c>
       <c r="L74" s="14" t="inlineStr">
@@ -7554,7 +7554,7 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-03</t>
+          <t>TC-EMP-02</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -7564,7 +7564,7 @@
       </c>
       <c r="C75" s="18" t="inlineStr">
         <is>
-          <t>Invalid national ID</t>
+          <t>Lookup fields only offer their own list</t>
         </is>
       </c>
       <c r="D75" s="14" t="inlineStr">
@@ -7574,22 +7574,22 @@
       </c>
       <c r="E75" s="18" t="inlineStr">
         <is>
+          <t>Employee form open.</t>
+        </is>
+      </c>
+      <c r="F75" s="18" t="inlineStr">
+        <is>
+          <t>Open Gender, Nationality, Identity Type and Religion drop-downs.</t>
+        </is>
+      </c>
+      <c r="G75" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F75" s="18" t="inlineStr">
-        <is>
-          <t>Set Identity Number to 12345 and Save.</t>
-        </is>
-      </c>
-      <c r="G75" s="18" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
       <c r="H75" s="18" t="inlineStr">
         <is>
-          <t>Refused: a National ID has exactly 10 digits.</t>
+          <t>Each shows only its Ministry list (e.g. Gender: Male, Female).</t>
         </is>
       </c>
       <c r="I75" s="14" t="inlineStr">
@@ -7599,12 +7599,12 @@
       </c>
       <c r="J75" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K75" s="14" t="inlineStr">
         <is>
-          <t>EMP-05</t>
+          <t>EMP-02/03</t>
         </is>
       </c>
       <c r="L75" s="14" t="inlineStr">
@@ -7635,7 +7635,7 @@
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-04</t>
+          <t>TC-EMP-03</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="C76" s="18" t="inlineStr">
         <is>
-          <t>Duplicate identity number</t>
+          <t>Invalid national ID</t>
         </is>
       </c>
       <c r="D76" s="14" t="inlineStr">
@@ -7655,22 +7655,22 @@
       </c>
       <c r="E76" s="18" t="inlineStr">
         <is>
-          <t>Another employee's ID number.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F76" s="18" t="inlineStr">
         <is>
-          <t>Enter it on a different employee; Save.</t>
+          <t>Set Identity Number to 12345 and Save.</t>
         </is>
       </c>
       <c r="G76" s="18" t="inlineStr">
         <is>
-          <t>Existing ID</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>Refused: already registered to &lt;employee&gt;.</t>
+          <t>Refused: a National ID has exactly 10 digits.</t>
         </is>
       </c>
       <c r="I76" s="14" t="inlineStr">
@@ -7685,7 +7685,7 @@
       </c>
       <c r="K76" s="14" t="inlineStr">
         <is>
-          <t>EMP-06</t>
+          <t>EMP-05</t>
         </is>
       </c>
       <c r="L76" s="14" t="inlineStr">
@@ -7716,7 +7716,7 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-05</t>
+          <t>TC-EMP-04</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
@@ -7726,7 +7726,7 @@
       </c>
       <c r="C77" s="18" t="inlineStr">
         <is>
-          <t>National ID for a non-Saudi</t>
+          <t>Duplicate identity number</t>
         </is>
       </c>
       <c r="D77" s="14" t="inlineStr">
@@ -7736,27 +7736,27 @@
       </c>
       <c r="E77" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Another employee's ID number.</t>
         </is>
       </c>
       <c r="F77" s="18" t="inlineStr">
         <is>
-          <t>Nationality not Saudi, Identity Type National ID; Save.</t>
+          <t>Enter it on a different employee; Save.</t>
         </is>
       </c>
       <c r="G77" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Existing ID</t>
         </is>
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
-          <t>Refused: National ID is only for Saudis.</t>
+          <t>Refused: already registered to &lt;employee&gt;.</t>
         </is>
       </c>
       <c r="I77" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J77" s="14" t="inlineStr">
@@ -7766,12 +7766,12 @@
       </c>
       <c r="K77" s="14" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>EMP-06</t>
         </is>
       </c>
       <c r="L77" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M77" s="19" t="inlineStr">
@@ -7797,7 +7797,7 @@
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-09</t>
+          <t>TC-EMP-05</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -7807,7 +7807,7 @@
       </c>
       <c r="C78" s="18" t="inlineStr">
         <is>
-          <t>Non-Saudi employee with an Iqama</t>
+          <t>National ID for a non-Saudi</t>
         </is>
       </c>
       <c r="D78" s="14" t="inlineStr">
@@ -7817,44 +7817,42 @@
       </c>
       <c r="E78" s="18" t="inlineStr">
         <is>
-          <t>An employee whose Nationality is not Saudi and Identity Type is Iqama.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F78" s="18" t="inlineStr">
         <is>
-          <t>1. Open the employee.
-2. Look at Identity Number and ID Number in Country of Origin.
-3. Change any field and Save.</t>
+          <t>Nationality not Saudi, Identity Type National ID; Save.</t>
         </is>
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
-          <t>Iqama 2XXXXXXXXX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>The record opens without 'Not Saved'. Identity Number still shows the Iqama and is mandatory; the home-country ID is optional. Save works.</t>
+          <t>Refused: National ID is only for Saudis.</t>
         </is>
       </c>
       <c r="I78" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>EMP-08</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M78" s="19" t="inlineStr">
@@ -7880,7 +7878,7 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-06</t>
+          <t>TC-EMP-09</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -7890,7 +7888,7 @@
       </c>
       <c r="C79" s="18" t="inlineStr">
         <is>
-          <t>Qualification 'Appreciation' list</t>
+          <t>Non-Saudi employee with an Iqama</t>
         </is>
       </c>
       <c r="D79" s="14" t="inlineStr">
@@ -7900,27 +7898,29 @@
       </c>
       <c r="E79" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>An employee whose Nationality is not Saudi and Identity Type is Iqama.</t>
         </is>
       </c>
       <c r="F79" s="18" t="inlineStr">
         <is>
-          <t>Add a qualification row; open Appreciation.</t>
+          <t>1. Open the employee.
+2. Look at Identity Number and ID Number in Country of Origin.
+3. Change any field and Save.</t>
         </is>
       </c>
       <c r="G79" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Iqama 2XXXXXXXXX</t>
         </is>
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>Grades are offered (Excellent, Very good, Good...), not GPA systems.</t>
+          <t>The record opens without 'Not Saved'. Identity Number still shows the Iqama and is mandatory; the home-country ID is optional. Save works.</t>
         </is>
       </c>
       <c r="I79" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
@@ -7930,7 +7930,7 @@
       </c>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>REC-05</t>
+          <t>EMP-08</t>
         </is>
       </c>
       <c r="L79" s="14" t="inlineStr">
@@ -7961,7 +7961,7 @@
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-07</t>
+          <t>TC-EMP-06</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -7971,7 +7971,7 @@
       </c>
       <c r="C80" s="18" t="inlineStr">
         <is>
-          <t>Ministry (Jameah) Data preview</t>
+          <t>Qualification 'Appreciation' list</t>
         </is>
       </c>
       <c r="D80" s="14" t="inlineStr">
@@ -7981,12 +7981,12 @@
       </c>
       <c r="E80" s="18" t="inlineStr">
         <is>
-          <t>An employee of Al Riyada College.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F80" s="18" t="inlineStr">
         <is>
-          <t>Employee form -&gt; View -&gt; Ministry (Jameah) Data.</t>
+          <t>Add a qualification row; open Appreciation.</t>
         </is>
       </c>
       <c r="G80" s="18" t="inlineStr">
@@ -7996,22 +7996,22 @@
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>Pop-up with the 5 Ministry sections; lookup columns show codes (e.g. Nationality 101).</t>
+          <t>Grades are offered (Excellent, Very good, Good...), not GPA systems.</t>
         </is>
       </c>
       <c r="I80" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K80" s="14" t="inlineStr">
         <is>
-          <t>EMP-07</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="L80" s="14" t="inlineStr">
@@ -8042,7 +8042,7 @@
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-08</t>
+          <t>TC-EMP-07</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -8052,7 +8052,7 @@
       </c>
       <c r="C81" s="18" t="inlineStr">
         <is>
-          <t>Teaching staff are not sent as Employees</t>
+          <t>Ministry (Jameah) Data preview</t>
         </is>
       </c>
       <c r="D81" s="14" t="inlineStr">
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E81" s="18" t="inlineStr">
         <is>
-          <t>An employee linked to an Instructor.</t>
+          <t>An employee of Al Riyada College.</t>
         </is>
       </c>
       <c r="F81" s="18" t="inlineStr">
         <is>
-          <t>Open the Ministry (Jameah) Data preview.</t>
+          <t>Employee form -&gt; View -&gt; Ministry (Jameah) Data.</t>
         </is>
       </c>
       <c r="G81" s="18" t="inlineStr">
@@ -8077,7 +8077,7 @@
       </c>
       <c r="H81" s="18" t="inlineStr">
         <is>
-          <t>Says the person is sent as Faculty, not as an Employee.</t>
+          <t>Pop-up with the 5 Ministry sections; lookup columns show codes (e.g. Nationality 101).</t>
         </is>
       </c>
       <c r="I81" s="14" t="inlineStr">
@@ -8092,7 +8092,7 @@
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>REC-07</t>
+          <t>EMP-07</t>
         </is>
       </c>
       <c r="L81" s="14" t="inlineStr">
@@ -8123,7 +8123,7 @@
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-10</t>
+          <t>TC-EMP-08</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -8133,7 +8133,7 @@
       </c>
       <c r="C82" s="18" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Teaching staff are not sent as Employees</t>
         </is>
       </c>
       <c r="D82" s="14" t="inlineStr">
@@ -8143,14 +8143,12 @@
       </c>
       <c r="E82" s="18" t="inlineStr">
         <is>
-          <t>Some employees with empty Ministry fields.</t>
+          <t>An employee linked to an Instructor.</t>
         </is>
       </c>
       <c r="F82" s="18" t="inlineStr">
         <is>
-          <t>1. HR Portal menu &gt; Ministry (Jameah) &gt; Employees Missing Ministry Data.
-2. Tick 'Show complete employees too'.
-3. Filter by a department.</t>
+          <t>Open the Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="G82" s="18" t="inlineStr">
@@ -8160,12 +8158,12 @@
       </c>
       <c r="H82" s="18" t="inlineStr">
         <is>
-          <t>Each employee with gaps is listed with the number of missing values and their names as on the Employee form (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). The tick also lists complete employees; the filter works.</t>
+          <t>Says the person is sent as Faculty, not as an Employee.</t>
         </is>
       </c>
       <c r="I82" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
@@ -8175,7 +8173,7 @@
       </c>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>RPT-01</t>
+          <t>REC-07</t>
         </is>
       </c>
       <c r="L82" s="14" t="inlineStr">
@@ -8206,7 +8204,7 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-11</t>
+          <t>TC-EMP-10</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -8216,7 +8214,7 @@
       </c>
       <c r="C83" s="18" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff: download, check, import</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="D83" s="14" t="inlineStr">
@@ -8226,25 +8224,24 @@
       </c>
       <c r="E83" s="18" t="inlineStr">
         <is>
-          <t>HR Manager account.</t>
+          <t>Some employees with empty Ministry fields.</t>
         </is>
       </c>
       <c r="F83" s="18" t="inlineStr">
         <is>
-          <t>1. In the report: Download Data Sheet.
-2. Fill one red cell for an employee; type 31-31-2020 as another employee's date of birth.
-3. Check / Import Data Sheet &gt; attach the file &gt; Check.
-4. Fix the date and click Import.</t>
+          <t>1. HR Portal menu &gt; Ministry (Jameah) &gt; Employees Missing Ministry Data.
+2. Tick 'Show complete employees too'.
+3. Filter by a department.</t>
         </is>
       </c>
       <c r="G83" s="18" t="inlineStr">
         <is>
-          <t>Edited .xlsx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H83" s="18" t="inlineStr">
         <is>
-          <t>The sheet lists the non-teaching employees, red = Ministry-required and empty. Check reports the wrong date and saves nothing. Import updates only the changed cells; the result sheet gives each row's status.</t>
+          <t>Each employee with gaps is listed with the number of missing values and their names as on the Employee form (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). The tick also lists complete employees; the filter works.</t>
         </is>
       </c>
       <c r="I83" s="14" t="inlineStr">
@@ -8259,12 +8256,12 @@
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>RPT-01</t>
         </is>
       </c>
       <c r="L83" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M83" s="19" t="inlineStr">
@@ -8290,7 +8287,7 @@
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-12</t>
+          <t>TC-EMP-11</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -8300,52 +8297,55 @@
       </c>
       <c r="C84" s="18" t="inlineStr">
         <is>
-          <t>Only an HR Manager can import the data sheet</t>
+          <t>Data sheet for non-academic staff: download, check, import</t>
         </is>
       </c>
       <c r="D84" s="14" t="inlineStr">
         <is>
-          <t>HR User</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E84" s="18" t="inlineStr">
         <is>
-          <t>HR User account.</t>
+          <t>HR Manager account.</t>
         </is>
       </c>
       <c r="F84" s="18" t="inlineStr">
         <is>
-          <t>Open the Employees Missing Ministry Data report.</t>
+          <t>1. In the report: Download Data Sheet.
+2. Fill one red cell for an employee; type 31-31-2020 as another employee's date of birth.
+3. Check / Import Data Sheet &gt; attach the file &gt; Check.
+4. Fix the date and click Import.</t>
         </is>
       </c>
       <c r="G84" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Edited .xlsx</t>
         </is>
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>The report opens; there are no Download Data Sheet / Check / Import buttons.</t>
+          <t>The sheet lists the non-teaching employees, red = Ministry-required and empty. Check reports the wrong date and saves nothing. Import updates only the changed cells; the result sheet gives each row's status.</t>
         </is>
       </c>
       <c r="I84" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K84" s="14" t="inlineStr">
         <is>
-          <t>RPT-02</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M84" s="19" t="inlineStr">
@@ -8371,42 +8371,42 @@
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>TC-LIC-01</t>
+          <t>TC-EMP-12</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Medical licences</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="C85" s="18" t="inlineStr">
         <is>
-          <t>HR creates a licence</t>
+          <t>Only an HR Manager can import the data sheet</t>
         </is>
       </c>
       <c r="D85" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>HR User</t>
         </is>
       </c>
       <c r="E85" s="18" t="inlineStr">
         <is>
+          <t>HR User account.</t>
+        </is>
+      </c>
+      <c r="F85" s="18" t="inlineStr">
+        <is>
+          <t>Open the Employees Missing Ministry Data report.</t>
+        </is>
+      </c>
+      <c r="G85" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F85" s="18" t="inlineStr">
-        <is>
-          <t>New Employee Medical License: employee, type, number, expiry; Save.</t>
-        </is>
-      </c>
-      <c r="G85" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H85" s="18" t="inlineStr">
         <is>
-          <t>Saved.</t>
+          <t>The report opens; there are no Download Data Sheet / Check / Import buttons.</t>
         </is>
       </c>
       <c r="I85" s="14" t="inlineStr">
@@ -8416,12 +8416,12 @@
       </c>
       <c r="J85" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>LIC-01</t>
+          <t>RPT-02</t>
         </is>
       </c>
       <c r="L85" s="14" t="inlineStr">
@@ -8452,7 +8452,7 @@
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>TC-LIC-02</t>
+          <t>TC-LIC-01</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -8462,22 +8462,22 @@
       </c>
       <c r="C86" s="18" t="inlineStr">
         <is>
-          <t>Employees see only their own licence</t>
+          <t>HR creates a licence</t>
         </is>
       </c>
       <c r="D86" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E86" s="18" t="inlineStr">
         <is>
-          <t>Licences for two employees.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F86" s="18" t="inlineStr">
         <is>
-          <t>Each employee opens the licence list.</t>
+          <t>New Employee Medical License: employee, type, number, expiry; Save.</t>
         </is>
       </c>
       <c r="G86" s="18" t="inlineStr">
@@ -8487,22 +8487,22 @@
       </c>
       <c r="H86" s="18" t="inlineStr">
         <is>
-          <t>Only their own licence.</t>
+          <t>Saved.</t>
         </is>
       </c>
       <c r="I86" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>LIC-02</t>
+          <t>LIC-01</t>
         </is>
       </c>
       <c r="L86" s="14" t="inlineStr">
@@ -8533,45 +8533,42 @@
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-01</t>
+          <t>TC-LIC-02</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Medical licences</t>
         </is>
       </c>
       <c r="C87" s="18" t="inlineStr">
         <is>
-          <t>Create and generate an application link</t>
+          <t>Employees see only their own licence</t>
         </is>
       </c>
       <c r="D87" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E87" s="18" t="inlineStr">
         <is>
+          <t>Licences for two employees.</t>
+        </is>
+      </c>
+      <c r="F87" s="18" t="inlineStr">
+        <is>
+          <t>Each employee opens the licence list.</t>
+        </is>
+      </c>
+      <c r="G87" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F87" s="18" t="inlineStr">
-        <is>
-          <t>1. New Job Application Link.
-2. Category Academic Staff, Role Instructor, valid from/until.
-3. Save.
-4. Generate Link.</t>
-        </is>
-      </c>
-      <c r="G87" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H87" s="18" t="inlineStr">
         <is>
-          <t>A link is shown and can be copied.</t>
+          <t>Only their own licence.</t>
         </is>
       </c>
       <c r="I87" s="14" t="inlineStr">
@@ -8581,12 +8578,12 @@
       </c>
       <c r="J87" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>LIC-02</t>
         </is>
       </c>
       <c r="L87" s="14" t="inlineStr">
@@ -8617,7 +8614,7 @@
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-02</t>
+          <t>TC-REC-01</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -8627,12 +8624,12 @@
       </c>
       <c r="C88" s="18" t="inlineStr">
         <is>
-          <t>Invalid or expired link</t>
+          <t>Create and generate an application link</t>
         </is>
       </c>
       <c r="D88" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E88" s="18" t="inlineStr">
@@ -8642,7 +8639,10 @@
       </c>
       <c r="F88" s="18" t="inlineStr">
         <is>
-          <t>Open /job-application/abc123 and an expired link.</t>
+          <t>1. New Job Application Link.
+2. Category Academic Staff, Role Instructor, valid from/until.
+3. Save.
+4. Generate Link.</t>
         </is>
       </c>
       <c r="G88" s="18" t="inlineStr">
@@ -8652,22 +8652,22 @@
       </c>
       <c r="H88" s="18" t="inlineStr">
         <is>
-          <t>'Link is invalid / not active' message; no form.</t>
+          <t>A link is shown and can be copied.</t>
         </is>
       </c>
       <c r="I88" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>REC-01</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="L88" s="14" t="inlineStr">
@@ -8698,7 +8698,7 @@
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-03</t>
+          <t>TC-REC-02</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
@@ -8708,7 +8708,7 @@
       </c>
       <c r="C89" s="18" t="inlineStr">
         <is>
-          <t>Required fields on the public form</t>
+          <t>Invalid or expired link</t>
         </is>
       </c>
       <c r="D89" s="14" t="inlineStr">
@@ -8718,12 +8718,12 @@
       </c>
       <c r="E89" s="18" t="inlineStr">
         <is>
-          <t>Valid link.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F89" s="18" t="inlineStr">
         <is>
-          <t>Click Submit with the form empty.</t>
+          <t>Open /job-application/abc123 and an expired link.</t>
         </is>
       </c>
       <c r="G89" s="18" t="inlineStr">
@@ -8733,7 +8733,7 @@
       </c>
       <c r="H89" s="18" t="inlineStr">
         <is>
-          <t>Browser highlights the required fields; nothing is sent.</t>
+          <t>'Link is invalid / not active' message; no form.</t>
         </is>
       </c>
       <c r="I89" s="14" t="inlineStr">
@@ -8748,12 +8748,12 @@
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-01</t>
         </is>
       </c>
       <c r="L89" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M89" s="19" t="inlineStr">
@@ -8779,7 +8779,7 @@
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-04</t>
+          <t>TC-REC-03</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
@@ -8789,7 +8789,7 @@
       </c>
       <c r="C90" s="18" t="inlineStr">
         <is>
-          <t>Applicant submits the full form</t>
+          <t>Required fields on the public form</t>
         </is>
       </c>
       <c r="D90" s="14" t="inlineStr">
@@ -8804,37 +8804,37 @@
       </c>
       <c r="F90" s="18" t="inlineStr">
         <is>
-          <t>Fill every section (names in Arabic and English, ID, qualifications, experience) and Submit.</t>
+          <t>Click Submit with the form empty.</t>
         </is>
       </c>
       <c r="G90" s="18" t="inlineStr">
         <is>
-          <t>Saudi national ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>'Thank you' with a reference number APP-....</t>
+          <t>Browser highlights the required fields; nothing is sent.</t>
         </is>
       </c>
       <c r="I90" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>REC-03..05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M90" s="19" t="inlineStr">
@@ -8860,7 +8860,7 @@
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-05</t>
+          <t>TC-REC-04</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
@@ -8870,35 +8870,32 @@
       </c>
       <c r="C91" s="18" t="inlineStr">
         <is>
-          <t>Accept and create an Instructor</t>
+          <t>Applicant submits the full form</t>
         </is>
       </c>
       <c r="D91" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="E91" s="18" t="inlineStr">
         <is>
-          <t>TC-REC-04 for an Instructor link.</t>
+          <t>Valid link.</t>
         </is>
       </c>
       <c r="F91" s="18" t="inlineStr">
         <is>
-          <t>1. Open the applicant.
-2. Accept.
-3. Create Employee: Company Email = official college address, department.
-4. Confirm.</t>
+          <t>Fill every section (names in Arabic and English, ID, qualifications, experience) and Submit.</t>
         </is>
       </c>
       <c r="G91" s="18" t="inlineStr">
         <is>
-          <t>name.surname@alriyada.edu.sa</t>
+          <t>Saudi national ID</t>
         </is>
       </c>
       <c r="H91" s="18" t="inlineStr">
         <is>
-          <t>Message lists Employee and Instructor created; the new login has Employee + Instructor roles.</t>
+          <t>'Thank you' with a reference number APP-....</t>
         </is>
       </c>
       <c r="I91" s="14" t="inlineStr">
@@ -8913,7 +8910,7 @@
       </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>REC-03..05</t>
         </is>
       </c>
       <c r="L91" s="14" t="inlineStr">
@@ -8944,7 +8941,7 @@
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-06</t>
+          <t>TC-REC-05</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
@@ -8954,7 +8951,7 @@
       </c>
       <c r="C92" s="18" t="inlineStr">
         <is>
-          <t>Hire an Academic Advisor</t>
+          <t>Accept and create an Instructor</t>
         </is>
       </c>
       <c r="D92" s="14" t="inlineStr">
@@ -8964,37 +8961,40 @@
       </c>
       <c r="E92" s="18" t="inlineStr">
         <is>
-          <t>Applicant for an Academic Advisor link with a phone like 05XXXXXXXX.</t>
+          <t>TC-REC-04 for an Instructor link.</t>
         </is>
       </c>
       <c r="F92" s="18" t="inlineStr">
         <is>
-          <t>Accept -&gt; Create Employee with a @alriyada.edu.sa Company Email.</t>
+          <t>1. Open the applicant.
+2. Accept.
+3. Create Employee: Company Email = official college address, department.
+4. Confirm.</t>
         </is>
       </c>
       <c r="G92" s="18" t="inlineStr">
         <is>
-          <t>Local phone number</t>
+          <t>name.surname@alriyada.edu.sa</t>
         </is>
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>Employee, Academic Advisor and Instructor records created; no 'record not created' warning.</t>
+          <t>Message lists Employee and Instructor created; the new login has Employee + Instructor roles.</t>
         </is>
       </c>
       <c r="I92" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>REC-04</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="L92" s="14" t="inlineStr">
@@ -9025,7 +9025,7 @@
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-07</t>
+          <t>TC-REC-06</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="C93" s="18" t="inlineStr">
         <is>
-          <t>Hire non-academic staff</t>
+          <t>Hire an Academic Advisor</t>
         </is>
       </c>
       <c r="D93" s="14" t="inlineStr">
@@ -9045,22 +9045,22 @@
       </c>
       <c r="E93" s="18" t="inlineStr">
         <is>
-          <t>Applicant for a Non-Academic link.</t>
+          <t>Applicant for an Academic Advisor link with a phone like 05XXXXXXXX.</t>
         </is>
       </c>
       <c r="F93" s="18" t="inlineStr">
         <is>
-          <t>Accept -&gt; Create Employee.</t>
+          <t>Accept -&gt; Create Employee with a @alriyada.edu.sa Company Email.</t>
         </is>
       </c>
       <c r="G93" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Local phone number</t>
         </is>
       </c>
       <c r="H93" s="18" t="inlineStr">
         <is>
-          <t>Employee created; work phone and extension kept on the Employee.</t>
+          <t>Employee, Academic Advisor and Instructor records created; no 'record not created' warning.</t>
         </is>
       </c>
       <c r="I93" s="14" t="inlineStr">
@@ -9070,12 +9070,12 @@
       </c>
       <c r="J93" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>REC-05/06</t>
+          <t>REC-04</t>
         </is>
       </c>
       <c r="L93" s="14" t="inlineStr">
@@ -9106,7 +9106,7 @@
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-08</t>
+          <t>TC-REC-07</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
@@ -9116,7 +9116,7 @@
       </c>
       <c r="C94" s="18" t="inlineStr">
         <is>
-          <t>Reject an applicant</t>
+          <t>Hire non-academic staff</t>
         </is>
       </c>
       <c r="D94" s="14" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="E94" s="18" t="inlineStr">
         <is>
-          <t>A Pending applicant.</t>
+          <t>Applicant for a Non-Academic link.</t>
         </is>
       </c>
       <c r="F94" s="18" t="inlineStr">
         <is>
-          <t>Click Reject.</t>
+          <t>Accept -&gt; Create Employee.</t>
         </is>
       </c>
       <c r="G94" s="18" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="H94" s="18" t="inlineStr">
         <is>
-          <t>Status Rejected; Create Employee not offered.</t>
+          <t>Employee created; work phone and extension kept on the Employee.</t>
         </is>
       </c>
       <c r="I94" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J94" s="14" t="inlineStr">
@@ -9156,12 +9156,12 @@
       </c>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-05/06</t>
         </is>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M94" s="19" t="inlineStr">
@@ -9187,7 +9187,7 @@
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-09</t>
+          <t>TC-REC-08</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
@@ -9197,32 +9197,32 @@
       </c>
       <c r="C95" s="18" t="inlineStr">
         <is>
-          <t>Duplicate applicant identity</t>
+          <t>Reject an applicant</t>
         </is>
       </c>
       <c r="D95" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E95" s="18" t="inlineStr">
         <is>
-          <t>An employee already has the ID number.</t>
+          <t>A Pending applicant.</t>
         </is>
       </c>
       <c r="F95" s="18" t="inlineStr">
         <is>
-          <t>Submit a new application with that ID; HR tries to create the Employee.</t>
+          <t>Click Reject.</t>
         </is>
       </c>
       <c r="G95" s="18" t="inlineStr">
         <is>
-          <t>Existing ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>Creating the Employee is refused as a duplicate.</t>
+          <t>Status Rejected; Create Employee not offered.</t>
         </is>
       </c>
       <c r="I95" s="14" t="inlineStr">
@@ -9232,7 +9232,7 @@
       </c>
       <c r="J95" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K95" s="14" t="inlineStr">
@@ -9268,7 +9268,7 @@
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-11</t>
+          <t>TC-REC-09</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
@@ -9278,53 +9278,52 @@
       </c>
       <c r="C96" s="18" t="inlineStr">
         <is>
-          <t>A new hire's record opens clean</t>
+          <t>Duplicate applicant identity</t>
         </is>
       </c>
       <c r="D96" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="E96" s="18" t="inlineStr">
         <is>
-          <t>An applicant who answered 'Has Special Needs = No' but also picked a type (and, if Saudi, typed a home-country ID).</t>
+          <t>An employee already has the ID number.</t>
         </is>
       </c>
       <c r="F96" s="18" t="inlineStr">
         <is>
-          <t>1. Hire them (Create Employee).
-2. Open the new Employee record.</t>
+          <t>Submit a new application with that ID; HR tries to create the Employee.</t>
         </is>
       </c>
       <c r="G96" s="18" t="inlineStr">
         <is>
+          <t>Existing ID</t>
+        </is>
+      </c>
+      <c r="H96" s="18" t="inlineStr">
+        <is>
+          <t>Creating the Employee is refused as a duplicate.</t>
+        </is>
+      </c>
+      <c r="I96" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="J96" s="14" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="K96" s="14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H96" s="18" t="inlineStr">
-        <is>
-          <t>The record shows its status (not 'Not Saved'); special-needs type and home-country ID are empty.</t>
-        </is>
-      </c>
-      <c r="I96" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J96" s="14" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="K96" s="14" t="inlineStr">
-        <is>
-          <t>REC-09</t>
-        </is>
-      </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M96" s="19" t="inlineStr">
@@ -9350,7 +9349,7 @@
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-12</t>
+          <t>TC-REC-11</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
@@ -9360,7 +9359,7 @@
       </c>
       <c r="C97" s="18" t="inlineStr">
         <is>
-          <t>Create Employee asks for what the Employee form requires</t>
+          <t>A new hire's record opens clean</t>
         </is>
       </c>
       <c r="D97" s="14" t="inlineStr">
@@ -9370,15 +9369,13 @@
       </c>
       <c r="E97" s="18" t="inlineStr">
         <is>
-          <t>An Accepted applicant.</t>
+          <t>An applicant who answered 'Has Special Needs = No' but also picked a type (and, if Saudi, typed a home-country ID).</t>
         </is>
       </c>
       <c r="F97" s="18" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Look at the Employee Record section of the dialog.
-3. Fill it and confirm.
-4. Open the new Employee, change any field, Save.</t>
+          <t>1. Hire them (Create Employee).
+2. Open the new Employee record.</t>
         </is>
       </c>
       <c r="G97" s="18" t="inlineStr">
@@ -9388,7 +9385,7 @@
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>The dialog asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application), and Gender / Date of Birth only when the application left them empty. The Employee saves with no 'Missing Fields'.</t>
+          <t>The record shows its status (not 'Not Saved'); special-needs type and home-country ID are empty.</t>
         </is>
       </c>
       <c r="I97" s="14" t="inlineStr">
@@ -9403,7 +9400,7 @@
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>REC-10</t>
+          <t>REC-09</t>
         </is>
       </c>
       <c r="L97" s="14" t="inlineStr">
@@ -9434,7 +9431,7 @@
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-13</t>
+          <t>TC-REC-12</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
@@ -9444,55 +9441,55 @@
       </c>
       <c r="C98" s="18" t="inlineStr">
         <is>
-          <t>Phone number with country code</t>
+          <t>Create Employee asks for what the Employee form requires</t>
         </is>
       </c>
       <c r="D98" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E98" s="18" t="inlineStr">
         <is>
-          <t>A valid application link.</t>
+          <t>An Accepted applicant.</t>
         </is>
       </c>
       <c r="F98" s="18" t="inlineStr">
         <is>
-          <t>1. Open the link.
-2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
-3. Send.
-4. Correct it and send again.</t>
+          <t>1. Create Employee.
+2. Look at the Employee Record section of the dialog.
+3. Fill it and confirm.
+4. Open the new Employee, change any field, Save.</t>
         </is>
       </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t>123, then a full mobile number</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
+          <t>The dialog asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application), and Gender / Date of Birth only when the application left them empty. The Employee saves with no 'Missing Fields'.</t>
         </is>
       </c>
       <c r="I98" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-10</t>
         </is>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M98" s="19" t="inlineStr">
@@ -9506,19 +9503,19 @@
       <c r="Q98" s="19" t="inlineStr"/>
       <c r="R98" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="S98" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-14</t>
+          <t>TC-REC-13</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
@@ -9528,7 +9525,7 @@
       </c>
       <c r="C99" s="18" t="inlineStr">
         <is>
-          <t>Receipt after sending the application</t>
+          <t>Phone number with country code</t>
         </is>
       </c>
       <c r="D99" s="14" t="inlineStr">
@@ -9538,22 +9535,25 @@
       </c>
       <c r="E99" s="18" t="inlineStr">
         <is>
-          <t>TC-REC-13 done (application sent).</t>
+          <t>A valid application link.</t>
         </is>
       </c>
       <c r="F99" s="18" t="inlineStr">
         <is>
-          <t>On the confirmation screen click the receipt download button.</t>
+          <t>1. Open the link.
+2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
+3. Send.
+4. Correct it and send again.</t>
         </is>
       </c>
       <c r="G99" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123, then a full mobile number</t>
         </is>
       </c>
       <c r="H99" s="18" t="inlineStr">
         <is>
-          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
+          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
         </is>
       </c>
       <c r="I99" s="14" t="inlineStr">
@@ -9563,7 +9563,7 @@
       </c>
       <c r="J99" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K99" s="14" t="inlineStr">
@@ -9599,7 +9599,7 @@
     <row r="100">
       <c r="A100" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-10</t>
+          <t>TC-REC-14</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -9609,55 +9609,52 @@
       </c>
       <c r="C100" s="18" t="inlineStr">
         <is>
-          <t>Academic hire needs the college e-mail</t>
+          <t>Receipt after sending the application</t>
         </is>
       </c>
       <c r="D100" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="E100" s="18" t="inlineStr">
         <is>
-          <t>An Accepted applicant from an Instructor link.</t>
+          <t>TC-REC-13 done (application sent).</t>
         </is>
       </c>
       <c r="F100" s="18" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Leave Company Email empty (or a gmail address).
-3. Confirm.
-4. Then enter a @alriyada.edu.sa address and confirm again.</t>
+          <t>On the confirmation screen click the receipt download button.</t>
         </is>
       </c>
       <c r="G100" s="18" t="inlineStr">
         <is>
-          <t>Personal e-mail, then college e-mail</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H100" s="18" t="inlineStr">
         <is>
-          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
+          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
         </is>
       </c>
       <c r="I100" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K100" s="14" t="inlineStr">
         <is>
-          <t>REC-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M100" s="19" t="inlineStr">
@@ -9671,29 +9668,29 @@
       <c r="Q100" s="19" t="inlineStr"/>
       <c r="R100" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="S100" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-01</t>
+          <t>TC-REC-10</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="C101" s="18" t="inlineStr">
         <is>
-          <t>Faculty schedules</t>
+          <t>Academic hire needs the college e-mail</t>
         </is>
       </c>
       <c r="D101" s="14" t="inlineStr">
@@ -9703,22 +9700,25 @@
       </c>
       <c r="E101" s="18" t="inlineStr">
         <is>
-          <t>Published class timetables.</t>
+          <t>An Accepted applicant from an Instructor link.</t>
         </is>
       </c>
       <c r="F101" s="18" t="inlineStr">
         <is>
-          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
+          <t>1. Create Employee.
+2. Leave Company Email empty (or a gmail address).
+3. Confirm.
+4. Then enter a @alriyada.edu.sa address and confirm again.</t>
         </is>
       </c>
       <c r="G101" s="18" t="inlineStr">
         <is>
-          <t>6–12 Sep 2026</t>
+          <t>Personal e-mail, then college e-mail</t>
         </is>
       </c>
       <c r="H101" s="18" t="inlineStr">
         <is>
-          <t>Sessions per faculty member with day, time, course, room and mode.</t>
+          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
         </is>
       </c>
       <c r="I101" s="14" t="inlineStr">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="J101" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>PRS-01</t>
+          <t>REC-08</t>
         </is>
       </c>
       <c r="L101" s="14" t="inlineStr">
@@ -9764,7 +9764,7 @@
     <row r="102">
       <c r="A102" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-02</t>
+          <t>TC-PRS-01</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
@@ -9774,7 +9774,7 @@
       </c>
       <c r="C102" s="18" t="inlineStr">
         <is>
-          <t>Filter one faculty member</t>
+          <t>Faculty schedules</t>
         </is>
       </c>
       <c r="D102" s="14" t="inlineStr">
@@ -9784,27 +9784,27 @@
       </c>
       <c r="E102" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Published class timetables.</t>
         </is>
       </c>
       <c r="F102" s="18" t="inlineStr">
         <is>
-          <t>Pick a faculty member in the filter.</t>
+          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
         </is>
       </c>
       <c r="G102" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6–12 Sep 2026</t>
         </is>
       </c>
       <c r="H102" s="18" t="inlineStr">
         <is>
-          <t>Only that person's sessions.</t>
+          <t>Sessions per faculty member with day, time, course, room and mode.</t>
         </is>
       </c>
       <c r="I102" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J102" s="14" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>PRS-02</t>
+          <t>PRS-01</t>
         </is>
       </c>
       <c r="L102" s="14" t="inlineStr">
@@ -9845,7 +9845,7 @@
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-03</t>
+          <t>TC-PRS-02</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -9855,7 +9855,7 @@
       </c>
       <c r="C103" s="18" t="inlineStr">
         <is>
-          <t>Proctor schedules</t>
+          <t>Filter one faculty member</t>
         </is>
       </c>
       <c r="D103" s="14" t="inlineStr">
@@ -9865,22 +9865,22 @@
       </c>
       <c r="E103" s="18" t="inlineStr">
         <is>
-          <t>Exam committees with proctors.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F103" s="18" t="inlineStr">
         <is>
-          <t>Open Proctor Schedules for the exam week.</t>
+          <t>Pick a faculty member in the filter.</t>
         </is>
       </c>
       <c r="G103" s="18" t="inlineStr">
         <is>
-          <t>Exam week</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H103" s="18" t="inlineStr">
         <is>
-          <t>Proctor assignments, or a clear 'no assignments' message.</t>
+          <t>Only that person's sessions.</t>
         </is>
       </c>
       <c r="I103" s="14" t="inlineStr">
@@ -9895,7 +9895,7 @@
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>PRS-03</t>
+          <t>PRS-02</t>
         </is>
       </c>
       <c r="L103" s="14" t="inlineStr">
@@ -9926,7 +9926,7 @@
     <row r="104">
       <c r="A104" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-04</t>
+          <t>TC-PRS-03</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
@@ -9936,7 +9936,7 @@
       </c>
       <c r="C104" s="18" t="inlineStr">
         <is>
-          <t>Students on campus per hour</t>
+          <t>Proctor schedules</t>
         </is>
       </c>
       <c r="D104" s="14" t="inlineStr">
@@ -9946,27 +9946,27 @@
       </c>
       <c r="E104" s="18" t="inlineStr">
         <is>
-          <t>Attendance recorded.</t>
+          <t>Exam committees with proctors.</t>
         </is>
       </c>
       <c r="F104" s="18" t="inlineStr">
         <is>
-          <t>Open Students on Campus for a teaching day.</t>
+          <t>Open Proctor Schedules for the exam week.</t>
         </is>
       </c>
       <c r="G104" s="18" t="inlineStr">
         <is>
-          <t>8 Sep 2026</t>
+          <t>Exam week</t>
         </is>
       </c>
       <c r="H104" s="18" t="inlineStr">
         <is>
-          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
+          <t>Proctor assignments, or a clear 'no assignments' message.</t>
         </is>
       </c>
       <c r="I104" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
@@ -9976,7 +9976,7 @@
       </c>
       <c r="K104" s="14" t="inlineStr">
         <is>
-          <t>PRS-04</t>
+          <t>PRS-03</t>
         </is>
       </c>
       <c r="L104" s="14" t="inlineStr">
@@ -10007,7 +10007,7 @@
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-05</t>
+          <t>TC-PRS-04</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -10017,7 +10017,7 @@
       </c>
       <c r="C105" s="18" t="inlineStr">
         <is>
-          <t>Faculty after 4 PM</t>
+          <t>Students on campus per hour</t>
         </is>
       </c>
       <c r="D105" s="14" t="inlineStr">
@@ -10027,22 +10027,22 @@
       </c>
       <c r="E105" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Attendance recorded.</t>
         </is>
       </c>
       <c r="F105" s="18" t="inlineStr">
         <is>
-          <t>Open Faculty After 4 PM for a week.</t>
+          <t>Open Students on Campus for a teaching day.</t>
         </is>
       </c>
       <c r="G105" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8 Sep 2026</t>
         </is>
       </c>
       <c r="H105" s="18" t="inlineStr">
         <is>
-          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
+          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
         </is>
       </c>
       <c r="I105" s="14" t="inlineStr">
@@ -10057,7 +10057,7 @@
       </c>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>PRS-05</t>
+          <t>PRS-04</t>
         </is>
       </c>
       <c r="L105" s="14" t="inlineStr">
@@ -10088,7 +10088,7 @@
     <row r="106">
       <c r="A106" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-06</t>
+          <t>TC-PRS-05</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
@@ -10098,7 +10098,7 @@
       </c>
       <c r="C106" s="18" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Faculty after 4 PM</t>
         </is>
       </c>
       <c r="D106" s="14" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="E106" s="18" t="inlineStr">
         <is>
-          <t>A tab with data.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F106" s="18" t="inlineStr">
         <is>
-          <t>Click Export (Excel CSV).</t>
+          <t>Open Faculty After 4 PM for a week.</t>
         </is>
       </c>
       <c r="G106" s="18" t="inlineStr">
@@ -10123,12 +10123,12 @@
       </c>
       <c r="H106" s="18" t="inlineStr">
         <is>
-          <t>A CSV file downloads and opens in Excel with the same rows.</t>
+          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
         </is>
       </c>
       <c r="I106" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J106" s="14" t="inlineStr">
@@ -10138,7 +10138,7 @@
       </c>
       <c r="K106" s="14" t="inlineStr">
         <is>
-          <t>PRS-06</t>
+          <t>PRS-05</t>
         </is>
       </c>
       <c r="L106" s="14" t="inlineStr">
@@ -10169,7 +10169,7 @@
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-07</t>
+          <t>TC-PRS-06</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
@@ -10179,7 +10179,7 @@
       </c>
       <c r="C107" s="18" t="inlineStr">
         <is>
-          <t>Holiday and exam days</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="D107" s="14" t="inlineStr">
@@ -10189,12 +10189,12 @@
       </c>
       <c r="E107" s="18" t="inlineStr">
         <is>
-          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
+          <t>A tab with data.</t>
         </is>
       </c>
       <c r="F107" s="18" t="inlineStr">
         <is>
-          <t>Open Faculty Schedules over a holiday or exam week.</t>
+          <t>Click Export (Excel CSV).</t>
         </is>
       </c>
       <c r="G107" s="18" t="inlineStr">
@@ -10204,7 +10204,7 @@
       </c>
       <c r="H107" s="18" t="inlineStr">
         <is>
-          <t>No regular sessions on those days; the skipped dates are listed.</t>
+          <t>A CSV file downloads and opens in Excel with the same rows.</t>
         </is>
       </c>
       <c r="I107" s="14" t="inlineStr">
@@ -10219,12 +10219,12 @@
       </c>
       <c r="K107" s="14" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>PRS-06</t>
         </is>
       </c>
       <c r="L107" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M107" s="19" t="inlineStr">
@@ -10250,7 +10250,7 @@
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-08</t>
+          <t>TC-PRS-07</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="C108" s="18" t="inlineStr">
         <is>
-          <t>Cut-off time setting</t>
+          <t>Holiday and exam days</t>
         </is>
       </c>
       <c r="D108" s="14" t="inlineStr">
@@ -10270,27 +10270,27 @@
       </c>
       <c r="E108" s="18" t="inlineStr">
         <is>
+          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
+        </is>
+      </c>
+      <c r="F108" s="18" t="inlineStr">
+        <is>
+          <t>Open Faculty Schedules over a holiday or exam week.</t>
+        </is>
+      </c>
+      <c r="G108" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F108" s="18" t="inlineStr">
-        <is>
-          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
-        </is>
-      </c>
-      <c r="G108" s="18" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="H108" s="18" t="inlineStr">
         <is>
-          <t>List uses the new time.</t>
+          <t>No regular sessions on those days; the skipped dates are listed.</t>
         </is>
       </c>
       <c r="I108" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J108" s="14" t="inlineStr">
@@ -10300,12 +10300,12 @@
       </c>
       <c r="K108" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M108" s="19" t="inlineStr">
@@ -10331,17 +10331,17 @@
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-01</t>
+          <t>TC-PRS-08</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="C109" s="18" t="inlineStr">
         <is>
-          <t>Jameah Data Check page</t>
+          <t>Cut-off time setting</t>
         </is>
       </c>
       <c r="D109" s="14" t="inlineStr">
@@ -10356,37 +10356,37 @@
       </c>
       <c r="F109" s="18" t="inlineStr">
         <is>
-          <t>HR Dashboard -&gt; Jameah Data Check.</t>
+          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
         </is>
       </c>
       <c r="G109" s="18" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="H109" s="18" t="inlineStr">
+        <is>
+          <t>List uses the new time.</t>
+        </is>
+      </c>
+      <c r="I109" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J109" s="14" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="K109" s="14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H109" s="18" t="inlineStr">
-        <is>
-          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
-        </is>
-      </c>
-      <c r="I109" s="14" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="J109" s="14" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K109" s="14" t="inlineStr">
-        <is>
-          <t>JM-01</t>
-        </is>
-      </c>
       <c r="L109" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M109" s="19" t="inlineStr">
@@ -10412,7 +10412,7 @@
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-02</t>
+          <t>TC-JM-01</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
@@ -10422,12 +10422,12 @@
       </c>
       <c r="C110" s="18" t="inlineStr">
         <is>
-          <t>Jameah Settings pickers</t>
+          <t>Jameah Data Check page</t>
         </is>
       </c>
       <c r="D110" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E110" s="18" t="inlineStr">
@@ -10437,7 +10437,7 @@
       </c>
       <c r="F110" s="18" t="inlineStr">
         <is>
-          <t>Open Jameah Settings; open the College picker.</t>
+          <t>HR Dashboard -&gt; Jameah Data Check.</t>
         </is>
       </c>
       <c r="G110" s="18" t="inlineStr">
@@ -10447,12 +10447,12 @@
       </c>
       <c r="H110" s="18" t="inlineStr">
         <is>
-          <t>Only College Coding Guide codes are offered.</t>
+          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
         </is>
       </c>
       <c r="I110" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J110" s="14" t="inlineStr">
@@ -10462,7 +10462,7 @@
       </c>
       <c r="K110" s="14" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="L110" s="14" t="inlineStr">
@@ -10493,7 +10493,7 @@
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-03</t>
+          <t>TC-JM-02</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
@@ -10503,7 +10503,7 @@
       </c>
       <c r="C111" s="18" t="inlineStr">
         <is>
-          <t>Fill a setting and see it in the views</t>
+          <t>Jameah Settings pickers</t>
         </is>
       </c>
       <c r="D111" s="14" t="inlineStr">
@@ -10513,22 +10513,22 @@
       </c>
       <c r="E111" s="18" t="inlineStr">
         <is>
-          <t>Decision on the college code (DEC-02).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F111" s="18" t="inlineStr">
         <is>
-          <t>Set College; Save; reopen Jameah Data Check.</t>
+          <t>Open Jameah Settings; open the College picker.</t>
         </is>
       </c>
       <c r="G111" s="18" t="inlineStr">
         <is>
-          <t>College code</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H111" s="18" t="inlineStr">
         <is>
-          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
+          <t>Only College Coding Guide codes are offered.</t>
         </is>
       </c>
       <c r="I111" s="14" t="inlineStr">
@@ -10543,12 +10543,12 @@
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="L111" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M111" s="19" t="inlineStr">
@@ -10574,7 +10574,7 @@
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-04</t>
+          <t>TC-JM-03</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
@@ -10584,7 +10584,7 @@
       </c>
       <c r="C112" s="18" t="inlineStr">
         <is>
-          <t>Map a value in the Code Map</t>
+          <t>Fill a setting and see it in the views</t>
         </is>
       </c>
       <c r="D112" s="14" t="inlineStr">
@@ -10594,22 +10594,22 @@
       </c>
       <c r="E112" s="18" t="inlineStr">
         <is>
-          <t>A 'Needs Review' row.</t>
+          <t>Decision on the college code (DEC-02).</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
         <is>
-          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
+          <t>Set College; Save; reopen Jameah Data Check.</t>
         </is>
       </c>
       <c r="G112" s="18" t="inlineStr">
         <is>
-          <t>e.g. Internship -&gt; 0</t>
+          <t>College code</t>
         </is>
       </c>
       <c r="H112" s="18" t="inlineStr">
         <is>
-          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
+          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
         </is>
       </c>
       <c r="I112" s="14" t="inlineStr">
@@ -10624,12 +10624,12 @@
       </c>
       <c r="K112" s="14" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M112" s="19" t="inlineStr">
@@ -10655,7 +10655,7 @@
     <row r="113">
       <c r="A113" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-05</t>
+          <t>TC-JM-04</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
@@ -10665,7 +10665,7 @@
       </c>
       <c r="C113" s="18" t="inlineStr">
         <is>
-          <t>Code Map refuses a code from another list</t>
+          <t>Map a value in the Code Map</t>
         </is>
       </c>
       <c r="D113" s="14" t="inlineStr">
@@ -10675,42 +10675,42 @@
       </c>
       <c r="E113" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A 'Needs Review' row.</t>
         </is>
       </c>
       <c r="F113" s="18" t="inlineStr">
         <is>
-          <t>Try to save a Religion row with a Gender code.</t>
+          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
         </is>
       </c>
       <c r="G113" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>e.g. Internship -&gt; 0</t>
         </is>
       </c>
       <c r="H113" s="18" t="inlineStr">
         <is>
-          <t>Refused with a clear message.</t>
+          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
         </is>
       </c>
       <c r="I113" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J113" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K113" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="L113" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M113" s="19" t="inlineStr">
@@ -10736,7 +10736,7 @@
     <row r="114">
       <c r="A114" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-06</t>
+          <t>TC-JM-05</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -10746,12 +10746,12 @@
       </c>
       <c r="C114" s="18" t="inlineStr">
         <is>
-          <t>Refresh academic figures</t>
+          <t>Code Map refuses a code from another list</t>
         </is>
       </c>
       <c r="D114" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E114" s="18" t="inlineStr">
@@ -10761,7 +10761,7 @@
       </c>
       <c r="F114" s="18" t="inlineStr">
         <is>
-          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
+          <t>Try to save a Religion row with a Gender code.</t>
         </is>
       </c>
       <c r="G114" s="18" t="inlineStr">
@@ -10771,7 +10771,7 @@
       </c>
       <c r="H114" s="18" t="inlineStr">
         <is>
-          <t>'Last refreshed' time updates.</t>
+          <t>Refused with a clear message.</t>
         </is>
       </c>
       <c r="I114" s="14" t="inlineStr">
@@ -10781,17 +10781,17 @@
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="K114" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M114" s="19" t="inlineStr">
@@ -10817,7 +10817,7 @@
     <row r="115">
       <c r="A115" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-07</t>
+          <t>TC-JM-06</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
@@ -10827,7 +10827,7 @@
       </c>
       <c r="C115" s="18" t="inlineStr">
         <is>
-          <t>Employee data reaches the Employee views</t>
+          <t>Refresh academic figures</t>
         </is>
       </c>
       <c r="D115" s="14" t="inlineStr">
@@ -10837,12 +10837,12 @@
       </c>
       <c r="E115" s="18" t="inlineStr">
         <is>
-          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F115" s="18" t="inlineStr">
         <is>
-          <t>Open their Ministry (Jameah) Data preview.</t>
+          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
         </is>
       </c>
       <c r="G115" s="18" t="inlineStr">
@@ -10852,12 +10852,12 @@
       </c>
       <c r="H115" s="18" t="inlineStr">
         <is>
-          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
+          <t>'Last refreshed' time updates.</t>
         </is>
       </c>
       <c r="I115" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J115" s="14" t="inlineStr">
@@ -10867,12 +10867,12 @@
       </c>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>REC-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L115" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M115" s="19" t="inlineStr">
@@ -10898,7 +10898,7 @@
     <row r="116">
       <c r="A116" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-10</t>
+          <t>TC-JM-07</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
@@ -10908,32 +10908,32 @@
       </c>
       <c r="C116" s="18" t="inlineStr">
         <is>
-          <t>Ministry GPA and hours equal the student's transcript</t>
+          <t>Employee data reaches the Employee views</t>
         </is>
       </c>
       <c r="D116" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E116" s="18" t="inlineStr">
         <is>
-          <t>Academic figures refreshed (TC-JM-06).</t>
+          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
         </is>
       </c>
       <c r="F116" s="18" t="inlineStr">
         <is>
-          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
+          <t>Open their Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="G116" s="18" t="inlineStr">
         <is>
-          <t>10 students</t>
+          <t>—</t>
         </is>
       </c>
       <c r="H116" s="18" t="inlineStr">
         <is>
-          <t>All four figures are identical for every student.</t>
+          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
         </is>
       </c>
       <c r="I116" s="14" t="inlineStr">
@@ -10943,12 +10943,12 @@
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K116" s="14" t="inlineStr">
         <is>
-          <t>verify.run</t>
+          <t>REC-06</t>
         </is>
       </c>
       <c r="L116" s="14" t="inlineStr">
@@ -10979,7 +10979,7 @@
     <row r="117">
       <c r="A117" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-08</t>
+          <t>TC-JM-10</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -10989,32 +10989,32 @@
       </c>
       <c r="C117" s="18" t="inlineStr">
         <is>
-          <t>Full value-by-value check (developer)</t>
+          <t>Ministry GPA and hours equal the student's transcript</t>
         </is>
       </c>
       <c r="D117" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E117" s="18" t="inlineStr">
         <is>
-          <t>Server access.</t>
+          <t>Academic figures refreshed (TC-JM-06).</t>
         </is>
       </c>
       <c r="F117" s="18" t="inlineStr">
         <is>
-          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
+          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
         </is>
       </c>
       <c r="G117" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 students</t>
         </is>
       </c>
       <c r="H117" s="18" t="inlineStr">
         <is>
-          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
+          <t>All four figures are identical for every student.</t>
         </is>
       </c>
       <c r="I117" s="14" t="inlineStr">
@@ -11060,7 +11060,7 @@
     <row r="118">
       <c r="A118" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-09</t>
+          <t>TC-JM-08</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
@@ -11070,22 +11070,22 @@
       </c>
       <c r="C118" s="18" t="inlineStr">
         <is>
-          <t>Ministry read-only account</t>
+          <t>Full value-by-value check (developer)</t>
         </is>
       </c>
       <c r="D118" s="14" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="E118" s="18" t="inlineStr">
         <is>
-          <t>Account created with the grant statements.</t>
+          <t>Server access.</t>
         </is>
       </c>
       <c r="F118" s="18" t="inlineStr">
         <is>
-          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
+          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="G118" s="18" t="inlineStr">
@@ -11095,27 +11095,27 @@
       </c>
       <c r="H118" s="18" t="inlineStr">
         <is>
-          <t>Views readable; ERP tables refused.</t>
+          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
         </is>
       </c>
       <c r="I118" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="K118" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verify.run</t>
         </is>
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M118" s="19" t="inlineStr">
@@ -11141,7 +11141,7 @@
     <row r="119">
       <c r="A119" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-11</t>
+          <t>TC-JM-09</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
@@ -11151,52 +11151,52 @@
       </c>
       <c r="C119" s="18" t="inlineStr">
         <is>
-          <t>Faculty views on the Data Check page</t>
+          <t>Ministry read-only account</t>
         </is>
       </c>
       <c r="D119" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="E119" s="18" t="inlineStr">
         <is>
+          <t>Account created with the grant statements.</t>
+        </is>
+      </c>
+      <c r="F119" s="18" t="inlineStr">
+        <is>
+          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
+        </is>
+      </c>
+      <c r="G119" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F119" s="18" t="inlineStr">
-        <is>
-          <t>Open Jameah Data Check and look at the Views table.</t>
-        </is>
-      </c>
-      <c r="G119" s="18" t="inlineStr">
+      <c r="H119" s="18" t="inlineStr">
+        <is>
+          <t>Views readable; ERP tables refused.</t>
+        </is>
+      </c>
+      <c r="I119" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J119" s="14" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="K119" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="H119" s="18" t="inlineStr">
-        <is>
-          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
-        </is>
-      </c>
-      <c r="I119" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="J119" s="14" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="K119" s="14" t="inlineStr">
-        <is>
-          <t>JM-01</t>
-        </is>
-      </c>
       <c r="L119" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M119" s="19" t="inlineStr">
@@ -11222,7 +11222,7 @@
     <row r="120">
       <c r="A120" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-12</t>
+          <t>TC-JM-11</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
@@ -11232,7 +11232,7 @@
       </c>
       <c r="C120" s="18" t="inlineStr">
         <is>
-          <t>A teacher is sent once, as Faculty</t>
+          <t>Faculty views on the Data Check page</t>
         </is>
       </c>
       <c r="D120" s="14" t="inlineStr">
@@ -11242,13 +11242,12 @@
       </c>
       <c r="E120" s="18" t="inlineStr">
         <is>
-          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F120" s="18" t="inlineStr">
         <is>
-          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
-2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
+          <t>Open Jameah Data Check and look at the Views table.</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
@@ -11258,27 +11257,27 @@
       </c>
       <c r="H120" s="18" t="inlineStr">
         <is>
-          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
+          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
         </is>
       </c>
       <c r="I120" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="K120" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M120" s="19" t="inlineStr">
@@ -11304,7 +11303,7 @@
     <row r="121">
       <c r="A121" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-13</t>
+          <t>TC-JM-12</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
@@ -11314,23 +11313,23 @@
       </c>
       <c r="C121" s="18" t="inlineStr">
         <is>
-          <t>Faculty status and contract codes</t>
+          <t>A teacher is sent once, as Faculty</t>
         </is>
       </c>
       <c r="D121" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E121" s="18" t="inlineStr">
         <is>
-          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
         </is>
       </c>
       <c r="F121" s="18" t="inlineStr">
         <is>
-          <t>1. Open each row, pick the Ministry code, Status = Verified.
-2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
+2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
         </is>
       </c>
       <c r="G121" s="18" t="inlineStr">
@@ -11340,12 +11339,12 @@
       </c>
       <c r="H121" s="18" t="inlineStr">
         <is>
-          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
+          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
         </is>
       </c>
       <c r="I121" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J121" s="14" t="inlineStr">
@@ -11355,12 +11354,12 @@
       </c>
       <c r="K121" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="L121" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="M121" s="19" t="inlineStr">
@@ -11386,52 +11385,53 @@
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-01</t>
+          <t>TC-JM-13</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="C122" s="18" t="inlineStr">
         <is>
-          <t>Error Log after each test day</t>
+          <t>Faculty status and contract codes</t>
         </is>
       </c>
       <c r="D122" s="14" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="E122" s="18" t="inlineStr">
         <is>
+          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+        </is>
+      </c>
+      <c r="F122" s="18" t="inlineStr">
+        <is>
+          <t>1. Open each row, pick the Ministry code, Status = Verified.
+2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+        </is>
+      </c>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="F122" s="18" t="inlineStr">
-        <is>
-          <t>Open /app/error-log; sort by newest.</t>
-        </is>
-      </c>
-      <c r="G122" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="H122" s="18" t="inlineStr">
         <is>
-          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
+          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
         </is>
       </c>
       <c r="I122" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="K122" s="14" t="inlineStr">
@@ -11467,7 +11467,7 @@
     <row r="123">
       <c r="A123" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-02</t>
+          <t>TC-ERR-01</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
@@ -11477,7 +11477,7 @@
       </c>
       <c r="C123" s="18" t="inlineStr">
         <is>
-          <t>System e-mail works</t>
+          <t>Error Log after each test day</t>
         </is>
       </c>
       <c r="D123" s="14" t="inlineStr">
@@ -11492,7 +11492,7 @@
       </c>
       <c r="F123" s="18" t="inlineStr">
         <is>
-          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
+          <t>Open /app/error-log; sort by newest.</t>
         </is>
       </c>
       <c r="G123" s="18" t="inlineStr">
@@ -11502,7 +11502,7 @@
       </c>
       <c r="H123" s="18" t="inlineStr">
         <is>
-          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
+          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
         </is>
       </c>
       <c r="I123" s="14" t="inlineStr">
@@ -11548,7 +11548,7 @@
     <row r="124">
       <c r="A124" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-03</t>
+          <t>TC-ERR-02</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
@@ -11558,7 +11558,7 @@
       </c>
       <c r="C124" s="18" t="inlineStr">
         <is>
-          <t>Background jobs</t>
+          <t>System e-mail works</t>
         </is>
       </c>
       <c r="D124" s="14" t="inlineStr">
@@ -11573,7 +11573,7 @@
       </c>
       <c r="F124" s="18" t="inlineStr">
         <is>
-          <t>Open Scheduled Job Log; filter Status = Failed.</t>
+          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
         </is>
       </c>
       <c r="G124" s="18" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="H124" s="18" t="inlineStr">
         <is>
-          <t>No failed jobs (or each one reported).</t>
+          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
         </is>
       </c>
       <c r="I124" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="J124" s="14" t="inlineStr">
@@ -11629,7 +11629,7 @@
     <row r="125">
       <c r="A125" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-04</t>
+          <t>TC-ERR-03</t>
         </is>
       </c>
       <c r="B125" s="14" t="inlineStr">
@@ -11639,22 +11639,22 @@
       </c>
       <c r="C125" s="18" t="inlineStr">
         <is>
-          <t>Browser console during testing</t>
+          <t>Background jobs</t>
         </is>
       </c>
       <c r="D125" s="14" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="E125" s="18" t="inlineStr">
         <is>
-          <t>Chrome DevTools open (F12 -&gt; Console).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F125" s="18" t="inlineStr">
         <is>
-          <t>Use the system as normal while the console is open.</t>
+          <t>Open Scheduled Job Log; filter Status = Failed.</t>
         </is>
       </c>
       <c r="G125" s="18" t="inlineStr">
@@ -11664,12 +11664,12 @@
       </c>
       <c r="H125" s="18" t="inlineStr">
         <is>
-          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
+          <t>No failed jobs (or each one reported).</t>
         </is>
       </c>
       <c r="I125" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J125" s="14" t="inlineStr">
@@ -11679,12 +11679,12 @@
       </c>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>Error sweep SWP-01..04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L125" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M125" s="19" t="inlineStr">
@@ -11710,7 +11710,7 @@
     <row r="126">
       <c r="A126" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-05</t>
+          <t>TC-ERR-04</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
@@ -11720,22 +11720,22 @@
       </c>
       <c r="C126" s="18" t="inlineStr">
         <is>
-          <t>Migrate output after deploying</t>
+          <t>Browser console during testing</t>
         </is>
       </c>
       <c r="D126" s="14" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="E126" s="18" t="inlineStr">
         <is>
-          <t>New branch pulled on the server.</t>
+          <t>Chrome DevTools open (F12 -&gt; Console).</t>
         </is>
       </c>
       <c r="F126" s="18" t="inlineStr">
         <is>
-          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
+          <t>Use the system as normal while the console is open.</t>
         </is>
       </c>
       <c r="G126" s="18" t="inlineStr">
@@ -11745,7 +11745,7 @@
       </c>
       <c r="H126" s="18" t="inlineStr">
         <is>
-          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
+          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
         </is>
       </c>
       <c r="I126" s="14" t="inlineStr">
@@ -11760,12 +11760,12 @@
       </c>
       <c r="K126" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Error sweep SWP-01..04</t>
         </is>
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="M126" s="19" t="inlineStr">
@@ -11791,7 +11791,7 @@
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-06</t>
+          <t>TC-ERR-05</t>
         </is>
       </c>
       <c r="B127" s="14" t="inlineStr">
@@ -11801,22 +11801,22 @@
       </c>
       <c r="C127" s="18" t="inlineStr">
         <is>
-          <t>Every Medical HRMS page and form opens</t>
+          <t>Migrate output after deploying</t>
         </is>
       </c>
       <c r="D127" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="E127" s="18" t="inlineStr">
         <is>
-          <t>Logged in as HR Manager (then repeat as HR User).</t>
+          <t>New branch pulled on the server.</t>
         </is>
       </c>
       <c r="F127" s="18" t="inlineStr">
         <is>
-          <t>Open each Medical HRMS doctype list, its New form and its newest saved record; the four pages, the report and both workspaces.</t>
+          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
         </is>
       </c>
       <c r="G127" s="18" t="inlineStr">
@@ -11826,27 +11826,27 @@
       </c>
       <c r="H127" s="18" t="inlineStr">
         <is>
-          <t>Each opens; no red error, no 'Not permitted' for HR, no blank page.</t>
+          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
         </is>
       </c>
       <c r="I127" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J127" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>SWP-01/02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="L127" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="M127" s="19" t="inlineStr">
@@ -11860,19 +11860,19 @@
       <c r="Q127" s="19" t="inlineStr"/>
       <c r="R127" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="S127" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-07</t>
+          <t>TC-ERR-06</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
@@ -11882,22 +11882,22 @@
       </c>
       <c r="C128" s="18" t="inlineStr">
         <is>
-          <t>Employees' own request lists open</t>
+          <t>Every Medical HRMS page and form opens</t>
         </is>
       </c>
       <c r="D128" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="E128" s="18" t="inlineStr">
         <is>
-          <t>Logged in as an employee.</t>
+          <t>Logged in as HR Manager (then repeat as HR User).</t>
         </is>
       </c>
       <c r="F128" s="18" t="inlineStr">
         <is>
-          <t>Open the list of each self-service request type (Permission Request ... Employee Medical License) and the Employee Self Service workspace.</t>
+          <t>Open each Medical HRMS doctype list, its New form and its newest saved record; the four pages, the report and both workspaces.</t>
         </is>
       </c>
       <c r="G128" s="18" t="inlineStr">
@@ -11907,12 +11907,12 @@
       </c>
       <c r="H128" s="18" t="inlineStr">
         <is>
-          <t>Each opens with only the employee's own records; no error.</t>
+          <t>Each opens; no red error, no 'Not permitted' for HR, no blank page.</t>
         </is>
       </c>
       <c r="I128" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="J128" s="14" t="inlineStr">
@@ -11922,7 +11922,7 @@
       </c>
       <c r="K128" s="14" t="inlineStr">
         <is>
-          <t>SWP-03</t>
+          <t>SWP-01/02</t>
         </is>
       </c>
       <c r="L128" s="14" t="inlineStr">
@@ -11953,7 +11953,7 @@
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-08</t>
+          <t>TC-ERR-07</t>
         </is>
       </c>
       <c r="B129" s="14" t="inlineStr">
@@ -11963,22 +11963,22 @@
       </c>
       <c r="C129" s="18" t="inlineStr">
         <is>
-          <t>Every file of the app is valid</t>
+          <t>Employees' own request lists open</t>
         </is>
       </c>
       <c r="D129" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="E129" s="18" t="inlineStr">
         <is>
-          <t>A checkout of develop.</t>
+          <t>Logged in as an employee.</t>
         </is>
       </c>
       <c r="F129" s="18" t="inlineStr">
         <is>
-          <t>python3 tests/checks/files.py</t>
+          <t>Open the list of each self-service request type (Permission Request ... Employee Medical License) and the Employee Self Service workspace.</t>
         </is>
       </c>
       <c r="G129" s="18" t="inlineStr">
@@ -11988,12 +11988,12 @@
       </c>
       <c r="H129" s="18" t="inlineStr">
         <is>
-          <t>PROBLEMS: 0 (Python compiles, JS parses, JSON loads, translations keep their placeholders, no stray files).</t>
+          <t>Each opens with only the employee's own records; no error.</t>
         </is>
       </c>
       <c r="I129" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="J129" s="14" t="inlineStr">
@@ -12003,7 +12003,7 @@
       </c>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/files.py</t>
+          <t>SWP-03</t>
         </is>
       </c>
       <c r="L129" s="14" t="inlineStr">
@@ -12034,7 +12034,7 @@
     <row r="130">
       <c r="A130" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-09</t>
+          <t>TC-ERR-08</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
@@ -12044,7 +12044,7 @@
       </c>
       <c r="C130" s="18" t="inlineStr">
         <is>
-          <t>Every hook, doctype and record is valid on the site</t>
+          <t>Every file of the app is valid</t>
         </is>
       </c>
       <c r="D130" s="14" t="inlineStr">
@@ -12054,12 +12054,12 @@
       </c>
       <c r="E130" s="18" t="inlineStr">
         <is>
-          <t>Site migrated.</t>
+          <t>A checkout of develop.</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
         <is>
-          <t>../../env/bin/python tests/e2e/fx.py tests/checks/site.py</t>
+          <t>python3 tests/checks/files.py</t>
         </is>
       </c>
       <c r="G130" s="18" t="inlineStr">
@@ -12069,7 +12069,7 @@
       </c>
       <c r="H130" s="18" t="inlineStr">
         <is>
-          <t>PROBLEMS: 0; every hook, patch and asset resolves; saved records pass validation.</t>
+          <t>PROBLEMS: 0 (Python compiles, JS parses, JSON loads, translations keep their placeholders, no stray files).</t>
         </is>
       </c>
       <c r="I130" s="14" t="inlineStr">
@@ -12084,7 +12084,7 @@
       </c>
       <c r="K130" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/site.py</t>
+          <t>tests/checks/files.py</t>
         </is>
       </c>
       <c r="L130" s="14" t="inlineStr">
@@ -12112,9 +12112,90 @@
         </is>
       </c>
     </row>
+    <row r="131">
+      <c r="A131" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-09</t>
+        </is>
+      </c>
+      <c r="B131" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="C131" s="18" t="inlineStr">
+        <is>
+          <t>Every hook, doctype and record is valid on the site</t>
+        </is>
+      </c>
+      <c r="D131" s="14" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="E131" s="18" t="inlineStr">
+        <is>
+          <t>Site migrated.</t>
+        </is>
+      </c>
+      <c r="F131" s="18" t="inlineStr">
+        <is>
+          <t>../../env/bin/python tests/e2e/fx.py tests/checks/site.py</t>
+        </is>
+      </c>
+      <c r="G131" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="H131" s="18" t="inlineStr">
+        <is>
+          <t>PROBLEMS: 0; every hook, patch and asset resolves; saved records pass validation.</t>
+        </is>
+      </c>
+      <c r="I131" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="J131" s="14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="K131" s="14" t="inlineStr">
+        <is>
+          <t>tests/checks/site.py</t>
+        </is>
+      </c>
+      <c r="L131" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="M131" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="N131" s="19" t="inlineStr"/>
+      <c r="O131" s="19" t="inlineStr"/>
+      <c r="P131" s="20" t="inlineStr"/>
+      <c r="Q131" s="19" t="inlineStr"/>
+      <c r="R131" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="S131" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:S130"/>
-  <conditionalFormatting sqref="M2:M330">
+  <autoFilter ref="A1:S131"/>
+  <conditionalFormatting sqref="M2:M331">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$M2="Pass"</formula>
     </cfRule>
@@ -12131,7 +12212,7 @@
       <formula>$M2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="L2:L330">
+  <conditionalFormatting sqref="L2:L331">
     <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
       <formula>$L2="Pass"</formula>
     </cfRule>
@@ -12148,7 +12229,7 @@
       <formula>$L2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="I2:I330">
+  <conditionalFormatting sqref="I2:I331">
     <cfRule type="expression" priority="11" dxfId="4" stopIfTrue="1">
       <formula>$I2="Critical"</formula>
     </cfRule>
@@ -12163,7 +12244,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="M2:M330" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="M2:M331" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -14075,7 +14156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E13"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14120,17 +14201,17 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -14152,12 +14233,12 @@
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -14174,17 +14255,17 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -14196,7 +14277,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -14206,12 +14287,12 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -14233,12 +14314,12 @@
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -14255,17 +14336,17 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -14277,22 +14358,22 @@
     <row r="8">
       <c r="A8" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -14309,17 +14390,17 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -14336,17 +14417,17 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -14358,7 +14439,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -14368,12 +14449,12 @@
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -14385,7 +14466,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -14395,12 +14476,12 @@
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -14412,25 +14493,52 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B13" s="14" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C13" s="18" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D13" s="18" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E13" s="14" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="14" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B13" s="14" t="inlineStr">
+      <c r="B14" s="14" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C13" s="18" t="inlineStr">
+      <c r="C14" s="18" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D13" s="18" t="inlineStr">
+      <c r="D14" s="18" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E13" s="14" t="inlineStr">
+      <c r="E14" s="14" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -14156,7 +14156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E14"/>
+  <dimension ref="A1:E15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14206,12 +14206,12 @@
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -14228,17 +14228,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -14260,12 +14260,12 @@
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -14282,17 +14282,17 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -14304,7 +14304,7 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -14314,12 +14314,12 @@
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -14363,17 +14363,17 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -14385,22 +14385,22 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -14417,17 +14417,17 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -14444,17 +14444,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -14466,7 +14466,7 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
@@ -14476,12 +14476,12 @@
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -14493,7 +14493,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -14520,25 +14520,52 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B14" s="14" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C14" s="18" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D14" s="18" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E14" s="14" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="14" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B14" s="14" t="inlineStr">
+      <c r="B15" s="14" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C14" s="18" t="inlineStr">
+      <c r="C15" s="18" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D14" s="18" t="inlineStr">
+      <c r="D15" s="18" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E14" s="14" t="inlineStr">
+      <c r="E15" s="14" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>For the testing team · last updated 23 Oct 2026 · last automated run 23 Oct 2026 11:15 AST (95/95 browser checks passed)</t>
+          <t>For the testing team · last updated 27 Oct 2026 · last automated run 23 Oct 2026 11:15 AST (95/95 browser checks passed)</t>
         </is>
       </c>
     </row>
@@ -14156,7 +14156,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:E16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -14196,22 +14196,22 @@
     <row r="2">
       <c r="A2" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -14233,12 +14233,12 @@
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -14255,17 +14255,17 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -14287,12 +14287,12 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -14309,17 +14309,17 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -14331,7 +14331,7 @@
     <row r="7">
       <c r="A7" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B7" s="14" t="inlineStr">
@@ -14341,12 +14341,12 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -14368,12 +14368,12 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -14390,17 +14390,17 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -14412,22 +14412,22 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -14444,17 +14444,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -14471,17 +14471,17 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -14493,7 +14493,7 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
@@ -14503,12 +14503,12 @@
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -14520,7 +14520,7 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
@@ -14530,12 +14530,12 @@
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -14547,25 +14547,52 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B15" s="14" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C15" s="18" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D15" s="18" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E15" s="14" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="14" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B15" s="14" t="inlineStr">
+      <c r="B16" s="14" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C15" s="18" t="inlineStr">
+      <c r="C16" s="18" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D15" s="18" t="inlineStr">
+      <c r="D16" s="18" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E15" s="14" t="inlineStr">
+      <c r="E16" s="14" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -16240,7 +16240,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E17"/>
+  <dimension ref="A1:E18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16285,17 +16285,17 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -16312,17 +16312,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -16334,22 +16334,22 @@
     <row r="4">
       <c r="A4" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -16371,12 +16371,12 @@
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -16393,17 +16393,17 @@
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -16425,12 +16425,12 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -16447,17 +16447,17 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -16469,7 +16469,7 @@
     <row r="9">
       <c r="A9" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B9" s="14" t="inlineStr">
@@ -16479,12 +16479,12 @@
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -16506,12 +16506,12 @@
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -16528,17 +16528,17 @@
       </c>
       <c r="B11" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -16550,22 +16550,22 @@
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -16582,17 +16582,17 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -16609,17 +16609,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -16631,7 +16631,7 @@
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B15" s="14" t="inlineStr">
@@ -16641,12 +16641,12 @@
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -16658,7 +16658,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -16668,12 +16668,12 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -16685,25 +16685,52 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B17" s="14" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C17" s="18" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D17" s="18" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E17" s="14" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="14" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B17" s="14" t="inlineStr">
+      <c r="B18" s="14" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C17" s="18" t="inlineStr">
+      <c r="C18" s="18" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D17" s="18" t="inlineStr">
+      <c r="D18" s="18" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E17" s="14" t="inlineStr">
+      <c r="E18" s="14" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$T$146</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$T$147</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -936,27 +936,27 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A5)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A5,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A5,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A5,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A5,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A5,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H5" s="15">
@@ -964,7 +964,7 @@
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A5,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A5,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -975,27 +975,27 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A6)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A6,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A6,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A6,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A6,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A6,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H6" s="15">
@@ -1003,7 +1003,7 @@
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A6,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A6,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1014,27 +1014,27 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A7)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A7,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A7,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A7,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A7,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A7,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H7" s="15">
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="I7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A7,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A7,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1053,27 +1053,27 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A8)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A8,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A8,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A8,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A8,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A8,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H8" s="15">
@@ -1081,7 +1081,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A8,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A8,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1092,27 +1092,27 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A9)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A9,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A9,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A9,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A9,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A9,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H9" s="15">
@@ -1120,7 +1120,7 @@
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A9,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A9,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1131,27 +1131,27 @@
         </is>
       </c>
       <c r="B10" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A10)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A10,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A10,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A10,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A10,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A10,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H10" s="15">
@@ -1159,7 +1159,7 @@
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A10,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A10,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1170,27 +1170,27 @@
         </is>
       </c>
       <c r="B11" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A11)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A11,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A11,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A11,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A11,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A11,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H11" s="15">
@@ -1198,7 +1198,7 @@
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A11,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A11,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1209,27 +1209,27 @@
         </is>
       </c>
       <c r="B12" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A12)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A12,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A12,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A12,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A12,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A12,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H12" s="15">
@@ -1237,7 +1237,7 @@
         <v/>
       </c>
       <c r="I12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A12,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A12,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1248,27 +1248,27 @@
         </is>
       </c>
       <c r="B13" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A13)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A13,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A13,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A13,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A13,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A13,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H13" s="15">
@@ -1276,7 +1276,7 @@
         <v/>
       </c>
       <c r="I13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A13,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A13,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1287,27 +1287,27 @@
         </is>
       </c>
       <c r="B14" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A14)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A14,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A14,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A14,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A14,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A14,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H14" s="15">
@@ -1315,7 +1315,7 @@
         <v/>
       </c>
       <c r="I14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A14,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A14,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1326,27 +1326,27 @@
         </is>
       </c>
       <c r="B15" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A15)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A15,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A15,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A15,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A15,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A15,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H15" s="15">
@@ -1354,7 +1354,7 @@
         <v/>
       </c>
       <c r="I15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A15,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A15,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1365,27 +1365,27 @@
         </is>
       </c>
       <c r="B16" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$346,$A16)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A16,'Test Cases'!$N$2:$N$346,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,C$4)</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A16,'Test Cases'!$N$2:$N$346,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,D$4)</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A16,'Test Cases'!$N$2:$N$346,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,E$4)</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A16,'Test Cases'!$N$2:$N$346,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,F$4)</f>
         <v/>
       </c>
       <c r="G16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A16,'Test Cases'!$N$2:$N$346,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,G$4)</f>
         <v/>
       </c>
       <c r="H16" s="15">
@@ -1393,7 +1393,7 @@
         <v/>
       </c>
       <c r="I16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$346,$A16,'Test Cases'!$J$2:$J$346,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$346,$A16,'Test Cases'!$J$2:$J$346,"Critical",'Test Cases'!$N$2:$N$346,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1485,27 +1485,27 @@
         </is>
       </c>
       <c r="B20" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$346,$A20)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$347,$A20)</f>
         <v/>
       </c>
       <c r="C20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A20,'Test Cases'!$N$2:$N$346,C$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,C$19)</f>
         <v/>
       </c>
       <c r="D20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A20,'Test Cases'!$N$2:$N$346,D$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,D$19)</f>
         <v/>
       </c>
       <c r="E20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A20,'Test Cases'!$N$2:$N$346,E$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,E$19)</f>
         <v/>
       </c>
       <c r="F20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A20,'Test Cases'!$N$2:$N$346,F$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,F$19)</f>
         <v/>
       </c>
       <c r="G20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A20,'Test Cases'!$N$2:$N$346,G$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,G$19)</f>
         <v/>
       </c>
       <c r="H20" s="15">
@@ -1520,27 +1520,27 @@
         </is>
       </c>
       <c r="B21" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$346,$A21)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$347,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A21,'Test Cases'!$N$2:$N$346,C$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,C$19)</f>
         <v/>
       </c>
       <c r="D21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A21,'Test Cases'!$N$2:$N$346,D$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,D$19)</f>
         <v/>
       </c>
       <c r="E21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A21,'Test Cases'!$N$2:$N$346,E$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,E$19)</f>
         <v/>
       </c>
       <c r="F21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A21,'Test Cases'!$N$2:$N$346,F$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,F$19)</f>
         <v/>
       </c>
       <c r="G21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$346,$A21,'Test Cases'!$N$2:$N$346,G$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,G$19)</f>
         <v/>
       </c>
       <c r="H21" s="15">
@@ -1562,7 +1562,7 @@
         </is>
       </c>
       <c r="B24" s="14">
-        <f>COUNTIF('Test Cases'!$M$2:$M$346,"Pass")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$347,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1573,7 +1573,7 @@
         </is>
       </c>
       <c r="B25" s="14">
-        <f>COUNTIF('Test Cases'!$M$2:$M$346,"Fail")</f>
+        <f>COUNTIF('Test Cases'!$M$2:$M$347,"Fail")</f>
         <v/>
       </c>
     </row>
@@ -1584,7 +1584,7 @@
         </is>
       </c>
       <c r="B26" s="14">
-        <f>COUNTA('Test Cases'!$M$2:$M$146)-B24-B25</f>
+        <f>COUNTA('Test Cases'!$M$2:$M$147)-B24-B25</f>
         <v/>
       </c>
     </row>
@@ -1599,7 +1599,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T146"/>
+  <dimension ref="A1:T147"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -7105,22 +7105,22 @@
     <row r="64">
       <c r="A64" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-01</t>
+          <t>TC-LV-19</t>
         </is>
       </c>
       <c r="B64" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C64" s="14" t="inlineStr">
         <is>
-          <t>HR approvals</t>
+          <t>Leave</t>
         </is>
       </c>
       <c r="D64" s="18" t="inlineStr">
         <is>
-          <t>Approve a Permission Request</t>
+          <t>Leave e-mails use the Medical HRMS templates</t>
         </is>
       </c>
       <c r="E64" s="14" t="inlineStr">
@@ -7130,12 +7130,14 @@
       </c>
       <c r="F64" s="18" t="inlineStr">
         <is>
-          <t>A Pending request.</t>
+          <t>Round 2 migrated. Steps 2-3 only where e-mail works (Checklist CL-41).</t>
         </is>
       </c>
       <c r="G64" s="18" t="inlineStr">
         <is>
-          <t>Open it, Status = Approved, Save.</t>
+          <t>1. Open HR Settings (Leave Settings).
+2. An employee applies for leave.
+3. The leave approver rejects it with a reason and submits.</t>
         </is>
       </c>
       <c r="H64" s="18" t="inlineStr">
@@ -7145,12 +7147,14 @@
       </c>
       <c r="I64" s="18" t="inlineStr">
         <is>
-          <t>Saved; the employee sees Approved.</t>
+          <t>1. Leave Approval Notification Template = Leave Approval Notification (Medical HRMS); Leave Status Notification Template = Leave Status Notification (Medical HRMS).
+2. The approver gets 'New Leave Application from &lt;employee&gt; (&lt;number&gt;)' with the dates and the employee's reason.
+3. The employee gets 'Your Leave Application &lt;number&gt; is now Rejected' with the rejection reason; Open Now opens it on the Employee Portal.</t>
         </is>
       </c>
       <c r="J64" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K64" s="14" t="inlineStr">
@@ -7160,12 +7164,12 @@
       </c>
       <c r="L64" s="14" t="inlineStr">
         <is>
-          <t>APR-01</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M64" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N64" s="19" t="inlineStr">
@@ -7179,24 +7183,24 @@
       <c r="R64" s="19" t="inlineStr"/>
       <c r="S64" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T64" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-02</t>
+          <t>TC-APR-01</t>
         </is>
       </c>
       <c r="B65" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Round 1</t>
         </is>
       </c>
       <c r="C65" s="14" t="inlineStr">
@@ -7206,7 +7210,7 @@
       </c>
       <c r="D65" s="18" t="inlineStr">
         <is>
-          <t>Reject a Training Request with a reason</t>
+          <t>Approve a Permission Request</t>
         </is>
       </c>
       <c r="E65" s="14" t="inlineStr">
@@ -7221,19 +7225,17 @@
       </c>
       <c r="G65" s="18" t="inlineStr">
         <is>
-          <t>1. Status = Rejected.
-2. Click Save without a reason.
-3. Fill Rejection Reason and Save.</t>
+          <t>Open it, Status = Approved, Save.</t>
         </is>
       </c>
       <c r="H65" s="18" t="inlineStr">
         <is>
-          <t>Reason text</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I65" s="18" t="inlineStr">
         <is>
-          <t>Step 2: 'Missing Fields: Rejection Reason'; nothing is saved. Step 3: saved as Rejected with the reason; the employee sees the reason.</t>
+          <t>Saved; the employee sees Approved.</t>
         </is>
       </c>
       <c r="J65" s="14" t="inlineStr">
@@ -7248,7 +7250,7 @@
       </c>
       <c r="L65" s="14" t="inlineStr">
         <is>
-          <t>APR-02</t>
+          <t>APR-01</t>
         </is>
       </c>
       <c r="M65" s="14" t="inlineStr">
@@ -7272,19 +7274,19 @@
       </c>
       <c r="T65" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-03</t>
+          <t>TC-APR-02</t>
         </is>
       </c>
       <c r="B66" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C66" s="14" t="inlineStr">
@@ -7294,7 +7296,7 @@
       </c>
       <c r="D66" s="18" t="inlineStr">
         <is>
-          <t>Issue a Salary Certificate</t>
+          <t>Reject a Training Request with a reason</t>
         </is>
       </c>
       <c r="E66" s="14" t="inlineStr">
@@ -7309,22 +7311,24 @@
       </c>
       <c r="G66" s="18" t="inlineStr">
         <is>
-          <t>Status = Issued, Save.</t>
+          <t>1. Status = Rejected.
+2. Click Save without a reason.
+3. Fill Rejection Reason and Save.</t>
         </is>
       </c>
       <c r="H66" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reason text</t>
         </is>
       </c>
       <c r="I66" s="18" t="inlineStr">
         <is>
-          <t>Saved as Issued.</t>
+          <t>Step 2: 'Missing Fields: Rejection Reason'; nothing is saved. Step 3: saved as Rejected with the reason; the employee sees the reason.</t>
         </is>
       </c>
       <c r="J66" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K66" s="14" t="inlineStr">
@@ -7334,7 +7338,7 @@
       </c>
       <c r="L66" s="14" t="inlineStr">
         <is>
-          <t>APR-03</t>
+          <t>APR-02</t>
         </is>
       </c>
       <c r="M66" s="14" t="inlineStr">
@@ -7358,14 +7362,14 @@
       </c>
       <c r="T66" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-04</t>
+          <t>TC-APR-03</t>
         </is>
       </c>
       <c r="B67" s="14" t="inlineStr">
@@ -7380,22 +7384,22 @@
       </c>
       <c r="D67" s="18" t="inlineStr">
         <is>
-          <t>HR User sees all employees' requests</t>
+          <t>Issue a Salary Certificate</t>
         </is>
       </c>
       <c r="E67" s="14" t="inlineStr">
         <is>
-          <t>HR User</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F67" s="18" t="inlineStr">
         <is>
-          <t>Requests from two employees.</t>
+          <t>A Pending request.</t>
         </is>
       </c>
       <c r="G67" s="18" t="inlineStr">
         <is>
-          <t>Open each request list.</t>
+          <t>Status = Issued, Save.</t>
         </is>
       </c>
       <c r="H67" s="18" t="inlineStr">
@@ -7405,12 +7409,12 @@
       </c>
       <c r="I67" s="18" t="inlineStr">
         <is>
-          <t>Requests of all employees are listed, including Leave Return Request.</t>
+          <t>Saved as Issued.</t>
         </is>
       </c>
       <c r="J67" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K67" s="14" t="inlineStr">
@@ -7420,7 +7424,7 @@
       </c>
       <c r="L67" s="14" t="inlineStr">
         <is>
-          <t>APR-07</t>
+          <t>APR-03</t>
         </is>
       </c>
       <c r="M67" s="14" t="inlineStr">
@@ -7451,7 +7455,7 @@
     <row r="68">
       <c r="A68" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-05</t>
+          <t>TC-APR-04</t>
         </is>
       </c>
       <c r="B68" s="14" t="inlineStr">
@@ -7466,22 +7470,22 @@
       </c>
       <c r="D68" s="18" t="inlineStr">
         <is>
-          <t>Finance step on money requests</t>
+          <t>HR User sees all employees' requests</t>
         </is>
       </c>
       <c r="E68" s="14" t="inlineStr">
         <is>
-          <t>Finance Manager</t>
+          <t>HR User</t>
         </is>
       </c>
       <c r="F68" s="18" t="inlineStr">
         <is>
-          <t>A Training / Car / Allowance request at the finance step.</t>
+          <t>Requests from two employees.</t>
         </is>
       </c>
       <c r="G68" s="18" t="inlineStr">
         <is>
-          <t>Open and approve.</t>
+          <t>Open each request list.</t>
         </is>
       </c>
       <c r="H68" s="18" t="inlineStr">
@@ -7491,7 +7495,7 @@
       </c>
       <c r="I68" s="18" t="inlineStr">
         <is>
-          <t>Finance Manager can approve; HR cannot skip the finance step.</t>
+          <t>Requests of all employees are listed, including Leave Return Request.</t>
         </is>
       </c>
       <c r="J68" s="14" t="inlineStr">
@@ -7506,12 +7510,12 @@
       </c>
       <c r="L68" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APR-07</t>
         </is>
       </c>
       <c r="M68" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N68" s="19" t="inlineStr">
@@ -7537,7 +7541,7 @@
     <row r="69">
       <c r="A69" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-06</t>
+          <t>TC-APR-05</t>
         </is>
       </c>
       <c r="B69" s="14" t="inlineStr">
@@ -7552,52 +7556,52 @@
       </c>
       <c r="D69" s="18" t="inlineStr">
         <is>
-          <t>Travel Request</t>
+          <t>Finance step on money requests</t>
         </is>
       </c>
       <c r="E69" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Finance Manager</t>
         </is>
       </c>
       <c r="F69" s="18" t="inlineStr">
         <is>
+          <t>A Training / Car / Allowance request at the finance step.</t>
+        </is>
+      </c>
+      <c r="G69" s="18" t="inlineStr">
+        <is>
+          <t>Open and approve.</t>
+        </is>
+      </c>
+      <c r="H69" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G69" s="18" t="inlineStr">
-        <is>
-          <t>Create a Travel Request with costings; save; submit.</t>
-        </is>
-      </c>
-      <c r="H69" s="18" t="inlineStr">
-        <is>
-          <t>Costs</t>
-        </is>
-      </c>
       <c r="I69" s="18" t="inlineStr">
         <is>
-          <t>Saves and submits without error.</t>
+          <t>Finance Manager can approve; HR cannot skip the finance step.</t>
         </is>
       </c>
       <c r="J69" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K69" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L69" s="14" t="inlineStr">
         <is>
-          <t>HRD-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M69" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N69" s="19" t="inlineStr">
@@ -7623,7 +7627,7 @@
     <row r="70">
       <c r="A70" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-07</t>
+          <t>TC-APR-06</t>
         </is>
       </c>
       <c r="B70" s="14" t="inlineStr">
@@ -7638,7 +7642,7 @@
       </c>
       <c r="D70" s="18" t="inlineStr">
         <is>
-          <t>HR opens a new Expense Claim</t>
+          <t>Travel Request</t>
         </is>
       </c>
       <c r="E70" s="14" t="inlineStr">
@@ -7648,27 +7652,27 @@
       </c>
       <c r="F70" s="18" t="inlineStr">
         <is>
-          <t>HR account (also try the HR User account).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G70" s="18" t="inlineStr">
         <is>
-          <t>Open Expense Claim -&gt; + Add.</t>
+          <t>Create a Travel Request with costings; save; submit.</t>
         </is>
       </c>
       <c r="H70" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Costs</t>
         </is>
       </c>
       <c r="I70" s="18" t="inlineStr">
         <is>
-          <t>Form opens with the cost center filled; NO 'You do not have Read or Select Permissions for Cost Center' pop-up.</t>
+          <t>Saves and submits without error.</t>
         </is>
       </c>
       <c r="J70" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K70" s="14" t="inlineStr">
@@ -7678,7 +7682,7 @@
       </c>
       <c r="L70" s="14" t="inlineStr">
         <is>
-          <t>SWP-01/02</t>
+          <t>HRD-03</t>
         </is>
       </c>
       <c r="M70" s="14" t="inlineStr">
@@ -7709,7 +7713,7 @@
     <row r="71">
       <c r="A71" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-08</t>
+          <t>TC-APR-07</t>
         </is>
       </c>
       <c r="B71" s="14" t="inlineStr">
@@ -7724,23 +7728,22 @@
       </c>
       <c r="D71" s="18" t="inlineStr">
         <is>
-          <t>HR User opens the Holiday List</t>
+          <t>HR opens a new Expense Claim</t>
         </is>
       </c>
       <c r="E71" s="14" t="inlineStr">
         <is>
-          <t>HR User</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F71" s="18" t="inlineStr">
         <is>
-          <t>HR User account.</t>
+          <t>HR account (also try the HR User account).</t>
         </is>
       </c>
       <c r="G71" s="18" t="inlineStr">
         <is>
-          <t>1. Open /app/holiday-list.
-2. Open a holiday list.</t>
+          <t>Open Expense Claim -&gt; + Add.</t>
         </is>
       </c>
       <c r="H71" s="18" t="inlineStr">
@@ -7750,12 +7753,12 @@
       </c>
       <c r="I71" s="18" t="inlineStr">
         <is>
-          <t>List and record open read-only; no 'Not permitted'.</t>
+          <t>Form opens with the cost center filled; NO 'You do not have Read or Select Permissions for Cost Center' pop-up.</t>
         </is>
       </c>
       <c r="J71" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K71" s="14" t="inlineStr">
@@ -7765,7 +7768,7 @@
       </c>
       <c r="L71" s="14" t="inlineStr">
         <is>
-          <t>SWP-02</t>
+          <t>SWP-01/02</t>
         </is>
       </c>
       <c r="M71" s="14" t="inlineStr">
@@ -7796,12 +7799,12 @@
     <row r="72">
       <c r="A72" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-09</t>
+          <t>TC-APR-08</t>
         </is>
       </c>
       <c r="B72" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Round 1</t>
         </is>
       </c>
       <c r="C72" s="14" t="inlineStr">
@@ -7811,53 +7814,53 @@
       </c>
       <c r="D72" s="18" t="inlineStr">
         <is>
-          <t>Rejection reason on every request type and on leave</t>
+          <t>HR User opens the Holiday List</t>
         </is>
       </c>
       <c r="E72" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>HR User</t>
         </is>
       </c>
       <c r="F72" s="18" t="inlineStr">
         <is>
-          <t>Pending requests of other types; an Open Leave Application (log in as its leave approver).</t>
+          <t>HR User account.</t>
         </is>
       </c>
       <c r="G72" s="18" t="inlineStr">
         <is>
-          <t>1. Reject a Remote Work, an Overtime and a Salary Certificate request: Save without a reason, then with one.
-2. Leave Application: Status = Rejected, Save without a reason, then with one, then Submit.</t>
+          <t>1. Open /app/holiday-list.
+2. Open a holiday list.</t>
         </is>
       </c>
       <c r="H72" s="18" t="inlineStr">
         <is>
-          <t>Reason text</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I72" s="18" t="inlineStr">
         <is>
-          <t>Without a reason each one is refused ('Rejection Reason'); with a reason it saves. The employee sees the reason.</t>
+          <t>List and record open read-only; no 'Not permitted'.</t>
         </is>
       </c>
       <c r="J72" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K72" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L72" s="14" t="inlineStr">
         <is>
-          <t>unit tests</t>
+          <t>SWP-02</t>
         </is>
       </c>
       <c r="M72" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N72" s="19" t="inlineStr">
@@ -7871,19 +7874,19 @@
       <c r="R72" s="19" t="inlineStr"/>
       <c r="S72" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T72" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-10</t>
+          <t>TC-APR-09</t>
         </is>
       </c>
       <c r="B73" s="14" t="inlineStr">
@@ -7898,7 +7901,7 @@
       </c>
       <c r="D73" s="18" t="inlineStr">
         <is>
-          <t>HR is told about a new request</t>
+          <t>Rejection reason on every request type and on leave</t>
         </is>
       </c>
       <c r="E73" s="14" t="inlineStr">
@@ -7908,24 +7911,23 @@
       </c>
       <c r="F73" s="18" t="inlineStr">
         <is>
-          <t>An employee sends a request (not a draft).</t>
+          <t>Pending requests of other types; an Open Leave Application (log in as its leave approver).</t>
         </is>
       </c>
       <c r="G73" s="18" t="inlineStr">
         <is>
-          <t>1. Open the HR Portal.
-2. Click the bell at the top.
-3. Click the notification.</t>
+          <t>1. Reject a Remote Work, an Overtime and a Salary Certificate request: Save without a reason, then with one.
+2. Leave Application: Status = Rejected, Save without a reason, then with one, then Submit.</t>
         </is>
       </c>
       <c r="H73" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Reason text</t>
         </is>
       </c>
       <c r="I73" s="18" t="inlineStr">
         <is>
-          <t>'New &lt;request&gt; from &lt;employee&gt; (&lt;number&gt;)'; clicking it opens the request. A request saved as a draft sends nothing.</t>
+          <t>Without a reason each one is refused ('Rejection Reason'); with a reason it saves. The employee sees the reason.</t>
         </is>
       </c>
       <c r="J73" s="14" t="inlineStr">
@@ -7935,17 +7937,17 @@
       </c>
       <c r="K73" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L73" s="14" t="inlineStr">
         <is>
-          <t>APR-09</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="M73" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N73" s="19" t="inlineStr">
@@ -7971,7 +7973,7 @@
     <row r="74">
       <c r="A74" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-11</t>
+          <t>TC-APR-10</t>
         </is>
       </c>
       <c r="B74" s="14" t="inlineStr">
@@ -7986,7 +7988,7 @@
       </c>
       <c r="D74" s="18" t="inlineStr">
         <is>
-          <t>Set a rejected request back to a pending step</t>
+          <t>HR is told about a new request</t>
         </is>
       </c>
       <c r="E74" s="14" t="inlineStr">
@@ -7996,12 +7998,14 @@
       </c>
       <c r="F74" s="18" t="inlineStr">
         <is>
-          <t>A Rejected request.</t>
+          <t>An employee sends a request (not a draft).</t>
         </is>
       </c>
       <c r="G74" s="18" t="inlineStr">
         <is>
-          <t>Status = a Pending step -&gt; Save.</t>
+          <t>1. Open the HR Portal.
+2. Click the bell at the top.
+3. Click the notification.</t>
         </is>
       </c>
       <c r="H74" s="18" t="inlineStr">
@@ -8011,12 +8015,12 @@
       </c>
       <c r="I74" s="18" t="inlineStr">
         <is>
-          <t>Saved; the Rejection Reason is cleared (it no longer applies); the employee is told about the new step.</t>
+          <t>'New &lt;request&gt; from &lt;employee&gt; (&lt;number&gt;)'; clicking it opens the request. A request saved as a draft sends nothing.</t>
         </is>
       </c>
       <c r="J74" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K74" s="14" t="inlineStr">
@@ -8026,12 +8030,12 @@
       </c>
       <c r="L74" s="14" t="inlineStr">
         <is>
-          <t>unit tests</t>
+          <t>APR-09</t>
         </is>
       </c>
       <c r="M74" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N74" s="19" t="inlineStr">
@@ -8057,7 +8061,7 @@
     <row r="75">
       <c r="A75" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-12</t>
+          <t>TC-APR-11</t>
         </is>
       </c>
       <c r="B75" s="14" t="inlineStr">
@@ -8072,7 +8076,7 @@
       </c>
       <c r="D75" s="18" t="inlineStr">
         <is>
-          <t>A request sent again shows the rejected one</t>
+          <t>Set a rejected request back to a pending step</t>
         </is>
       </c>
       <c r="E75" s="14" t="inlineStr">
@@ -8082,12 +8086,12 @@
       </c>
       <c r="F75" s="18" t="inlineStr">
         <is>
-          <t>TC-ESS-20 done.</t>
+          <t>A Rejected request.</t>
         </is>
       </c>
       <c r="G75" s="18" t="inlineStr">
         <is>
-          <t>Open the new request.</t>
+          <t>Status = a Pending step -&gt; Save.</t>
         </is>
       </c>
       <c r="H75" s="18" t="inlineStr">
@@ -8097,12 +8101,12 @@
       </c>
       <c r="I75" s="18" t="inlineStr">
         <is>
-          <t>'Sent Again From' shows the rejected request; clicking it opens that request with its rejection reason.</t>
+          <t>Saved; the Rejection Reason is cleared (it no longer applies); the employee is told about the new step.</t>
         </is>
       </c>
       <c r="J75" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K75" s="14" t="inlineStr">
@@ -8112,12 +8116,12 @@
       </c>
       <c r="L75" s="14" t="inlineStr">
         <is>
-          <t>APR-11</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="M75" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N75" s="19" t="inlineStr">
@@ -8143,7 +8147,7 @@
     <row r="76">
       <c r="A76" s="16" t="inlineStr">
         <is>
-          <t>TC-APR-13</t>
+          <t>TC-APR-12</t>
         </is>
       </c>
       <c r="B76" s="14" t="inlineStr">
@@ -8158,7 +8162,7 @@
       </c>
       <c r="D76" s="18" t="inlineStr">
         <is>
-          <t>Amount limits are in SAR</t>
+          <t>A request sent again shows the rejected one</t>
         </is>
       </c>
       <c r="E76" s="14" t="inlineStr">
@@ -8168,42 +8172,42 @@
       </c>
       <c r="F76" s="18" t="inlineStr">
         <is>
-          <t>A Training Request above 10,000 at Pending Manager.</t>
+          <t>TC-ESS-20 done.</t>
         </is>
       </c>
       <c r="G76" s="18" t="inlineStr">
         <is>
-          <t>Status = Approved -&gt; Save.</t>
+          <t>Open the new request.</t>
         </is>
       </c>
       <c r="H76" s="18" t="inlineStr">
         <is>
-          <t>Estimated cost 12,000</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I76" s="18" t="inlineStr">
         <is>
-          <t>Refused with 'Training programs exceeding SAR 10,000 require Department Head approval.' (SAR, not AED).</t>
+          <t>'Sent Again From' shows the rejected request; clicking it opens that request with its rejection reason.</t>
         </is>
       </c>
       <c r="J76" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K76" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L76" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>APR-11</t>
         </is>
       </c>
       <c r="M76" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N76" s="19" t="inlineStr">
@@ -8229,67 +8233,67 @@
     <row r="77">
       <c r="A77" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-01</t>
+          <t>TC-APR-13</t>
         </is>
       </c>
       <c r="B77" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C77" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>HR approvals</t>
         </is>
       </c>
       <c r="D77" s="18" t="inlineStr">
         <is>
-          <t>Employees see only their own requests</t>
+          <t>Amount limits are in SAR</t>
         </is>
       </c>
       <c r="E77" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F77" s="18" t="inlineStr">
         <is>
-          <t>Two employees each sent a request.</t>
+          <t>A Training Request above 10,000 at Pending Manager.</t>
         </is>
       </c>
       <c r="G77" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 opens each request list.</t>
+          <t>Status = Approved -&gt; Save.</t>
         </is>
       </c>
       <c r="H77" s="18" t="inlineStr">
         <is>
+          <t>Estimated cost 12,000</t>
+        </is>
+      </c>
+      <c r="I77" s="18" t="inlineStr">
+        <is>
+          <t>Refused with 'Training programs exceeding SAR 10,000 require Department Head approval.' (SAR, not AED).</t>
+        </is>
+      </c>
+      <c r="J77" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K77" s="14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="L77" s="14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I77" s="18" t="inlineStr">
-        <is>
-          <t>Only their own requests appear.</t>
-        </is>
-      </c>
-      <c r="J77" s="14" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K77" s="14" t="inlineStr">
-        <is>
-          <t>Security</t>
-        </is>
-      </c>
-      <c r="L77" s="14" t="inlineStr">
-        <is>
-          <t>SEC-01</t>
-        </is>
-      </c>
       <c r="M77" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N77" s="19" t="inlineStr">
@@ -8303,19 +8307,19 @@
       <c r="R77" s="19" t="inlineStr"/>
       <c r="S77" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T77" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-02</t>
+          <t>TC-SEC-01</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
@@ -8330,7 +8334,7 @@
       </c>
       <c r="D78" s="18" t="inlineStr">
         <is>
-          <t>Another employee's request URL</t>
+          <t>Employees see only their own requests</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
@@ -8340,22 +8344,22 @@
       </c>
       <c r="F78" s="18" t="inlineStr">
         <is>
-          <t>URL of employee 2's request.</t>
+          <t>Two employees each sent a request.</t>
         </is>
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 opens that URL.</t>
+          <t>Employee 1 opens each request list.</t>
         </is>
       </c>
       <c r="H78" s="18" t="inlineStr">
         <is>
-          <t>Employee 2 request link</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I78" s="18" t="inlineStr">
         <is>
-          <t>Not permitted; none of its details are shown.</t>
+          <t>Only their own requests appear.</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
@@ -8370,7 +8374,7 @@
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>SEC-02</t>
+          <t>SEC-01</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
@@ -8401,7 +8405,7 @@
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-03</t>
+          <t>TC-SEC-02</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
@@ -8416,7 +8420,7 @@
       </c>
       <c r="D79" s="18" t="inlineStr">
         <is>
-          <t>Own Employee record only, read-only</t>
+          <t>Another employee's request URL</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
@@ -8426,28 +8430,27 @@
       </c>
       <c r="F79" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>URL of employee 2's request.</t>
         </is>
       </c>
       <c r="G79" s="18" t="inlineStr">
         <is>
-          <t>1. Open /app/employee.
-2. Try to edit own record.</t>
+          <t>Employee 1 opens that URL.</t>
         </is>
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Employee 2 request link</t>
         </is>
       </c>
       <c r="I79" s="18" t="inlineStr">
         <is>
-          <t>Only own record listed; cannot edit.</t>
+          <t>Not permitted; none of its details are shown.</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K79" s="14" t="inlineStr">
@@ -8457,7 +8460,7 @@
       </c>
       <c r="L79" s="14" t="inlineStr">
         <is>
-          <t>SEC-03/04</t>
+          <t>SEC-02</t>
         </is>
       </c>
       <c r="M79" s="14" t="inlineStr">
@@ -8488,7 +8491,7 @@
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-04</t>
+          <t>TC-SEC-03</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
@@ -8503,7 +8506,7 @@
       </c>
       <c r="D80" s="18" t="inlineStr">
         <is>
-          <t>HR-only processes</t>
+          <t>Own Employee record only, read-only</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
@@ -8518,8 +8521,8 @@
       </c>
       <c r="G80" s="18" t="inlineStr">
         <is>
-          <t>1. Try to create a Contract Renewal request.
-2. Send a Leave Plan, then try to set its status to Approved (or ask a developer to try through the API).</t>
+          <t>1. Open /app/employee.
+2. Try to edit own record.</t>
         </is>
       </c>
       <c r="H80" s="18" t="inlineStr">
@@ -8529,7 +8532,7 @@
       </c>
       <c r="I80" s="18" t="inlineStr">
         <is>
-          <t>Contract Renewal refused ('managed by HR'); the Leave Plan is sent but the employee cannot approve it.</t>
+          <t>Only own record listed; cannot edit.</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
@@ -8544,7 +8547,7 @@
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>SEC-07</t>
+          <t>SEC-03/04</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
@@ -8568,14 +8571,14 @@
       </c>
       <c r="T80" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-05</t>
+          <t>TC-SEC-04</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
@@ -8590,7 +8593,7 @@
       </c>
       <c r="D81" s="18" t="inlineStr">
         <is>
-          <t>Employee cannot open HR pages</t>
+          <t>HR-only processes</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
@@ -8605,7 +8608,8 @@
       </c>
       <c r="G81" s="18" t="inlineStr">
         <is>
-          <t>Open /app/hr-dashboard, /app/hr-academic-presence/faculty and /app/jameah-data-check.</t>
+          <t>1. Try to create a Contract Renewal request.
+2. Send a Leave Plan, then try to set its status to Approved (or ask a developer to try through the API).</t>
         </is>
       </c>
       <c r="H81" s="18" t="inlineStr">
@@ -8615,12 +8619,12 @@
       </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
-          <t>'Not authorized' or 'Not permitted'; no HR data.</t>
+          <t>Contract Renewal refused ('managed by HR'); the Leave Plan is sent but the employee cannot approve it.</t>
         </is>
       </c>
       <c r="J81" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K81" s="14" t="inlineStr">
@@ -8630,7 +8634,7 @@
       </c>
       <c r="L81" s="14" t="inlineStr">
         <is>
-          <t>SEC-09</t>
+          <t>SEC-07</t>
         </is>
       </c>
       <c r="M81" s="14" t="inlineStr">
@@ -8654,14 +8658,14 @@
       </c>
       <c r="T81" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-06</t>
+          <t>TC-SEC-05</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
@@ -8676,12 +8680,12 @@
       </c>
       <c r="D82" s="18" t="inlineStr">
         <is>
-          <t>Login without an Employee record</t>
+          <t>Employee cannot open HR pages</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>User with no Employee record</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F82" s="18" t="inlineStr">
@@ -8691,7 +8695,7 @@
       </c>
       <c r="G82" s="18" t="inlineStr">
         <is>
-          <t>Log in and open the Employee Dashboard.</t>
+          <t>Open /app/hr-dashboard, /app/hr-academic-presence/faculty and /app/jameah-data-check.</t>
         </is>
       </c>
       <c r="H82" s="18" t="inlineStr">
@@ -8701,12 +8705,12 @@
       </c>
       <c r="I82" s="18" t="inlineStr">
         <is>
-          <t>Not permitted / not linked message; cannot send requests.</t>
+          <t>'Not authorized' or 'Not permitted'; no HR data.</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K82" s="14" t="inlineStr">
@@ -8716,7 +8720,7 @@
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>SEC-11</t>
+          <t>SEC-09</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
@@ -8747,7 +8751,7 @@
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-07</t>
+          <t>TC-SEC-06</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
@@ -8762,12 +8766,12 @@
       </c>
       <c r="D83" s="18" t="inlineStr">
         <is>
-          <t>Staff without HR/Employee roles</t>
+          <t>Login without an Employee record</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>Other staff</t>
+          <t>User with no Employee record</t>
         </is>
       </c>
       <c r="F83" s="18" t="inlineStr">
@@ -8777,7 +8781,7 @@
       </c>
       <c r="G83" s="18" t="inlineStr">
         <is>
-          <t>Open the HR and Employee dashboards.</t>
+          <t>Log in and open the Employee Dashboard.</t>
         </is>
       </c>
       <c r="H83" s="18" t="inlineStr">
@@ -8787,7 +8791,7 @@
       </c>
       <c r="I83" s="18" t="inlineStr">
         <is>
-          <t>Both refused.</t>
+          <t>Not permitted / not linked message; cannot send requests.</t>
         </is>
       </c>
       <c r="J83" s="14" t="inlineStr">
@@ -8802,7 +8806,7 @@
       </c>
       <c r="L83" s="14" t="inlineStr">
         <is>
-          <t>SEC-12</t>
+          <t>SEC-11</t>
         </is>
       </c>
       <c r="M83" s="14" t="inlineStr">
@@ -8833,7 +8837,7 @@
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-08</t>
+          <t>TC-SEC-07</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
@@ -8848,37 +8852,37 @@
       </c>
       <c r="D84" s="18" t="inlineStr">
         <is>
-          <t>Private attachments</t>
+          <t>Staff without HR/Employee roles</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Second employee</t>
+          <t>Other staff</t>
         </is>
       </c>
       <c r="F84" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 uploaded an invoice (TC-ESS-08).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G84" s="18" t="inlineStr">
         <is>
-          <t>Employee 2 opens the file link.</t>
+          <t>Open the HR and Employee dashboards.</t>
         </is>
       </c>
       <c r="H84" s="18" t="inlineStr">
         <is>
-          <t>File URL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I84" s="18" t="inlineStr">
         <is>
-          <t>Refused (403/404). HR can open it.</t>
+          <t>Both refused.</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K84" s="14" t="inlineStr">
@@ -8888,7 +8892,7 @@
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>APR-08</t>
+          <t>SEC-12</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
@@ -8919,7 +8923,7 @@
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-09</t>
+          <t>TC-SEC-08</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
@@ -8934,32 +8938,32 @@
       </c>
       <c r="D85" s="18" t="inlineStr">
         <is>
-          <t>Job application cannot grant admin rights</t>
+          <t>Private attachments</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Second employee</t>
         </is>
       </c>
       <c r="F85" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Employee 1 uploaded an invoice (TC-ESS-08).</t>
         </is>
       </c>
       <c r="G85" s="18" t="inlineStr">
         <is>
-          <t>Create a Job Application Link and look at the Role list.</t>
+          <t>Employee 2 opens the file link.</t>
         </is>
       </c>
       <c r="H85" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>File URL</t>
         </is>
       </c>
       <c r="I85" s="18" t="inlineStr">
         <is>
-          <t>Only hireable roles are offered (Employee, Instructor, Academic Advisor...), never System Manager or HR roles.</t>
+          <t>Refused (403/404). HR can open it.</t>
         </is>
       </c>
       <c r="J85" s="14" t="inlineStr">
@@ -8974,7 +8978,7 @@
       </c>
       <c r="L85" s="14" t="inlineStr">
         <is>
-          <t>REC-02</t>
+          <t>APR-08</t>
         </is>
       </c>
       <c r="M85" s="14" t="inlineStr">
@@ -9005,7 +9009,7 @@
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-10</t>
+          <t>TC-SEC-09</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
@@ -9020,22 +9024,22 @@
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>Server methods refuse the wrong role</t>
+          <t>Job application cannot grant admin rights</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F86" s="18" t="inlineStr">
         <is>
-          <t>QA logins loaded (qa_fixtures.py), bench running.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G86" s="18" t="inlineStr">
         <is>
-          <t>python3 tests/checks/api_methods.py</t>
+          <t>Create a Job Application Link and look at the Role list.</t>
         </is>
       </c>
       <c r="H86" s="18" t="inlineStr">
@@ -9045,7 +9049,7 @@
       </c>
       <c r="I86" s="18" t="inlineStr">
         <is>
-          <t>Every method: refused (403) for a visitor except the job form and receipt; HR-only methods refused for employees; no server error (500); no method left out of the check.</t>
+          <t>Only hireable roles are offered (Employee, Instructor, Academic Advisor...), never System Manager or HR roles.</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
@@ -9060,7 +9064,7 @@
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/api_methods.py</t>
+          <t>REC-02</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
@@ -9079,19 +9083,19 @@
       <c r="R86" s="19" t="inlineStr"/>
       <c r="S86" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T86" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-01</t>
+          <t>TC-SEC-10</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
@@ -9101,37 +9105,37 @@
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D87" s="18" t="inlineStr">
         <is>
-          <t>Edit and save an employee who has a login</t>
+          <t>Server methods refuse the wrong role</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
         <is>
-          <t>Employee with a user login.</t>
+          <t>QA logins loaded (qa_fixtures.py), bench running.</t>
         </is>
       </c>
       <c r="G87" s="18" t="inlineStr">
         <is>
-          <t>Change the mobile number; Save.</t>
+          <t>python3 tests/checks/api_methods.py</t>
         </is>
       </c>
       <c r="H87" s="18" t="inlineStr">
         <is>
-          <t>New mobile</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I87" s="18" t="inlineStr">
         <is>
-          <t>Saved with no error (this used to fail with 'Could not find Gender').</t>
+          <t>Every method: refused (403) for a visitor except the job form and receipt; HR-only methods refused for employees; no server error (500); no method left out of the check.</t>
         </is>
       </c>
       <c r="J87" s="14" t="inlineStr">
@@ -9141,12 +9145,12 @@
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L87" s="14" t="inlineStr">
         <is>
-          <t>EMP-01</t>
+          <t>tests/checks/api_methods.py</t>
         </is>
       </c>
       <c r="M87" s="14" t="inlineStr">
@@ -9165,19 +9169,19 @@
       <c r="R87" s="19" t="inlineStr"/>
       <c r="S87" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="T87" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-02</t>
+          <t>TC-EMP-01</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -9192,7 +9196,7 @@
       </c>
       <c r="D88" s="18" t="inlineStr">
         <is>
-          <t>Lookup fields only offer their own list</t>
+          <t>Edit and save an employee who has a login</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
@@ -9202,37 +9206,37 @@
       </c>
       <c r="F88" s="18" t="inlineStr">
         <is>
-          <t>Employee form open.</t>
+          <t>Employee with a user login.</t>
         </is>
       </c>
       <c r="G88" s="18" t="inlineStr">
         <is>
-          <t>Open Gender, Nationality, Identity Type and Religion drop-downs.</t>
+          <t>Change the mobile number; Save.</t>
         </is>
       </c>
       <c r="H88" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>New mobile</t>
         </is>
       </c>
       <c r="I88" s="18" t="inlineStr">
         <is>
-          <t>Each shows only its Ministry list (e.g. Gender: Male, Female).</t>
+          <t>Saved with no error (this used to fail with 'Could not find Gender').</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>EMP-02/03</t>
+          <t>EMP-01</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
@@ -9263,7 +9267,7 @@
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-03</t>
+          <t>TC-EMP-02</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
@@ -9278,7 +9282,7 @@
       </c>
       <c r="D89" s="18" t="inlineStr">
         <is>
-          <t>Invalid national ID</t>
+          <t>Lookup fields only offer their own list</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
@@ -9288,22 +9292,22 @@
       </c>
       <c r="F89" s="18" t="inlineStr">
         <is>
+          <t>Employee form open.</t>
+        </is>
+      </c>
+      <c r="G89" s="18" t="inlineStr">
+        <is>
+          <t>Open Gender, Nationality, Identity Type and Religion drop-downs.</t>
+        </is>
+      </c>
+      <c r="H89" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G89" s="18" t="inlineStr">
-        <is>
-          <t>Set Identity Number to 12345 and Save.</t>
-        </is>
-      </c>
-      <c r="H89" s="18" t="inlineStr">
-        <is>
-          <t>12345</t>
-        </is>
-      </c>
       <c r="I89" s="18" t="inlineStr">
         <is>
-          <t>Refused: a National ID has exactly 10 digits.</t>
+          <t>Each shows only its Ministry list (e.g. Gender: Male, Female).</t>
         </is>
       </c>
       <c r="J89" s="14" t="inlineStr">
@@ -9313,12 +9317,12 @@
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L89" s="14" t="inlineStr">
         <is>
-          <t>EMP-05</t>
+          <t>EMP-02/03</t>
         </is>
       </c>
       <c r="M89" s="14" t="inlineStr">
@@ -9349,7 +9353,7 @@
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-04</t>
+          <t>TC-EMP-03</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
@@ -9364,7 +9368,7 @@
       </c>
       <c r="D90" s="18" t="inlineStr">
         <is>
-          <t>Duplicate identity number</t>
+          <t>Invalid national ID</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
@@ -9374,22 +9378,22 @@
       </c>
       <c r="F90" s="18" t="inlineStr">
         <is>
-          <t>Another employee's ID number.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G90" s="18" t="inlineStr">
         <is>
-          <t>Enter it on a different employee; Save.</t>
+          <t>Set Identity Number to 12345 and Save.</t>
         </is>
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>Existing ID</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="I90" s="18" t="inlineStr">
         <is>
-          <t>Refused: already registered to &lt;employee&gt;.</t>
+          <t>Refused: a National ID has exactly 10 digits.</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
@@ -9404,7 +9408,7 @@
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>EMP-06</t>
+          <t>EMP-05</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
@@ -9435,7 +9439,7 @@
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-05</t>
+          <t>TC-EMP-04</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
@@ -9450,7 +9454,7 @@
       </c>
       <c r="D91" s="18" t="inlineStr">
         <is>
-          <t>National ID for a non-Saudi</t>
+          <t>Duplicate identity number</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
@@ -9460,27 +9464,27 @@
       </c>
       <c r="F91" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Another employee's ID number.</t>
         </is>
       </c>
       <c r="G91" s="18" t="inlineStr">
         <is>
-          <t>Nationality not Saudi, Identity Type National ID; Save.</t>
+          <t>Enter it on a different employee; Save.</t>
         </is>
       </c>
       <c r="H91" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Existing ID</t>
         </is>
       </c>
       <c r="I91" s="18" t="inlineStr">
         <is>
-          <t>Refused: National ID is only for Saudis.</t>
+          <t>Refused: already registered to &lt;employee&gt;.</t>
         </is>
       </c>
       <c r="J91" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K91" s="14" t="inlineStr">
@@ -9490,12 +9494,12 @@
       </c>
       <c r="L91" s="14" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>EMP-06</t>
         </is>
       </c>
       <c r="M91" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N91" s="19" t="inlineStr">
@@ -9521,7 +9525,7 @@
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-09</t>
+          <t>TC-EMP-05</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
@@ -9536,7 +9540,7 @@
       </c>
       <c r="D92" s="18" t="inlineStr">
         <is>
-          <t>Non-Saudi employee with an Iqama</t>
+          <t>National ID for a non-Saudi</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
@@ -9546,44 +9550,42 @@
       </c>
       <c r="F92" s="18" t="inlineStr">
         <is>
-          <t>An employee whose Nationality is not Saudi and Identity Type is Iqama.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G92" s="18" t="inlineStr">
         <is>
-          <t>1. Open the employee.
-2. Look at Identity Number and ID Number in Country of Origin.
-3. Change any field and Save.</t>
+          <t>Nationality not Saudi, Identity Type National ID; Save.</t>
         </is>
       </c>
       <c r="H92" s="18" t="inlineStr">
         <is>
-          <t>Iqama 2XXXXXXXXX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I92" s="18" t="inlineStr">
         <is>
-          <t>The record opens without 'Not Saved'. Identity Number still shows the Iqama and is mandatory; the home-country ID is optional. Save works.</t>
+          <t>Refused: National ID is only for Saudis.</t>
         </is>
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>EMP-08</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N92" s="19" t="inlineStr">
@@ -9609,7 +9611,7 @@
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-06</t>
+          <t>TC-EMP-09</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
@@ -9624,7 +9626,7 @@
       </c>
       <c r="D93" s="18" t="inlineStr">
         <is>
-          <t>Qualification 'Appreciation' list</t>
+          <t>Non-Saudi employee with an Iqama</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
@@ -9634,27 +9636,29 @@
       </c>
       <c r="F93" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>An employee whose Nationality is not Saudi and Identity Type is Iqama.</t>
         </is>
       </c>
       <c r="G93" s="18" t="inlineStr">
         <is>
-          <t>Add a qualification row; open Appreciation.</t>
+          <t>1. Open the employee.
+2. Look at Identity Number and ID Number in Country of Origin.
+3. Change any field and Save.</t>
         </is>
       </c>
       <c r="H93" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Iqama 2XXXXXXXXX</t>
         </is>
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
-          <t>Grades are offered (Excellent, Very good, Good...), not GPA systems.</t>
+          <t>The record opens without 'Not Saved'. Identity Number still shows the Iqama and is mandatory; the home-country ID is optional. Save works.</t>
         </is>
       </c>
       <c r="J93" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K93" s="14" t="inlineStr">
@@ -9664,7 +9668,7 @@
       </c>
       <c r="L93" s="14" t="inlineStr">
         <is>
-          <t>REC-05</t>
+          <t>EMP-08</t>
         </is>
       </c>
       <c r="M93" s="14" t="inlineStr">
@@ -9695,7 +9699,7 @@
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-07</t>
+          <t>TC-EMP-06</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
@@ -9710,7 +9714,7 @@
       </c>
       <c r="D94" s="18" t="inlineStr">
         <is>
-          <t>Ministry (Jameah) Data preview</t>
+          <t>Qualification 'Appreciation' list</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
@@ -9720,12 +9724,12 @@
       </c>
       <c r="F94" s="18" t="inlineStr">
         <is>
-          <t>An employee of Al Riyada College.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G94" s="18" t="inlineStr">
         <is>
-          <t>Employee form -&gt; View -&gt; Ministry (Jameah) Data.</t>
+          <t>Add a qualification row; open Appreciation.</t>
         </is>
       </c>
       <c r="H94" s="18" t="inlineStr">
@@ -9735,22 +9739,22 @@
       </c>
       <c r="I94" s="18" t="inlineStr">
         <is>
-          <t>Pop-up with the 5 Ministry sections; lookup columns show codes (e.g. Nationality 101).</t>
+          <t>Grades are offered (Excellent, Very good, Good...), not GPA systems.</t>
         </is>
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>EMP-07</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
@@ -9781,7 +9785,7 @@
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-08</t>
+          <t>TC-EMP-07</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
@@ -9796,7 +9800,7 @@
       </c>
       <c r="D95" s="18" t="inlineStr">
         <is>
-          <t>Teaching staff are not sent as Employees</t>
+          <t>Ministry (Jameah) Data preview</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
@@ -9806,12 +9810,12 @@
       </c>
       <c r="F95" s="18" t="inlineStr">
         <is>
-          <t>An employee linked to an Instructor.</t>
+          <t>An employee of Al Riyada College.</t>
         </is>
       </c>
       <c r="G95" s="18" t="inlineStr">
         <is>
-          <t>Open the Ministry (Jameah) Data preview.</t>
+          <t>Employee form -&gt; View -&gt; Ministry (Jameah) Data.</t>
         </is>
       </c>
       <c r="H95" s="18" t="inlineStr">
@@ -9821,7 +9825,7 @@
       </c>
       <c r="I95" s="18" t="inlineStr">
         <is>
-          <t>Says the person is sent as Faculty, not as an Employee.</t>
+          <t>Pop-up with the 5 Ministry sections; lookup columns show codes (e.g. Nationality 101).</t>
         </is>
       </c>
       <c r="J95" s="14" t="inlineStr">
@@ -9836,7 +9840,7 @@
       </c>
       <c r="L95" s="14" t="inlineStr">
         <is>
-          <t>REC-07</t>
+          <t>EMP-07</t>
         </is>
       </c>
       <c r="M95" s="14" t="inlineStr">
@@ -9867,7 +9871,7 @@
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-10</t>
+          <t>TC-EMP-08</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
@@ -9882,7 +9886,7 @@
       </c>
       <c r="D96" s="18" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Teaching staff are not sent as Employees</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -9892,14 +9896,12 @@
       </c>
       <c r="F96" s="18" t="inlineStr">
         <is>
-          <t>Some employees with empty Ministry fields.</t>
+          <t>An employee linked to an Instructor.</t>
         </is>
       </c>
       <c r="G96" s="18" t="inlineStr">
         <is>
-          <t>1. HR Portal menu &gt; Ministry (Jameah) &gt; Employees Missing Ministry Data.
-2. Tick 'Show complete employees too'.
-3. Filter by a department.</t>
+          <t>Open the Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="H96" s="18" t="inlineStr">
@@ -9909,12 +9911,12 @@
       </c>
       <c r="I96" s="18" t="inlineStr">
         <is>
-          <t>Each employee with gaps is listed with the number of missing values and their names as on the Employee form (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). The tick also lists complete employees; the filter works.</t>
+          <t>Says the person is sent as Faculty, not as an Employee.</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K96" s="14" t="inlineStr">
@@ -9924,7 +9926,7 @@
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>RPT-01</t>
+          <t>REC-07</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
@@ -9955,7 +9957,7 @@
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-11</t>
+          <t>TC-EMP-10</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
@@ -9970,7 +9972,7 @@
       </c>
       <c r="D97" s="18" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff: download, check, import</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
@@ -9980,25 +9982,24 @@
       </c>
       <c r="F97" s="18" t="inlineStr">
         <is>
-          <t>HR Manager account.</t>
+          <t>Some employees with empty Ministry fields.</t>
         </is>
       </c>
       <c r="G97" s="18" t="inlineStr">
         <is>
-          <t>1. In the report: Download Data Sheet.
-2. Fill one red cell for an employee; type 31-31-2020 as another employee's date of birth.
-3. Check / Import Data Sheet &gt; attach the file &gt; Check.
-4. Fix the date and click Import.</t>
+          <t>1. HR Portal menu &gt; Ministry (Jameah) &gt; Employees Missing Ministry Data.
+2. Tick 'Show complete employees too'.
+3. Filter by a department.</t>
         </is>
       </c>
       <c r="H97" s="18" t="inlineStr">
         <is>
-          <t>Edited .xlsx</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
-          <t>The sheet lists the non-teaching employees, red = Ministry-required and empty. Check reports the wrong date and saves nothing. Import updates only the changed cells; the result sheet gives each row's status.</t>
+          <t>Each employee with gaps is listed with the number of missing values and their names as on the Employee form (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). The tick also lists complete employees; the filter works.</t>
         </is>
       </c>
       <c r="J97" s="14" t="inlineStr">
@@ -10013,12 +10014,12 @@
       </c>
       <c r="L97" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>RPT-01</t>
         </is>
       </c>
       <c r="M97" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N97" s="19" t="inlineStr">
@@ -10044,7 +10045,7 @@
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-12</t>
+          <t>TC-EMP-11</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
@@ -10059,52 +10060,55 @@
       </c>
       <c r="D98" s="18" t="inlineStr">
         <is>
-          <t>Only an HR Manager can import the data sheet</t>
+          <t>Data sheet for non-academic staff: download, check, import</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
         <is>
-          <t>HR User</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F98" s="18" t="inlineStr">
         <is>
-          <t>HR User account.</t>
+          <t>HR Manager account.</t>
         </is>
       </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t>Open the Employees Missing Ministry Data report.</t>
+          <t>1. In the report: Download Data Sheet.
+2. Fill one red cell for an employee; type 31-31-2020 as another employee's date of birth.
+3. Check / Import Data Sheet &gt; attach the file &gt; Check.
+4. Fix the date and click Import.</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Edited .xlsx</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
         <is>
-          <t>The report opens; there are no Download Data Sheet / Check / Import buttons.</t>
+          <t>The sheet lists the non-teaching employees, red = Ministry-required and empty. Check reports the wrong date and saves nothing. Import updates only the changed cells; the result sheet gives each row's status.</t>
         </is>
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>RPT-02</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N98" s="19" t="inlineStr">
@@ -10130,12 +10134,12 @@
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-13</t>
+          <t>TC-EMP-12</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Round 1</t>
         </is>
       </c>
       <c r="C99" s="14" t="inlineStr">
@@ -10145,24 +10149,22 @@
       </c>
       <c r="D99" s="18" t="inlineStr">
         <is>
-          <t>Link an Employee on the Instructor form</t>
+          <t>Only an HR Manager can import the data sheet</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR User</t>
         </is>
       </c>
       <c r="F99" s="18" t="inlineStr">
         <is>
-          <t>A login that can edit Instructors and see Employees; an Instructor without an Employee and that person's Employee record.</t>
+          <t>HR User account.</t>
         </is>
       </c>
       <c r="G99" s="18" t="inlineStr">
         <is>
-          <t>1. Open the Instructor.
-2. Pick the Employee.
-3. Save.</t>
+          <t>Open the Employees Missing Ministry Data report.</t>
         </is>
       </c>
       <c r="H99" s="18" t="inlineStr">
@@ -10172,22 +10174,22 @@
       </c>
       <c r="I99" s="18" t="inlineStr">
         <is>
-          <t>Department fills in when it is in the academic list; Gender fills in (or, for a login that cannot open the Gender list, on save). The Instructor saves with Gender set. Before the fix: 'Could not find Gender: Gender::1'.</t>
+          <t>The report opens; there are no Download Data Sheet / Check / Import buttons.</t>
         </is>
       </c>
       <c r="J99" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L99" s="14" t="inlineStr">
         <is>
-          <t>REC-11</t>
+          <t>RPT-02</t>
         </is>
       </c>
       <c r="M99" s="14" t="inlineStr">
@@ -10206,19 +10208,19 @@
       <c r="R99" s="19" t="inlineStr"/>
       <c r="S99" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T99" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-14</t>
+          <t>TC-EMP-13</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
@@ -10233,7 +10235,7 @@
       </c>
       <c r="D100" s="18" t="inlineStr">
         <is>
-          <t>Link an Employee on the Academic Advisor form</t>
+          <t>Link an Employee on the Instructor form</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
@@ -10243,12 +10245,12 @@
       </c>
       <c r="F100" s="18" t="inlineStr">
         <is>
-          <t>As TC-EMP-13, for an Academic Advisor.</t>
+          <t>A login that can edit Instructors and see Employees; an Instructor without an Employee and that person's Employee record.</t>
         </is>
       </c>
       <c r="G100" s="18" t="inlineStr">
         <is>
-          <t>1. Open the Academic Advisor.
+          <t>1. Open the Instructor.
 2. Pick the Employee.
 3. Save.</t>
         </is>
@@ -10260,12 +10262,12 @@
       </c>
       <c r="I100" s="18" t="inlineStr">
         <is>
-          <t>The record saves with Gender set from the Employee.</t>
+          <t>Department fills in when it is in the academic list; Gender fills in (or, for a login that cannot open the Gender list, on save). The Instructor saves with Gender set. Before the fix: 'Could not find Gender: Gender::1'.</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K100" s="14" t="inlineStr">
@@ -10275,12 +10277,12 @@
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>unit tests</t>
+          <t>REC-11</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N100" s="19" t="inlineStr">
@@ -10306,47 +10308,49 @@
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>TC-LIC-01</t>
+          <t>TC-EMP-14</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
         <is>
-          <t>Medical licences</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D101" s="18" t="inlineStr">
         <is>
-          <t>HR creates a licence</t>
+          <t>Link an Employee on the Academic Advisor form</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F101" s="18" t="inlineStr">
         <is>
+          <t>As TC-EMP-13, for an Academic Advisor.</t>
+        </is>
+      </c>
+      <c r="G101" s="18" t="inlineStr">
+        <is>
+          <t>1. Open the Academic Advisor.
+2. Pick the Employee.
+3. Save.</t>
+        </is>
+      </c>
+      <c r="H101" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G101" s="18" t="inlineStr">
-        <is>
-          <t>New Employee Medical License: employee, type, number, expiry; Save.</t>
-        </is>
-      </c>
-      <c r="H101" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I101" s="18" t="inlineStr">
         <is>
-          <t>Saved.</t>
+          <t>The record saves with Gender set from the Employee.</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
@@ -10356,17 +10360,17 @@
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L101" s="14" t="inlineStr">
         <is>
-          <t>LIC-01</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="M101" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N101" s="19" t="inlineStr">
@@ -10380,19 +10384,19 @@
       <c r="R101" s="19" t="inlineStr"/>
       <c r="S101" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T101" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="16" t="inlineStr">
         <is>
-          <t>TC-LIC-02</t>
+          <t>TC-LIC-01</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
@@ -10407,22 +10411,22 @@
       </c>
       <c r="D102" s="18" t="inlineStr">
         <is>
-          <t>Employees see only their own licence</t>
+          <t>HR creates a licence</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F102" s="18" t="inlineStr">
         <is>
-          <t>Licences for two employees.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G102" s="18" t="inlineStr">
         <is>
-          <t>Each employee opens the licence list.</t>
+          <t>New Employee Medical License: employee, type, number, expiry; Save.</t>
         </is>
       </c>
       <c r="H102" s="18" t="inlineStr">
@@ -10432,22 +10436,22 @@
       </c>
       <c r="I102" s="18" t="inlineStr">
         <is>
-          <t>Only their own licence.</t>
+          <t>Saved.</t>
         </is>
       </c>
       <c r="J102" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>LIC-02</t>
+          <t>LIC-01</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
@@ -10478,7 +10482,7 @@
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-01</t>
+          <t>TC-LIC-02</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -10488,40 +10492,37 @@
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Medical licences</t>
         </is>
       </c>
       <c r="D103" s="18" t="inlineStr">
         <is>
-          <t>Create and generate an application link</t>
+          <t>Employees see only their own licence</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F103" s="18" t="inlineStr">
         <is>
+          <t>Licences for two employees.</t>
+        </is>
+      </c>
+      <c r="G103" s="18" t="inlineStr">
+        <is>
+          <t>Each employee opens the licence list.</t>
+        </is>
+      </c>
+      <c r="H103" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G103" s="18" t="inlineStr">
-        <is>
-          <t>1. New Job Application Link.
-2. Category Academic Staff, Role Instructor, valid from/until.
-3. Save.
-4. Generate Link.</t>
-        </is>
-      </c>
-      <c r="H103" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I103" s="18" t="inlineStr">
         <is>
-          <t>A link is shown and can be copied.</t>
+          <t>Only their own licence.</t>
         </is>
       </c>
       <c r="J103" s="14" t="inlineStr">
@@ -10531,12 +10532,12 @@
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L103" s="14" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>LIC-02</t>
         </is>
       </c>
       <c r="M103" s="14" t="inlineStr">
@@ -10567,7 +10568,7 @@
     <row r="104">
       <c r="A104" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-02</t>
+          <t>TC-REC-01</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
@@ -10582,12 +10583,12 @@
       </c>
       <c r="D104" s="18" t="inlineStr">
         <is>
-          <t>Invalid or expired link</t>
+          <t>Create and generate an application link</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F104" s="18" t="inlineStr">
@@ -10597,7 +10598,10 @@
       </c>
       <c r="G104" s="18" t="inlineStr">
         <is>
-          <t>Open /job-application/abc123 and an expired link.</t>
+          <t>1. New Job Application Link.
+2. Category Academic Staff, Role Instructor, valid from/until.
+3. Save.
+4. Generate Link.</t>
         </is>
       </c>
       <c r="H104" s="18" t="inlineStr">
@@ -10607,22 +10611,22 @@
       </c>
       <c r="I104" s="18" t="inlineStr">
         <is>
-          <t>'Link is invalid / not active' message; no form.</t>
+          <t>A link is shown and can be copied.</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K104" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>REC-01</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
@@ -10653,7 +10657,7 @@
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-03</t>
+          <t>TC-REC-02</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -10668,7 +10672,7 @@
       </c>
       <c r="D105" s="18" t="inlineStr">
         <is>
-          <t>Required fields on the public form</t>
+          <t>Invalid or expired link</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
@@ -10678,12 +10682,12 @@
       </c>
       <c r="F105" s="18" t="inlineStr">
         <is>
-          <t>Valid link.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G105" s="18" t="inlineStr">
         <is>
-          <t>Click Submit with the form empty.</t>
+          <t>Open /job-application/abc123 and an expired link.</t>
         </is>
       </c>
       <c r="H105" s="18" t="inlineStr">
@@ -10693,7 +10697,7 @@
       </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
-          <t>Browser highlights the required fields; nothing is sent.</t>
+          <t>'Link is invalid / not active' message; no form.</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
@@ -10708,12 +10712,12 @@
       </c>
       <c r="L105" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-01</t>
         </is>
       </c>
       <c r="M105" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N105" s="19" t="inlineStr">
@@ -10739,7 +10743,7 @@
     <row r="106">
       <c r="A106" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-04</t>
+          <t>TC-REC-03</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
@@ -10754,7 +10758,7 @@
       </c>
       <c r="D106" s="18" t="inlineStr">
         <is>
-          <t>Applicant submits the full form</t>
+          <t>Required fields on the public form</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
@@ -10769,37 +10773,37 @@
       </c>
       <c r="G106" s="18" t="inlineStr">
         <is>
-          <t>Fill every section (names in Arabic and English, ID, qualifications, experience) and Submit.</t>
+          <t>Click Submit with the form empty.</t>
         </is>
       </c>
       <c r="H106" s="18" t="inlineStr">
         <is>
-          <t>Saudi national ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I106" s="18" t="inlineStr">
         <is>
-          <t>'Thank you' with a reference number APP-....</t>
+          <t>Browser highlights the required fields; nothing is sent.</t>
         </is>
       </c>
       <c r="J106" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K106" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>REC-03..05</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N106" s="19" t="inlineStr">
@@ -10825,7 +10829,7 @@
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-05</t>
+          <t>TC-REC-04</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
@@ -10840,35 +10844,32 @@
       </c>
       <c r="D107" s="18" t="inlineStr">
         <is>
-          <t>Accept and create an Instructor</t>
+          <t>Applicant submits the full form</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="F107" s="18" t="inlineStr">
         <is>
-          <t>TC-REC-04 for an Instructor link.</t>
+          <t>Valid link.</t>
         </is>
       </c>
       <c r="G107" s="18" t="inlineStr">
         <is>
-          <t>1. Open the applicant.
-2. Accept.
-3. Create Employee: Company Email = official college address, department.
-4. Confirm.</t>
+          <t>Fill every section (names in Arabic and English, ID, qualifications, experience) and Submit.</t>
         </is>
       </c>
       <c r="H107" s="18" t="inlineStr">
         <is>
-          <t>name.surname@alriyada.edu.sa</t>
+          <t>Saudi national ID</t>
         </is>
       </c>
       <c r="I107" s="18" t="inlineStr">
         <is>
-          <t>Message lists Employee and Instructor created; the new login has Employee + Instructor roles.</t>
+          <t>'Thank you' with a reference number APP-....</t>
         </is>
       </c>
       <c r="J107" s="14" t="inlineStr">
@@ -10883,7 +10884,7 @@
       </c>
       <c r="L107" s="14" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>REC-03..05</t>
         </is>
       </c>
       <c r="M107" s="14" t="inlineStr">
@@ -10914,7 +10915,7 @@
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-06</t>
+          <t>TC-REC-05</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
@@ -10929,7 +10930,7 @@
       </c>
       <c r="D108" s="18" t="inlineStr">
         <is>
-          <t>Hire an Academic Advisor</t>
+          <t>Accept and create an Instructor</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -10939,37 +10940,40 @@
       </c>
       <c r="F108" s="18" t="inlineStr">
         <is>
-          <t>Applicant for an Academic Advisor link with a phone like 05XXXXXXXX.</t>
+          <t>TC-REC-04 for an Instructor link.</t>
         </is>
       </c>
       <c r="G108" s="18" t="inlineStr">
         <is>
-          <t>Accept -&gt; Create Employee with a @alriyada.edu.sa Company Email.</t>
+          <t>1. Open the applicant.
+2. Accept.
+3. Create Employee: Company Email = official college address, department.
+4. Confirm.</t>
         </is>
       </c>
       <c r="H108" s="18" t="inlineStr">
         <is>
-          <t>Local phone number</t>
+          <t>name.surname@alriyada.edu.sa</t>
         </is>
       </c>
       <c r="I108" s="18" t="inlineStr">
         <is>
-          <t>Employee, Academic Advisor and Instructor records created; no 'record not created' warning.</t>
+          <t>Message lists Employee and Instructor created; the new login has Employee + Instructor roles.</t>
         </is>
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K108" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>REC-04</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
@@ -11000,7 +11004,7 @@
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-07</t>
+          <t>TC-REC-06</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
@@ -11015,7 +11019,7 @@
       </c>
       <c r="D109" s="18" t="inlineStr">
         <is>
-          <t>Hire non-academic staff</t>
+          <t>Hire an Academic Advisor</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
@@ -11025,22 +11029,22 @@
       </c>
       <c r="F109" s="18" t="inlineStr">
         <is>
-          <t>Applicant for a Non-Academic link.</t>
+          <t>Applicant for an Academic Advisor link with a phone like 05XXXXXXXX.</t>
         </is>
       </c>
       <c r="G109" s="18" t="inlineStr">
         <is>
-          <t>Accept -&gt; Create Employee.</t>
+          <t>Accept -&gt; Create Employee with a @alriyada.edu.sa Company Email.</t>
         </is>
       </c>
       <c r="H109" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Local phone number</t>
         </is>
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
-          <t>Employee created; work phone and extension kept on the Employee.</t>
+          <t>Employee, Academic Advisor and Instructor records created; no 'record not created' warning.</t>
         </is>
       </c>
       <c r="J109" s="14" t="inlineStr">
@@ -11050,12 +11054,12 @@
       </c>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L109" s="14" t="inlineStr">
         <is>
-          <t>REC-05/06</t>
+          <t>REC-04</t>
         </is>
       </c>
       <c r="M109" s="14" t="inlineStr">
@@ -11086,7 +11090,7 @@
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-08</t>
+          <t>TC-REC-07</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
@@ -11101,7 +11105,7 @@
       </c>
       <c r="D110" s="18" t="inlineStr">
         <is>
-          <t>Reject an applicant</t>
+          <t>Hire non-academic staff</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
@@ -11111,12 +11115,12 @@
       </c>
       <c r="F110" s="18" t="inlineStr">
         <is>
-          <t>A Pending applicant.</t>
+          <t>Applicant for a Non-Academic link.</t>
         </is>
       </c>
       <c r="G110" s="18" t="inlineStr">
         <is>
-          <t>Click Reject.</t>
+          <t>Accept -&gt; Create Employee.</t>
         </is>
       </c>
       <c r="H110" s="18" t="inlineStr">
@@ -11126,12 +11130,12 @@
       </c>
       <c r="I110" s="18" t="inlineStr">
         <is>
-          <t>Status Rejected; Create Employee not offered.</t>
+          <t>Employee created; work phone and extension kept on the Employee.</t>
         </is>
       </c>
       <c r="J110" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K110" s="14" t="inlineStr">
@@ -11141,12 +11145,12 @@
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-05/06</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N110" s="19" t="inlineStr">
@@ -11172,7 +11176,7 @@
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-09</t>
+          <t>TC-REC-08</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
@@ -11187,32 +11191,32 @@
       </c>
       <c r="D111" s="18" t="inlineStr">
         <is>
-          <t>Duplicate applicant identity</t>
+          <t>Reject an applicant</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F111" s="18" t="inlineStr">
         <is>
-          <t>An employee already has the ID number.</t>
+          <t>A Pending applicant.</t>
         </is>
       </c>
       <c r="G111" s="18" t="inlineStr">
         <is>
-          <t>Submit a new application with that ID; HR tries to create the Employee.</t>
+          <t>Click Reject.</t>
         </is>
       </c>
       <c r="H111" s="18" t="inlineStr">
         <is>
-          <t>Existing ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I111" s="18" t="inlineStr">
         <is>
-          <t>Creating the Employee is refused as a duplicate.</t>
+          <t>Status Rejected; Create Employee not offered.</t>
         </is>
       </c>
       <c r="J111" s="14" t="inlineStr">
@@ -11222,7 +11226,7 @@
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L111" s="14" t="inlineStr">
@@ -11258,7 +11262,7 @@
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-11</t>
+          <t>TC-REC-09</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
@@ -11273,53 +11277,52 @@
       </c>
       <c r="D112" s="18" t="inlineStr">
         <is>
-          <t>A new hire's record opens clean</t>
+          <t>Duplicate applicant identity</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
         <is>
-          <t>An applicant who answered 'Has Special Needs = No' but also picked a type (and, if Saudi, typed a home-country ID).</t>
+          <t>An employee already has the ID number.</t>
         </is>
       </c>
       <c r="G112" s="18" t="inlineStr">
         <is>
-          <t>1. Hire them (Create Employee).
-2. Open the new Employee record.</t>
+          <t>Submit a new application with that ID; HR tries to create the Employee.</t>
         </is>
       </c>
       <c r="H112" s="18" t="inlineStr">
         <is>
+          <t>Existing ID</t>
+        </is>
+      </c>
+      <c r="I112" s="18" t="inlineStr">
+        <is>
+          <t>Creating the Employee is refused as a duplicate.</t>
+        </is>
+      </c>
+      <c r="J112" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K112" s="14" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L112" s="14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I112" s="18" t="inlineStr">
-        <is>
-          <t>The record shows its status (not 'Not Saved'); special-needs type and home-country ID are empty.</t>
-        </is>
-      </c>
-      <c r="J112" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K112" s="14" t="inlineStr">
-        <is>
-          <t>Regression</t>
-        </is>
-      </c>
-      <c r="L112" s="14" t="inlineStr">
-        <is>
-          <t>REC-09</t>
-        </is>
-      </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N112" s="19" t="inlineStr">
@@ -11345,7 +11348,7 @@
     <row r="113">
       <c r="A113" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-12</t>
+          <t>TC-REC-11</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
@@ -11360,7 +11363,7 @@
       </c>
       <c r="D113" s="18" t="inlineStr">
         <is>
-          <t>Create Employee asks for what the Employee form requires</t>
+          <t>A new hire's record opens clean</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
@@ -11370,15 +11373,13 @@
       </c>
       <c r="F113" s="18" t="inlineStr">
         <is>
-          <t>An Accepted applicant.</t>
+          <t>An applicant who answered 'Has Special Needs = No' but also picked a type (and, if Saudi, typed a home-country ID).</t>
         </is>
       </c>
       <c r="G113" s="18" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Look at the Employee Record section of the dialog.
-3. Fill it and confirm.
-4. Open the new Employee, change any field, Save.</t>
+          <t>1. Hire them (Create Employee).
+2. Open the new Employee record.</t>
         </is>
       </c>
       <c r="H113" s="18" t="inlineStr">
@@ -11388,7 +11389,7 @@
       </c>
       <c r="I113" s="18" t="inlineStr">
         <is>
-          <t>The dialog asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application), and Gender / Date of Birth only when the application left them empty. The Employee saves with no 'Missing Fields'.</t>
+          <t>The record shows its status (not 'Not Saved'); special-needs type and home-country ID are empty.</t>
         </is>
       </c>
       <c r="J113" s="14" t="inlineStr">
@@ -11403,7 +11404,7 @@
       </c>
       <c r="L113" s="14" t="inlineStr">
         <is>
-          <t>REC-10</t>
+          <t>REC-09</t>
         </is>
       </c>
       <c r="M113" s="14" t="inlineStr">
@@ -11434,7 +11435,7 @@
     <row r="114">
       <c r="A114" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-13</t>
+          <t>TC-REC-12</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -11449,55 +11450,55 @@
       </c>
       <c r="D114" s="18" t="inlineStr">
         <is>
-          <t>Phone number with country code</t>
+          <t>Create Employee asks for what the Employee form requires</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F114" s="18" t="inlineStr">
         <is>
-          <t>A valid application link.</t>
+          <t>An Accepted applicant.</t>
         </is>
       </c>
       <c r="G114" s="18" t="inlineStr">
         <is>
-          <t>1. Open the link.
-2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
-3. Send.
-4. Correct it and send again.</t>
+          <t>1. Create Employee.
+2. Look at the Employee Record section of the dialog.
+3. Fill it and confirm.
+4. Open the new Employee, change any field, Save.</t>
         </is>
       </c>
       <c r="H114" s="18" t="inlineStr">
         <is>
-          <t>123, then a full mobile number</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I114" s="18" t="inlineStr">
         <is>
-          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
+          <t>The dialog asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application), and Gender / Date of Birth only when the application left them empty. The Employee saves with no 'Missing Fields'.</t>
         </is>
       </c>
       <c r="J114" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K114" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-10</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N114" s="19" t="inlineStr">
@@ -11511,19 +11512,19 @@
       <c r="R114" s="19" t="inlineStr"/>
       <c r="S114" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T114" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-14</t>
+          <t>TC-REC-13</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
@@ -11538,7 +11539,7 @@
       </c>
       <c r="D115" s="18" t="inlineStr">
         <is>
-          <t>Receipt after sending the application</t>
+          <t>Phone number with country code</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
@@ -11548,22 +11549,25 @@
       </c>
       <c r="F115" s="18" t="inlineStr">
         <is>
-          <t>TC-REC-13 done (application sent).</t>
+          <t>A valid application link.</t>
         </is>
       </c>
       <c r="G115" s="18" t="inlineStr">
         <is>
-          <t>On the confirmation screen click the receipt download button.</t>
+          <t>1. Open the link.
+2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
+3. Send.
+4. Correct it and send again.</t>
         </is>
       </c>
       <c r="H115" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>123, then a full mobile number</t>
         </is>
       </c>
       <c r="I115" s="18" t="inlineStr">
         <is>
-          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
+          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
         </is>
       </c>
       <c r="J115" s="14" t="inlineStr">
@@ -11573,7 +11577,7 @@
       </c>
       <c r="K115" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L115" s="14" t="inlineStr">
@@ -11609,7 +11613,7 @@
     <row r="116">
       <c r="A116" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-10</t>
+          <t>TC-REC-14</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
@@ -11624,55 +11628,52 @@
       </c>
       <c r="D116" s="18" t="inlineStr">
         <is>
-          <t>Academic hire needs the college e-mail</t>
+          <t>Receipt after sending the application</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="F116" s="18" t="inlineStr">
         <is>
-          <t>An Accepted applicant from an Instructor link.</t>
+          <t>TC-REC-13 done (application sent).</t>
         </is>
       </c>
       <c r="G116" s="18" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Leave Company Email empty (or a gmail address).
-3. Confirm.
-4. Then enter a @alriyada.edu.sa address and confirm again.</t>
+          <t>On the confirmation screen click the receipt download button.</t>
         </is>
       </c>
       <c r="H116" s="18" t="inlineStr">
         <is>
-          <t>Personal e-mail, then college e-mail</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I116" s="18" t="inlineStr">
         <is>
-          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
+          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
         </is>
       </c>
       <c r="J116" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K116" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L116" s="14" t="inlineStr">
         <is>
-          <t>REC-08</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M116" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N116" s="19" t="inlineStr">
@@ -11686,19 +11687,19 @@
       <c r="R116" s="19" t="inlineStr"/>
       <c r="S116" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="T116" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-01</t>
+          <t>TC-REC-10</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -11708,12 +11709,12 @@
       </c>
       <c r="C117" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D117" s="18" t="inlineStr">
         <is>
-          <t>Faculty schedules</t>
+          <t>Academic hire needs the college e-mail</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
@@ -11723,22 +11724,25 @@
       </c>
       <c r="F117" s="18" t="inlineStr">
         <is>
-          <t>Published class timetables.</t>
+          <t>An Accepted applicant from an Instructor link.</t>
         </is>
       </c>
       <c r="G117" s="18" t="inlineStr">
         <is>
-          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
+          <t>1. Create Employee.
+2. Leave Company Email empty (or a gmail address).
+3. Confirm.
+4. Then enter a @alriyada.edu.sa address and confirm again.</t>
         </is>
       </c>
       <c r="H117" s="18" t="inlineStr">
         <is>
-          <t>6–12 Sep 2026</t>
+          <t>Personal e-mail, then college e-mail</t>
         </is>
       </c>
       <c r="I117" s="18" t="inlineStr">
         <is>
-          <t>Sessions per faculty member with day, time, course, room and mode.</t>
+          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
         </is>
       </c>
       <c r="J117" s="14" t="inlineStr">
@@ -11748,12 +11752,12 @@
       </c>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L117" s="14" t="inlineStr">
         <is>
-          <t>PRS-01</t>
+          <t>REC-08</t>
         </is>
       </c>
       <c r="M117" s="14" t="inlineStr">
@@ -11784,7 +11788,7 @@
     <row r="118">
       <c r="A118" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-02</t>
+          <t>TC-PRS-01</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
@@ -11799,7 +11803,7 @@
       </c>
       <c r="D118" s="18" t="inlineStr">
         <is>
-          <t>Filter one faculty member</t>
+          <t>Faculty schedules</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -11809,27 +11813,27 @@
       </c>
       <c r="F118" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Published class timetables.</t>
         </is>
       </c>
       <c r="G118" s="18" t="inlineStr">
         <is>
-          <t>Pick a faculty member in the filter.</t>
+          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
         </is>
       </c>
       <c r="H118" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>6–12 Sep 2026</t>
         </is>
       </c>
       <c r="I118" s="18" t="inlineStr">
         <is>
-          <t>Only that person's sessions.</t>
+          <t>Sessions per faculty member with day, time, course, room and mode.</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K118" s="14" t="inlineStr">
@@ -11839,7 +11843,7 @@
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PRS-02</t>
+          <t>PRS-01</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
@@ -11870,7 +11874,7 @@
     <row r="119">
       <c r="A119" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-03</t>
+          <t>TC-PRS-02</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
@@ -11885,7 +11889,7 @@
       </c>
       <c r="D119" s="18" t="inlineStr">
         <is>
-          <t>Proctor schedules</t>
+          <t>Filter one faculty member</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
@@ -11895,22 +11899,22 @@
       </c>
       <c r="F119" s="18" t="inlineStr">
         <is>
-          <t>Exam committees with proctors.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G119" s="18" t="inlineStr">
         <is>
-          <t>Open Proctor Schedules for the exam week.</t>
+          <t>Pick a faculty member in the filter.</t>
         </is>
       </c>
       <c r="H119" s="18" t="inlineStr">
         <is>
-          <t>Exam week</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I119" s="18" t="inlineStr">
         <is>
-          <t>Proctor assignments, or a clear 'no assignments' message.</t>
+          <t>Only that person's sessions.</t>
         </is>
       </c>
       <c r="J119" s="14" t="inlineStr">
@@ -11925,7 +11929,7 @@
       </c>
       <c r="L119" s="14" t="inlineStr">
         <is>
-          <t>PRS-03</t>
+          <t>PRS-02</t>
         </is>
       </c>
       <c r="M119" s="14" t="inlineStr">
@@ -11956,7 +11960,7 @@
     <row r="120">
       <c r="A120" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-04</t>
+          <t>TC-PRS-03</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
@@ -11971,7 +11975,7 @@
       </c>
       <c r="D120" s="18" t="inlineStr">
         <is>
-          <t>Students on campus per hour</t>
+          <t>Proctor schedules</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
@@ -11981,27 +11985,27 @@
       </c>
       <c r="F120" s="18" t="inlineStr">
         <is>
-          <t>Attendance recorded.</t>
+          <t>Exam committees with proctors.</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
         <is>
-          <t>Open Students on Campus for a teaching day.</t>
+          <t>Open Proctor Schedules for the exam week.</t>
         </is>
       </c>
       <c r="H120" s="18" t="inlineStr">
         <is>
-          <t>8 Sep 2026</t>
+          <t>Exam week</t>
         </is>
       </c>
       <c r="I120" s="18" t="inlineStr">
         <is>
-          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
+          <t>Proctor assignments, or a clear 'no assignments' message.</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K120" s="14" t="inlineStr">
@@ -12011,7 +12015,7 @@
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PRS-04</t>
+          <t>PRS-03</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
@@ -12042,7 +12046,7 @@
     <row r="121">
       <c r="A121" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-05</t>
+          <t>TC-PRS-04</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
@@ -12057,7 +12061,7 @@
       </c>
       <c r="D121" s="18" t="inlineStr">
         <is>
-          <t>Faculty after 4 PM</t>
+          <t>Students on campus per hour</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -12067,22 +12071,22 @@
       </c>
       <c r="F121" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Attendance recorded.</t>
         </is>
       </c>
       <c r="G121" s="18" t="inlineStr">
         <is>
-          <t>Open Faculty After 4 PM for a week.</t>
+          <t>Open Students on Campus for a teaching day.</t>
         </is>
       </c>
       <c r="H121" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8 Sep 2026</t>
         </is>
       </c>
       <c r="I121" s="18" t="inlineStr">
         <is>
-          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
+          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
         </is>
       </c>
       <c r="J121" s="14" t="inlineStr">
@@ -12097,7 +12101,7 @@
       </c>
       <c r="L121" s="14" t="inlineStr">
         <is>
-          <t>PRS-05</t>
+          <t>PRS-04</t>
         </is>
       </c>
       <c r="M121" s="14" t="inlineStr">
@@ -12128,7 +12132,7 @@
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-06</t>
+          <t>TC-PRS-05</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
@@ -12143,7 +12147,7 @@
       </c>
       <c r="D122" s="18" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>Faculty after 4 PM</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
@@ -12153,12 +12157,12 @@
       </c>
       <c r="F122" s="18" t="inlineStr">
         <is>
-          <t>A tab with data.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G122" s="18" t="inlineStr">
         <is>
-          <t>Click Export (Excel CSV).</t>
+          <t>Open Faculty After 4 PM for a week.</t>
         </is>
       </c>
       <c r="H122" s="18" t="inlineStr">
@@ -12168,12 +12172,12 @@
       </c>
       <c r="I122" s="18" t="inlineStr">
         <is>
-          <t>A CSV file downloads and opens in Excel with the same rows.</t>
+          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
         </is>
       </c>
       <c r="J122" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K122" s="14" t="inlineStr">
@@ -12183,7 +12187,7 @@
       </c>
       <c r="L122" s="14" t="inlineStr">
         <is>
-          <t>PRS-06</t>
+          <t>PRS-05</t>
         </is>
       </c>
       <c r="M122" s="14" t="inlineStr">
@@ -12214,7 +12218,7 @@
     <row r="123">
       <c r="A123" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-07</t>
+          <t>TC-PRS-06</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
@@ -12229,7 +12233,7 @@
       </c>
       <c r="D123" s="18" t="inlineStr">
         <is>
-          <t>Holiday and exam days</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
@@ -12239,12 +12243,12 @@
       </c>
       <c r="F123" s="18" t="inlineStr">
         <is>
-          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
+          <t>A tab with data.</t>
         </is>
       </c>
       <c r="G123" s="18" t="inlineStr">
         <is>
-          <t>Open Faculty Schedules over a holiday or exam week.</t>
+          <t>Click Export (Excel CSV).</t>
         </is>
       </c>
       <c r="H123" s="18" t="inlineStr">
@@ -12254,7 +12258,7 @@
       </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
-          <t>No regular sessions on those days; the skipped dates are listed.</t>
+          <t>A CSV file downloads and opens in Excel with the same rows.</t>
         </is>
       </c>
       <c r="J123" s="14" t="inlineStr">
@@ -12269,12 +12273,12 @@
       </c>
       <c r="L123" s="14" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>PRS-06</t>
         </is>
       </c>
       <c r="M123" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N123" s="19" t="inlineStr">
@@ -12300,7 +12304,7 @@
     <row r="124">
       <c r="A124" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-08</t>
+          <t>TC-PRS-07</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
@@ -12315,7 +12319,7 @@
       </c>
       <c r="D124" s="18" t="inlineStr">
         <is>
-          <t>Cut-off time setting</t>
+          <t>Holiday and exam days</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
@@ -12325,27 +12329,27 @@
       </c>
       <c r="F124" s="18" t="inlineStr">
         <is>
+          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
+        </is>
+      </c>
+      <c r="G124" s="18" t="inlineStr">
+        <is>
+          <t>Open Faculty Schedules over a holiday or exam week.</t>
+        </is>
+      </c>
+      <c r="H124" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G124" s="18" t="inlineStr">
-        <is>
-          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
-        </is>
-      </c>
-      <c r="H124" s="18" t="inlineStr">
-        <is>
-          <t>15:00</t>
-        </is>
-      </c>
       <c r="I124" s="18" t="inlineStr">
         <is>
-          <t>List uses the new time.</t>
+          <t>No regular sessions on those days; the skipped dates are listed.</t>
         </is>
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K124" s="14" t="inlineStr">
@@ -12355,12 +12359,12 @@
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N124" s="19" t="inlineStr">
@@ -12386,7 +12390,7 @@
     <row r="125">
       <c r="A125" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-01</t>
+          <t>TC-PRS-08</t>
         </is>
       </c>
       <c r="B125" s="14" t="inlineStr">
@@ -12396,12 +12400,12 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D125" s="18" t="inlineStr">
         <is>
-          <t>Jameah Data Check page</t>
+          <t>Cut-off time setting</t>
         </is>
       </c>
       <c r="E125" s="14" t="inlineStr">
@@ -12416,37 +12420,37 @@
       </c>
       <c r="G125" s="18" t="inlineStr">
         <is>
-          <t>HR Dashboard -&gt; Jameah Data Check.</t>
+          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
         </is>
       </c>
       <c r="H125" s="18" t="inlineStr">
         <is>
+          <t>15:00</t>
+        </is>
+      </c>
+      <c r="I125" s="18" t="inlineStr">
+        <is>
+          <t>List uses the new time.</t>
+        </is>
+      </c>
+      <c r="J125" s="14" t="inlineStr">
+        <is>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="K125" s="14" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L125" s="14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I125" s="18" t="inlineStr">
-        <is>
-          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
-        </is>
-      </c>
-      <c r="J125" s="14" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K125" s="14" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="L125" s="14" t="inlineStr">
-        <is>
-          <t>JM-01</t>
-        </is>
-      </c>
       <c r="M125" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N125" s="19" t="inlineStr">
@@ -12472,7 +12476,7 @@
     <row r="126">
       <c r="A126" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-02</t>
+          <t>TC-JM-01</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
@@ -12487,12 +12491,12 @@
       </c>
       <c r="D126" s="18" t="inlineStr">
         <is>
-          <t>Jameah Settings pickers</t>
+          <t>Jameah Data Check page</t>
         </is>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F126" s="18" t="inlineStr">
@@ -12502,7 +12506,7 @@
       </c>
       <c r="G126" s="18" t="inlineStr">
         <is>
-          <t>Open Jameah Settings; open the College picker.</t>
+          <t>HR Dashboard -&gt; Jameah Data Check.</t>
         </is>
       </c>
       <c r="H126" s="18" t="inlineStr">
@@ -12512,12 +12516,12 @@
       </c>
       <c r="I126" s="18" t="inlineStr">
         <is>
-          <t>Only College Coding Guide codes are offered.</t>
+          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
         </is>
       </c>
       <c r="J126" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K126" s="14" t="inlineStr">
@@ -12527,7 +12531,7 @@
       </c>
       <c r="L126" s="14" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="M126" s="14" t="inlineStr">
@@ -12558,7 +12562,7 @@
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-03</t>
+          <t>TC-JM-02</t>
         </is>
       </c>
       <c r="B127" s="14" t="inlineStr">
@@ -12573,7 +12577,7 @@
       </c>
       <c r="D127" s="18" t="inlineStr">
         <is>
-          <t>Fill a setting and see it in the views</t>
+          <t>Jameah Settings pickers</t>
         </is>
       </c>
       <c r="E127" s="14" t="inlineStr">
@@ -12583,22 +12587,22 @@
       </c>
       <c r="F127" s="18" t="inlineStr">
         <is>
-          <t>Decision on the college code (DEC-02).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G127" s="18" t="inlineStr">
         <is>
-          <t>Set College; Save; reopen Jameah Data Check.</t>
+          <t>Open Jameah Settings; open the College picker.</t>
         </is>
       </c>
       <c r="H127" s="18" t="inlineStr">
         <is>
-          <t>College code</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I127" s="18" t="inlineStr">
         <is>
-          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
+          <t>Only College Coding Guide codes are offered.</t>
         </is>
       </c>
       <c r="J127" s="14" t="inlineStr">
@@ -12613,12 +12617,12 @@
       </c>
       <c r="L127" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="M127" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N127" s="19" t="inlineStr">
@@ -12644,7 +12648,7 @@
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-04</t>
+          <t>TC-JM-03</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
@@ -12659,7 +12663,7 @@
       </c>
       <c r="D128" s="18" t="inlineStr">
         <is>
-          <t>Map a value in the Code Map</t>
+          <t>Fill a setting and see it in the views</t>
         </is>
       </c>
       <c r="E128" s="14" t="inlineStr">
@@ -12669,22 +12673,22 @@
       </c>
       <c r="F128" s="18" t="inlineStr">
         <is>
-          <t>A 'Needs Review' row.</t>
+          <t>Decision on the college code (DEC-02).</t>
         </is>
       </c>
       <c r="G128" s="18" t="inlineStr">
         <is>
-          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
+          <t>Set College; Save; reopen Jameah Data Check.</t>
         </is>
       </c>
       <c r="H128" s="18" t="inlineStr">
         <is>
-          <t>e.g. Internship -&gt; 0</t>
+          <t>College code</t>
         </is>
       </c>
       <c r="I128" s="18" t="inlineStr">
         <is>
-          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
+          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
         </is>
       </c>
       <c r="J128" s="14" t="inlineStr">
@@ -12699,12 +12703,12 @@
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N128" s="19" t="inlineStr">
@@ -12730,7 +12734,7 @@
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-05</t>
+          <t>TC-JM-04</t>
         </is>
       </c>
       <c r="B129" s="14" t="inlineStr">
@@ -12745,7 +12749,7 @@
       </c>
       <c r="D129" s="18" t="inlineStr">
         <is>
-          <t>Code Map refuses a code from another list</t>
+          <t>Map a value in the Code Map</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
@@ -12755,42 +12759,42 @@
       </c>
       <c r="F129" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A 'Needs Review' row.</t>
         </is>
       </c>
       <c r="G129" s="18" t="inlineStr">
         <is>
-          <t>Try to save a Religion row with a Gender code.</t>
+          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
         </is>
       </c>
       <c r="H129" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>e.g. Internship -&gt; 0</t>
         </is>
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
-          <t>Refused with a clear message.</t>
+          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
         </is>
       </c>
       <c r="J129" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K129" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L129" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="M129" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N129" s="19" t="inlineStr">
@@ -12816,7 +12820,7 @@
     <row r="130">
       <c r="A130" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-06</t>
+          <t>TC-JM-05</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
@@ -12831,12 +12835,12 @@
       </c>
       <c r="D130" s="18" t="inlineStr">
         <is>
-          <t>Refresh academic figures</t>
+          <t>Code Map refuses a code from another list</t>
         </is>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
@@ -12846,7 +12850,7 @@
       </c>
       <c r="G130" s="18" t="inlineStr">
         <is>
-          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
+          <t>Try to save a Religion row with a Gender code.</t>
         </is>
       </c>
       <c r="H130" s="18" t="inlineStr">
@@ -12856,7 +12860,7 @@
       </c>
       <c r="I130" s="18" t="inlineStr">
         <is>
-          <t>'Last refreshed' time updates.</t>
+          <t>Refused with a clear message.</t>
         </is>
       </c>
       <c r="J130" s="14" t="inlineStr">
@@ -12866,17 +12870,17 @@
       </c>
       <c r="K130" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N130" s="19" t="inlineStr">
@@ -12902,7 +12906,7 @@
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-07</t>
+          <t>TC-JM-06</t>
         </is>
       </c>
       <c r="B131" s="14" t="inlineStr">
@@ -12917,7 +12921,7 @@
       </c>
       <c r="D131" s="18" t="inlineStr">
         <is>
-          <t>Employee data reaches the Employee views</t>
+          <t>Refresh academic figures</t>
         </is>
       </c>
       <c r="E131" s="14" t="inlineStr">
@@ -12927,12 +12931,12 @@
       </c>
       <c r="F131" s="18" t="inlineStr">
         <is>
-          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G131" s="18" t="inlineStr">
         <is>
-          <t>Open their Ministry (Jameah) Data preview.</t>
+          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
         </is>
       </c>
       <c r="H131" s="18" t="inlineStr">
@@ -12942,12 +12946,12 @@
       </c>
       <c r="I131" s="18" t="inlineStr">
         <is>
-          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
+          <t>'Last refreshed' time updates.</t>
         </is>
       </c>
       <c r="J131" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K131" s="14" t="inlineStr">
@@ -12957,12 +12961,12 @@
       </c>
       <c r="L131" s="14" t="inlineStr">
         <is>
-          <t>REC-06</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N131" s="19" t="inlineStr">
@@ -12988,7 +12992,7 @@
     <row r="132">
       <c r="A132" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-10</t>
+          <t>TC-JM-07</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
@@ -13003,32 +13007,32 @@
       </c>
       <c r="D132" s="18" t="inlineStr">
         <is>
-          <t>Ministry GPA and hours equal the student's transcript</t>
+          <t>Employee data reaches the Employee views</t>
         </is>
       </c>
       <c r="E132" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F132" s="18" t="inlineStr">
         <is>
-          <t>Academic figures refreshed (TC-JM-06).</t>
+          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
         </is>
       </c>
       <c r="G132" s="18" t="inlineStr">
         <is>
-          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
+          <t>Open their Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="H132" s="18" t="inlineStr">
         <is>
-          <t>10 students</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I132" s="18" t="inlineStr">
         <is>
-          <t>All four figures are identical for every student.</t>
+          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
         </is>
       </c>
       <c r="J132" s="14" t="inlineStr">
@@ -13038,12 +13042,12 @@
       </c>
       <c r="K132" s="14" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>verify.run</t>
+          <t>REC-06</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
@@ -13074,7 +13078,7 @@
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-08</t>
+          <t>TC-JM-10</t>
         </is>
       </c>
       <c r="B133" s="14" t="inlineStr">
@@ -13089,32 +13093,32 @@
       </c>
       <c r="D133" s="18" t="inlineStr">
         <is>
-          <t>Full value-by-value check (developer)</t>
+          <t>Ministry GPA and hours equal the student's transcript</t>
         </is>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F133" s="18" t="inlineStr">
         <is>
-          <t>Server access.</t>
+          <t>Academic figures refreshed (TC-JM-06).</t>
         </is>
       </c>
       <c r="G133" s="18" t="inlineStr">
         <is>
-          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
+          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
         </is>
       </c>
       <c r="H133" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 students</t>
         </is>
       </c>
       <c r="I133" s="18" t="inlineStr">
         <is>
-          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
+          <t>All four figures are identical for every student.</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
@@ -13160,7 +13164,7 @@
     <row r="134">
       <c r="A134" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-09</t>
+          <t>TC-JM-08</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
@@ -13175,22 +13179,22 @@
       </c>
       <c r="D134" s="18" t="inlineStr">
         <is>
-          <t>Ministry read-only account</t>
+          <t>Full value-by-value check (developer)</t>
         </is>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F134" s="18" t="inlineStr">
         <is>
-          <t>Account created with the grant statements.</t>
+          <t>Server access.</t>
         </is>
       </c>
       <c r="G134" s="18" t="inlineStr">
         <is>
-          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
+          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="H134" s="18" t="inlineStr">
@@ -13200,27 +13204,27 @@
       </c>
       <c r="I134" s="18" t="inlineStr">
         <is>
-          <t>Views readable; ERP tables refused.</t>
+          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
         </is>
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K134" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verify.run</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N134" s="19" t="inlineStr">
@@ -13246,7 +13250,7 @@
     <row r="135">
       <c r="A135" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-11</t>
+          <t>TC-JM-09</t>
         </is>
       </c>
       <c r="B135" s="14" t="inlineStr">
@@ -13261,52 +13265,52 @@
       </c>
       <c r="D135" s="18" t="inlineStr">
         <is>
-          <t>Faculty views on the Data Check page</t>
+          <t>Ministry read-only account</t>
         </is>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="F135" s="18" t="inlineStr">
         <is>
+          <t>Account created with the grant statements.</t>
+        </is>
+      </c>
+      <c r="G135" s="18" t="inlineStr">
+        <is>
+          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
+        </is>
+      </c>
+      <c r="H135" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G135" s="18" t="inlineStr">
-        <is>
-          <t>Open Jameah Data Check and look at the Views table.</t>
-        </is>
-      </c>
-      <c r="H135" s="18" t="inlineStr">
+      <c r="I135" s="18" t="inlineStr">
+        <is>
+          <t>Views readable; ERP tables refused.</t>
+        </is>
+      </c>
+      <c r="J135" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K135" s="14" t="inlineStr">
+        <is>
+          <t>Security</t>
+        </is>
+      </c>
+      <c r="L135" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I135" s="18" t="inlineStr">
-        <is>
-          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
-        </is>
-      </c>
-      <c r="J135" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K135" s="14" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="L135" s="14" t="inlineStr">
-        <is>
-          <t>JM-01</t>
-        </is>
-      </c>
       <c r="M135" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N135" s="19" t="inlineStr">
@@ -13332,7 +13336,7 @@
     <row r="136">
       <c r="A136" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-12</t>
+          <t>TC-JM-11</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
@@ -13347,7 +13351,7 @@
       </c>
       <c r="D136" s="18" t="inlineStr">
         <is>
-          <t>A teacher is sent once, as Faculty</t>
+          <t>Faculty views on the Data Check page</t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
@@ -13357,13 +13361,12 @@
       </c>
       <c r="F136" s="18" t="inlineStr">
         <is>
-          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G136" s="18" t="inlineStr">
         <is>
-          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
-2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
+          <t>Open Jameah Data Check and look at the Views table.</t>
         </is>
       </c>
       <c r="H136" s="18" t="inlineStr">
@@ -13373,27 +13376,27 @@
       </c>
       <c r="I136" s="18" t="inlineStr">
         <is>
-          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
+          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
         </is>
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K136" s="14" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L136" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="M136" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N136" s="19" t="inlineStr">
@@ -13419,7 +13422,7 @@
     <row r="137">
       <c r="A137" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-13</t>
+          <t>TC-JM-12</t>
         </is>
       </c>
       <c r="B137" s="14" t="inlineStr">
@@ -13434,23 +13437,23 @@
       </c>
       <c r="D137" s="18" t="inlineStr">
         <is>
-          <t>Faculty status and contract codes</t>
+          <t>A teacher is sent once, as Faculty</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F137" s="18" t="inlineStr">
         <is>
-          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
         </is>
       </c>
       <c r="G137" s="18" t="inlineStr">
         <is>
-          <t>1. Open each row, pick the Ministry code, Status = Verified.
-2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
+2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
         </is>
       </c>
       <c r="H137" s="18" t="inlineStr">
@@ -13460,12 +13463,12 @@
       </c>
       <c r="I137" s="18" t="inlineStr">
         <is>
-          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
+          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
         </is>
       </c>
       <c r="J137" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K137" s="14" t="inlineStr">
@@ -13475,12 +13478,12 @@
       </c>
       <c r="L137" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N137" s="19" t="inlineStr">
@@ -13506,7 +13509,7 @@
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-01</t>
+          <t>TC-JM-13</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
@@ -13516,47 +13519,48 @@
       </c>
       <c r="C138" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D138" s="18" t="inlineStr">
         <is>
-          <t>Error Log after each test day</t>
+          <t>Faculty status and contract codes</t>
         </is>
       </c>
       <c r="E138" s="14" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F138" s="18" t="inlineStr">
         <is>
+          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+        </is>
+      </c>
+      <c r="G138" s="18" t="inlineStr">
+        <is>
+          <t>1. Open each row, pick the Ministry code, Status = Verified.
+2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+        </is>
+      </c>
+      <c r="H138" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G138" s="18" t="inlineStr">
-        <is>
-          <t>Open /app/error-log; sort by newest.</t>
-        </is>
-      </c>
-      <c r="H138" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I138" s="18" t="inlineStr">
         <is>
-          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
+          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
         </is>
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K138" s="14" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="L138" s="14" t="inlineStr">
@@ -13592,7 +13596,7 @@
     <row r="139">
       <c r="A139" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-02</t>
+          <t>TC-ERR-01</t>
         </is>
       </c>
       <c r="B139" s="14" t="inlineStr">
@@ -13607,7 +13611,7 @@
       </c>
       <c r="D139" s="18" t="inlineStr">
         <is>
-          <t>System e-mail works</t>
+          <t>Error Log after each test day</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
@@ -13622,7 +13626,7 @@
       </c>
       <c r="G139" s="18" t="inlineStr">
         <is>
-          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
+          <t>Open /app/error-log; sort by newest.</t>
         </is>
       </c>
       <c r="H139" s="18" t="inlineStr">
@@ -13632,7 +13636,7 @@
       </c>
       <c r="I139" s="18" t="inlineStr">
         <is>
-          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
+          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
@@ -13678,7 +13682,7 @@
     <row r="140">
       <c r="A140" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-03</t>
+          <t>TC-ERR-02</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
@@ -13693,7 +13697,7 @@
       </c>
       <c r="D140" s="18" t="inlineStr">
         <is>
-          <t>Background jobs</t>
+          <t>System e-mail works</t>
         </is>
       </c>
       <c r="E140" s="14" t="inlineStr">
@@ -13708,7 +13712,7 @@
       </c>
       <c r="G140" s="18" t="inlineStr">
         <is>
-          <t>Open Scheduled Job Log; filter Status = Failed.</t>
+          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
         </is>
       </c>
       <c r="H140" s="18" t="inlineStr">
@@ -13718,12 +13722,12 @@
       </c>
       <c r="I140" s="18" t="inlineStr">
         <is>
-          <t>No failed jobs (or each one reported).</t>
+          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
         </is>
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K140" s="14" t="inlineStr">
@@ -13764,7 +13768,7 @@
     <row r="141">
       <c r="A141" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-04</t>
+          <t>TC-ERR-03</t>
         </is>
       </c>
       <c r="B141" s="14" t="inlineStr">
@@ -13779,22 +13783,22 @@
       </c>
       <c r="D141" s="18" t="inlineStr">
         <is>
-          <t>Browser console during testing</t>
+          <t>Background jobs</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="F141" s="18" t="inlineStr">
         <is>
-          <t>Chrome DevTools open (F12 -&gt; Console).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G141" s="18" t="inlineStr">
         <is>
-          <t>Use the system as normal while the console is open.</t>
+          <t>Open Scheduled Job Log; filter Status = Failed.</t>
         </is>
       </c>
       <c r="H141" s="18" t="inlineStr">
@@ -13804,12 +13808,12 @@
       </c>
       <c r="I141" s="18" t="inlineStr">
         <is>
-          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
+          <t>No failed jobs (or each one reported).</t>
         </is>
       </c>
       <c r="J141" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K141" s="14" t="inlineStr">
@@ -13819,12 +13823,12 @@
       </c>
       <c r="L141" s="14" t="inlineStr">
         <is>
-          <t>Error sweep SWP-01..04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M141" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N141" s="19" t="inlineStr">
@@ -13850,7 +13854,7 @@
     <row r="142">
       <c r="A142" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-05</t>
+          <t>TC-ERR-04</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
@@ -13865,22 +13869,22 @@
       </c>
       <c r="D142" s="18" t="inlineStr">
         <is>
-          <t>Migrate output after deploying</t>
+          <t>Browser console during testing</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Any</t>
         </is>
       </c>
       <c r="F142" s="18" t="inlineStr">
         <is>
-          <t>New branch pulled on the server.</t>
+          <t>Chrome DevTools open (F12 -&gt; Console).</t>
         </is>
       </c>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
+          <t>Use the system as normal while the console is open.</t>
         </is>
       </c>
       <c r="H142" s="18" t="inlineStr">
@@ -13890,7 +13894,7 @@
       </c>
       <c r="I142" s="18" t="inlineStr">
         <is>
-          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
+          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
         </is>
       </c>
       <c r="J142" s="14" t="inlineStr">
@@ -13905,12 +13909,12 @@
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Error sweep SWP-01..04</t>
         </is>
       </c>
       <c r="M142" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N142" s="19" t="inlineStr">
@@ -13936,7 +13940,7 @@
     <row r="143">
       <c r="A143" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-06</t>
+          <t>TC-ERR-05</t>
         </is>
       </c>
       <c r="B143" s="14" t="inlineStr">
@@ -13951,22 +13955,22 @@
       </c>
       <c r="D143" s="18" t="inlineStr">
         <is>
-          <t>Every Medical HRMS page and form opens</t>
+          <t>Migrate output after deploying</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Administrator</t>
         </is>
       </c>
       <c r="F143" s="18" t="inlineStr">
         <is>
-          <t>Logged in as HR Manager (then repeat as HR User).</t>
+          <t>New branch pulled on the server.</t>
         </is>
       </c>
       <c r="G143" s="18" t="inlineStr">
         <is>
-          <t>Open each Medical HRMS doctype list, its New form and its newest saved record; the four pages, the report and both workspaces.</t>
+          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
         </is>
       </c>
       <c r="H143" s="18" t="inlineStr">
@@ -13976,27 +13980,27 @@
       </c>
       <c r="I143" s="18" t="inlineStr">
         <is>
-          <t>Each opens; no red error, no 'Not permitted' for HR, no blank page.</t>
+          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
         </is>
       </c>
       <c r="J143" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K143" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Monitoring</t>
         </is>
       </c>
       <c r="L143" s="14" t="inlineStr">
         <is>
-          <t>SWP-01/02</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M143" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N143" s="19" t="inlineStr">
@@ -14010,19 +14014,19 @@
       <c r="R143" s="19" t="inlineStr"/>
       <c r="S143" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T143" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-07</t>
+          <t>TC-ERR-06</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
@@ -14037,22 +14041,22 @@
       </c>
       <c r="D144" s="18" t="inlineStr">
         <is>
-          <t>Employees' own request lists open</t>
+          <t>Every Medical HRMS page and form opens</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F144" s="18" t="inlineStr">
         <is>
-          <t>Logged in as an employee.</t>
+          <t>Logged in as HR Manager (then repeat as HR User).</t>
         </is>
       </c>
       <c r="G144" s="18" t="inlineStr">
         <is>
-          <t>Open the list of each self-service request type (Permission Request ... Employee Medical License) and the Employee Self Service workspace.</t>
+          <t>Open each Medical HRMS doctype list, its New form and its newest saved record; the four pages, the report and both workspaces.</t>
         </is>
       </c>
       <c r="H144" s="18" t="inlineStr">
@@ -14062,12 +14066,12 @@
       </c>
       <c r="I144" s="18" t="inlineStr">
         <is>
-          <t>Each opens with only the employee's own records; no error.</t>
+          <t>Each opens; no red error, no 'Not permitted' for HR, no blank page.</t>
         </is>
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K144" s="14" t="inlineStr">
@@ -14077,7 +14081,7 @@
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>SWP-03</t>
+          <t>SWP-01/02</t>
         </is>
       </c>
       <c r="M144" s="14" t="inlineStr">
@@ -14108,7 +14112,7 @@
     <row r="145">
       <c r="A145" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-08</t>
+          <t>TC-ERR-07</t>
         </is>
       </c>
       <c r="B145" s="14" t="inlineStr">
@@ -14123,22 +14127,22 @@
       </c>
       <c r="D145" s="18" t="inlineStr">
         <is>
-          <t>Every file of the app is valid</t>
+          <t>Employees' own request lists open</t>
         </is>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F145" s="18" t="inlineStr">
         <is>
-          <t>A checkout of develop.</t>
+          <t>Logged in as an employee.</t>
         </is>
       </c>
       <c r="G145" s="18" t="inlineStr">
         <is>
-          <t>python3 tests/checks/files.py</t>
+          <t>Open the list of each self-service request type (Permission Request ... Employee Medical License) and the Employee Self Service workspace.</t>
         </is>
       </c>
       <c r="H145" s="18" t="inlineStr">
@@ -14148,12 +14152,12 @@
       </c>
       <c r="I145" s="18" t="inlineStr">
         <is>
-          <t>PROBLEMS: 0 (Python compiles, JS parses, JSON loads, translations keep their placeholders, no stray files).</t>
+          <t>Each opens with only the employee's own records; no error.</t>
         </is>
       </c>
       <c r="J145" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K145" s="14" t="inlineStr">
@@ -14163,7 +14167,7 @@
       </c>
       <c r="L145" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/files.py</t>
+          <t>SWP-03</t>
         </is>
       </c>
       <c r="M145" s="14" t="inlineStr">
@@ -14194,7 +14198,7 @@
     <row r="146">
       <c r="A146" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-09</t>
+          <t>TC-ERR-08</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
@@ -14209,7 +14213,7 @@
       </c>
       <c r="D146" s="18" t="inlineStr">
         <is>
-          <t>Every hook, doctype and record is valid on the site</t>
+          <t>Every file of the app is valid</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr">
@@ -14219,12 +14223,12 @@
       </c>
       <c r="F146" s="18" t="inlineStr">
         <is>
-          <t>Site migrated.</t>
+          <t>A checkout of develop.</t>
         </is>
       </c>
       <c r="G146" s="18" t="inlineStr">
         <is>
-          <t>../../env/bin/python tests/e2e/fx.py tests/checks/site.py</t>
+          <t>python3 tests/checks/files.py</t>
         </is>
       </c>
       <c r="H146" s="18" t="inlineStr">
@@ -14234,7 +14238,7 @@
       </c>
       <c r="I146" s="18" t="inlineStr">
         <is>
-          <t>PROBLEMS: 0; every hook, patch and asset resolves; saved records pass validation.</t>
+          <t>PROBLEMS: 0 (Python compiles, JS parses, JSON loads, translations keep their placeholders, no stray files).</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
@@ -14249,7 +14253,7 @@
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/site.py</t>
+          <t>tests/checks/files.py</t>
         </is>
       </c>
       <c r="M146" s="14" t="inlineStr">
@@ -14277,9 +14281,95 @@
         </is>
       </c>
     </row>
+    <row r="147">
+      <c r="A147" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-09</t>
+        </is>
+      </c>
+      <c r="B147" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C147" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D147" s="18" t="inlineStr">
+        <is>
+          <t>Every hook, doctype and record is valid on the site</t>
+        </is>
+      </c>
+      <c r="E147" s="14" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F147" s="18" t="inlineStr">
+        <is>
+          <t>Site migrated.</t>
+        </is>
+      </c>
+      <c r="G147" s="18" t="inlineStr">
+        <is>
+          <t>../../env/bin/python tests/e2e/fx.py tests/checks/site.py</t>
+        </is>
+      </c>
+      <c r="H147" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I147" s="18" t="inlineStr">
+        <is>
+          <t>PROBLEMS: 0; every hook, patch and asset resolves; saved records pass validation.</t>
+        </is>
+      </c>
+      <c r="J147" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K147" s="14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="L147" s="14" t="inlineStr">
+        <is>
+          <t>tests/checks/site.py</t>
+        </is>
+      </c>
+      <c r="M147" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N147" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O147" s="19" t="inlineStr"/>
+      <c r="P147" s="19" t="inlineStr"/>
+      <c r="Q147" s="20" t="inlineStr"/>
+      <c r="R147" s="19" t="inlineStr"/>
+      <c r="S147" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T147" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T146"/>
-  <conditionalFormatting sqref="N2:N346">
+  <autoFilter ref="A1:T147"/>
+  <conditionalFormatting sqref="N2:N347">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$N2="Pass"</formula>
     </cfRule>
@@ -14296,7 +14386,7 @@
       <formula>$N2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M346">
+  <conditionalFormatting sqref="M2:M347">
     <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
       <formula>$M2="Pass"</formula>
     </cfRule>
@@ -14313,7 +14403,7 @@
       <formula>$M2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J346">
+  <conditionalFormatting sqref="J2:J347">
     <cfRule type="expression" priority="11" dxfId="4" stopIfTrue="1">
       <formula>$J2="Critical"</formula>
     </cfRule>
@@ -14328,7 +14418,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N346" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N347" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16240,7 +16330,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E18"/>
+  <dimension ref="A1:E19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16285,17 +16375,17 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Leave e-mails</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>HR-76</t>
+          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
+          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -16312,17 +16402,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -16339,17 +16429,17 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -16361,22 +16451,22 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -16398,12 +16488,12 @@
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -16420,17 +16510,17 @@
       </c>
       <c r="B7" s="14" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -16452,12 +16542,12 @@
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -16474,17 +16564,17 @@
       </c>
       <c r="B9" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -16496,7 +16586,7 @@
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B10" s="14" t="inlineStr">
@@ -16506,12 +16596,12 @@
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -16533,12 +16623,12 @@
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -16555,17 +16645,17 @@
       </c>
       <c r="B12" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -16577,22 +16667,22 @@
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -16609,17 +16699,17 @@
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -16636,17 +16726,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -16658,7 +16748,7 @@
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B16" s="14" t="inlineStr">
@@ -16668,12 +16758,12 @@
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -16685,7 +16775,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -16695,12 +16785,12 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -16712,25 +16802,52 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B18" s="14" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C18" s="18" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D18" s="18" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E18" s="14" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="14" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B18" s="14" t="inlineStr">
+      <c r="B19" s="14" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C18" s="18" t="inlineStr">
+      <c r="C19" s="18" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D18" s="18" t="inlineStr">
+      <c r="D19" s="18" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E18" s="14" t="inlineStr">
+      <c r="E19" s="14" t="inlineStr">
         <is>
           <t>Team</t>
         </is>

--- a/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
+++ b/project_tracking/Medical_HRMS_Jameah_Test_Cases.xlsx
@@ -15,7 +15,7 @@
     <sheet name="Change Log" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$T$147</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Test Cases'!$A$1:$T$157</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -689,7 +689,7 @@
     <row r="2">
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>For the testing team · last updated 27 Oct 2026 · last automated run 27 Oct 2026 09:11 AST (101/101 browser checks passed)</t>
+          <t>For the testing team · last updated 27 Oct 2026 · last automated run 27 Oct 2026 13:33 AST (111/111 browser checks passed)</t>
         </is>
       </c>
     </row>
@@ -854,7 +854,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I26"/>
+  <dimension ref="A1:I28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="32" customWidth="1" min="1" max="1"/>
@@ -936,27 +936,27 @@
         </is>
       </c>
       <c r="B5" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A5)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A5)</f>
         <v/>
       </c>
       <c r="C5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A5,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A5,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A5,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A5,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A5,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H5" s="15">
@@ -964,7 +964,7 @@
         <v/>
       </c>
       <c r="I5" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A5,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A5,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A5,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -975,27 +975,27 @@
         </is>
       </c>
       <c r="B6" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A6)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A6)</f>
         <v/>
       </c>
       <c r="C6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A6,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A6,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A6,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A6,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A6,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H6" s="15">
@@ -1003,7 +1003,7 @@
         <v/>
       </c>
       <c r="I6" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A6,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A6,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A6,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1014,27 +1014,27 @@
         </is>
       </c>
       <c r="B7" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A7)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A7)</f>
         <v/>
       </c>
       <c r="C7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A7,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A7,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A7,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A7,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A7,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H7" s="15">
@@ -1042,7 +1042,7 @@
         <v/>
       </c>
       <c r="I7" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A7,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A7,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A7,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1053,27 +1053,27 @@
         </is>
       </c>
       <c r="B8" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A8)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A8)</f>
         <v/>
       </c>
       <c r="C8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A8,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A8,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A8,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A8,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A8,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H8" s="15">
@@ -1081,7 +1081,7 @@
         <v/>
       </c>
       <c r="I8" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A8,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A8,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A8,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
@@ -1092,27 +1092,27 @@
         </is>
       </c>
       <c r="B9" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A9)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A9)</f>
         <v/>
       </c>
       <c r="C9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A9,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A9,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A9,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A9,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A9,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H9" s="15">
@@ -1120,38 +1120,38 @@
         <v/>
       </c>
       <c r="I9" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A9,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A9,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A9,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="B10" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A10)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A10)</f>
         <v/>
       </c>
       <c r="C10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A10,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A10,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A10,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A10,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A10,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H10" s="15">
@@ -1159,38 +1159,38 @@
         <v/>
       </c>
       <c r="I10" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A10,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A10,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A10,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="B11" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A11)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A11)</f>
         <v/>
       </c>
       <c r="C11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A11,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A11,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A11,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A11,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A11,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H11" s="15">
@@ -1198,38 +1198,38 @@
         <v/>
       </c>
       <c r="I11" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A11,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A11,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A11,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="14" t="inlineStr">
         <is>
-          <t>Medical licences</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="B12" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A12)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A12)</f>
         <v/>
       </c>
       <c r="C12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A12,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A12,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A12,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A12,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A12,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H12" s="15">
@@ -1237,38 +1237,38 @@
         <v/>
       </c>
       <c r="I12" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A12,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A12,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A12,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Medical licences</t>
         </is>
       </c>
       <c r="B13" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A13)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A13)</f>
         <v/>
       </c>
       <c r="C13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A13,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A13,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A13,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A13,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A13,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H13" s="15">
@@ -1276,38 +1276,38 @@
         <v/>
       </c>
       <c r="I13" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A13,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A13,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A13,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="B14" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A14)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A14)</f>
         <v/>
       </c>
       <c r="C14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A14,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A14,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A14,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A14,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A14,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H14" s="15">
@@ -1315,38 +1315,38 @@
         <v/>
       </c>
       <c r="I14" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A14,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A14,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A14,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="B15" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A15)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A15)</f>
         <v/>
       </c>
       <c r="C15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A15,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A15,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A15,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A15,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A15,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H15" s="15">
@@ -1354,38 +1354,38 @@
         <v/>
       </c>
       <c r="I15" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A15,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A15,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A15,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="B16" s="14">
-        <f>COUNTIF('Test Cases'!$C$2:$C$347,$A16)</f>
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A16)</f>
         <v/>
       </c>
       <c r="C16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,C$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A16,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
       <c r="D16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,D$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A16,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
       <c r="E16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,E$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A16,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
       <c r="F16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,F$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A16,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
       <c r="G16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$N$2:$N$347,G$4)</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A16,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
       <c r="H16" s="15">
@@ -1393,154 +1393,158 @@
         <v/>
       </c>
       <c r="I16" s="14">
-        <f>COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$J$2:$J$347,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$347,$A16,'Test Cases'!$J$2:$J$347,"Critical",'Test Cases'!$N$2:$N$347,"Pass")</f>
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A16,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A16,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="16" t="inlineStr">
-        <is>
-          <t>All modules</t>
-        </is>
-      </c>
-      <c r="B17" s="16">
-        <f>SUM(B5:B16)</f>
+      <c r="A17" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="B17" s="14">
+        <f>COUNTIF('Test Cases'!$C$2:$C$357,$A17)</f>
         <v/>
       </c>
-      <c r="C17" s="16">
-        <f>SUM(C5:C16)</f>
+      <c r="C17" s="14">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A17,'Test Cases'!$N$2:$N$357,C$4)</f>
         <v/>
       </c>
-      <c r="D17" s="16">
-        <f>SUM(D5:D16)</f>
+      <c r="D17" s="14">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A17,'Test Cases'!$N$2:$N$357,D$4)</f>
         <v/>
       </c>
-      <c r="E17" s="16">
-        <f>SUM(E5:E16)</f>
+      <c r="E17" s="14">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A17,'Test Cases'!$N$2:$N$357,E$4)</f>
         <v/>
       </c>
-      <c r="F17" s="16">
-        <f>SUM(F5:F16)</f>
+      <c r="F17" s="14">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A17,'Test Cases'!$N$2:$N$357,F$4)</f>
         <v/>
       </c>
-      <c r="G17" s="16">
-        <f>SUM(G5:G16)</f>
+      <c r="G17" s="14">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A17,'Test Cases'!$N$2:$N$357,G$4)</f>
         <v/>
       </c>
-      <c r="H17" s="17">
+      <c r="H17" s="15">
         <f>IFERROR(D17/(D17+E17+F17),"-")</f>
         <v/>
       </c>
-      <c r="I17" s="16">
-        <f>SUM(I5:I16)</f>
+      <c r="I17" s="14">
+        <f>COUNTIFS('Test Cases'!$C$2:$C$357,$A17,'Test Cases'!$J$2:$J$357,"Critical")-COUNTIFS('Test Cases'!$C$2:$C$357,$A17,'Test Cases'!$J$2:$J$357,"Critical",'Test Cases'!$N$2:$N$357,"Pass")</f>
         <v/>
       </c>
     </row>
-    <row r="19" ht="32" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="18">
+      <c r="A18" s="16" t="inlineStr">
+        <is>
+          <t>All modules</t>
+        </is>
+      </c>
+      <c r="B18" s="16">
+        <f>SUM(B5:B17)</f>
+        <v/>
+      </c>
+      <c r="C18" s="16">
+        <f>SUM(C5:C17)</f>
+        <v/>
+      </c>
+      <c r="D18" s="16">
+        <f>SUM(D5:D17)</f>
+        <v/>
+      </c>
+      <c r="E18" s="16">
+        <f>SUM(E5:E17)</f>
+        <v/>
+      </c>
+      <c r="F18" s="16">
+        <f>SUM(F5:F17)</f>
+        <v/>
+      </c>
+      <c r="G18" s="16">
+        <f>SUM(G5:G17)</f>
+        <v/>
+      </c>
+      <c r="H18" s="17">
+        <f>IFERROR(D18/(D18+E18+F18),"-")</f>
+        <v/>
+      </c>
+      <c r="I18" s="16">
+        <f>SUM(I5:I17)</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" ht="32" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>Round</t>
         </is>
       </c>
-      <c r="B19" s="13" t="inlineStr">
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>Cases</t>
         </is>
       </c>
-      <c r="C19" s="13" t="inlineStr">
+      <c r="C20" s="13" t="inlineStr">
         <is>
           <t>Not run</t>
         </is>
       </c>
-      <c r="D19" s="13" t="inlineStr">
+      <c r="D20" s="13" t="inlineStr">
         <is>
           <t>Pass</t>
         </is>
       </c>
-      <c r="E19" s="13" t="inlineStr">
+      <c r="E20" s="13" t="inlineStr">
         <is>
           <t>Fail</t>
         </is>
       </c>
-      <c r="F19" s="13" t="inlineStr">
+      <c r="F20" s="13" t="inlineStr">
         <is>
           <t>Blocked</t>
         </is>
       </c>
-      <c r="G19" s="13" t="inlineStr">
+      <c r="G20" s="13" t="inlineStr">
         <is>
           <t>N/A</t>
         </is>
       </c>
-      <c r="H19" s="13" t="inlineStr">
+      <c r="H20" s="13" t="inlineStr">
         <is>
           <t>% passed (of run)</t>
         </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="14" t="inlineStr">
-        <is>
-          <t>Round 1</t>
-        </is>
-      </c>
-      <c r="B20" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$347,$A20)</f>
-        <v/>
-      </c>
-      <c r="C20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,C$19)</f>
-        <v/>
-      </c>
-      <c r="D20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,D$19)</f>
-        <v/>
-      </c>
-      <c r="E20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,E$19)</f>
-        <v/>
-      </c>
-      <c r="F20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,F$19)</f>
-        <v/>
-      </c>
-      <c r="G20" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A20,'Test Cases'!$N$2:$N$347,G$19)</f>
-        <v/>
-      </c>
-      <c r="H20" s="15">
-        <f>IFERROR(D20/(D20+E20+F20),"-")</f>
-        <v/>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Round 1</t>
         </is>
       </c>
       <c r="B21" s="14">
-        <f>COUNTIF('Test Cases'!$B$2:$B$347,$A21)</f>
+        <f>COUNTIF('Test Cases'!$B$2:$B$357,$A21)</f>
         <v/>
       </c>
       <c r="C21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,C$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A21,'Test Cases'!$N$2:$N$357,C$20)</f>
         <v/>
       </c>
       <c r="D21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,D$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A21,'Test Cases'!$N$2:$N$357,D$20)</f>
         <v/>
       </c>
       <c r="E21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,E$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A21,'Test Cases'!$N$2:$N$357,E$20)</f>
         <v/>
       </c>
       <c r="F21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,F$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A21,'Test Cases'!$N$2:$N$357,F$20)</f>
         <v/>
       </c>
       <c r="G21" s="14">
-        <f>COUNTIFS('Test Cases'!$B$2:$B$347,$A21,'Test Cases'!$N$2:$N$347,G$19)</f>
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A21,'Test Cases'!$N$2:$N$357,G$20)</f>
         <v/>
       </c>
       <c r="H21" s="15">
@@ -1548,43 +1552,113 @@
         <v/>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
+        <is>
+          <t>Round 2</t>
+        </is>
+      </c>
+      <c r="B22" s="14">
+        <f>COUNTIF('Test Cases'!$B$2:$B$357,$A22)</f>
+        <v/>
+      </c>
+      <c r="C22" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A22,'Test Cases'!$N$2:$N$357,C$20)</f>
+        <v/>
+      </c>
+      <c r="D22" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A22,'Test Cases'!$N$2:$N$357,D$20)</f>
+        <v/>
+      </c>
+      <c r="E22" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A22,'Test Cases'!$N$2:$N$357,E$20)</f>
+        <v/>
+      </c>
+      <c r="F22" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A22,'Test Cases'!$N$2:$N$357,F$20)</f>
+        <v/>
+      </c>
+      <c r="G22" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A22,'Test Cases'!$N$2:$N$357,G$20)</f>
+        <v/>
+      </c>
+      <c r="H22" s="15">
+        <f>IFERROR(D22/(D22+E22+F22),"-")</f>
+        <v/>
+      </c>
+    </row>
     <row r="23">
-      <c r="A23" s="16" t="inlineStr">
+      <c r="A23" s="14" t="inlineStr">
+        <is>
+          <t>Round 3</t>
+        </is>
+      </c>
+      <c r="B23" s="14">
+        <f>COUNTIF('Test Cases'!$B$2:$B$357,$A23)</f>
+        <v/>
+      </c>
+      <c r="C23" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A23,'Test Cases'!$N$2:$N$357,C$20)</f>
+        <v/>
+      </c>
+      <c r="D23" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A23,'Test Cases'!$N$2:$N$357,D$20)</f>
+        <v/>
+      </c>
+      <c r="E23" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A23,'Test Cases'!$N$2:$N$357,E$20)</f>
+        <v/>
+      </c>
+      <c r="F23" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A23,'Test Cases'!$N$2:$N$357,F$20)</f>
+        <v/>
+      </c>
+      <c r="G23" s="14">
+        <f>COUNTIFS('Test Cases'!$B$2:$B$357,$A23,'Test Cases'!$N$2:$N$357,G$20)</f>
+        <v/>
+      </c>
+      <c r="H23" s="15">
+        <f>IFERROR(D23/(D23+E23+F23),"-")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="16" t="inlineStr">
         <is>
           <t>Last automated run (developer)</t>
         </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="14" t="inlineStr">
-        <is>
-          <t>Pass</t>
-        </is>
-      </c>
-      <c r="B24" s="14">
-        <f>COUNTIF('Test Cases'!$M$2:$M$347,"Pass")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="14" t="inlineStr">
-        <is>
-          <t>Fail</t>
-        </is>
-      </c>
-      <c r="B25" s="14">
-        <f>COUNTIF('Test Cases'!$M$2:$M$347,"Fail")</f>
-        <v/>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="14" t="inlineStr">
         <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B26" s="14">
+        <f>COUNTIF('Test Cases'!$M$2:$M$357,"Pass")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="14" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B27" s="14">
+        <f>COUNTIF('Test Cases'!$M$2:$M$357,"Fail")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="14" t="inlineStr">
+        <is>
           <t>Manual only / unit test</t>
         </is>
       </c>
-      <c r="B26" s="14">
-        <f>COUNTA('Test Cases'!$M$2:$M$147)-B24-B25</f>
+      <c r="B28" s="14">
+        <f>COUNTA('Test Cases'!$M$2:$M$157)-B26-B27</f>
         <v/>
       </c>
     </row>
@@ -1599,7 +1673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T147"/>
+  <dimension ref="A1:T157"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="11" customWidth="1" min="1" max="1"/>
@@ -8319,37 +8393,38 @@
     <row r="78">
       <c r="A78" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-01</t>
+          <t>TC-STF-01</t>
         </is>
       </c>
       <c r="B78" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C78" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D78" s="18" t="inlineStr">
         <is>
-          <t>Employees see only their own requests</t>
+          <t>My HR on the Instructor dashboard</t>
         </is>
       </c>
       <c r="E78" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Instructor</t>
         </is>
       </c>
       <c r="F78" s="18" t="inlineStr">
         <is>
-          <t>Two employees each sent a request.</t>
+          <t>Instructor login linked to an Employee record (HR links them: HR-55).</t>
         </is>
       </c>
       <c r="G78" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 opens each request list.</t>
+          <t>1. Log in as the instructor.
+2. Look under the four figures (Active Class, Total Students ...).</t>
         </is>
       </c>
       <c r="H78" s="18" t="inlineStr">
@@ -8359,22 +8434,22 @@
       </c>
       <c r="I78" s="18" t="inlineStr">
         <is>
-          <t>Only their own requests appear.</t>
+          <t>A 'My HR' card with the Employee ID, the leave balances and the latest requests, and the buttons Apply for Leave, New Request and Employee Portal. The rest of the Instructor dashboard is unchanged.</t>
         </is>
       </c>
       <c r="J78" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K78" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L78" s="14" t="inlineStr">
         <is>
-          <t>SEC-01</t>
+          <t>SHR-01</t>
         </is>
       </c>
       <c r="M78" s="14" t="inlineStr">
@@ -8393,74 +8468,75 @@
       <c r="R78" s="19" t="inlineStr"/>
       <c r="S78" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T78" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-02</t>
+          <t>TC-STF-02</t>
         </is>
       </c>
       <c r="B79" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C79" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D79" s="18" t="inlineStr">
         <is>
-          <t>Another employee's request URL</t>
+          <t>My HR on the Department Head dashboard</t>
         </is>
       </c>
       <c r="E79" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Head of department</t>
         </is>
       </c>
       <c r="F79" s="18" t="inlineStr">
         <is>
-          <t>URL of employee 2's request.</t>
+          <t>A head of department with an Employee record and annual leave.</t>
         </is>
       </c>
       <c r="G79" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 opens that URL.</t>
+          <t>1. Open the Department Head dashboard.
+2. Look under the coloured figures.</t>
         </is>
       </c>
       <c r="H79" s="18" t="inlineStr">
         <is>
-          <t>Employee 2 request link</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I79" s="18" t="inlineStr">
         <is>
-          <t>Not permitted; none of its details are shown.</t>
+          <t>The My HR card, in the dashboard's own colours, shows the annual leave left (e.g. 21 of 21 days).</t>
         </is>
       </c>
       <c r="J79" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K79" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L79" s="14" t="inlineStr">
         <is>
-          <t>SEC-02</t>
+          <t>SHR-02</t>
         </is>
       </c>
       <c r="M79" s="14" t="inlineStr">
@@ -8479,60 +8555,61 @@
       <c r="R79" s="19" t="inlineStr"/>
       <c r="S79" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T79" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-03</t>
+          <t>TC-STF-03</t>
         </is>
       </c>
       <c r="B80" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C80" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D80" s="18" t="inlineStr">
         <is>
-          <t>Own Employee record only, read-only</t>
+          <t>Send a request from the card</t>
         </is>
       </c>
       <c r="E80" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Instructor</t>
         </is>
       </c>
       <c r="F80" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-STF-01.</t>
         </is>
       </c>
       <c r="G80" s="18" t="inlineStr">
         <is>
-          <t>1. Open /app/employee.
-2. Try to edit own record.</t>
+          <t>1. New Request &gt; Salary Certificate.
+2. Fill Purpose and Addressee.
+3. Send Request.</t>
         </is>
       </c>
       <c r="H80" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Bank Loan, QA Bank</t>
         </is>
       </c>
       <c r="I80" s="18" t="inlineStr">
         <is>
-          <t>Only own record listed; cannot edit.</t>
+          <t>'Request sent for review'. The card lists the request as Pending with '1 waiting'; HR sees it (bell, TC-APR-10).</t>
         </is>
       </c>
       <c r="J80" s="14" t="inlineStr">
@@ -8542,12 +8619,12 @@
       </c>
       <c r="K80" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L80" s="14" t="inlineStr">
         <is>
-          <t>SEC-03/04</t>
+          <t>SHR-03</t>
         </is>
       </c>
       <c r="M80" s="14" t="inlineStr">
@@ -8566,75 +8643,74 @@
       <c r="R80" s="19" t="inlineStr"/>
       <c r="S80" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T80" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-04</t>
+          <t>TC-STF-04</t>
         </is>
       </c>
       <c r="B81" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C81" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D81" s="18" t="inlineStr">
         <is>
-          <t>HR-only processes</t>
+          <t>Open a request from the card</t>
         </is>
       </c>
       <c r="E81" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Instructor</t>
         </is>
       </c>
       <c r="F81" s="18" t="inlineStr">
         <is>
+          <t>TC-STF-03.</t>
+        </is>
+      </c>
+      <c r="G81" s="18" t="inlineStr">
+        <is>
+          <t>Click View next to the request.</t>
+        </is>
+      </c>
+      <c r="H81" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G81" s="18" t="inlineStr">
-        <is>
-          <t>1. Try to create a Contract Renewal request.
-2. Send a Leave Plan, then try to set its status to Approved (or ask a developer to try through the API).</t>
-        </is>
-      </c>
-      <c r="H81" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I81" s="18" t="inlineStr">
         <is>
-          <t>Contract Renewal refused ('managed by HR'); the Leave Plan is sent but the employee cannot approve it.</t>
+          <t>The same window as on the Employee Portal: status, details, and after a rejection the reason, the history and Send Again.</t>
         </is>
       </c>
       <c r="J81" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K81" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L81" s="14" t="inlineStr">
         <is>
-          <t>SEC-07</t>
+          <t>SHR-04</t>
         </is>
       </c>
       <c r="M81" s="14" t="inlineStr">
@@ -8653,74 +8729,76 @@
       <c r="R81" s="19" t="inlineStr"/>
       <c r="S81" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T81" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-05</t>
+          <t>TC-STF-05</t>
         </is>
       </c>
       <c r="B82" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C82" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D82" s="18" t="inlineStr">
         <is>
-          <t>Employee cannot open HR pages</t>
+          <t>Apply for leave from the card</t>
         </is>
       </c>
       <c r="E82" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Head of department</t>
         </is>
       </c>
       <c r="F82" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>TC-STF-02.</t>
         </is>
       </c>
       <c r="G82" s="18" t="inlineStr">
         <is>
-          <t>Open /app/hr-dashboard, /app/hr-academic-presence/faculty and /app/jameah-data-check.</t>
+          <t>1. Apply for Leave.
+2. Pick the leave type, two working days next month, a reason.
+3. Send Request.</t>
         </is>
       </c>
       <c r="H82" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Two working days</t>
         </is>
       </c>
       <c r="I82" s="18" t="inlineStr">
         <is>
-          <t>'Not authorized' or 'Not permitted'; no HR data.</t>
+          <t>Only the leave the person holds is offered, with the days left. After sending, the card shows 'Waiting for your manager's approval' for those dates.</t>
         </is>
       </c>
       <c r="J82" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K82" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L82" s="14" t="inlineStr">
         <is>
-          <t>SEC-09</t>
+          <t>SHR-05</t>
         </is>
       </c>
       <c r="M82" s="14" t="inlineStr">
@@ -8739,59 +8817,59 @@
       <c r="R82" s="19" t="inlineStr"/>
       <c r="S82" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T82" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-06</t>
+          <t>TC-STF-06</t>
         </is>
       </c>
       <c r="B83" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C83" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D83" s="18" t="inlineStr">
         <is>
-          <t>Login without an Employee record</t>
+          <t>Same requests on the Employee Portal</t>
         </is>
       </c>
       <c r="E83" s="14" t="inlineStr">
         <is>
-          <t>User with no Employee record</t>
+          <t>Instructor</t>
         </is>
       </c>
       <c r="F83" s="18" t="inlineStr">
         <is>
+          <t>TC-STF-03.</t>
+        </is>
+      </c>
+      <c r="G83" s="18" t="inlineStr">
+        <is>
+          <t>Click Employee Portal on the card.</t>
+        </is>
+      </c>
+      <c r="H83" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G83" s="18" t="inlineStr">
-        <is>
-          <t>Log in and open the Employee Dashboard.</t>
-        </is>
-      </c>
-      <c r="H83" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I83" s="18" t="inlineStr">
         <is>
-          <t>Not permitted / not linked message; cannot send requests.</t>
+          <t>The Employee Portal opens and lists the request sent from the card.</t>
         </is>
       </c>
       <c r="J83" s="14" t="inlineStr">
@@ -8801,12 +8879,12 @@
       </c>
       <c r="K83" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L83" s="14" t="inlineStr">
         <is>
-          <t>SEC-11</t>
+          <t>SHR-06</t>
         </is>
       </c>
       <c r="M83" s="14" t="inlineStr">
@@ -8825,59 +8903,59 @@
       <c r="R83" s="19" t="inlineStr"/>
       <c r="S83" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T83" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-07</t>
+          <t>TC-STF-07</t>
         </is>
       </c>
       <c r="B84" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C84" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D84" s="18" t="inlineStr">
         <is>
-          <t>Staff without HR/Employee roles</t>
+          <t>The other staff dashboards</t>
         </is>
       </c>
       <c r="E84" s="14" t="inlineStr">
         <is>
-          <t>Other staff</t>
+          <t>Dean, vice deans, IT, Academic Operations, Student Affairs, Admission, Finance, Clinical, Advisor</t>
         </is>
       </c>
       <c r="F84" s="18" t="inlineStr">
         <is>
+          <t>Each of these logins linked to an Employee record.</t>
+        </is>
+      </c>
+      <c r="G84" s="18" t="inlineStr">
+        <is>
+          <t>Open each dashboard.</t>
+        </is>
+      </c>
+      <c r="H84" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G84" s="18" t="inlineStr">
-        <is>
-          <t>Open the HR and Employee dashboards.</t>
-        </is>
-      </c>
-      <c r="H84" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I84" s="18" t="inlineStr">
         <is>
-          <t>Both refused.</t>
+          <t>The card appears after the dashboard's first row of figures (Advisor: under the heading) and the dashboard works as before.</t>
         </is>
       </c>
       <c r="J84" s="14" t="inlineStr">
@@ -8887,12 +8965,12 @@
       </c>
       <c r="K84" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L84" s="14" t="inlineStr">
         <is>
-          <t>SEC-12</t>
+          <t>SHR-09</t>
         </is>
       </c>
       <c r="M84" s="14" t="inlineStr">
@@ -8911,74 +8989,74 @@
       <c r="R84" s="19" t="inlineStr"/>
       <c r="S84" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T84" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-08</t>
+          <t>TC-STF-08</t>
         </is>
       </c>
       <c r="B85" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C85" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D85" s="18" t="inlineStr">
         <is>
-          <t>Private attachments</t>
+          <t>Staff without an Employee record</t>
         </is>
       </c>
       <c r="E85" s="14" t="inlineStr">
         <is>
-          <t>Second employee</t>
+          <t>Instructor</t>
         </is>
       </c>
       <c r="F85" s="18" t="inlineStr">
         <is>
-          <t>Employee 1 uploaded an invoice (TC-ESS-08).</t>
+          <t>An instructor login not linked to an Employee record.</t>
         </is>
       </c>
       <c r="G85" s="18" t="inlineStr">
         <is>
-          <t>Employee 2 opens the file link.</t>
+          <t>Open the Instructor dashboard.</t>
         </is>
       </c>
       <c r="H85" s="18" t="inlineStr">
         <is>
-          <t>File URL</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I85" s="18" t="inlineStr">
         <is>
-          <t>Refused (403/404). HR can open it.</t>
+          <t>No My HR card and no error: the dashboard is exactly as before.</t>
         </is>
       </c>
       <c r="J85" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K85" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L85" s="14" t="inlineStr">
         <is>
-          <t>APR-08</t>
+          <t>SHR-10</t>
         </is>
       </c>
       <c r="M85" s="14" t="inlineStr">
@@ -8997,74 +9075,76 @@
       <c r="R85" s="19" t="inlineStr"/>
       <c r="S85" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T85" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-09</t>
+          <t>TC-STF-09</t>
         </is>
       </c>
       <c r="B86" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C86" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D86" s="18" t="inlineStr">
         <is>
-          <t>Job application cannot grant admin rights</t>
+          <t>Phone, dark mode and Arabic</t>
         </is>
       </c>
       <c r="E86" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Instructor</t>
         </is>
       </c>
       <c r="F86" s="18" t="inlineStr">
         <is>
+          <t>TC-STF-01.</t>
+        </is>
+      </c>
+      <c r="G86" s="18" t="inlineStr">
+        <is>
+          <t>1. Open the dashboard on a phone (or a narrow window).
+2. Switch to dark mode.
+3. Switch to AR, then back to EN.</t>
+        </is>
+      </c>
+      <c r="H86" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G86" s="18" t="inlineStr">
-        <is>
-          <t>Create a Job Application Link and look at the Role list.</t>
-        </is>
-      </c>
-      <c r="H86" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I86" s="18" t="inlineStr">
         <is>
-          <t>Only hireable roles are offered (Employee, Instructor, Academic Advisor...), never System Manager or HR roles.</t>
+          <t>The card fits the screen with no sideways scrolling; it is readable in dark mode; in Arabic it reads 'شؤوني الوظيفية', right to left.</t>
         </is>
       </c>
       <c r="J86" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K86" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L86" s="14" t="inlineStr">
         <is>
-          <t>REC-02</t>
+          <t>SHR-07, SHR-08</t>
         </is>
       </c>
       <c r="M86" s="14" t="inlineStr">
@@ -9083,49 +9163,49 @@
       <c r="R86" s="19" t="inlineStr"/>
       <c r="S86" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T86" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" s="16" t="inlineStr">
         <is>
-          <t>TC-SEC-10</t>
+          <t>TC-STF-10</t>
         </is>
       </c>
       <c r="B87" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C87" s="14" t="inlineStr">
         <is>
-          <t>Security &amp; privacy</t>
+          <t>Staff dashboards (My HR)</t>
         </is>
       </c>
       <c r="D87" s="18" t="inlineStr">
         <is>
-          <t>Server methods refuse the wrong role</t>
+          <t>Employee Portal unchanged</t>
         </is>
       </c>
       <c r="E87" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F87" s="18" t="inlineStr">
         <is>
-          <t>QA logins loaded (qa_fixtures.py), bench running.</t>
+          <t>Employee login.</t>
         </is>
       </c>
       <c r="G87" s="18" t="inlineStr">
         <is>
-          <t>python3 tests/checks/api_methods.py</t>
+          <t>Repeat TC-ESS-17 (Edit Draft), TC-ESS-19 (rejection reason and history) and TC-ESS-20 (Send Again) on the Employee Portal.</t>
         </is>
       </c>
       <c r="H87" s="18" t="inlineStr">
@@ -9135,22 +9215,22 @@
       </c>
       <c r="I87" s="18" t="inlineStr">
         <is>
-          <t>Every method: refused (403) for a visitor except the job form and receipt; HR-only methods refused for employees; no server error (500); no method left out of the check.</t>
+          <t>All work as in Round 2 (the request windows are now shared with the card).</t>
         </is>
       </c>
       <c r="J87" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K87" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L87" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/api_methods.py</t>
+          <t>ESS-01..19</t>
         </is>
       </c>
       <c r="M87" s="14" t="inlineStr">
@@ -9169,19 +9249,19 @@
       <c r="R87" s="19" t="inlineStr"/>
       <c r="S87" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T87" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-01</t>
+          <t>TC-SEC-01</t>
         </is>
       </c>
       <c r="B88" s="14" t="inlineStr">
@@ -9191,37 +9271,37 @@
       </c>
       <c r="C88" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D88" s="18" t="inlineStr">
         <is>
-          <t>Edit and save an employee who has a login</t>
+          <t>Employees see only their own requests</t>
         </is>
       </c>
       <c r="E88" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F88" s="18" t="inlineStr">
         <is>
-          <t>Employee with a user login.</t>
+          <t>Two employees each sent a request.</t>
         </is>
       </c>
       <c r="G88" s="18" t="inlineStr">
         <is>
-          <t>Change the mobile number; Save.</t>
+          <t>Employee 1 opens each request list.</t>
         </is>
       </c>
       <c r="H88" s="18" t="inlineStr">
         <is>
-          <t>New mobile</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I88" s="18" t="inlineStr">
         <is>
-          <t>Saved with no error (this used to fail with 'Could not find Gender').</t>
+          <t>Only their own requests appear.</t>
         </is>
       </c>
       <c r="J88" s="14" t="inlineStr">
@@ -9231,12 +9311,12 @@
       </c>
       <c r="K88" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L88" s="14" t="inlineStr">
         <is>
-          <t>EMP-01</t>
+          <t>SEC-01</t>
         </is>
       </c>
       <c r="M88" s="14" t="inlineStr">
@@ -9267,7 +9347,7 @@
     <row r="89">
       <c r="A89" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-02</t>
+          <t>TC-SEC-02</t>
         </is>
       </c>
       <c r="B89" s="14" t="inlineStr">
@@ -9277,52 +9357,52 @@
       </c>
       <c r="C89" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D89" s="18" t="inlineStr">
         <is>
-          <t>Lookup fields only offer their own list</t>
+          <t>Another employee's request URL</t>
         </is>
       </c>
       <c r="E89" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F89" s="18" t="inlineStr">
         <is>
-          <t>Employee form open.</t>
+          <t>URL of employee 2's request.</t>
         </is>
       </c>
       <c r="G89" s="18" t="inlineStr">
         <is>
-          <t>Open Gender, Nationality, Identity Type and Religion drop-downs.</t>
+          <t>Employee 1 opens that URL.</t>
         </is>
       </c>
       <c r="H89" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Employee 2 request link</t>
         </is>
       </c>
       <c r="I89" s="18" t="inlineStr">
         <is>
-          <t>Each shows only its Ministry list (e.g. Gender: Male, Female).</t>
+          <t>Not permitted; none of its details are shown.</t>
         </is>
       </c>
       <c r="J89" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K89" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L89" s="14" t="inlineStr">
         <is>
-          <t>EMP-02/03</t>
+          <t>SEC-02</t>
         </is>
       </c>
       <c r="M89" s="14" t="inlineStr">
@@ -9353,7 +9433,7 @@
     <row r="90">
       <c r="A90" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-03</t>
+          <t>TC-SEC-03</t>
         </is>
       </c>
       <c r="B90" s="14" t="inlineStr">
@@ -9363,17 +9443,17 @@
       </c>
       <c r="C90" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D90" s="18" t="inlineStr">
         <is>
-          <t>Invalid national ID</t>
+          <t>Own Employee record only, read-only</t>
         </is>
       </c>
       <c r="E90" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F90" s="18" t="inlineStr">
@@ -9383,17 +9463,18 @@
       </c>
       <c r="G90" s="18" t="inlineStr">
         <is>
-          <t>Set Identity Number to 12345 and Save.</t>
+          <t>1. Open /app/employee.
+2. Try to edit own record.</t>
         </is>
       </c>
       <c r="H90" s="18" t="inlineStr">
         <is>
-          <t>12345</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I90" s="18" t="inlineStr">
         <is>
-          <t>Refused: a National ID has exactly 10 digits.</t>
+          <t>Only own record listed; cannot edit.</t>
         </is>
       </c>
       <c r="J90" s="14" t="inlineStr">
@@ -9403,12 +9484,12 @@
       </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L90" s="14" t="inlineStr">
         <is>
-          <t>EMP-05</t>
+          <t>SEC-03/04</t>
         </is>
       </c>
       <c r="M90" s="14" t="inlineStr">
@@ -9439,7 +9520,7 @@
     <row r="91">
       <c r="A91" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-04</t>
+          <t>TC-SEC-04</t>
         </is>
       </c>
       <c r="B91" s="14" t="inlineStr">
@@ -9449,37 +9530,38 @@
       </c>
       <c r="C91" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D91" s="18" t="inlineStr">
         <is>
-          <t>Duplicate identity number</t>
+          <t>HR-only processes</t>
         </is>
       </c>
       <c r="E91" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F91" s="18" t="inlineStr">
         <is>
-          <t>Another employee's ID number.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G91" s="18" t="inlineStr">
         <is>
-          <t>Enter it on a different employee; Save.</t>
+          <t>1. Try to create a Contract Renewal request.
+2. Send a Leave Plan, then try to set its status to Approved (or ask a developer to try through the API).</t>
         </is>
       </c>
       <c r="H91" s="18" t="inlineStr">
         <is>
-          <t>Existing ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I91" s="18" t="inlineStr">
         <is>
-          <t>Refused: already registered to &lt;employee&gt;.</t>
+          <t>Contract Renewal refused ('managed by HR'); the Leave Plan is sent but the employee cannot approve it.</t>
         </is>
       </c>
       <c r="J91" s="14" t="inlineStr">
@@ -9489,12 +9571,12 @@
       </c>
       <c r="K91" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L91" s="14" t="inlineStr">
         <is>
-          <t>EMP-06</t>
+          <t>SEC-07</t>
         </is>
       </c>
       <c r="M91" s="14" t="inlineStr">
@@ -9518,14 +9600,14 @@
       </c>
       <c r="T91" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-05</t>
+          <t>TC-SEC-05</t>
         </is>
       </c>
       <c r="B92" s="14" t="inlineStr">
@@ -9535,17 +9617,17 @@
       </c>
       <c r="C92" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D92" s="18" t="inlineStr">
         <is>
-          <t>National ID for a non-Saudi</t>
+          <t>Employee cannot open HR pages</t>
         </is>
       </c>
       <c r="E92" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F92" s="18" t="inlineStr">
@@ -9555,7 +9637,7 @@
       </c>
       <c r="G92" s="18" t="inlineStr">
         <is>
-          <t>Nationality not Saudi, Identity Type National ID; Save.</t>
+          <t>Open /app/hr-dashboard, /app/hr-academic-presence/faculty and /app/jameah-data-check.</t>
         </is>
       </c>
       <c r="H92" s="18" t="inlineStr">
@@ -9565,27 +9647,27 @@
       </c>
       <c r="I92" s="18" t="inlineStr">
         <is>
-          <t>Refused: National ID is only for Saudis.</t>
+          <t>'Not authorized' or 'Not permitted'; no HR data.</t>
         </is>
       </c>
       <c r="J92" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K92" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L92" s="14" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>SEC-09</t>
         </is>
       </c>
       <c r="M92" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N92" s="19" t="inlineStr">
@@ -9611,7 +9693,7 @@
     <row r="93">
       <c r="A93" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-09</t>
+          <t>TC-SEC-06</t>
         </is>
       </c>
       <c r="B93" s="14" t="inlineStr">
@@ -9621,54 +9703,52 @@
       </c>
       <c r="C93" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D93" s="18" t="inlineStr">
         <is>
-          <t>Non-Saudi employee with an Iqama</t>
+          <t>Login without an Employee record</t>
         </is>
       </c>
       <c r="E93" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>User with no Employee record</t>
         </is>
       </c>
       <c r="F93" s="18" t="inlineStr">
         <is>
-          <t>An employee whose Nationality is not Saudi and Identity Type is Iqama.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G93" s="18" t="inlineStr">
         <is>
-          <t>1. Open the employee.
-2. Look at Identity Number and ID Number in Country of Origin.
-3. Change any field and Save.</t>
+          <t>Log in and open the Employee Dashboard.</t>
         </is>
       </c>
       <c r="H93" s="18" t="inlineStr">
         <is>
-          <t>Iqama 2XXXXXXXXX</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I93" s="18" t="inlineStr">
         <is>
-          <t>The record opens without 'Not Saved'. Identity Number still shows the Iqama and is mandatory; the home-country ID is optional. Save works.</t>
+          <t>Not permitted / not linked message; cannot send requests.</t>
         </is>
       </c>
       <c r="J93" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K93" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L93" s="14" t="inlineStr">
         <is>
-          <t>EMP-08</t>
+          <t>SEC-11</t>
         </is>
       </c>
       <c r="M93" s="14" t="inlineStr">
@@ -9699,7 +9779,7 @@
     <row r="94">
       <c r="A94" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-06</t>
+          <t>TC-SEC-07</t>
         </is>
       </c>
       <c r="B94" s="14" t="inlineStr">
@@ -9709,17 +9789,17 @@
       </c>
       <c r="C94" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D94" s="18" t="inlineStr">
         <is>
-          <t>Qualification 'Appreciation' list</t>
+          <t>Staff without HR/Employee roles</t>
         </is>
       </c>
       <c r="E94" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Other staff</t>
         </is>
       </c>
       <c r="F94" s="18" t="inlineStr">
@@ -9729,7 +9809,7 @@
       </c>
       <c r="G94" s="18" t="inlineStr">
         <is>
-          <t>Add a qualification row; open Appreciation.</t>
+          <t>Open the HR and Employee dashboards.</t>
         </is>
       </c>
       <c r="H94" s="18" t="inlineStr">
@@ -9739,22 +9819,22 @@
       </c>
       <c r="I94" s="18" t="inlineStr">
         <is>
-          <t>Grades are offered (Excellent, Very good, Good...), not GPA systems.</t>
+          <t>Both refused.</t>
         </is>
       </c>
       <c r="J94" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K94" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L94" s="14" t="inlineStr">
         <is>
-          <t>REC-05</t>
+          <t>SEC-12</t>
         </is>
       </c>
       <c r="M94" s="14" t="inlineStr">
@@ -9785,7 +9865,7 @@
     <row r="95">
       <c r="A95" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-07</t>
+          <t>TC-SEC-08</t>
         </is>
       </c>
       <c r="B95" s="14" t="inlineStr">
@@ -9795,52 +9875,52 @@
       </c>
       <c r="C95" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D95" s="18" t="inlineStr">
         <is>
-          <t>Ministry (Jameah) Data preview</t>
+          <t>Private attachments</t>
         </is>
       </c>
       <c r="E95" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Second employee</t>
         </is>
       </c>
       <c r="F95" s="18" t="inlineStr">
         <is>
-          <t>An employee of Al Riyada College.</t>
+          <t>Employee 1 uploaded an invoice (TC-ESS-08).</t>
         </is>
       </c>
       <c r="G95" s="18" t="inlineStr">
         <is>
-          <t>Employee form -&gt; View -&gt; Ministry (Jameah) Data.</t>
+          <t>Employee 2 opens the file link.</t>
         </is>
       </c>
       <c r="H95" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>File URL</t>
         </is>
       </c>
       <c r="I95" s="18" t="inlineStr">
         <is>
-          <t>Pop-up with the 5 Ministry sections; lookup columns show codes (e.g. Nationality 101).</t>
+          <t>Refused (403/404). HR can open it.</t>
         </is>
       </c>
       <c r="J95" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K95" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L95" s="14" t="inlineStr">
         <is>
-          <t>EMP-07</t>
+          <t>APR-08</t>
         </is>
       </c>
       <c r="M95" s="14" t="inlineStr">
@@ -9871,7 +9951,7 @@
     <row r="96">
       <c r="A96" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-08</t>
+          <t>TC-SEC-09</t>
         </is>
       </c>
       <c r="B96" s="14" t="inlineStr">
@@ -9881,12 +9961,12 @@
       </c>
       <c r="C96" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D96" s="18" t="inlineStr">
         <is>
-          <t>Teaching staff are not sent as Employees</t>
+          <t>Job application cannot grant admin rights</t>
         </is>
       </c>
       <c r="E96" s="14" t="inlineStr">
@@ -9896,12 +9976,12 @@
       </c>
       <c r="F96" s="18" t="inlineStr">
         <is>
-          <t>An employee linked to an Instructor.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G96" s="18" t="inlineStr">
         <is>
-          <t>Open the Ministry (Jameah) Data preview.</t>
+          <t>Create a Job Application Link and look at the Role list.</t>
         </is>
       </c>
       <c r="H96" s="18" t="inlineStr">
@@ -9911,22 +9991,22 @@
       </c>
       <c r="I96" s="18" t="inlineStr">
         <is>
-          <t>Says the person is sent as Faculty, not as an Employee.</t>
+          <t>Only hireable roles are offered (Employee, Instructor, Academic Advisor...), never System Manager or HR roles.</t>
         </is>
       </c>
       <c r="J96" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K96" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L96" s="14" t="inlineStr">
         <is>
-          <t>REC-07</t>
+          <t>REC-02</t>
         </is>
       </c>
       <c r="M96" s="14" t="inlineStr">
@@ -9957,7 +10037,7 @@
     <row r="97">
       <c r="A97" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-10</t>
+          <t>TC-SEC-10</t>
         </is>
       </c>
       <c r="B97" s="14" t="inlineStr">
@@ -9967,29 +10047,27 @@
       </c>
       <c r="C97" s="14" t="inlineStr">
         <is>
-          <t>Employee master &amp; Ministry fields</t>
+          <t>Security &amp; privacy</t>
         </is>
       </c>
       <c r="D97" s="18" t="inlineStr">
         <is>
-          <t>Report: Employees Missing Ministry Data</t>
+          <t>Server methods refuse the wrong role</t>
         </is>
       </c>
       <c r="E97" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F97" s="18" t="inlineStr">
         <is>
-          <t>Some employees with empty Ministry fields.</t>
+          <t>QA logins loaded (qa_fixtures.py), bench running.</t>
         </is>
       </c>
       <c r="G97" s="18" t="inlineStr">
         <is>
-          <t>1. HR Portal menu &gt; Ministry (Jameah) &gt; Employees Missing Ministry Data.
-2. Tick 'Show complete employees too'.
-3. Filter by a department.</t>
+          <t>python3 tests/checks/api_methods.py</t>
         </is>
       </c>
       <c r="H97" s="18" t="inlineStr">
@@ -9999,22 +10077,22 @@
       </c>
       <c r="I97" s="18" t="inlineStr">
         <is>
-          <t>Each employee with gaps is listed with the number of missing values and their names as on the Employee form (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). The tick also lists complete employees; the filter works.</t>
+          <t>Every method: refused (403) for a visitor except the job form and receipt; HR-only methods refused for employees; no server error (500); no method left out of the check.</t>
         </is>
       </c>
       <c r="J97" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K97" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L97" s="14" t="inlineStr">
         <is>
-          <t>RPT-01</t>
+          <t>tests/checks/api_methods.py</t>
         </is>
       </c>
       <c r="M97" s="14" t="inlineStr">
@@ -10033,19 +10111,19 @@
       <c r="R97" s="19" t="inlineStr"/>
       <c r="S97" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="T97" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-11</t>
+          <t>TC-EMP-01</t>
         </is>
       </c>
       <c r="B98" s="14" t="inlineStr">
@@ -10060,7 +10138,7 @@
       </c>
       <c r="D98" s="18" t="inlineStr">
         <is>
-          <t>Data sheet for non-academic staff: download, check, import</t>
+          <t>Edit and save an employee who has a login</t>
         </is>
       </c>
       <c r="E98" s="14" t="inlineStr">
@@ -10070,45 +10148,42 @@
       </c>
       <c r="F98" s="18" t="inlineStr">
         <is>
-          <t>HR Manager account.</t>
+          <t>Employee with a user login.</t>
         </is>
       </c>
       <c r="G98" s="18" t="inlineStr">
         <is>
-          <t>1. In the report: Download Data Sheet.
-2. Fill one red cell for an employee; type 31-31-2020 as another employee's date of birth.
-3. Check / Import Data Sheet &gt; attach the file &gt; Check.
-4. Fix the date and click Import.</t>
+          <t>Change the mobile number; Save.</t>
         </is>
       </c>
       <c r="H98" s="18" t="inlineStr">
         <is>
-          <t>Edited .xlsx</t>
+          <t>New mobile</t>
         </is>
       </c>
       <c r="I98" s="18" t="inlineStr">
         <is>
-          <t>The sheet lists the non-teaching employees, red = Ministry-required and empty. Check reports the wrong date and saves nothing. Import updates only the changed cells; the result sheet gives each row's status.</t>
+          <t>Saved with no error (this used to fail with 'Could not find Gender').</t>
         </is>
       </c>
       <c r="J98" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K98" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L98" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>EMP-01</t>
         </is>
       </c>
       <c r="M98" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N98" s="19" t="inlineStr">
@@ -10134,7 +10209,7 @@
     <row r="99">
       <c r="A99" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-12</t>
+          <t>TC-EMP-02</t>
         </is>
       </c>
       <c r="B99" s="14" t="inlineStr">
@@ -10149,22 +10224,22 @@
       </c>
       <c r="D99" s="18" t="inlineStr">
         <is>
-          <t>Only an HR Manager can import the data sheet</t>
+          <t>Lookup fields only offer their own list</t>
         </is>
       </c>
       <c r="E99" s="14" t="inlineStr">
         <is>
-          <t>HR User</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F99" s="18" t="inlineStr">
         <is>
-          <t>HR User account.</t>
+          <t>Employee form open.</t>
         </is>
       </c>
       <c r="G99" s="18" t="inlineStr">
         <is>
-          <t>Open the Employees Missing Ministry Data report.</t>
+          <t>Open Gender, Nationality, Identity Type and Religion drop-downs.</t>
         </is>
       </c>
       <c r="H99" s="18" t="inlineStr">
@@ -10174,22 +10249,22 @@
       </c>
       <c r="I99" s="18" t="inlineStr">
         <is>
-          <t>The report opens; there are no Download Data Sheet / Check / Import buttons.</t>
+          <t>Each shows only its Ministry list (e.g. Gender: Male, Female).</t>
         </is>
       </c>
       <c r="J99" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K99" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L99" s="14" t="inlineStr">
         <is>
-          <t>RPT-02</t>
+          <t>EMP-02/03</t>
         </is>
       </c>
       <c r="M99" s="14" t="inlineStr">
@@ -10220,12 +10295,12 @@
     <row r="100">
       <c r="A100" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-13</t>
+          <t>TC-EMP-03</t>
         </is>
       </c>
       <c r="B100" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Round 1</t>
         </is>
       </c>
       <c r="C100" s="14" t="inlineStr">
@@ -10235,34 +10310,32 @@
       </c>
       <c r="D100" s="18" t="inlineStr">
         <is>
-          <t>Link an Employee on the Instructor form</t>
+          <t>Invalid national ID</t>
         </is>
       </c>
       <c r="E100" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F100" s="18" t="inlineStr">
         <is>
-          <t>A login that can edit Instructors and see Employees; an Instructor without an Employee and that person's Employee record.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G100" s="18" t="inlineStr">
         <is>
-          <t>1. Open the Instructor.
-2. Pick the Employee.
-3. Save.</t>
+          <t>Set Identity Number to 12345 and Save.</t>
         </is>
       </c>
       <c r="H100" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>12345</t>
         </is>
       </c>
       <c r="I100" s="18" t="inlineStr">
         <is>
-          <t>Department fills in when it is in the academic list; Gender fills in (or, for a login that cannot open the Gender list, on save). The Instructor saves with Gender set. Before the fix: 'Could not find Gender: Gender::1'.</t>
+          <t>Refused: a National ID has exactly 10 digits.</t>
         </is>
       </c>
       <c r="J100" s="14" t="inlineStr">
@@ -10272,12 +10345,12 @@
       </c>
       <c r="K100" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L100" s="14" t="inlineStr">
         <is>
-          <t>REC-11</t>
+          <t>EMP-05</t>
         </is>
       </c>
       <c r="M100" s="14" t="inlineStr">
@@ -10296,24 +10369,24 @@
       <c r="R100" s="19" t="inlineStr"/>
       <c r="S100" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T100" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="16" t="inlineStr">
         <is>
-          <t>TC-EMP-14</t>
+          <t>TC-EMP-04</t>
         </is>
       </c>
       <c r="B101" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Round 1</t>
         </is>
       </c>
       <c r="C101" s="14" t="inlineStr">
@@ -10323,54 +10396,52 @@
       </c>
       <c r="D101" s="18" t="inlineStr">
         <is>
-          <t>Link an Employee on the Academic Advisor form</t>
+          <t>Duplicate identity number</t>
         </is>
       </c>
       <c r="E101" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F101" s="18" t="inlineStr">
         <is>
-          <t>As TC-EMP-13, for an Academic Advisor.</t>
+          <t>Another employee's ID number.</t>
         </is>
       </c>
       <c r="G101" s="18" t="inlineStr">
         <is>
-          <t>1. Open the Academic Advisor.
-2. Pick the Employee.
-3. Save.</t>
+          <t>Enter it on a different employee; Save.</t>
         </is>
       </c>
       <c r="H101" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Existing ID</t>
         </is>
       </c>
       <c r="I101" s="18" t="inlineStr">
         <is>
-          <t>The record saves with Gender set from the Employee.</t>
+          <t>Refused: already registered to &lt;employee&gt;.</t>
         </is>
       </c>
       <c r="J101" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K101" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L101" s="14" t="inlineStr">
         <is>
-          <t>unit tests</t>
+          <t>EMP-06</t>
         </is>
       </c>
       <c r="M101" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N101" s="19" t="inlineStr">
@@ -10384,19 +10455,19 @@
       <c r="R101" s="19" t="inlineStr"/>
       <c r="S101" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T101" s="14" t="inlineStr">
         <is>
-          <t>27 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="16" t="inlineStr">
         <is>
-          <t>TC-LIC-01</t>
+          <t>TC-EMP-05</t>
         </is>
       </c>
       <c r="B102" s="14" t="inlineStr">
@@ -10406,12 +10477,12 @@
       </c>
       <c r="C102" s="14" t="inlineStr">
         <is>
-          <t>Medical licences</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D102" s="18" t="inlineStr">
         <is>
-          <t>HR creates a licence</t>
+          <t>National ID for a non-Saudi</t>
         </is>
       </c>
       <c r="E102" s="14" t="inlineStr">
@@ -10426,7 +10497,7 @@
       </c>
       <c r="G102" s="18" t="inlineStr">
         <is>
-          <t>New Employee Medical License: employee, type, number, expiry; Save.</t>
+          <t>Nationality not Saudi, Identity Type National ID; Save.</t>
         </is>
       </c>
       <c r="H102" s="18" t="inlineStr">
@@ -10436,7 +10507,7 @@
       </c>
       <c r="I102" s="18" t="inlineStr">
         <is>
-          <t>Saved.</t>
+          <t>Refused: National ID is only for Saudis.</t>
         </is>
       </c>
       <c r="J102" s="14" t="inlineStr">
@@ -10446,17 +10517,17 @@
       </c>
       <c r="K102" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L102" s="14" t="inlineStr">
         <is>
-          <t>LIC-01</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="M102" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N102" s="19" t="inlineStr">
@@ -10482,7 +10553,7 @@
     <row r="103">
       <c r="A103" s="16" t="inlineStr">
         <is>
-          <t>TC-LIC-02</t>
+          <t>TC-EMP-09</t>
         </is>
       </c>
       <c r="B103" s="14" t="inlineStr">
@@ -10492,52 +10563,54 @@
       </c>
       <c r="C103" s="14" t="inlineStr">
         <is>
-          <t>Medical licences</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D103" s="18" t="inlineStr">
         <is>
-          <t>Employees see only their own licence</t>
+          <t>Non-Saudi employee with an Iqama</t>
         </is>
       </c>
       <c r="E103" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F103" s="18" t="inlineStr">
         <is>
-          <t>Licences for two employees.</t>
+          <t>An employee whose Nationality is not Saudi and Identity Type is Iqama.</t>
         </is>
       </c>
       <c r="G103" s="18" t="inlineStr">
         <is>
-          <t>Each employee opens the licence list.</t>
+          <t>1. Open the employee.
+2. Look at Identity Number and ID Number in Country of Origin.
+3. Change any field and Save.</t>
         </is>
       </c>
       <c r="H103" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Iqama 2XXXXXXXXX</t>
         </is>
       </c>
       <c r="I103" s="18" t="inlineStr">
         <is>
-          <t>Only their own licence.</t>
+          <t>The record opens without 'Not Saved'. Identity Number still shows the Iqama and is mandatory; the home-country ID is optional. Save works.</t>
         </is>
       </c>
       <c r="J103" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K103" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L103" s="14" t="inlineStr">
         <is>
-          <t>LIC-02</t>
+          <t>EMP-08</t>
         </is>
       </c>
       <c r="M103" s="14" t="inlineStr">
@@ -10568,7 +10641,7 @@
     <row r="104">
       <c r="A104" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-01</t>
+          <t>TC-EMP-06</t>
         </is>
       </c>
       <c r="B104" s="14" t="inlineStr">
@@ -10578,12 +10651,12 @@
       </c>
       <c r="C104" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D104" s="18" t="inlineStr">
         <is>
-          <t>Create and generate an application link</t>
+          <t>Qualification 'Appreciation' list</t>
         </is>
       </c>
       <c r="E104" s="14" t="inlineStr">
@@ -10598,10 +10671,7 @@
       </c>
       <c r="G104" s="18" t="inlineStr">
         <is>
-          <t>1. New Job Application Link.
-2. Category Academic Staff, Role Instructor, valid from/until.
-3. Save.
-4. Generate Link.</t>
+          <t>Add a qualification row; open Appreciation.</t>
         </is>
       </c>
       <c r="H104" s="18" t="inlineStr">
@@ -10611,7 +10681,7 @@
       </c>
       <c r="I104" s="18" t="inlineStr">
         <is>
-          <t>A link is shown and can be copied.</t>
+          <t>Grades are offered (Excellent, Very good, Good...), not GPA systems.</t>
         </is>
       </c>
       <c r="J104" s="14" t="inlineStr">
@@ -10621,12 +10691,12 @@
       </c>
       <c r="K104" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L104" s="14" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>REC-05</t>
         </is>
       </c>
       <c r="M104" s="14" t="inlineStr">
@@ -10657,7 +10727,7 @@
     <row r="105">
       <c r="A105" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-02</t>
+          <t>TC-EMP-07</t>
         </is>
       </c>
       <c r="B105" s="14" t="inlineStr">
@@ -10667,37 +10737,37 @@
       </c>
       <c r="C105" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D105" s="18" t="inlineStr">
         <is>
-          <t>Invalid or expired link</t>
+          <t>Ministry (Jameah) Data preview</t>
         </is>
       </c>
       <c r="E105" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F105" s="18" t="inlineStr">
         <is>
+          <t>An employee of Al Riyada College.</t>
+        </is>
+      </c>
+      <c r="G105" s="18" t="inlineStr">
+        <is>
+          <t>Employee form -&gt; View -&gt; Ministry (Jameah) Data.</t>
+        </is>
+      </c>
+      <c r="H105" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G105" s="18" t="inlineStr">
-        <is>
-          <t>Open /job-application/abc123 and an expired link.</t>
-        </is>
-      </c>
-      <c r="H105" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
       <c r="I105" s="18" t="inlineStr">
         <is>
-          <t>'Link is invalid / not active' message; no form.</t>
+          <t>Pop-up with the 5 Ministry sections; lookup columns show codes (e.g. Nationality 101).</t>
         </is>
       </c>
       <c r="J105" s="14" t="inlineStr">
@@ -10707,12 +10777,12 @@
       </c>
       <c r="K105" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L105" s="14" t="inlineStr">
         <is>
-          <t>REC-01</t>
+          <t>EMP-07</t>
         </is>
       </c>
       <c r="M105" s="14" t="inlineStr">
@@ -10743,7 +10813,7 @@
     <row r="106">
       <c r="A106" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-03</t>
+          <t>TC-EMP-08</t>
         </is>
       </c>
       <c r="B106" s="14" t="inlineStr">
@@ -10753,27 +10823,27 @@
       </c>
       <c r="C106" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D106" s="18" t="inlineStr">
         <is>
-          <t>Required fields on the public form</t>
+          <t>Teaching staff are not sent as Employees</t>
         </is>
       </c>
       <c r="E106" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F106" s="18" t="inlineStr">
         <is>
-          <t>Valid link.</t>
+          <t>An employee linked to an Instructor.</t>
         </is>
       </c>
       <c r="G106" s="18" t="inlineStr">
         <is>
-          <t>Click Submit with the form empty.</t>
+          <t>Open the Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="H106" s="18" t="inlineStr">
@@ -10783,7 +10853,7 @@
       </c>
       <c r="I106" s="18" t="inlineStr">
         <is>
-          <t>Browser highlights the required fields; nothing is sent.</t>
+          <t>Says the person is sent as Faculty, not as an Employee.</t>
         </is>
       </c>
       <c r="J106" s="14" t="inlineStr">
@@ -10793,17 +10863,17 @@
       </c>
       <c r="K106" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L106" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-07</t>
         </is>
       </c>
       <c r="M106" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N106" s="19" t="inlineStr">
@@ -10829,7 +10899,7 @@
     <row r="107">
       <c r="A107" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-04</t>
+          <t>TC-EMP-10</t>
         </is>
       </c>
       <c r="B107" s="14" t="inlineStr">
@@ -10839,42 +10909,44 @@
       </c>
       <c r="C107" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D107" s="18" t="inlineStr">
         <is>
-          <t>Applicant submits the full form</t>
+          <t>Report: Employees Missing Ministry Data</t>
         </is>
       </c>
       <c r="E107" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F107" s="18" t="inlineStr">
         <is>
-          <t>Valid link.</t>
+          <t>Some employees with empty Ministry fields.</t>
         </is>
       </c>
       <c r="G107" s="18" t="inlineStr">
         <is>
-          <t>Fill every section (names in Arabic and English, ID, qualifications, experience) and Submit.</t>
+          <t>1. HR Portal menu &gt; Ministry (Jameah) &gt; Employees Missing Ministry Data.
+2. Tick 'Show complete employees too'.
+3. Filter by a department.</t>
         </is>
       </c>
       <c r="H107" s="18" t="inlineStr">
         <is>
-          <t>Saudi national ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I107" s="18" t="inlineStr">
         <is>
-          <t>'Thank you' with a reference number APP-....</t>
+          <t>Each employee with gaps is listed with the number of missing values and their names as on the Employee form (e.g. 'First Name (Arabic)', 'Academic Qualification (1 row): Academic qualification'). The tick also lists complete employees; the filter works.</t>
         </is>
       </c>
       <c r="J107" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K107" s="14" t="inlineStr">
@@ -10884,7 +10956,7 @@
       </c>
       <c r="L107" s="14" t="inlineStr">
         <is>
-          <t>REC-03..05</t>
+          <t>RPT-01</t>
         </is>
       </c>
       <c r="M107" s="14" t="inlineStr">
@@ -10915,7 +10987,7 @@
     <row r="108">
       <c r="A108" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-05</t>
+          <t>TC-EMP-11</t>
         </is>
       </c>
       <c r="B108" s="14" t="inlineStr">
@@ -10925,12 +10997,12 @@
       </c>
       <c r="C108" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D108" s="18" t="inlineStr">
         <is>
-          <t>Accept and create an Instructor</t>
+          <t>Data sheet for non-academic staff: download, check, import</t>
         </is>
       </c>
       <c r="E108" s="14" t="inlineStr">
@@ -10940,30 +11012,30 @@
       </c>
       <c r="F108" s="18" t="inlineStr">
         <is>
-          <t>TC-REC-04 for an Instructor link.</t>
+          <t>HR Manager account.</t>
         </is>
       </c>
       <c r="G108" s="18" t="inlineStr">
         <is>
-          <t>1. Open the applicant.
-2. Accept.
-3. Create Employee: Company Email = official college address, department.
-4. Confirm.</t>
+          <t>1. In the report: Download Data Sheet.
+2. Fill one red cell for an employee; type 31-31-2020 as another employee's date of birth.
+3. Check / Import Data Sheet &gt; attach the file &gt; Check.
+4. Fix the date and click Import.</t>
         </is>
       </c>
       <c r="H108" s="18" t="inlineStr">
         <is>
-          <t>name.surname@alriyada.edu.sa</t>
+          <t>Edited .xlsx</t>
         </is>
       </c>
       <c r="I108" s="18" t="inlineStr">
         <is>
-          <t>Message lists Employee and Instructor created; the new login has Employee + Instructor roles.</t>
+          <t>The sheet lists the non-teaching employees, red = Ministry-required and empty. Check reports the wrong date and saves nothing. Import updates only the changed cells; the result sheet gives each row's status.</t>
         </is>
       </c>
       <c r="J108" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K108" s="14" t="inlineStr">
@@ -10973,12 +11045,12 @@
       </c>
       <c r="L108" s="14" t="inlineStr">
         <is>
-          <t>REC-03</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="M108" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N108" s="19" t="inlineStr">
@@ -11004,7 +11076,7 @@
     <row r="109">
       <c r="A109" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-06</t>
+          <t>TC-EMP-12</t>
         </is>
       </c>
       <c r="B109" s="14" t="inlineStr">
@@ -11014,52 +11086,52 @@
       </c>
       <c r="C109" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D109" s="18" t="inlineStr">
         <is>
-          <t>Hire an Academic Advisor</t>
+          <t>Only an HR Manager can import the data sheet</t>
         </is>
       </c>
       <c r="E109" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>HR User</t>
         </is>
       </c>
       <c r="F109" s="18" t="inlineStr">
         <is>
-          <t>Applicant for an Academic Advisor link with a phone like 05XXXXXXXX.</t>
+          <t>HR User account.</t>
         </is>
       </c>
       <c r="G109" s="18" t="inlineStr">
         <is>
-          <t>Accept -&gt; Create Employee with a @alriyada.edu.sa Company Email.</t>
+          <t>Open the Employees Missing Ministry Data report.</t>
         </is>
       </c>
       <c r="H109" s="18" t="inlineStr">
         <is>
-          <t>Local phone number</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I109" s="18" t="inlineStr">
         <is>
-          <t>Employee, Academic Advisor and Instructor records created; no 'record not created' warning.</t>
+          <t>The report opens; there are no Download Data Sheet / Check / Import buttons.</t>
         </is>
       </c>
       <c r="J109" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K109" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L109" s="14" t="inlineStr">
         <is>
-          <t>REC-04</t>
+          <t>RPT-02</t>
         </is>
       </c>
       <c r="M109" s="14" t="inlineStr">
@@ -11090,37 +11162,39 @@
     <row r="110">
       <c r="A110" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-07</t>
+          <t>TC-EMP-13</t>
         </is>
       </c>
       <c r="B110" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C110" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D110" s="18" t="inlineStr">
         <is>
-          <t>Hire non-academic staff</t>
+          <t>Link an Employee on the Instructor form</t>
         </is>
       </c>
       <c r="E110" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F110" s="18" t="inlineStr">
         <is>
-          <t>Applicant for a Non-Academic link.</t>
+          <t>A login that can edit Instructors and see Employees; an Instructor without an Employee and that person's Employee record.</t>
         </is>
       </c>
       <c r="G110" s="18" t="inlineStr">
         <is>
-          <t>Accept -&gt; Create Employee.</t>
+          <t>1. Open the Instructor.
+2. Pick the Employee.
+3. Save.</t>
         </is>
       </c>
       <c r="H110" s="18" t="inlineStr">
@@ -11130,7 +11204,7 @@
       </c>
       <c r="I110" s="18" t="inlineStr">
         <is>
-          <t>Employee created; work phone and extension kept on the Employee.</t>
+          <t>Department fills in when it is in the academic list; Gender fills in (or, for a login that cannot open the Gender list, on save). The Instructor saves with Gender set. Before the fix: 'Could not find Gender: Gender::1'.</t>
         </is>
       </c>
       <c r="J110" s="14" t="inlineStr">
@@ -11140,12 +11214,12 @@
       </c>
       <c r="K110" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L110" s="14" t="inlineStr">
         <is>
-          <t>REC-05/06</t>
+          <t>REC-11</t>
         </is>
       </c>
       <c r="M110" s="14" t="inlineStr">
@@ -11164,49 +11238,51 @@
       <c r="R110" s="19" t="inlineStr"/>
       <c r="S110" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T110" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-08</t>
+          <t>TC-EMP-14</t>
         </is>
       </c>
       <c r="B111" s="14" t="inlineStr">
         <is>
-          <t>Round 1</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C111" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Employee master &amp; Ministry fields</t>
         </is>
       </c>
       <c r="D111" s="18" t="inlineStr">
         <is>
-          <t>Reject an applicant</t>
+          <t>Link an Employee on the Academic Advisor form</t>
         </is>
       </c>
       <c r="E111" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F111" s="18" t="inlineStr">
         <is>
-          <t>A Pending applicant.</t>
+          <t>As TC-EMP-13, for an Academic Advisor.</t>
         </is>
       </c>
       <c r="G111" s="18" t="inlineStr">
         <is>
-          <t>Click Reject.</t>
+          <t>1. Open the Academic Advisor.
+2. Pick the Employee.
+3. Save.</t>
         </is>
       </c>
       <c r="H111" s="18" t="inlineStr">
@@ -11216,7 +11292,7 @@
       </c>
       <c r="I111" s="18" t="inlineStr">
         <is>
-          <t>Status Rejected; Create Employee not offered.</t>
+          <t>The record saves with Gender set from the Employee.</t>
         </is>
       </c>
       <c r="J111" s="14" t="inlineStr">
@@ -11226,17 +11302,17 @@
       </c>
       <c r="K111" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L111" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit tests</t>
         </is>
       </c>
       <c r="M111" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N111" s="19" t="inlineStr">
@@ -11250,19 +11326,19 @@
       <c r="R111" s="19" t="inlineStr"/>
       <c r="S111" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="T111" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-09</t>
+          <t>TC-LIC-01</t>
         </is>
       </c>
       <c r="B112" s="14" t="inlineStr">
@@ -11272,37 +11348,37 @@
       </c>
       <c r="C112" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Medical licences</t>
         </is>
       </c>
       <c r="D112" s="18" t="inlineStr">
         <is>
-          <t>Duplicate applicant identity</t>
+          <t>HR creates a licence</t>
         </is>
       </c>
       <c r="E112" s="14" t="inlineStr">
         <is>
-          <t>Applicant (not logged in)</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F112" s="18" t="inlineStr">
         <is>
-          <t>An employee already has the ID number.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G112" s="18" t="inlineStr">
         <is>
-          <t>Submit a new application with that ID; HR tries to create the Employee.</t>
+          <t>New Employee Medical License: employee, type, number, expiry; Save.</t>
         </is>
       </c>
       <c r="H112" s="18" t="inlineStr">
         <is>
-          <t>Existing ID</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I112" s="18" t="inlineStr">
         <is>
-          <t>Creating the Employee is refused as a duplicate.</t>
+          <t>Saved.</t>
         </is>
       </c>
       <c r="J112" s="14" t="inlineStr">
@@ -11312,17 +11388,17 @@
       </c>
       <c r="K112" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L112" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>LIC-01</t>
         </is>
       </c>
       <c r="M112" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N112" s="19" t="inlineStr">
@@ -11348,7 +11424,7 @@
     <row r="113">
       <c r="A113" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-11</t>
+          <t>TC-LIC-02</t>
         </is>
       </c>
       <c r="B113" s="14" t="inlineStr">
@@ -11358,28 +11434,27 @@
       </c>
       <c r="C113" s="14" t="inlineStr">
         <is>
-          <t>Recruitment</t>
+          <t>Medical licences</t>
         </is>
       </c>
       <c r="D113" s="18" t="inlineStr">
         <is>
-          <t>A new hire's record opens clean</t>
+          <t>Employees see only their own licence</t>
         </is>
       </c>
       <c r="E113" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Employee</t>
         </is>
       </c>
       <c r="F113" s="18" t="inlineStr">
         <is>
-          <t>An applicant who answered 'Has Special Needs = No' but also picked a type (and, if Saudi, typed a home-country ID).</t>
+          <t>Licences for two employees.</t>
         </is>
       </c>
       <c r="G113" s="18" t="inlineStr">
         <is>
-          <t>1. Hire them (Create Employee).
-2. Open the new Employee record.</t>
+          <t>Each employee opens the licence list.</t>
         </is>
       </c>
       <c r="H113" s="18" t="inlineStr">
@@ -11389,7 +11464,7 @@
       </c>
       <c r="I113" s="18" t="inlineStr">
         <is>
-          <t>The record shows its status (not 'Not Saved'); special-needs type and home-country ID are empty.</t>
+          <t>Only their own licence.</t>
         </is>
       </c>
       <c r="J113" s="14" t="inlineStr">
@@ -11399,12 +11474,12 @@
       </c>
       <c r="K113" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L113" s="14" t="inlineStr">
         <is>
-          <t>REC-09</t>
+          <t>LIC-02</t>
         </is>
       </c>
       <c r="M113" s="14" t="inlineStr">
@@ -11435,7 +11510,7 @@
     <row r="114">
       <c r="A114" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-12</t>
+          <t>TC-REC-01</t>
         </is>
       </c>
       <c r="B114" s="14" t="inlineStr">
@@ -11450,7 +11525,7 @@
       </c>
       <c r="D114" s="18" t="inlineStr">
         <is>
-          <t>Create Employee asks for what the Employee form requires</t>
+          <t>Create and generate an application link</t>
         </is>
       </c>
       <c r="E114" s="14" t="inlineStr">
@@ -11460,15 +11535,15 @@
       </c>
       <c r="F114" s="18" t="inlineStr">
         <is>
-          <t>An Accepted applicant.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G114" s="18" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Look at the Employee Record section of the dialog.
-3. Fill it and confirm.
-4. Open the new Employee, change any field, Save.</t>
+          <t>1. New Job Application Link.
+2. Category Academic Staff, Role Instructor, valid from/until.
+3. Save.
+4. Generate Link.</t>
         </is>
       </c>
       <c r="H114" s="18" t="inlineStr">
@@ -11478,7 +11553,7 @@
       </c>
       <c r="I114" s="18" t="inlineStr">
         <is>
-          <t>The dialog asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application), and Gender / Date of Birth only when the application left them empty. The Employee saves with no 'Missing Fields'.</t>
+          <t>A link is shown and can be copied.</t>
         </is>
       </c>
       <c r="J114" s="14" t="inlineStr">
@@ -11488,12 +11563,12 @@
       </c>
       <c r="K114" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L114" s="14" t="inlineStr">
         <is>
-          <t>REC-10</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="M114" s="14" t="inlineStr">
@@ -11524,7 +11599,7 @@
     <row r="115">
       <c r="A115" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-13</t>
+          <t>TC-REC-02</t>
         </is>
       </c>
       <c r="B115" s="14" t="inlineStr">
@@ -11539,7 +11614,7 @@
       </c>
       <c r="D115" s="18" t="inlineStr">
         <is>
-          <t>Phone number with country code</t>
+          <t>Invalid or expired link</t>
         </is>
       </c>
       <c r="E115" s="14" t="inlineStr">
@@ -11549,25 +11624,22 @@
       </c>
       <c r="F115" s="18" t="inlineStr">
         <is>
-          <t>A valid application link.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G115" s="18" t="inlineStr">
         <is>
-          <t>1. Open the link.
-2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
-3. Send.
-4. Correct it and send again.</t>
+          <t>Open /job-application/abc123 and an expired link.</t>
         </is>
       </c>
       <c r="H115" s="18" t="inlineStr">
         <is>
-          <t>123, then a full mobile number</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I115" s="18" t="inlineStr">
         <is>
-          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
+          <t>'Link is invalid / not active' message; no form.</t>
         </is>
       </c>
       <c r="J115" s="14" t="inlineStr">
@@ -11582,12 +11654,12 @@
       </c>
       <c r="L115" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>REC-01</t>
         </is>
       </c>
       <c r="M115" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N115" s="19" t="inlineStr">
@@ -11601,19 +11673,19 @@
       <c r="R115" s="19" t="inlineStr"/>
       <c r="S115" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T115" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-14</t>
+          <t>TC-REC-03</t>
         </is>
       </c>
       <c r="B116" s="14" t="inlineStr">
@@ -11628,7 +11700,7 @@
       </c>
       <c r="D116" s="18" t="inlineStr">
         <is>
-          <t>Receipt after sending the application</t>
+          <t>Required fields on the public form</t>
         </is>
       </c>
       <c r="E116" s="14" t="inlineStr">
@@ -11638,12 +11710,12 @@
       </c>
       <c r="F116" s="18" t="inlineStr">
         <is>
-          <t>TC-REC-13 done (application sent).</t>
+          <t>Valid link.</t>
         </is>
       </c>
       <c r="G116" s="18" t="inlineStr">
         <is>
-          <t>On the confirmation screen click the receipt download button.</t>
+          <t>Click Submit with the form empty.</t>
         </is>
       </c>
       <c r="H116" s="18" t="inlineStr">
@@ -11653,7 +11725,7 @@
       </c>
       <c r="I116" s="18" t="inlineStr">
         <is>
-          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
+          <t>Browser highlights the required fields; nothing is sent.</t>
         </is>
       </c>
       <c r="J116" s="14" t="inlineStr">
@@ -11663,7 +11735,7 @@
       </c>
       <c r="K116" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L116" s="14" t="inlineStr">
@@ -11687,19 +11759,19 @@
       <c r="R116" s="19" t="inlineStr"/>
       <c r="S116" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T116" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" s="16" t="inlineStr">
         <is>
-          <t>TC-REC-10</t>
+          <t>TC-REC-04</t>
         </is>
       </c>
       <c r="B117" s="14" t="inlineStr">
@@ -11714,50 +11786,47 @@
       </c>
       <c r="D117" s="18" t="inlineStr">
         <is>
-          <t>Academic hire needs the college e-mail</t>
+          <t>Applicant submits the full form</t>
         </is>
       </c>
       <c r="E117" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="F117" s="18" t="inlineStr">
         <is>
-          <t>An Accepted applicant from an Instructor link.</t>
+          <t>Valid link.</t>
         </is>
       </c>
       <c r="G117" s="18" t="inlineStr">
         <is>
-          <t>1. Create Employee.
-2. Leave Company Email empty (or a gmail address).
-3. Confirm.
-4. Then enter a @alriyada.edu.sa address and confirm again.</t>
+          <t>Fill every section (names in Arabic and English, ID, qualifications, experience) and Submit.</t>
         </is>
       </c>
       <c r="H117" s="18" t="inlineStr">
         <is>
-          <t>Personal e-mail, then college e-mail</t>
+          <t>Saudi national ID</t>
         </is>
       </c>
       <c r="I117" s="18" t="inlineStr">
         <is>
-          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
+          <t>'Thank you' with a reference number APP-....</t>
         </is>
       </c>
       <c r="J117" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K117" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L117" s="14" t="inlineStr">
         <is>
-          <t>REC-08</t>
+          <t>REC-03..05</t>
         </is>
       </c>
       <c r="M117" s="14" t="inlineStr">
@@ -11788,7 +11857,7 @@
     <row r="118">
       <c r="A118" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-01</t>
+          <t>TC-REC-05</t>
         </is>
       </c>
       <c r="B118" s="14" t="inlineStr">
@@ -11798,12 +11867,12 @@
       </c>
       <c r="C118" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D118" s="18" t="inlineStr">
         <is>
-          <t>Faculty schedules</t>
+          <t>Accept and create an Instructor</t>
         </is>
       </c>
       <c r="E118" s="14" t="inlineStr">
@@ -11813,27 +11882,30 @@
       </c>
       <c r="F118" s="18" t="inlineStr">
         <is>
-          <t>Published class timetables.</t>
+          <t>TC-REC-04 for an Instructor link.</t>
         </is>
       </c>
       <c r="G118" s="18" t="inlineStr">
         <is>
-          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
+          <t>1. Open the applicant.
+2. Accept.
+3. Create Employee: Company Email = official college address, department.
+4. Confirm.</t>
         </is>
       </c>
       <c r="H118" s="18" t="inlineStr">
         <is>
-          <t>6–12 Sep 2026</t>
+          <t>name.surname@alriyada.edu.sa</t>
         </is>
       </c>
       <c r="I118" s="18" t="inlineStr">
         <is>
-          <t>Sessions per faculty member with day, time, course, room and mode.</t>
+          <t>Message lists Employee and Instructor created; the new login has Employee + Instructor roles.</t>
         </is>
       </c>
       <c r="J118" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K118" s="14" t="inlineStr">
@@ -11843,7 +11915,7 @@
       </c>
       <c r="L118" s="14" t="inlineStr">
         <is>
-          <t>PRS-01</t>
+          <t>REC-03</t>
         </is>
       </c>
       <c r="M118" s="14" t="inlineStr">
@@ -11874,7 +11946,7 @@
     <row r="119">
       <c r="A119" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-02</t>
+          <t>TC-REC-06</t>
         </is>
       </c>
       <c r="B119" s="14" t="inlineStr">
@@ -11884,12 +11956,12 @@
       </c>
       <c r="C119" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D119" s="18" t="inlineStr">
         <is>
-          <t>Filter one faculty member</t>
+          <t>Hire an Academic Advisor</t>
         </is>
       </c>
       <c r="E119" s="14" t="inlineStr">
@@ -11899,37 +11971,37 @@
       </c>
       <c r="F119" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Applicant for an Academic Advisor link with a phone like 05XXXXXXXX.</t>
         </is>
       </c>
       <c r="G119" s="18" t="inlineStr">
         <is>
-          <t>Pick a faculty member in the filter.</t>
+          <t>Accept -&gt; Create Employee with a @alriyada.edu.sa Company Email.</t>
         </is>
       </c>
       <c r="H119" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Local phone number</t>
         </is>
       </c>
       <c r="I119" s="18" t="inlineStr">
         <is>
-          <t>Only that person's sessions.</t>
+          <t>Employee, Academic Advisor and Instructor records created; no 'record not created' warning.</t>
         </is>
       </c>
       <c r="J119" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K119" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L119" s="14" t="inlineStr">
         <is>
-          <t>PRS-02</t>
+          <t>REC-04</t>
         </is>
       </c>
       <c r="M119" s="14" t="inlineStr">
@@ -11960,7 +12032,7 @@
     <row r="120">
       <c r="A120" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-03</t>
+          <t>TC-REC-07</t>
         </is>
       </c>
       <c r="B120" s="14" t="inlineStr">
@@ -11970,12 +12042,12 @@
       </c>
       <c r="C120" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D120" s="18" t="inlineStr">
         <is>
-          <t>Proctor schedules</t>
+          <t>Hire non-academic staff</t>
         </is>
       </c>
       <c r="E120" s="14" t="inlineStr">
@@ -11985,27 +12057,27 @@
       </c>
       <c r="F120" s="18" t="inlineStr">
         <is>
-          <t>Exam committees with proctors.</t>
+          <t>Applicant for a Non-Academic link.</t>
         </is>
       </c>
       <c r="G120" s="18" t="inlineStr">
         <is>
-          <t>Open Proctor Schedules for the exam week.</t>
+          <t>Accept -&gt; Create Employee.</t>
         </is>
       </c>
       <c r="H120" s="18" t="inlineStr">
         <is>
-          <t>Exam week</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I120" s="18" t="inlineStr">
         <is>
-          <t>Proctor assignments, or a clear 'no assignments' message.</t>
+          <t>Employee created; work phone and extension kept on the Employee.</t>
         </is>
       </c>
       <c r="J120" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K120" s="14" t="inlineStr">
@@ -12015,7 +12087,7 @@
       </c>
       <c r="L120" s="14" t="inlineStr">
         <is>
-          <t>PRS-03</t>
+          <t>REC-05/06</t>
         </is>
       </c>
       <c r="M120" s="14" t="inlineStr">
@@ -12046,7 +12118,7 @@
     <row r="121">
       <c r="A121" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-04</t>
+          <t>TC-REC-08</t>
         </is>
       </c>
       <c r="B121" s="14" t="inlineStr">
@@ -12056,12 +12128,12 @@
       </c>
       <c r="C121" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D121" s="18" t="inlineStr">
         <is>
-          <t>Students on campus per hour</t>
+          <t>Reject an applicant</t>
         </is>
       </c>
       <c r="E121" s="14" t="inlineStr">
@@ -12071,27 +12143,27 @@
       </c>
       <c r="F121" s="18" t="inlineStr">
         <is>
-          <t>Attendance recorded.</t>
+          <t>A Pending applicant.</t>
         </is>
       </c>
       <c r="G121" s="18" t="inlineStr">
         <is>
-          <t>Open Students on Campus for a teaching day.</t>
+          <t>Click Reject.</t>
         </is>
       </c>
       <c r="H121" s="18" t="inlineStr">
         <is>
-          <t>8 Sep 2026</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I121" s="18" t="inlineStr">
         <is>
-          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
+          <t>Status Rejected; Create Employee not offered.</t>
         </is>
       </c>
       <c r="J121" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K121" s="14" t="inlineStr">
@@ -12101,12 +12173,12 @@
       </c>
       <c r="L121" s="14" t="inlineStr">
         <is>
-          <t>PRS-04</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M121" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N121" s="19" t="inlineStr">
@@ -12132,7 +12204,7 @@
     <row r="122">
       <c r="A122" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-05</t>
+          <t>TC-REC-09</t>
         </is>
       </c>
       <c r="B122" s="14" t="inlineStr">
@@ -12142,57 +12214,57 @@
       </c>
       <c r="C122" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D122" s="18" t="inlineStr">
         <is>
-          <t>Faculty after 4 PM</t>
+          <t>Duplicate applicant identity</t>
         </is>
       </c>
       <c r="E122" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="F122" s="18" t="inlineStr">
         <is>
+          <t>An employee already has the ID number.</t>
+        </is>
+      </c>
+      <c r="G122" s="18" t="inlineStr">
+        <is>
+          <t>Submit a new application with that ID; HR tries to create the Employee.</t>
+        </is>
+      </c>
+      <c r="H122" s="18" t="inlineStr">
+        <is>
+          <t>Existing ID</t>
+        </is>
+      </c>
+      <c r="I122" s="18" t="inlineStr">
+        <is>
+          <t>Creating the Employee is refused as a duplicate.</t>
+        </is>
+      </c>
+      <c r="J122" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K122" s="14" t="inlineStr">
+        <is>
+          <t>Negative</t>
+        </is>
+      </c>
+      <c r="L122" s="14" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G122" s="18" t="inlineStr">
-        <is>
-          <t>Open Faculty After 4 PM for a week.</t>
-        </is>
-      </c>
-      <c r="H122" s="18" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="I122" s="18" t="inlineStr">
-        <is>
-          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
-        </is>
-      </c>
-      <c r="J122" s="14" t="inlineStr">
-        <is>
-          <t>High</t>
-        </is>
-      </c>
-      <c r="K122" s="14" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="L122" s="14" t="inlineStr">
-        <is>
-          <t>PRS-05</t>
-        </is>
-      </c>
       <c r="M122" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N122" s="19" t="inlineStr">
@@ -12218,7 +12290,7 @@
     <row r="123">
       <c r="A123" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-06</t>
+          <t>TC-REC-11</t>
         </is>
       </c>
       <c r="B123" s="14" t="inlineStr">
@@ -12228,12 +12300,12 @@
       </c>
       <c r="C123" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D123" s="18" t="inlineStr">
         <is>
-          <t>Export</t>
+          <t>A new hire's record opens clean</t>
         </is>
       </c>
       <c r="E123" s="14" t="inlineStr">
@@ -12243,12 +12315,13 @@
       </c>
       <c r="F123" s="18" t="inlineStr">
         <is>
-          <t>A tab with data.</t>
+          <t>An applicant who answered 'Has Special Needs = No' but also picked a type (and, if Saudi, typed a home-country ID).</t>
         </is>
       </c>
       <c r="G123" s="18" t="inlineStr">
         <is>
-          <t>Click Export (Excel CSV).</t>
+          <t>1. Hire them (Create Employee).
+2. Open the new Employee record.</t>
         </is>
       </c>
       <c r="H123" s="18" t="inlineStr">
@@ -12258,22 +12331,22 @@
       </c>
       <c r="I123" s="18" t="inlineStr">
         <is>
-          <t>A CSV file downloads and opens in Excel with the same rows.</t>
+          <t>The record shows its status (not 'Not Saved'); special-needs type and home-country ID are empty.</t>
         </is>
       </c>
       <c r="J123" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K123" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L123" s="14" t="inlineStr">
         <is>
-          <t>PRS-06</t>
+          <t>REC-09</t>
         </is>
       </c>
       <c r="M123" s="14" t="inlineStr">
@@ -12304,7 +12377,7 @@
     <row r="124">
       <c r="A124" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-07</t>
+          <t>TC-REC-12</t>
         </is>
       </c>
       <c r="B124" s="14" t="inlineStr">
@@ -12314,12 +12387,12 @@
       </c>
       <c r="C124" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D124" s="18" t="inlineStr">
         <is>
-          <t>Holiday and exam days</t>
+          <t>Create Employee asks for what the Employee form requires</t>
         </is>
       </c>
       <c r="E124" s="14" t="inlineStr">
@@ -12329,12 +12402,15 @@
       </c>
       <c r="F124" s="18" t="inlineStr">
         <is>
-          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
+          <t>An Accepted applicant.</t>
         </is>
       </c>
       <c r="G124" s="18" t="inlineStr">
         <is>
-          <t>Open Faculty Schedules over a holiday or exam week.</t>
+          <t>1. Create Employee.
+2. Look at the Employee Record section of the dialog.
+3. Fill it and confirm.
+4. Open the new Employee, change any field, Save.</t>
         </is>
       </c>
       <c r="H124" s="18" t="inlineStr">
@@ -12344,27 +12420,27 @@
       </c>
       <c r="I124" s="18" t="inlineStr">
         <is>
-          <t>No regular sessions on those days; the skipped dates are listed.</t>
+          <t>The dialog asks for Academic Department, Geographical Work Location, City and Job Rank (pre-filled from the application), and Gender / Date of Birth only when the application left them empty. The Employee saves with no 'Missing Fields'.</t>
         </is>
       </c>
       <c r="J124" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K124" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Regression</t>
         </is>
       </c>
       <c r="L124" s="14" t="inlineStr">
         <is>
-          <t>unit/manual</t>
+          <t>REC-10</t>
         </is>
       </c>
       <c r="M124" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N124" s="19" t="inlineStr">
@@ -12390,7 +12466,7 @@
     <row r="125">
       <c r="A125" s="16" t="inlineStr">
         <is>
-          <t>TC-PRS-08</t>
+          <t>TC-REC-13</t>
         </is>
       </c>
       <c r="B125" s="14" t="inlineStr">
@@ -12400,47 +12476,50 @@
       </c>
       <c r="C125" s="14" t="inlineStr">
         <is>
-          <t>Academic presence</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D125" s="18" t="inlineStr">
         <is>
-          <t>Cut-off time setting</t>
+          <t>Phone number with country code</t>
         </is>
       </c>
       <c r="E125" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="F125" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A valid application link.</t>
         </is>
       </c>
       <c r="G125" s="18" t="inlineStr">
         <is>
-          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
+          <t>1. Open the link.
+2. Pick a country code next to Phone Number and enter a number that is too short (e.g. 123).
+3. Send.
+4. Correct it and send again.</t>
         </is>
       </c>
       <c r="H125" s="18" t="inlineStr">
         <is>
-          <t>15:00</t>
+          <t>123, then a full mobile number</t>
         </is>
       </c>
       <c r="I125" s="18" t="inlineStr">
         <is>
-          <t>List uses the new time.</t>
+          <t>Too short: 'Enter a valid phone number including the country code.' Corrected: the application is sent.</t>
         </is>
       </c>
       <c r="J125" s="14" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K125" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L125" s="14" t="inlineStr">
@@ -12464,19 +12543,19 @@
       <c r="R125" s="19" t="inlineStr"/>
       <c r="S125" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="T125" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-01</t>
+          <t>TC-REC-14</t>
         </is>
       </c>
       <c r="B126" s="14" t="inlineStr">
@@ -12486,57 +12565,57 @@
       </c>
       <c r="C126" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D126" s="18" t="inlineStr">
         <is>
-          <t>Jameah Data Check page</t>
+          <t>Receipt after sending the application</t>
         </is>
       </c>
       <c r="E126" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Applicant (not logged in)</t>
         </is>
       </c>
       <c r="F126" s="18" t="inlineStr">
         <is>
+          <t>TC-REC-13 done (application sent).</t>
+        </is>
+      </c>
+      <c r="G126" s="18" t="inlineStr">
+        <is>
+          <t>On the confirmation screen click the receipt download button.</t>
+        </is>
+      </c>
+      <c r="H126" s="18" t="inlineStr">
+        <is>
           <t>—</t>
         </is>
       </c>
-      <c r="G126" s="18" t="inlineStr">
-        <is>
-          <t>HR Dashboard -&gt; Jameah Data Check.</t>
-        </is>
-      </c>
-      <c r="H126" s="18" t="inlineStr">
+      <c r="I126" s="18" t="inlineStr">
+        <is>
+          <t>A PDF receipt with the reference number and the applicant's answers downloads; changing the link's key gives 'This download link is not valid'.</t>
+        </is>
+      </c>
+      <c r="J126" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K126" s="14" t="inlineStr">
+        <is>
+          <t>Functional</t>
+        </is>
+      </c>
+      <c r="L126" s="14" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="I126" s="18" t="inlineStr">
-        <is>
-          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
-        </is>
-      </c>
-      <c r="J126" s="14" t="inlineStr">
-        <is>
-          <t>Critical</t>
-        </is>
-      </c>
-      <c r="K126" s="14" t="inlineStr">
-        <is>
-          <t>Functional</t>
-        </is>
-      </c>
-      <c r="L126" s="14" t="inlineStr">
-        <is>
-          <t>JM-01</t>
-        </is>
-      </c>
       <c r="M126" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N126" s="19" t="inlineStr">
@@ -12550,19 +12629,19 @@
       <c r="R126" s="19" t="inlineStr"/>
       <c r="S126" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="T126" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-02</t>
+          <t>TC-REC-10</t>
         </is>
       </c>
       <c r="B127" s="14" t="inlineStr">
@@ -12572,37 +12651,40 @@
       </c>
       <c r="C127" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Recruitment</t>
         </is>
       </c>
       <c r="D127" s="18" t="inlineStr">
         <is>
-          <t>Jameah Settings pickers</t>
+          <t>Academic hire needs the college e-mail</t>
         </is>
       </c>
       <c r="E127" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F127" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>An Accepted applicant from an Instructor link.</t>
         </is>
       </c>
       <c r="G127" s="18" t="inlineStr">
         <is>
-          <t>Open Jameah Settings; open the College picker.</t>
+          <t>1. Create Employee.
+2. Leave Company Email empty (or a gmail address).
+3. Confirm.
+4. Then enter a @alriyada.edu.sa address and confirm again.</t>
         </is>
       </c>
       <c r="H127" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Personal e-mail, then college e-mail</t>
         </is>
       </c>
       <c r="I127" s="18" t="inlineStr">
         <is>
-          <t>Only College Coding Guide codes are offered.</t>
+          <t>Step 3: 'College E-mail Needed' message and NO Employee is created. Step 4: Employee and Instructor are created, no orange warning.</t>
         </is>
       </c>
       <c r="J127" s="14" t="inlineStr">
@@ -12612,12 +12694,12 @@
       </c>
       <c r="K127" s="14" t="inlineStr">
         <is>
-          <t>Functional</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L127" s="14" t="inlineStr">
         <is>
-          <t>JM-02</t>
+          <t>REC-08</t>
         </is>
       </c>
       <c r="M127" s="14" t="inlineStr">
@@ -12648,7 +12730,7 @@
     <row r="128">
       <c r="A128" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-03</t>
+          <t>TC-PRS-01</t>
         </is>
       </c>
       <c r="B128" s="14" t="inlineStr">
@@ -12658,37 +12740,37 @@
       </c>
       <c r="C128" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D128" s="18" t="inlineStr">
         <is>
-          <t>Fill a setting and see it in the views</t>
+          <t>Faculty schedules</t>
         </is>
       </c>
       <c r="E128" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F128" s="18" t="inlineStr">
         <is>
-          <t>Decision on the college code (DEC-02).</t>
+          <t>Published class timetables.</t>
         </is>
       </c>
       <c r="G128" s="18" t="inlineStr">
         <is>
-          <t>Set College; Save; reopen Jameah Data Check.</t>
+          <t>HR Dashboard -&gt; Faculty Schedules; choose a week.</t>
         </is>
       </c>
       <c r="H128" s="18" t="inlineStr">
         <is>
-          <t>College code</t>
+          <t>6–12 Sep 2026</t>
         </is>
       </c>
       <c r="I128" s="18" t="inlineStr">
         <is>
-          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
+          <t>Sessions per faculty member with day, time, course, room and mode.</t>
         </is>
       </c>
       <c r="J128" s="14" t="inlineStr">
@@ -12703,12 +12785,12 @@
       </c>
       <c r="L128" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PRS-01</t>
         </is>
       </c>
       <c r="M128" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N128" s="19" t="inlineStr">
@@ -12734,7 +12816,7 @@
     <row r="129">
       <c r="A129" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-04</t>
+          <t>TC-PRS-02</t>
         </is>
       </c>
       <c r="B129" s="14" t="inlineStr">
@@ -12744,42 +12826,42 @@
       </c>
       <c r="C129" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D129" s="18" t="inlineStr">
         <is>
-          <t>Map a value in the Code Map</t>
+          <t>Filter one faculty member</t>
         </is>
       </c>
       <c r="E129" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F129" s="18" t="inlineStr">
         <is>
-          <t>A 'Needs Review' row.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G129" s="18" t="inlineStr">
         <is>
-          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
+          <t>Pick a faculty member in the filter.</t>
         </is>
       </c>
       <c r="H129" s="18" t="inlineStr">
         <is>
-          <t>e.g. Internship -&gt; 0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I129" s="18" t="inlineStr">
         <is>
-          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
+          <t>Only that person's sessions.</t>
         </is>
       </c>
       <c r="J129" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K129" s="14" t="inlineStr">
@@ -12789,7 +12871,7 @@
       </c>
       <c r="L129" s="14" t="inlineStr">
         <is>
-          <t>JM-03</t>
+          <t>PRS-02</t>
         </is>
       </c>
       <c r="M129" s="14" t="inlineStr">
@@ -12820,7 +12902,7 @@
     <row r="130">
       <c r="A130" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-05</t>
+          <t>TC-PRS-03</t>
         </is>
       </c>
       <c r="B130" s="14" t="inlineStr">
@@ -12830,37 +12912,37 @@
       </c>
       <c r="C130" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D130" s="18" t="inlineStr">
         <is>
-          <t>Code Map refuses a code from another list</t>
+          <t>Proctor schedules</t>
         </is>
       </c>
       <c r="E130" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F130" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Exam committees with proctors.</t>
         </is>
       </c>
       <c r="G130" s="18" t="inlineStr">
         <is>
-          <t>Try to save a Religion row with a Gender code.</t>
+          <t>Open Proctor Schedules for the exam week.</t>
         </is>
       </c>
       <c r="H130" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Exam week</t>
         </is>
       </c>
       <c r="I130" s="18" t="inlineStr">
         <is>
-          <t>Refused with a clear message.</t>
+          <t>Proctor assignments, or a clear 'no assignments' message.</t>
         </is>
       </c>
       <c r="J130" s="14" t="inlineStr">
@@ -12870,17 +12952,17 @@
       </c>
       <c r="K130" s="14" t="inlineStr">
         <is>
-          <t>Negative</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L130" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>PRS-03</t>
         </is>
       </c>
       <c r="M130" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N130" s="19" t="inlineStr">
@@ -12906,7 +12988,7 @@
     <row r="131">
       <c r="A131" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-06</t>
+          <t>TC-PRS-04</t>
         </is>
       </c>
       <c r="B131" s="14" t="inlineStr">
@@ -12916,12 +12998,12 @@
       </c>
       <c r="C131" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D131" s="18" t="inlineStr">
         <is>
-          <t>Refresh academic figures</t>
+          <t>Students on campus per hour</t>
         </is>
       </c>
       <c r="E131" s="14" t="inlineStr">
@@ -12931,27 +13013,27 @@
       </c>
       <c r="F131" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>Attendance recorded.</t>
         </is>
       </c>
       <c r="G131" s="18" t="inlineStr">
         <is>
-          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
+          <t>Open Students on Campus for a teaching day.</t>
         </is>
       </c>
       <c r="H131" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>8 Sep 2026</t>
         </is>
       </c>
       <c r="I131" s="18" t="inlineStr">
         <is>
-          <t>'Last refreshed' time updates.</t>
+          <t>Hourly table: expected, present, absent, not recorded. Totals match attendance.</t>
         </is>
       </c>
       <c r="J131" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K131" s="14" t="inlineStr">
@@ -12961,12 +13043,12 @@
       </c>
       <c r="L131" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>PRS-04</t>
         </is>
       </c>
       <c r="M131" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N131" s="19" t="inlineStr">
@@ -12992,7 +13074,7 @@
     <row r="132">
       <c r="A132" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-07</t>
+          <t>TC-PRS-05</t>
         </is>
       </c>
       <c r="B132" s="14" t="inlineStr">
@@ -13002,12 +13084,12 @@
       </c>
       <c r="C132" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D132" s="18" t="inlineStr">
         <is>
-          <t>Employee data reaches the Employee views</t>
+          <t>Faculty after 4 PM</t>
         </is>
       </c>
       <c r="E132" s="14" t="inlineStr">
@@ -13017,12 +13099,12 @@
       </c>
       <c r="F132" s="18" t="inlineStr">
         <is>
-          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G132" s="18" t="inlineStr">
         <is>
-          <t>Open their Ministry (Jameah) Data preview.</t>
+          <t>Open Faculty After 4 PM for a week.</t>
         </is>
       </c>
       <c r="H132" s="18" t="inlineStr">
@@ -13032,12 +13114,12 @@
       </c>
       <c r="I132" s="18" t="inlineStr">
         <is>
-          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
+          <t>People on campus after 16:00 with evidence (device / attendance / timetable).</t>
         </is>
       </c>
       <c r="J132" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K132" s="14" t="inlineStr">
@@ -13047,7 +13129,7 @@
       </c>
       <c r="L132" s="14" t="inlineStr">
         <is>
-          <t>REC-06</t>
+          <t>PRS-05</t>
         </is>
       </c>
       <c r="M132" s="14" t="inlineStr">
@@ -13078,7 +13160,7 @@
     <row r="133">
       <c r="A133" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-10</t>
+          <t>TC-PRS-06</t>
         </is>
       </c>
       <c r="B133" s="14" t="inlineStr">
@@ -13088,52 +13170,52 @@
       </c>
       <c r="C133" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D133" s="18" t="inlineStr">
         <is>
-          <t>Ministry GPA and hours equal the student's transcript</t>
+          <t>Export</t>
         </is>
       </c>
       <c r="E133" s="14" t="inlineStr">
         <is>
-          <t>Academic Affairs / Education Manager</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F133" s="18" t="inlineStr">
         <is>
-          <t>Academic figures refreshed (TC-JM-06).</t>
+          <t>A tab with data.</t>
         </is>
       </c>
       <c r="G133" s="18" t="inlineStr">
         <is>
-          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
+          <t>Click Export (Excel CSV).</t>
         </is>
       </c>
       <c r="H133" s="18" t="inlineStr">
         <is>
-          <t>10 students</t>
+          <t>—</t>
         </is>
       </c>
       <c r="I133" s="18" t="inlineStr">
         <is>
-          <t>All four figures are identical for every student.</t>
+          <t>A CSV file downloads and opens in Excel with the same rows.</t>
         </is>
       </c>
       <c r="J133" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K133" s="14" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L133" s="14" t="inlineStr">
         <is>
-          <t>verify.run</t>
+          <t>PRS-06</t>
         </is>
       </c>
       <c r="M133" s="14" t="inlineStr">
@@ -13164,7 +13246,7 @@
     <row r="134">
       <c r="A134" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-08</t>
+          <t>TC-PRS-07</t>
         </is>
       </c>
       <c r="B134" s="14" t="inlineStr">
@@ -13174,27 +13256,27 @@
       </c>
       <c r="C134" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D134" s="18" t="inlineStr">
         <is>
-          <t>Full value-by-value check (developer)</t>
+          <t>Holiday and exam days</t>
         </is>
       </c>
       <c r="E134" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F134" s="18" t="inlineStr">
         <is>
-          <t>Server access.</t>
+          <t>Academic Holiday List set; an exam period in the academic calendar.</t>
         </is>
       </c>
       <c r="G134" s="18" t="inlineStr">
         <is>
-          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
+          <t>Open Faculty Schedules over a holiday or exam week.</t>
         </is>
       </c>
       <c r="H134" s="18" t="inlineStr">
@@ -13204,27 +13286,27 @@
       </c>
       <c r="I134" s="18" t="inlineStr">
         <is>
-          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
+          <t>No regular sessions on those days; the skipped dates are listed.</t>
         </is>
       </c>
       <c r="J134" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K134" s="14" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L134" s="14" t="inlineStr">
         <is>
-          <t>verify.run</t>
+          <t>unit/manual</t>
         </is>
       </c>
       <c r="M134" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N134" s="19" t="inlineStr">
@@ -13250,7 +13332,7 @@
     <row r="135">
       <c r="A135" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-09</t>
+          <t>TC-PRS-08</t>
         </is>
       </c>
       <c r="B135" s="14" t="inlineStr">
@@ -13260,47 +13342,47 @@
       </c>
       <c r="C135" s="14" t="inlineStr">
         <is>
-          <t>Jameah (Ministry)</t>
+          <t>Academic presence</t>
         </is>
       </c>
       <c r="D135" s="18" t="inlineStr">
         <is>
-          <t>Ministry read-only account</t>
+          <t>Cut-off time setting</t>
         </is>
       </c>
       <c r="E135" s="14" t="inlineStr">
         <is>
-          <t>Server admin</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F135" s="18" t="inlineStr">
         <is>
-          <t>Account created with the grant statements.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G135" s="18" t="inlineStr">
         <is>
-          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
+          <t>HR Settings -&gt; Faculty After-hours Cut-off = 15:00; reopen Faculty After 4 PM.</t>
         </is>
       </c>
       <c r="H135" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>15:00</t>
         </is>
       </c>
       <c r="I135" s="18" t="inlineStr">
         <is>
-          <t>Views readable; ERP tables refused.</t>
+          <t>List uses the new time.</t>
         </is>
       </c>
       <c r="J135" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="K135" s="14" t="inlineStr">
         <is>
-          <t>Security</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L135" s="14" t="inlineStr">
@@ -13336,7 +13418,7 @@
     <row r="136">
       <c r="A136" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-11</t>
+          <t>TC-JM-01</t>
         </is>
       </c>
       <c r="B136" s="14" t="inlineStr">
@@ -13351,7 +13433,7 @@
       </c>
       <c r="D136" s="18" t="inlineStr">
         <is>
-          <t>Faculty views on the Data Check page</t>
+          <t>Jameah Data Check page</t>
         </is>
       </c>
       <c r="E136" s="14" t="inlineStr">
@@ -13366,7 +13448,7 @@
       </c>
       <c r="G136" s="18" t="inlineStr">
         <is>
-          <t>Open Jameah Data Check and look at the Views table.</t>
+          <t>HR Dashboard -&gt; Jameah Data Check.</t>
         </is>
       </c>
       <c r="H136" s="18" t="inlineStr">
@@ -13376,12 +13458,12 @@
       </c>
       <c r="I136" s="18" t="inlineStr">
         <is>
-          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
+          <t>Cards show 0 invalid Ministry codes; table lists 15 views with row counts; settings to fill and values to review are listed.</t>
         </is>
       </c>
       <c r="J136" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K136" s="14" t="inlineStr">
@@ -13422,7 +13504,7 @@
     <row r="137">
       <c r="A137" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-12</t>
+          <t>TC-JM-02</t>
         </is>
       </c>
       <c r="B137" s="14" t="inlineStr">
@@ -13437,23 +13519,22 @@
       </c>
       <c r="D137" s="18" t="inlineStr">
         <is>
-          <t>A teacher is sent once, as Faculty</t>
+          <t>Jameah Settings pickers</t>
         </is>
       </c>
       <c r="E137" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F137" s="18" t="inlineStr">
         <is>
-          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G137" s="18" t="inlineStr">
         <is>
-          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
-2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
+          <t>Open Jameah Settings; open the College picker.</t>
         </is>
       </c>
       <c r="H137" s="18" t="inlineStr">
@@ -13463,27 +13544,27 @@
       </c>
       <c r="I137" s="18" t="inlineStr">
         <is>
-          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
+          <t>Only College Coding Guide codes are offered.</t>
         </is>
       </c>
       <c r="J137" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K137" s="14" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L137" s="14" t="inlineStr">
         <is>
-          <t>unit test</t>
+          <t>JM-02</t>
         </is>
       </c>
       <c r="M137" s="14" t="inlineStr">
         <is>
-          <t>Unit test</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N137" s="19" t="inlineStr">
@@ -13509,7 +13590,7 @@
     <row r="138">
       <c r="A138" s="16" t="inlineStr">
         <is>
-          <t>TC-JM-13</t>
+          <t>TC-JM-03</t>
         </is>
       </c>
       <c r="B138" s="14" t="inlineStr">
@@ -13524,7 +13605,7 @@
       </c>
       <c r="D138" s="18" t="inlineStr">
         <is>
-          <t>Faculty status and contract codes</t>
+          <t>Fill a setting and see it in the views</t>
         </is>
       </c>
       <c r="E138" s="14" t="inlineStr">
@@ -13534,33 +13615,32 @@
       </c>
       <c r="F138" s="18" t="inlineStr">
         <is>
-          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+          <t>Decision on the college code (DEC-02).</t>
         </is>
       </c>
       <c r="G138" s="18" t="inlineStr">
         <is>
-          <t>1. Open each row, pick the Ministry code, Status = Verified.
-2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+          <t>Set College; Save; reopen Jameah Data Check.</t>
         </is>
       </c>
       <c r="H138" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>College code</t>
         </is>
       </c>
       <c r="I138" s="18" t="inlineStr">
         <is>
-          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
+          <t>The AdmissionCollegeId / CurrentCollegeId gap disappears.</t>
         </is>
       </c>
       <c r="J138" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K138" s="14" t="inlineStr">
         <is>
-          <t>Data</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L138" s="14" t="inlineStr">
@@ -13596,7 +13676,7 @@
     <row r="139">
       <c r="A139" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-01</t>
+          <t>TC-JM-04</t>
         </is>
       </c>
       <c r="B139" s="14" t="inlineStr">
@@ -13606,57 +13686,57 @@
       </c>
       <c r="C139" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D139" s="18" t="inlineStr">
         <is>
-          <t>Error Log after each test day</t>
+          <t>Map a value in the Code Map</t>
         </is>
       </c>
       <c r="E139" s="14" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F139" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>A 'Needs Review' row.</t>
         </is>
       </c>
       <c r="G139" s="18" t="inlineStr">
         <is>
-          <t>Open /app/error-log; sort by newest.</t>
+          <t>Open it, pick the Ministry code, Status = Verified, Save.</t>
         </is>
       </c>
       <c r="H139" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>e.g. Internship -&gt; 0</t>
         </is>
       </c>
       <c r="I139" s="18" t="inlineStr">
         <is>
-          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
+          <t>Saved; 'Matched By' becomes Manual; the Data Check gap shrinks.</t>
         </is>
       </c>
       <c r="J139" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K139" s="14" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L139" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>JM-03</t>
         </is>
       </c>
       <c r="M139" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N139" s="19" t="inlineStr">
@@ -13682,7 +13762,7 @@
     <row r="140">
       <c r="A140" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-02</t>
+          <t>TC-JM-05</t>
         </is>
       </c>
       <c r="B140" s="14" t="inlineStr">
@@ -13692,17 +13772,17 @@
       </c>
       <c r="C140" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D140" s="18" t="inlineStr">
         <is>
-          <t>System e-mail works</t>
+          <t>Code Map refuses a code from another list</t>
         </is>
       </c>
       <c r="E140" s="14" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F140" s="18" t="inlineStr">
@@ -13712,7 +13792,7 @@
       </c>
       <c r="G140" s="18" t="inlineStr">
         <is>
-          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
+          <t>Try to save a Religion row with a Gender code.</t>
         </is>
       </c>
       <c r="H140" s="18" t="inlineStr">
@@ -13722,27 +13802,27 @@
       </c>
       <c r="I140" s="18" t="inlineStr">
         <is>
-          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
+          <t>Refused with a clear message.</t>
         </is>
       </c>
       <c r="J140" s="14" t="inlineStr">
         <is>
-          <t>Critical</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K140" s="14" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Negative</t>
         </is>
       </c>
       <c r="L140" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="M140" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N140" s="19" t="inlineStr">
@@ -13768,7 +13848,7 @@
     <row r="141">
       <c r="A141" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-03</t>
+          <t>TC-JM-06</t>
         </is>
       </c>
       <c r="B141" s="14" t="inlineStr">
@@ -13778,17 +13858,17 @@
       </c>
       <c r="C141" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D141" s="18" t="inlineStr">
         <is>
-          <t>Background jobs</t>
+          <t>Refresh academic figures</t>
         </is>
       </c>
       <c r="E141" s="14" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F141" s="18" t="inlineStr">
@@ -13798,7 +13878,7 @@
       </c>
       <c r="G141" s="18" t="inlineStr">
         <is>
-          <t>Open Scheduled Job Log; filter Status = Failed.</t>
+          <t>Jameah Data Check -&gt; Refresh Academic Figures; wait a minute; Refresh.</t>
         </is>
       </c>
       <c r="H141" s="18" t="inlineStr">
@@ -13808,17 +13888,17 @@
       </c>
       <c r="I141" s="18" t="inlineStr">
         <is>
-          <t>No failed jobs (or each one reported).</t>
+          <t>'Last refreshed' time updates.</t>
         </is>
       </c>
       <c r="J141" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Medium</t>
         </is>
       </c>
       <c r="K141" s="14" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L141" s="14" t="inlineStr">
@@ -13854,7 +13934,7 @@
     <row r="142">
       <c r="A142" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-04</t>
+          <t>TC-JM-07</t>
         </is>
       </c>
       <c r="B142" s="14" t="inlineStr">
@@ -13864,27 +13944,27 @@
       </c>
       <c r="C142" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D142" s="18" t="inlineStr">
         <is>
-          <t>Browser console during testing</t>
+          <t>Employee data reaches the Employee views</t>
         </is>
       </c>
       <c r="E142" s="14" t="inlineStr">
         <is>
-          <t>Any</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F142" s="18" t="inlineStr">
         <is>
-          <t>Chrome DevTools open (F12 -&gt; Console).</t>
+          <t>A non-teaching employee of Al Riyada College with Ministry fields filled.</t>
         </is>
       </c>
       <c r="G142" s="18" t="inlineStr">
         <is>
-          <t>Use the system as normal while the console is open.</t>
+          <t>Open their Ministry (Jameah) Data preview.</t>
         </is>
       </c>
       <c r="H142" s="18" t="inlineStr">
@@ -13894,22 +13974,22 @@
       </c>
       <c r="I142" s="18" t="inlineStr">
         <is>
-          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
+          <t>Codes match the form (e.g. Nationality 101, Identity Type 01); phones are digits only.</t>
         </is>
       </c>
       <c r="J142" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K142" s="14" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L142" s="14" t="inlineStr">
         <is>
-          <t>Error sweep SWP-01..04</t>
+          <t>REC-06</t>
         </is>
       </c>
       <c r="M142" s="14" t="inlineStr">
@@ -13940,7 +14020,7 @@
     <row r="143">
       <c r="A143" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-05</t>
+          <t>TC-JM-10</t>
         </is>
       </c>
       <c r="B143" s="14" t="inlineStr">
@@ -13950,57 +14030,57 @@
       </c>
       <c r="C143" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D143" s="18" t="inlineStr">
         <is>
-          <t>Migrate output after deploying</t>
+          <t>Ministry GPA and hours equal the student's transcript</t>
         </is>
       </c>
       <c r="E143" s="14" t="inlineStr">
         <is>
-          <t>Administrator</t>
+          <t>Academic Affairs / Education Manager</t>
         </is>
       </c>
       <c r="F143" s="18" t="inlineStr">
         <is>
-          <t>New branch pulled on the server.</t>
+          <t>Academic figures refreshed (TC-JM-06).</t>
         </is>
       </c>
       <c r="G143" s="18" t="inlineStr">
         <is>
-          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
+          <t>Pick 10 students (include a student who retook a failed course). Compare GPA, Required, Passed and Remaining hours in the Ministry data with the student's My Transcript page.</t>
         </is>
       </c>
       <c r="H143" s="18" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>10 students</t>
         </is>
       </c>
       <c r="I143" s="18" t="inlineStr">
         <is>
-          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
+          <t>All four figures are identical for every student.</t>
         </is>
       </c>
       <c r="J143" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K143" s="14" t="inlineStr">
         <is>
-          <t>Monitoring</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="L143" s="14" t="inlineStr">
         <is>
-          <t>—</t>
+          <t>verify.run</t>
         </is>
       </c>
       <c r="M143" s="14" t="inlineStr">
         <is>
-          <t>Manual only</t>
+          <t>Pass</t>
         </is>
       </c>
       <c r="N143" s="19" t="inlineStr">
@@ -14026,7 +14106,7 @@
     <row r="144">
       <c r="A144" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-06</t>
+          <t>TC-JM-08</t>
         </is>
       </c>
       <c r="B144" s="14" t="inlineStr">
@@ -14036,27 +14116,27 @@
       </c>
       <c r="C144" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D144" s="18" t="inlineStr">
         <is>
-          <t>Every Medical HRMS page and form opens</t>
+          <t>Full value-by-value check (developer)</t>
         </is>
       </c>
       <c r="E144" s="14" t="inlineStr">
         <is>
-          <t>HR Manager</t>
+          <t>Developer</t>
         </is>
       </c>
       <c r="F144" s="18" t="inlineStr">
         <is>
-          <t>Logged in as HR Manager (then repeat as HR User).</t>
+          <t>Server access.</t>
         </is>
       </c>
       <c r="G144" s="18" t="inlineStr">
         <is>
-          <t>Open each Medical HRMS doctype list, its New form and its newest saved record; the four pages, the report and both workspaces.</t>
+          <t>Run: bench --site &lt;site&gt; execute medical_hrms.jameah.verify.run</t>
         </is>
       </c>
       <c r="H144" s="18" t="inlineStr">
@@ -14066,22 +14146,22 @@
       </c>
       <c r="I144" s="18" t="inlineStr">
         <is>
-          <t>Each opens; no red error, no 'Not permitted' for HR, no blank page.</t>
+          <t>Every view prints OK (0 missing, 0 extra, 0 mismatched, 0 invalid codes).</t>
         </is>
       </c>
       <c r="J144" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K144" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="L144" s="14" t="inlineStr">
         <is>
-          <t>SWP-01/02</t>
+          <t>verify.run</t>
         </is>
       </c>
       <c r="M144" s="14" t="inlineStr">
@@ -14100,19 +14180,19 @@
       <c r="R144" s="19" t="inlineStr"/>
       <c r="S144" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T144" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-07</t>
+          <t>TC-JM-09</t>
         </is>
       </c>
       <c r="B145" s="14" t="inlineStr">
@@ -14122,27 +14202,27 @@
       </c>
       <c r="C145" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D145" s="18" t="inlineStr">
         <is>
-          <t>Employees' own request lists open</t>
+          <t>Ministry read-only account</t>
         </is>
       </c>
       <c r="E145" s="14" t="inlineStr">
         <is>
-          <t>Employee</t>
+          <t>Server admin</t>
         </is>
       </c>
       <c r="F145" s="18" t="inlineStr">
         <is>
-          <t>Logged in as an employee.</t>
+          <t>Account created with the grant statements.</t>
         </is>
       </c>
       <c r="G145" s="18" t="inlineStr">
         <is>
-          <t>Open the list of each self-service request type (Permission Request ... Employee Medical License) and the Employee Self Service workspace.</t>
+          <t>Connect with that account; SELECT from a jameah view; try SELECT from tabEmployee.</t>
         </is>
       </c>
       <c r="H145" s="18" t="inlineStr">
@@ -14152,27 +14232,27 @@
       </c>
       <c r="I145" s="18" t="inlineStr">
         <is>
-          <t>Each opens with only the employee's own records; no error.</t>
+          <t>Views readable; ERP tables refused.</t>
         </is>
       </c>
       <c r="J145" s="14" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>High</t>
         </is>
       </c>
       <c r="K145" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Security</t>
         </is>
       </c>
       <c r="L145" s="14" t="inlineStr">
         <is>
-          <t>SWP-03</t>
+          <t>—</t>
         </is>
       </c>
       <c r="M145" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Manual only</t>
         </is>
       </c>
       <c r="N145" s="19" t="inlineStr">
@@ -14186,19 +14266,19 @@
       <c r="R145" s="19" t="inlineStr"/>
       <c r="S145" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T145" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-08</t>
+          <t>TC-JM-11</t>
         </is>
       </c>
       <c r="B146" s="14" t="inlineStr">
@@ -14208,27 +14288,27 @@
       </c>
       <c r="C146" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D146" s="18" t="inlineStr">
         <is>
-          <t>Every file of the app is valid</t>
+          <t>Faculty views on the Data Check page</t>
         </is>
       </c>
       <c r="E146" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F146" s="18" t="inlineStr">
         <is>
-          <t>A checkout of develop.</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G146" s="18" t="inlineStr">
         <is>
-          <t>python3 tests/checks/files.py</t>
+          <t>Open Jameah Data Check and look at the Views table.</t>
         </is>
       </c>
       <c r="H146" s="18" t="inlineStr">
@@ -14238,7 +14318,7 @@
       </c>
       <c r="I146" s="18" t="inlineStr">
         <is>
-          <t>PROBLEMS: 0 (Python compiles, JS parses, JSON loads, translations keep their placeholders, no stray files).</t>
+          <t>23 views: 5 jameahEmployee*, 8 jameahFaculty*, 10 jameahStudent*; 0 invalid codes.</t>
         </is>
       </c>
       <c r="J146" s="14" t="inlineStr">
@@ -14248,12 +14328,12 @@
       </c>
       <c r="K146" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Functional</t>
         </is>
       </c>
       <c r="L146" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/files.py</t>
+          <t>JM-01</t>
         </is>
       </c>
       <c r="M146" s="14" t="inlineStr">
@@ -14272,19 +14352,19 @@
       <c r="R146" s="19" t="inlineStr"/>
       <c r="S146" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="T146" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" s="16" t="inlineStr">
         <is>
-          <t>TC-ERR-09</t>
+          <t>TC-JM-12</t>
         </is>
       </c>
       <c r="B147" s="14" t="inlineStr">
@@ -14294,27 +14374,28 @@
       </c>
       <c r="C147" s="14" t="inlineStr">
         <is>
-          <t>Errors &amp; monitoring</t>
+          <t>Jameah (Ministry)</t>
         </is>
       </c>
       <c r="D147" s="18" t="inlineStr">
         <is>
-          <t>Every hook, doctype and record is valid on the site</t>
+          <t>A teacher is sent once, as Faculty</t>
         </is>
       </c>
       <c r="E147" s="14" t="inlineStr">
         <is>
-          <t>Developer</t>
+          <t>HR Manager</t>
         </is>
       </c>
       <c r="F147" s="18" t="inlineStr">
         <is>
-          <t>Site migrated.</t>
+          <t>An Employee linked to an Instructor (or with the Instructor's e-mail).</t>
         </is>
       </c>
       <c r="G147" s="18" t="inlineStr">
         <is>
-          <t>../../env/bin/python tests/e2e/fx.py tests/checks/site.py</t>
+          <t>1. Employee form &gt; View &gt; Ministry (Jameah) Data.
+2. Developer: query jameahFacultyPersonalInfo for that Instructor.</t>
         </is>
       </c>
       <c r="H147" s="18" t="inlineStr">
@@ -14324,27 +14405,27 @@
       </c>
       <c r="I147" s="18" t="inlineStr">
         <is>
-          <t>PROBLEMS: 0; every hook, patch and asset resolves; saved records pass validation.</t>
+          <t>1 says 'Not sent as an Employee ... sent as Faculty'. 2 shows the person's ID number and nationality (taken from the Employee record when the Instructor has none).</t>
         </is>
       </c>
       <c r="J147" s="14" t="inlineStr">
         <is>
-          <t>High</t>
+          <t>Critical</t>
         </is>
       </c>
       <c r="K147" s="14" t="inlineStr">
         <is>
-          <t>Regression</t>
+          <t>Data</t>
         </is>
       </c>
       <c r="L147" s="14" t="inlineStr">
         <is>
-          <t>tests/checks/site.py</t>
+          <t>unit test</t>
         </is>
       </c>
       <c r="M147" s="14" t="inlineStr">
         <is>
-          <t>Pass</t>
+          <t>Unit test</t>
         </is>
       </c>
       <c r="N147" s="19" t="inlineStr">
@@ -14358,18 +14439,879 @@
       <c r="R147" s="19" t="inlineStr"/>
       <c r="S147" s="14" t="inlineStr">
         <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T147" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="16" t="inlineStr">
+        <is>
+          <t>TC-JM-13</t>
+        </is>
+      </c>
+      <c r="B148" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C148" s="14" t="inlineStr">
+        <is>
+          <t>Jameah (Ministry)</t>
+        </is>
+      </c>
+      <c r="D148" s="18" t="inlineStr">
+        <is>
+          <t>Faculty status and contract codes</t>
+        </is>
+      </c>
+      <c r="E148" s="14" t="inlineStr">
+        <is>
+          <t>Academic Affairs / Education Manager</t>
+        </is>
+      </c>
+      <c r="F148" s="18" t="inlineStr">
+        <is>
+          <t>Code Map rows for Faculty Status 'Active' and Contract Type 'Full Time' are Needs Review (DEC-13).</t>
+        </is>
+      </c>
+      <c r="G148" s="18" t="inlineStr">
+        <is>
+          <t>1. Open each row, pick the Ministry code, Status = Verified.
+2. Refresh Academic Figures / reopen Jameah Data Check.</t>
+        </is>
+      </c>
+      <c r="H148" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I148" s="18" t="inlineStr">
+        <is>
+          <t>Faculty Academic Experience sends the chosen codes for current positions; before that they are empty.</t>
+        </is>
+      </c>
+      <c r="J148" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K148" s="14" t="inlineStr">
+        <is>
+          <t>Data</t>
+        </is>
+      </c>
+      <c r="L148" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M148" s="14" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="N148" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O148" s="19" t="inlineStr"/>
+      <c r="P148" s="19" t="inlineStr"/>
+      <c r="Q148" s="20" t="inlineStr"/>
+      <c r="R148" s="19" t="inlineStr"/>
+      <c r="S148" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T148" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-01</t>
+        </is>
+      </c>
+      <c r="B149" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C149" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D149" s="18" t="inlineStr">
+        <is>
+          <t>Error Log after each test day</t>
+        </is>
+      </c>
+      <c r="E149" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="F149" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G149" s="18" t="inlineStr">
+        <is>
+          <t>Open /app/error-log; sort by newest.</t>
+        </is>
+      </c>
+      <c r="H149" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I149" s="18" t="inlineStr">
+        <is>
+          <t>No new errors. Note any error's time, title and the user who triggered it in the Bug Report sheet.</t>
+        </is>
+      </c>
+      <c r="J149" s="14" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K149" s="14" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="L149" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M149" s="14" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="N149" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O149" s="19" t="inlineStr"/>
+      <c r="P149" s="19" t="inlineStr"/>
+      <c r="Q149" s="20" t="inlineStr"/>
+      <c r="R149" s="19" t="inlineStr"/>
+      <c r="S149" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T149" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-02</t>
+        </is>
+      </c>
+      <c r="B150" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C150" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D150" s="18" t="inlineStr">
+        <is>
+          <t>System e-mail works</t>
+        </is>
+      </c>
+      <c r="E150" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="F150" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G150" s="18" t="inlineStr">
+        <is>
+          <t>Email Account 'Notifications' -&gt; send a test e-mail; then trigger a password reset for a test user.</t>
+        </is>
+      </c>
+      <c r="H150" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I150" s="18" t="inlineStr">
+        <is>
+          <t>E-mail arrives. No 'Failed to decrypt key' error in the Error Log.</t>
+        </is>
+      </c>
+      <c r="J150" s="14" t="inlineStr">
+        <is>
+          <t>Critical</t>
+        </is>
+      </c>
+      <c r="K150" s="14" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="L150" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M150" s="14" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="N150" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O150" s="19" t="inlineStr"/>
+      <c r="P150" s="19" t="inlineStr"/>
+      <c r="Q150" s="20" t="inlineStr"/>
+      <c r="R150" s="19" t="inlineStr"/>
+      <c r="S150" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T150" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-03</t>
+        </is>
+      </c>
+      <c r="B151" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C151" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D151" s="18" t="inlineStr">
+        <is>
+          <t>Background jobs</t>
+        </is>
+      </c>
+      <c r="E151" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="F151" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G151" s="18" t="inlineStr">
+        <is>
+          <t>Open Scheduled Job Log; filter Status = Failed.</t>
+        </is>
+      </c>
+      <c r="H151" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I151" s="18" t="inlineStr">
+        <is>
+          <t>No failed jobs (or each one reported).</t>
+        </is>
+      </c>
+      <c r="J151" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K151" s="14" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="L151" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M151" s="14" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="N151" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O151" s="19" t="inlineStr"/>
+      <c r="P151" s="19" t="inlineStr"/>
+      <c r="Q151" s="20" t="inlineStr"/>
+      <c r="R151" s="19" t="inlineStr"/>
+      <c r="S151" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T151" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-04</t>
+        </is>
+      </c>
+      <c r="B152" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C152" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D152" s="18" t="inlineStr">
+        <is>
+          <t>Browser console during testing</t>
+        </is>
+      </c>
+      <c r="E152" s="14" t="inlineStr">
+        <is>
+          <t>Any</t>
+        </is>
+      </c>
+      <c r="F152" s="18" t="inlineStr">
+        <is>
+          <t>Chrome DevTools open (F12 -&gt; Console).</t>
+        </is>
+      </c>
+      <c r="G152" s="18" t="inlineStr">
+        <is>
+          <t>Use the system as normal while the console is open.</t>
+        </is>
+      </c>
+      <c r="H152" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I152" s="18" t="inlineStr">
+        <is>
+          <t>No red errors. If one appears, screenshot the console and record the time and page.</t>
+        </is>
+      </c>
+      <c r="J152" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K152" s="14" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="L152" s="14" t="inlineStr">
+        <is>
+          <t>Error sweep SWP-01..04</t>
+        </is>
+      </c>
+      <c r="M152" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N152" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O152" s="19" t="inlineStr"/>
+      <c r="P152" s="19" t="inlineStr"/>
+      <c r="Q152" s="20" t="inlineStr"/>
+      <c r="R152" s="19" t="inlineStr"/>
+      <c r="S152" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T152" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-05</t>
+        </is>
+      </c>
+      <c r="B153" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C153" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D153" s="18" t="inlineStr">
+        <is>
+          <t>Migrate output after deploying</t>
+        </is>
+      </c>
+      <c r="E153" s="14" t="inlineStr">
+        <is>
+          <t>Administrator</t>
+        </is>
+      </c>
+      <c r="F153" s="18" t="inlineStr">
+        <is>
+          <t>New branch pulled on the server.</t>
+        </is>
+      </c>
+      <c r="G153" s="18" t="inlineStr">
+        <is>
+          <t>Run bench --site &lt;site&gt; migrate and read the output.</t>
+        </is>
+      </c>
+      <c r="H153" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I153" s="18" t="inlineStr">
+        <is>
+          <t>No errors. If it prints 'Kept (they hold data, check before removing by hand)', send that line to the developer.</t>
+        </is>
+      </c>
+      <c r="J153" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K153" s="14" t="inlineStr">
+        <is>
+          <t>Monitoring</t>
+        </is>
+      </c>
+      <c r="L153" s="14" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M153" s="14" t="inlineStr">
+        <is>
+          <t>Manual only</t>
+        </is>
+      </c>
+      <c r="N153" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O153" s="19" t="inlineStr"/>
+      <c r="P153" s="19" t="inlineStr"/>
+      <c r="Q153" s="20" t="inlineStr"/>
+      <c r="R153" s="19" t="inlineStr"/>
+      <c r="S153" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T153" s="14" t="inlineStr">
+        <is>
+          <t>21 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-06</t>
+        </is>
+      </c>
+      <c r="B154" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C154" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D154" s="18" t="inlineStr">
+        <is>
+          <t>Every Medical HRMS page and form opens</t>
+        </is>
+      </c>
+      <c r="E154" s="14" t="inlineStr">
+        <is>
+          <t>HR Manager</t>
+        </is>
+      </c>
+      <c r="F154" s="18" t="inlineStr">
+        <is>
+          <t>Logged in as HR Manager (then repeat as HR User).</t>
+        </is>
+      </c>
+      <c r="G154" s="18" t="inlineStr">
+        <is>
+          <t>Open each Medical HRMS doctype list, its New form and its newest saved record; the four pages, the report and both workspaces.</t>
+        </is>
+      </c>
+      <c r="H154" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I154" s="18" t="inlineStr">
+        <is>
+          <t>Each opens; no red error, no 'Not permitted' for HR, no blank page.</t>
+        </is>
+      </c>
+      <c r="J154" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K154" s="14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="L154" s="14" t="inlineStr">
+        <is>
+          <t>SWP-01/02</t>
+        </is>
+      </c>
+      <c r="M154" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N154" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O154" s="19" t="inlineStr"/>
+      <c r="P154" s="19" t="inlineStr"/>
+      <c r="Q154" s="20" t="inlineStr"/>
+      <c r="R154" s="19" t="inlineStr"/>
+      <c r="S154" s="14" t="inlineStr">
+        <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
-      <c r="T147" s="14" t="inlineStr">
+      <c r="T154" s="14" t="inlineStr">
         <is>
           <t>23 Oct 2026</t>
         </is>
       </c>
     </row>
+    <row r="155">
+      <c r="A155" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-07</t>
+        </is>
+      </c>
+      <c r="B155" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C155" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D155" s="18" t="inlineStr">
+        <is>
+          <t>Employees' own request lists open</t>
+        </is>
+      </c>
+      <c r="E155" s="14" t="inlineStr">
+        <is>
+          <t>Employee</t>
+        </is>
+      </c>
+      <c r="F155" s="18" t="inlineStr">
+        <is>
+          <t>Logged in as an employee.</t>
+        </is>
+      </c>
+      <c r="G155" s="18" t="inlineStr">
+        <is>
+          <t>Open the list of each self-service request type (Permission Request ... Employee Medical License) and the Employee Self Service workspace.</t>
+        </is>
+      </c>
+      <c r="H155" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I155" s="18" t="inlineStr">
+        <is>
+          <t>Each opens with only the employee's own records; no error.</t>
+        </is>
+      </c>
+      <c r="J155" s="14" t="inlineStr">
+        <is>
+          <t>Medium</t>
+        </is>
+      </c>
+      <c r="K155" s="14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="L155" s="14" t="inlineStr">
+        <is>
+          <t>SWP-03</t>
+        </is>
+      </c>
+      <c r="M155" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N155" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O155" s="19" t="inlineStr"/>
+      <c r="P155" s="19" t="inlineStr"/>
+      <c r="Q155" s="20" t="inlineStr"/>
+      <c r="R155" s="19" t="inlineStr"/>
+      <c r="S155" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T155" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-08</t>
+        </is>
+      </c>
+      <c r="B156" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C156" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D156" s="18" t="inlineStr">
+        <is>
+          <t>Every file of the app is valid</t>
+        </is>
+      </c>
+      <c r="E156" s="14" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F156" s="18" t="inlineStr">
+        <is>
+          <t>A checkout of develop.</t>
+        </is>
+      </c>
+      <c r="G156" s="18" t="inlineStr">
+        <is>
+          <t>python3 tests/checks/files.py</t>
+        </is>
+      </c>
+      <c r="H156" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I156" s="18" t="inlineStr">
+        <is>
+          <t>PROBLEMS: 0 (Python compiles, JS parses, JSON loads, translations keep their placeholders, no stray files).</t>
+        </is>
+      </c>
+      <c r="J156" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K156" s="14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="L156" s="14" t="inlineStr">
+        <is>
+          <t>tests/checks/files.py</t>
+        </is>
+      </c>
+      <c r="M156" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N156" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O156" s="19" t="inlineStr"/>
+      <c r="P156" s="19" t="inlineStr"/>
+      <c r="Q156" s="20" t="inlineStr"/>
+      <c r="R156" s="19" t="inlineStr"/>
+      <c r="S156" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T156" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" s="16" t="inlineStr">
+        <is>
+          <t>TC-ERR-09</t>
+        </is>
+      </c>
+      <c r="B157" s="14" t="inlineStr">
+        <is>
+          <t>Round 1</t>
+        </is>
+      </c>
+      <c r="C157" s="14" t="inlineStr">
+        <is>
+          <t>Errors &amp; monitoring</t>
+        </is>
+      </c>
+      <c r="D157" s="18" t="inlineStr">
+        <is>
+          <t>Every hook, doctype and record is valid on the site</t>
+        </is>
+      </c>
+      <c r="E157" s="14" t="inlineStr">
+        <is>
+          <t>Developer</t>
+        </is>
+      </c>
+      <c r="F157" s="18" t="inlineStr">
+        <is>
+          <t>Site migrated.</t>
+        </is>
+      </c>
+      <c r="G157" s="18" t="inlineStr">
+        <is>
+          <t>../../env/bin/python tests/e2e/fx.py tests/checks/site.py</t>
+        </is>
+      </c>
+      <c r="H157" s="18" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="I157" s="18" t="inlineStr">
+        <is>
+          <t>PROBLEMS: 0; every hook, patch and asset resolves; saved records pass validation.</t>
+        </is>
+      </c>
+      <c r="J157" s="14" t="inlineStr">
+        <is>
+          <t>High</t>
+        </is>
+      </c>
+      <c r="K157" s="14" t="inlineStr">
+        <is>
+          <t>Regression</t>
+        </is>
+      </c>
+      <c r="L157" s="14" t="inlineStr">
+        <is>
+          <t>tests/checks/site.py</t>
+        </is>
+      </c>
+      <c r="M157" s="14" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N157" s="19" t="inlineStr">
+        <is>
+          <t>Not run</t>
+        </is>
+      </c>
+      <c r="O157" s="19" t="inlineStr"/>
+      <c r="P157" s="19" t="inlineStr"/>
+      <c r="Q157" s="20" t="inlineStr"/>
+      <c r="R157" s="19" t="inlineStr"/>
+      <c r="S157" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+      <c r="T157" s="14" t="inlineStr">
+        <is>
+          <t>23 Oct 2026</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:T147"/>
-  <conditionalFormatting sqref="N2:N347">
+  <autoFilter ref="A1:T157"/>
+  <conditionalFormatting sqref="N2:N357">
     <cfRule type="expression" priority="1" dxfId="0" stopIfTrue="1">
       <formula>$N2="Pass"</formula>
     </cfRule>
@@ -14386,7 +15328,7 @@
       <formula>$N2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="M2:M347">
+  <conditionalFormatting sqref="M2:M357">
     <cfRule type="expression" priority="6" dxfId="0" stopIfTrue="1">
       <formula>$M2="Pass"</formula>
     </cfRule>
@@ -14403,7 +15345,7 @@
       <formula>$M2="N/A"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="J2:J347">
+  <conditionalFormatting sqref="J2:J357">
     <cfRule type="expression" priority="11" dxfId="4" stopIfTrue="1">
       <formula>$J2="Critical"</formula>
     </cfRule>
@@ -14418,7 +15360,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation sqref="N2:N347" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
+    <dataValidation sqref="N2:N357" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" type="list">
       <formula1>"Not run,Pass,Fail,Blocked,N/A"</formula1>
     </dataValidation>
   </dataValidations>
@@ -16330,7 +17272,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E19"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -16375,17 +17317,17 @@
       </c>
       <c r="B2" s="14" t="inlineStr">
         <is>
-          <t>Leave e-mails</t>
+          <t>Round 3</t>
         </is>
       </c>
       <c r="C2" s="18" t="inlineStr">
         <is>
-          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
+          <t>HR-11, HR-78, B-58, B-59, CL-42, TC-STF-01 - TC-STF-10</t>
         </is>
       </c>
       <c r="D2" s="18" t="inlineStr">
         <is>
-          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
+          <t>Round 3: a My HR card on the education staff dashboards (Instructor, Department Head, Dean, Vice Deans, IT, Academic Operations, Student Affairs, Admission, Finance, Clinical, Advisor) for logins linked to an Employee record: leave balances and what's next, the latest requests, Apply for Leave, New Request and View, with the Employee Portal's own windows (now shared: public/js/self_service.js). Nothing in the education app changed. New: the Round 3 document for the testers, 10 test cases (Round 3), User Guide section 2.11, Installation Guide troubleshooting, QA logins qa.hod, qa.dean, qa.staff.nolink. Tested: 111/111 browser checks (10 new: SHR-01 - SHR-10), 53 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; card placement checked on 11 staff dashboards (8 with figures, Advisor under its heading, Dean and Department Head in the browser tests); Error Log: only test-caused entries, removed. The full run caught a script error of the card on every other page (B-59), fixed before release.</t>
         </is>
       </c>
       <c r="E2" s="14" t="inlineStr">
@@ -16402,17 +17344,17 @@
       </c>
       <c r="B3" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Leave e-mails</t>
         </is>
       </c>
       <c r="C3" s="18" t="inlineStr">
         <is>
-          <t>HR-76</t>
+          <t>HR-25, HR-76, DEC-16, CL-40, CL-41, TC-LV-19</t>
         </is>
       </c>
       <c r="D3" s="18" t="inlineStr">
         <is>
-          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
+          <t>DEC-16 answered: every HR User and HR Manager login is told about new requests (as built). Leave e-mails: two Medical HRMS templates (the employee's has the rejection reason and opens the application on the Employee Portal), chosen in HR Settings by the migrate where empty - CL-40 done, no HR step left. Checked on this copy with a local mail catcher (nothing left the machine): 7 e-mails with the right text and links; unit test added (11 in test_request_flow). Round 2 document, User Guide and Installation Guide updated; new case TC-LV-19.</t>
         </is>
       </c>
       <c r="E3" s="14" t="inlineStr">
@@ -16429,17 +17371,17 @@
       </c>
       <c r="B4" s="14" t="inlineStr">
         <is>
-          <t>Round 2</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C4" s="18" t="inlineStr">
         <is>
-          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
+          <t>HR-76</t>
         </is>
       </c>
       <c r="D4" s="18" t="inlineStr">
         <is>
-          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
+          <t>QA cleanup stops the unsent e-mails of removed QA records (status Error) instead of deleting them: the e-mail job could be sending them at that moment and logged 'Email Queue ... not found'.</t>
         </is>
       </c>
       <c r="E4" s="14" t="inlineStr">
@@ -16456,17 +17398,17 @@
       </c>
       <c r="B5" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Round 2</t>
         </is>
       </c>
       <c r="C5" s="18" t="inlineStr">
         <is>
-          <t>HR-75, CL-23, CL-37</t>
+          <t>HR-16, HR-24, HR-25, HR-48, HR-76, HR-77, B-26, B-56, B-57, DEC-16, CL-39 - CL-41, TC-APR-02, TC-APR-09 - TC-APR-13, TC-ESS-17 - TC-ESS-23, TC-EMP-13, TC-EMP-14, TC-LV-18</t>
         </is>
       </c>
       <c r="D5" s="18" t="inlineStr">
         <is>
-          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
+          <t>Round 2: employees change, send or delete their drafts and send a rejected request again; rejecting needs a reason, which the employee reads with the request's history; notifications in the bell (and e-mail where the mail account works) for HR on new requests and for the employee at every later step; the Instructor and Academic Advisor forms save after an Employee is picked (B-26, B-56); amounts say SAR; the bell shows the time as text (B-57). New: Round column in the Test Cases workbook, the Round 2 document for the testers, User Guide and Installation Guide updated. Re-tested: 101/101 browser checks, 52 unit tests (0 failures), 0 file and 0 site problems, 31 server methods x 3 roles; Error Log: only the known e-mail password error B-25 (notification e-mails this copy cannot send).</t>
         </is>
       </c>
       <c r="E5" s="14" t="inlineStr">
@@ -16478,22 +17420,22 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>23 Oct 2026</t>
+          <t>27 Oct 2026</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C6" s="18" t="inlineStr">
         <is>
-          <t>HR-37, HR-38, DEC-15, CL-38</t>
+          <t>HR-75, CL-23, CL-37</t>
         </is>
       </c>
       <c r="D6" s="18" t="inlineStr">
         <is>
-          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
+          <t>Test Cases workbook and both PDF guides given to the testing team; their UAT round has started (HR-75 In progress). Checklist: new status 'In progress' (blue); CL-23 Run the test cases and CL-37 Share the guides are In progress (the guides still go to HR, managers and the server admin). Testing team added to the Assigned to list.</t>
         </is>
       </c>
       <c r="E6" s="14" t="inlineStr">
@@ -16515,12 +17457,12 @@
       </c>
       <c r="C7" s="18" t="inlineStr">
         <is>
-          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
+          <t>HR-37, HR-38, DEC-15, CL-38</t>
         </is>
       </c>
       <c r="D7" s="18" t="inlineStr">
         <is>
-          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
+          <t>Academic Presence (HR requirements 1-4) checked against the client's request: all four are on the HR Dashboard and tested. The guides now say where each tab's data comes from, that Proctor Schedules stays empty until exam committees are entered (new Checklist CL-38), that Students on Campus counts by hour, and that after-4 PM times come from the timetable and class attendance until devices are connected. New decision DEC-15: hour slots or the college's own periods.</t>
         </is>
       </c>
       <c r="E7" s="14" t="inlineStr">
@@ -16537,17 +17479,17 @@
       </c>
       <c r="B8" s="14" t="inlineStr">
         <is>
-          <t>Project tracking</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="C8" s="18" t="inlineStr">
         <is>
-          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
+          <t>HR-74, B-54, B-55, TC-ESS-02, TC-ESS-04, TC-ESS-16, CL-37</t>
         </is>
       </c>
       <c r="D8" s="18" t="inlineStr">
         <is>
-          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
+          <t>Installation and Setup Guide (21 pages) and User Guide (30 pages) in PDF, with screenshots from the test site (QA data only); sources in docs/guides/src. Fixed while writing them: Remote Work Request duration and Permission Request hours were always 0 (now counted; reversed times refused; a patch fills in saved requests). Re-tested: 95/95 browser checks, 42 unit tests (0 failures), 0 file and 0 site problems, 29 server methods x 3 roles, no Error Log entries.</t>
         </is>
       </c>
       <c r="E8" s="14" t="inlineStr">
@@ -16569,12 +17511,12 @@
       </c>
       <c r="C9" s="18" t="inlineStr">
         <is>
-          <t>HR-72, B-52, B-53</t>
+          <t>All tasks; HR-04 - HR-06, HR-11, HR-12, HR-28 - HR-30, HR-48, HR-66, HR-70, HR-71, HR-73, JM-03, JM-06, JM-12, JM-13, JM-16, JM-17, B-26, B-34, CL-35</t>
         </is>
       </c>
       <c r="D9" s="18" t="inlineStr">
         <is>
-          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
+          <t>Owners corrected: Abdul Hakeem designed and built Medical HRMS and Jameah and leads every development task. New column 'Assigned to' (with a dropdown) shows who a task was given to: Dinesh (HR-06, and HR-04 at first), Fathir (HR-04, HR-05, HR-70), otherwise Abdul Hakeem; client-side tasks stay with HR, Academic Affairs, the Registrar or the server admin. Wording that credited others for this work removed. Status and Priority shown in clear colours in all three workbooks (Status, Priority, Result and Severity cells only), with a priority legend in the Read Me.</t>
         </is>
       </c>
       <c r="E9" s="14" t="inlineStr">
@@ -16591,17 +17533,17 @@
       </c>
       <c r="B10" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Project tracking</t>
         </is>
       </c>
       <c r="C10" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
+          <t>HR-72, B-52, B-53</t>
         </is>
       </c>
       <c r="D10" s="18" t="inlineStr">
         <is>
-          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
+          <t>The three check scripts (files, site, server methods) now record their result in the Test Cases workbook (Last automated run: Pass, 23 Oct). The file check found a missing import in the site check; fixed.</t>
         </is>
       </c>
       <c r="E10" s="14" t="inlineStr">
@@ -16613,7 +17555,7 @@
     <row r="11">
       <c r="A11" s="14" t="inlineStr">
         <is>
-          <t>22 Oct 2026</t>
+          <t>23 Oct 2026</t>
         </is>
       </c>
       <c r="B11" s="14" t="inlineStr">
@@ -16623,12 +17565,12 @@
       </c>
       <c r="C11" s="18" t="inlineStr">
         <is>
-          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
+          <t>HR-58, HR-69, HR-71 - HR-73, B-45 - B-51, CL-01, CL-30, CL-34 - CL-36, TC-ERR-06 - TC-ERR-09, TC-SEC-10</t>
         </is>
       </c>
       <c r="D11" s="18" t="inlineStr">
         <is>
-          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
+          <t>Every branch merged into develop (ministry-lookup last; employee-applicant recorded as merged without its July files, as decided); develop is now the branch to test and deploy. Full check of every file and page (files, site, server methods by role, unit tests, browser suite with a sweep of every Medical HRMS doctype); checks kept in tests/checks. Fixed: stray files, outdated README and developer guide, QA setup race, refresh-lock test, Ministry code search. HR-69 corrected (employee counts were test hires). Result: 95/95 browser checks (error sweep: 116 pages for HR, 20 for employees), 37/37 unit tests, 23/23 Ministry views, 29 server methods x 3 roles, 0 file and 0 site problems, no Error Log entries.</t>
         </is>
       </c>
       <c r="E11" s="14" t="inlineStr">
@@ -16650,12 +17592,12 @@
       </c>
       <c r="C12" s="18" t="inlineStr">
         <is>
-          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
+          <t>HR-58, HR-70, JM-05, JM-19, B-42 – B-44, TC-REC-13, TC-REC-14</t>
         </is>
       </c>
       <c r="D12" s="18" t="inlineStr">
         <is>
-          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
+          <t>develop (Fathir's job application update, PR #2) merged into feature/uat-2026-10-22; conflicts in job_application.py, job-application.html and ar.csv resolved keeping both sides; the Appreciation list restored and the work extension accepted again on the updated form (B-42, B-44); a migrate no longer fails when it overlaps the hourly Jameah refresh (B-43); test output removed from the repository. Re-tested: 95/95 browser checks, 37/37 unit tests, 23/23 Ministry views OK, no Error Log entries. Branch to test and deploy: feature/uat-2026-10-22.</t>
         </is>
       </c>
       <c r="E12" s="14" t="inlineStr">
@@ -16672,17 +17614,17 @@
       </c>
       <c r="B13" s="14" t="inlineStr">
         <is>
-          <t>Testing</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C13" s="18" t="inlineStr">
         <is>
-          <t>HR-67, B-41</t>
+          <t>HR-08, HR-09, HR-19, HR-20, HR-22, HR-68, HR-69, B-36 – B-40, DEC-14, CL-28 – CL-33</t>
         </is>
       </c>
       <c r="D13" s="18" t="inlineStr">
         <is>
-          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
+          <t>Leave made one flow: Leave Plan (employees send it; manager and department head approve) -&gt; Leave Application (only leave the employee holds, with the days left; Apply now from an approved plan) -&gt; Leave Return (asked for when a leave ends; certificate and occupational health only after sick leave). Sick-leave types renamed in pay order (Sick Leave 1 / 2 / 3) by a migration patch. HR Portal Leave section: setup check per company, daily leave counts, yearly setup in order. Arabic for 114 new texts. 5 unit tests and 7 browser tests (LV-01 - LV-07); test cases TC-LV-09 - 17, TC-HRD-06/07. Real company Al Riyada College still needs its leave setup (HR-69). Branch to test and deploy: feature/uat-2026-10-22 (all work to date).</t>
         </is>
       </c>
       <c r="E13" s="14" t="inlineStr">
@@ -16694,22 +17636,22 @@
     <row r="14">
       <c r="A14" s="14" t="inlineStr">
         <is>
-          <t>21 Oct 2026</t>
+          <t>22 Oct 2026</t>
         </is>
       </c>
       <c r="B14" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Testing</t>
         </is>
       </c>
       <c r="C14" s="18" t="inlineStr">
         <is>
-          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
+          <t>HR-67, B-41</t>
         </is>
       </c>
       <c r="D14" s="18" t="inlineStr">
         <is>
-          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
+          <t>Browser test suite, QA data scripts and the results helper kept in the repository (tests/e2e); the QA scripts only run on a site named in QA_TEST_SITE. The QA reset no longer leaves the QA HR User without access to its own My Settings (test data only). The leave unit test now attaches a real test file, so it no longer writes 'Error Attaching File' to the Error Log. Full run 22 Oct: 95/95 browser checks, 36/36 unit tests, 23/23 Ministry views OK, no new Error Log entries.</t>
         </is>
       </c>
       <c r="E14" s="14" t="inlineStr">
@@ -16726,17 +17668,17 @@
       </c>
       <c r="B15" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS</t>
+          <t>Medical HRMS + Jameah</t>
         </is>
       </c>
       <c r="C15" s="18" t="inlineStr">
         <is>
-          <t>HR-66</t>
+          <t>HR-49, HR-50, HR-51, HR-65, JM-14, B-35, DEC-12, DEC-13</t>
         </is>
       </c>
       <c r="D15" s="18" t="inlineStr">
         <is>
-          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
+          <t>Report 'Employees Missing Ministry Data'; data sheet for non-academic staff (download, check, import); unused duplicate applicant Ministry fields removed; Create Employee dialog asks for every field the Employee form requires; Jameah Faculty views (8) built and verified (23 views in all). Arabic for the 46 new labels. Documents moved to the project_tracking folder; Checklist workbook added; dates on every row; HRM_TASK_TRACKER.md marked as superseded.</t>
         </is>
       </c>
       <c r="E15" s="14" t="inlineStr">
@@ -16753,17 +17695,17 @@
       </c>
       <c r="B16" s="14" t="inlineStr">
         <is>
-          <t>Medical HRMS + Jameah</t>
+          <t>Medical HRMS</t>
         </is>
       </c>
       <c r="C16" s="18" t="inlineStr">
         <is>
-          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
+          <t>HR-66</t>
         </is>
       </c>
       <c r="D16" s="18" t="inlineStr">
         <is>
-          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
+          <t>HR Portal and Employee Portal in the new college portal design (menu, top bar, EN/AR, dark mode); Arabic translations for these pages.</t>
         </is>
       </c>
       <c r="E16" s="14" t="inlineStr">
@@ -16775,7 +17717,7 @@
     <row r="17">
       <c r="A17" s="14" t="inlineStr">
         <is>
-          <t>20 Oct 2026</t>
+          <t>21 Oct 2026</t>
         </is>
       </c>
       <c r="B17" s="14" t="inlineStr">
@@ -16785,12 +17727,12 @@
       </c>
       <c r="C17" s="18" t="inlineStr">
         <is>
-          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
+          <t>HR-12, HR-31, HR-32, HR-45, HR-46, HR-59 – HR-64, JM-17, JM-18, B-24 – B-34</t>
         </is>
       </c>
       <c r="D17" s="18" t="inlineStr">
         <is>
-          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
+          <t>End-to-end test round 3 with an error sweep of every page: fixes for the errors the client reported (non-Saudi employees, breadcrumb 'Not permitted', Cost Center pop-up, academic hire e-mail, Holiday List); HR login lands on the HR Dashboard; Ministry GPA and credit hours from the college's official calculation. Test Report, Test Cases and Task Tracker created.</t>
         </is>
       </c>
       <c r="E17" s="14" t="inlineStr">
@@ -16802,7 +17744,7 @@
     <row r="18">
       <c r="A18" s="14" t="inlineStr">
         <is>
-          <t>19 Oct 2026</t>
+          <t>20 Oct 2026</t>
         </is>
       </c>
       <c r="B18" s="14" t="inlineStr">
@@ -16812,12 +17754,12 @@
       </c>
       <c r="C18" s="18" t="inlineStr">
         <is>
-          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+          <t>HR-07 – HR-09, HR-13 – HR-15, HR-19, HR-22, HR-26, HR-36 – HR-44, JM-02 – JM-07, B-12 – B-23</t>
         </is>
       </c>
       <c r="D18" s="18" t="inlineStr">
         <is>
-          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+          <t>Jameah Employee (5) and Student (10) views built and verified value by value; Academic Presence; browser test round 2 fixes.</t>
         </is>
       </c>
       <c r="E18" s="14" t="inlineStr">
@@ -16829,25 +17771,52 @@
     <row r="19">
       <c r="A19" s="14" t="inlineStr">
         <is>
+          <t>19 Oct 2026</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="inlineStr">
+        <is>
+          <t>Medical HRMS + Jameah</t>
+        </is>
+      </c>
+      <c r="C19" s="18" t="inlineStr">
+        <is>
+          <t>HR-02, HR-05, HR-06, HR-24, HR-27, HR-33 – HR-35, JM-01, B-01 – B-11</t>
+        </is>
+      </c>
+      <c r="D19" s="18" t="inlineStr">
+        <is>
+          <t>Browser end-to-end test round 1 and fixes (approvals, recruitment security, Ministry identity rules); Instructor data sheet; Jameah research.</t>
+        </is>
+      </c>
+      <c r="E19" s="14" t="inlineStr">
+        <is>
+          <t>Abdul Hakeem</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="14" t="inlineStr">
+        <is>
           <t>1 Oct 2026</t>
         </is>
       </c>
-      <c r="B19" s="14" t="inlineStr">
+      <c r="B20" s="14" t="inlineStr">
         <is>
           <t>Medical HRMS</t>
         </is>
       </c>
-      <c r="C19" s="18" t="inlineStr">
+      <c r="C20" s="18" t="inlineStr">
         <is>
           <t>HR-01 – HR-32</t>
         </is>
       </c>
-      <c r="D19" s="18" t="inlineStr">
+      <c r="D20" s="18" t="inlineStr">
         <is>
           <t>First HRM task tracker (HRM_TASK_TRACKER.md / .csv).</t>
         </is>
       </c>
-      <c r="E19" s="14" t="inlineStr">
+      <c r="E20" s="14" t="inlineStr">
         <is>
           <t>Team</t>
         </is>
